--- a/morpg/morpg/Assets/TableData/Table_Text.xlsx
+++ b/morpg/morpg/Assets/TableData/Table_Text.xlsx
@@ -5,7 +5,7 @@
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\260226morpg\morpg\morpg\Assets\Resources\TableData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\260226morpg\morpg\morpg\Assets\TableData\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
@@ -19,51 +19,63 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+  <x:si>
+    <x:t>continue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CodeName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>save</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불러오기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>load</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새 시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Korean</x:t>
+  </x:si>
+  <x:si>
+    <x:t>option</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Array</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
   <x:si>
     <x:t>Index</x:t>
   </x:si>
   <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종료</x:t>
-  </x:si>
-  <x:si>
     <x:t>Comment</x:t>
   </x:si>
   <x:si>
-    <x:t>Korean</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Array</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
     <x:t>exit</x:t>
   </x:si>
   <x:si>
+    <x:t>이어하기</x:t>
+  </x:si>
+  <x:si>
     <x:t>newgame</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CodeName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>option</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이어하기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>새 시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>continue</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -135,7 +147,7 @@
     </x:xf>
   </x:cellStyleXfs>
   <x:cellXfs count="2">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1">
@@ -144,7 +156,7 @@
   </x:cellXfs>
   <x:cellStyles count="2">
     <x:cellStyle name="Normal" xfId="0" builtinId="0" iLevel="0"/>
-    <x:cellStyle name="표준" xfId="1" builtinId="0"/>
+    <x:cellStyle name="표준" xfId="1"/>
   </x:cellStyles>
   <x:dxfs count="12">
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -804,7 +816,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:D8"/>
+  <x:dimension ref="A1:D10"/>
   <x:sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="16.39999999999999857891"/>
   <x:cols>
     <x:col min="1" max="1" width="8.796875" bestFit="1" customWidth="1"/>
@@ -812,31 +824,31 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
         <x:v>10</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>4</x:v>
       </x:c>
       <x:c r="D2" s="1"/>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -844,7 +856,7 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B4" s="1"/>
       <x:c r="C4" s="1"/>
@@ -855,10 +867,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C5" t="s">
         <x:v>9</x:v>
-      </x:c>
-      <x:c r="C5" t="s">
-        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
@@ -866,10 +878,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" t="s">
-        <x:v>14</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C6" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
@@ -880,7 +892,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C7" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
@@ -888,14 +900,36 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" t="s">
-        <x:v>8</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C8" t="s">
         <x:v>2</x:v>
       </x:c>
     </x:row>
+    <x:row r="9" spans="1:3">
+      <x:c r="A9">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B9" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C9" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:3">
+      <x:c r="A10">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51180553436279296875" footer="0.51180553436279296875"/>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51166665554046630859" footer="0.51166665554046630859"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
 </x:worksheet>
 </file>
--- a/morpg/morpg/Assets/TableData/Table_Text.xlsx
+++ b/morpg/morpg/Assets/TableData/Table_Text.xlsx
@@ -19,7 +19,61 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+  <x:si>
+    <x:t>종료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Korean</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불러오기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>option</x:t>
+  </x:si>
+  <x:si>
+    <x:t>newgame</x:t>
+  </x:si>
+  <x:si>
+    <x:t>load</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새 시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Comment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Array</x:t>
+  </x:si>
+  <x:si>
+    <x:t>exit</x:t>
+  </x:si>
+  <x:si>
+    <x:t>save</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이어하기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Index</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
   <x:si>
     <x:t>continue</x:t>
   </x:si>
@@ -27,55 +81,7 @@
     <x:t>CodeName</x:t>
   </x:si>
   <x:si>
-    <x:t>종료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>저장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>save</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불러오기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>load</x:t>
-  </x:si>
-  <x:si>
-    <x:t>새 시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Korean</x:t>
-  </x:si>
-  <x:si>
-    <x:t>option</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Array</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Index</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Comment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>exit</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이어하기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>newgame</x:t>
+    <x:t>copy</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -816,7 +822,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:D10"/>
+  <x:dimension ref="A1:D11"/>
   <x:sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="16.39999999999999857891"/>
   <x:cols>
     <x:col min="1" max="1" width="8.796875" bestFit="1" customWidth="1"/>
@@ -824,25 +830,25 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D2" s="1"/>
     </x:row>
@@ -856,7 +862,7 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B4" s="1"/>
       <x:c r="C4" s="1"/>
@@ -867,10 +873,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C5" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
@@ -878,10 +884,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" t="s">
-        <x:v>0</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C6" t="s">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
@@ -889,10 +895,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" t="s">
-        <x:v>11</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C7" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
@@ -900,10 +906,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C8" t="s">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
@@ -911,10 +917,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B9" t="s">
-        <x:v>6</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C9" t="s">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
@@ -922,14 +928,25 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B10" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:3">
+      <x:c r="A11">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="B11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C11" t="s">
+        <x:v>4</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51166665554046630859" footer="0.51166665554046630859"/>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51138889789581298828" footer="0.51138889789581298828"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
 </x:worksheet>
 </file>
--- a/morpg/morpg/Assets/TableData/Table_Text.xlsx
+++ b/morpg/morpg/Assets/TableData/Table_Text.xlsx
@@ -19,11 +19,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+  <x:si>
+    <x:t>title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>메뉴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타이틀로 이동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>menu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CodeName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>continue</x:t>
+  </x:si>
   <x:si>
     <x:t>종료</x:t>
   </x:si>
   <x:si>
+    <x:t>복사</x:t>
+  </x:si>
+  <x:si>
     <x:t>int</x:t>
   </x:si>
   <x:si>
@@ -33,7 +54,7 @@
     <x:t>저장</x:t>
   </x:si>
   <x:si>
-    <x:t>복사</x:t>
+    <x:t>option</x:t>
   </x:si>
   <x:si>
     <x:t>Korean</x:t>
@@ -42,46 +63,37 @@
     <x:t>불러오기</x:t>
   </x:si>
   <x:si>
-    <x:t>option</x:t>
+    <x:t>exit</x:t>
+  </x:si>
+  <x:si>
+    <x:t>load</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Index</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Array</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이어하기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>copy</x:t>
   </x:si>
   <x:si>
     <x:t>newgame</x:t>
   </x:si>
   <x:si>
-    <x:t>load</x:t>
-  </x:si>
-  <x:si>
     <x:t>새 시작</x:t>
   </x:si>
   <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
     <x:t>Comment</x:t>
   </x:si>
   <x:si>
-    <x:t>Array</x:t>
-  </x:si>
-  <x:si>
-    <x:t>exit</x:t>
-  </x:si>
-  <x:si>
     <x:t>save</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이어하기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Index</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>continue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CodeName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>copy</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -152,12 +164,15 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="2">
+  <x:cellXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1">
       <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="2">
@@ -822,7 +837,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:D11"/>
+  <x:dimension ref="A1:D13"/>
   <x:sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="16.39999999999999857891"/>
   <x:cols>
     <x:col min="1" max="1" width="8.796875" bestFit="1" customWidth="1"/>
@@ -830,13 +845,13 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D1" s="1"/>
     </x:row>
@@ -845,16 +860,16 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D2" s="1"/>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -862,7 +877,7 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B4" s="1"/>
       <x:c r="C4" s="1"/>
@@ -873,10 +888,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" t="s">
-        <x:v>8</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C5" t="s">
-        <x:v>10</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
@@ -884,10 +899,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C6" t="s">
         <x:v>18</x:v>
-      </x:c>
-      <x:c r="C6" t="s">
-        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
@@ -895,10 +910,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" t="s">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C7" t="s">
-        <x:v>2</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
@@ -906,10 +921,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C8" t="s">
-        <x:v>0</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
@@ -917,10 +932,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B9" t="s">
-        <x:v>14</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C9" t="s">
-        <x:v>3</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
@@ -928,10 +943,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B10" t="s">
-        <x:v>9</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C10" t="s">
-        <x:v>6</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
@@ -939,10 +954,32 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B11" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C11" t="s">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:3">
+      <x:c r="A12">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C12" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:3">
+      <x:c r="A13">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B13" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C13" s="2" t="s">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/morpg/morpg/Assets/TableData/Table_Text.xlsx
+++ b/morpg/morpg/Assets/TableData/Table_Text.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="17556" windowHeight="6348" tabRatio="500"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="30468" windowHeight="12432" tabRatio="500"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="Sheet1" sheetId="1" r:id="rId4"/>
@@ -19,81 +19,87 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+  <x:si>
+    <x:t>버그리포트 바로가기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>메뉴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CodeName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>continue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bugreport</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Korean</x:t>
+  </x:si>
+  <x:si>
+    <x:t>menu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>option</x:t>
+  </x:si>
+  <x:si>
+    <x:t>exit</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타이틀로 이동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불러오기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>load</x:t>
+  </x:si>
   <x:si>
     <x:t>title</x:t>
   </x:si>
   <x:si>
-    <x:t>메뉴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타이틀로 이동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>menu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CodeName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>continue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>저장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>option</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Korean</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불러오기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>exit</x:t>
-  </x:si>
-  <x:si>
-    <x:t>load</x:t>
+    <x:t>copy</x:t>
   </x:si>
   <x:si>
     <x:t>Index</x:t>
   </x:si>
   <x:si>
+    <x:t>이어하기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>newgame</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새 시작</x:t>
+  </x:si>
+  <x:si>
     <x:t>Array</x:t>
   </x:si>
   <x:si>
-    <x:t>이어하기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>copy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>newgame</x:t>
-  </x:si>
-  <x:si>
-    <x:t>새 시작</x:t>
+    <x:t>save</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Comment</x:t>
   </x:si>
   <x:si>
     <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Comment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>save</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -837,7 +843,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:D13"/>
+  <x:dimension ref="A1:D14"/>
   <x:sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="16.39999999999999857891"/>
   <x:cols>
     <x:col min="1" max="1" width="8.796875" bestFit="1" customWidth="1"/>
@@ -845,31 +851,31 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D2" s="1"/>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -877,7 +883,7 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B4" s="1"/>
       <x:c r="C4" s="1"/>
@@ -888,10 +894,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C5" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
@@ -899,10 +905,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" t="s">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C6" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
@@ -910,10 +916,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C7" t="s">
-        <x:v>9</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
@@ -921,10 +927,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C8" t="s">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
@@ -935,7 +941,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="C9" t="s">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
@@ -943,10 +949,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B10" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C10" t="s">
         <x:v>15</x:v>
-      </x:c>
-      <x:c r="C10" t="s">
-        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
@@ -954,10 +960,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B11" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C11" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
@@ -965,7 +971,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B12" t="s">
-        <x:v>3</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C12" t="s">
         <x:v>1</x:v>
@@ -976,10 +982,21 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B13" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C13" s="2" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:3">
+      <x:c r="A14">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B14" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C14" t="s">
         <x:v>0</x:v>
-      </x:c>
-      <x:c r="C13" s="2" t="s">
-        <x:v>2</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/morpg/morpg/Assets/TableData/Table_Text.xlsx
+++ b/morpg/morpg/Assets/TableData/Table_Text.xlsx
@@ -19,27 +19,96 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
+  <x:si>
+    <x:t>cocruwa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코크루와</x:t>
+  </x:si>
+  <x:si>
+    <x:t>역사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도감</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>메뉴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>term</x:t>
+  </x:si>
+  <x:si>
+    <x:t>load</x:t>
+  </x:si>
+  <x:si>
+    <x:t>save</x:t>
+  </x:si>
+  <x:si>
+    <x:t>newgame</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Korean</x:t>
+  </x:si>
+  <x:si>
+    <x:t>menu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Comment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Index</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불러오기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이어하기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>option</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타이틀로 이동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Array</x:t>
+  </x:si>
+  <x:si>
+    <x:t>exit</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새 시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>copy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
   <x:si>
     <x:t>버그리포트 바로가기</x:t>
   </x:si>
   <x:si>
-    <x:t>메뉴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>저장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복사</x:t>
+    <x:t>bugreport</x:t>
   </x:si>
   <x:si>
     <x:t>CodeName</x:t>
@@ -48,58 +117,13 @@
     <x:t>continue</x:t>
   </x:si>
   <x:si>
-    <x:t>bugreport</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Korean</x:t>
-  </x:si>
-  <x:si>
-    <x:t>menu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>option</x:t>
-  </x:si>
-  <x:si>
-    <x:t>exit</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타이틀로 이동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불러오기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>load</x:t>
-  </x:si>
-  <x:si>
-    <x:t>title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>copy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Index</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이어하기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>newgame</x:t>
-  </x:si>
-  <x:si>
-    <x:t>새 시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Array</x:t>
-  </x:si>
-  <x:si>
-    <x:t>save</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Comment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
+    <x:t>encyclopedia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>용어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>history</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -843,7 +867,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:D14"/>
+  <x:dimension ref="A1:D18"/>
   <x:sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="16.39999999999999857891"/>
   <x:cols>
     <x:col min="1" max="1" width="8.796875" bestFit="1" customWidth="1"/>
@@ -851,25 +875,25 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D2" s="1"/>
     </x:row>
@@ -883,7 +907,7 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B4" s="1"/>
       <x:c r="C4" s="1"/>
@@ -894,10 +918,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" t="s">
-        <x:v>21</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C5" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
@@ -905,7 +929,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" t="s">
-        <x:v>8</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C6" t="s">
         <x:v>20</x:v>
@@ -916,10 +940,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C7" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
@@ -927,10 +951,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" t="s">
-        <x:v>13</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C8" t="s">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
@@ -938,10 +962,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B9" t="s">
-        <x:v>24</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C9" t="s">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
@@ -949,10 +973,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B10" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C10" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
@@ -960,10 +984,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B11" t="s">
-        <x:v>18</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C11" t="s">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
@@ -971,10 +995,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B12" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C12" t="s">
-        <x:v>1</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
@@ -985,7 +1009,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C13" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
@@ -993,10 +1017,54 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B14" t="s">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:3">
+      <x:c r="A15">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C15" t="s">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:3">
+      <x:c r="A16">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B16" t="s">
         <x:v>0</x:v>
+      </x:c>
+      <x:c r="C16" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:3">
+      <x:c r="A17">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B17" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C17" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:3">
+      <x:c r="A18">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C18" t="s">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/morpg/morpg/Assets/TableData/Table_Text.xlsx
+++ b/morpg/morpg/Assets/TableData/Table_Text.xlsx
@@ -19,7 +19,142 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="61">
+  <x:si>
+    <x:t>레노드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>continue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>버그리포트 바로가기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bugreport</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CodeName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tartaros</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gingarsion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GrenFomos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NarosaFomos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BultonKajon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IreanSorin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RoutonWinner</x:t>
+  </x:si>
+  <x:si>
+    <x:t>exit</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새 시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불러오기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Index</x:t>
+  </x:si>
+  <x:si>
+    <x:t>menu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>copy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이어하기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>history</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타이틀로 이동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Array</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Comment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>option</x:t>
+  </x:si>
+  <x:si>
+    <x:t>encyclopedia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도감</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>역사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>용어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>메뉴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>페르스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Perth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ehrlone</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레디닌</x:t>
+  </x:si>
+  <x:si>
+    <x:t>newgame</x:t>
+  </x:si>
+  <x:si>
+    <x:t>save</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Korean</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Renod</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Redinin</x:t>
+  </x:si>
   <x:si>
     <x:t>cocruwa</x:t>
   </x:si>
@@ -27,103 +162,46 @@
     <x:t>코크루와</x:t>
   </x:si>
   <x:si>
-    <x:t>역사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도감</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>저장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>메뉴</x:t>
+    <x:t>load</x:t>
   </x:si>
   <x:si>
     <x:t>term</x:t>
   </x:si>
   <x:si>
-    <x:t>load</x:t>
-  </x:si>
-  <x:si>
-    <x:t>save</x:t>
-  </x:si>
-  <x:si>
-    <x:t>newgame</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Korean</x:t>
-  </x:si>
-  <x:si>
-    <x:t>menu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Comment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Index</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불러오기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이어하기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>option</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타이틀로 이동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Array</x:t>
-  </x:si>
-  <x:si>
-    <x:t>exit</x:t>
-  </x:si>
-  <x:si>
-    <x:t>새 시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>copy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>버그리포트 바로가기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bugreport</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CodeName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>continue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>encyclopedia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>용어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>history</x:t>
+    <x:t>KaroukWingent</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GaremenTooskaDin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가레멘 투스카 딘</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나로사 포모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그렌 포모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>긴가르시온</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에를로네</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타르타로스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카루크 뷘젠트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라우톤 윈너</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불튼 카존</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이레안 소린</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -867,7 +945,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:D18"/>
+  <x:dimension ref="A1:D31"/>
   <x:sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="16.39999999999999857891"/>
   <x:cols>
     <x:col min="1" max="1" width="8.796875" bestFit="1" customWidth="1"/>
@@ -875,25 +953,25 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D2" s="1"/>
     </x:row>
@@ -907,7 +985,7 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B4" s="1"/>
       <x:c r="C4" s="1"/>
@@ -918,10 +996,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C5" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="C5" t="s">
-        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
@@ -929,7 +1007,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" t="s">
-        <x:v>31</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C6" t="s">
         <x:v>20</x:v>
@@ -940,10 +1018,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" t="s">
-        <x:v>21</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C7" t="s">
-        <x:v>4</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
@@ -951,10 +1029,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" t="s">
-        <x:v>24</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C8" t="s">
-        <x:v>6</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
@@ -962,10 +1040,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B9" t="s">
-        <x:v>12</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C9" t="s">
-        <x:v>8</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
@@ -973,10 +1051,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B10" t="s">
-        <x:v>11</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C10" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
@@ -984,10 +1062,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B11" t="s">
-        <x:v>26</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C11" t="s">
-        <x:v>5</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
@@ -995,10 +1073,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B12" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C12" t="s">
-        <x:v>9</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
@@ -1006,7 +1084,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B13" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C13" s="2" t="s">
         <x:v>22</x:v>
@@ -1017,10 +1095,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B14" t="s">
-        <x:v>29</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C14" t="s">
-        <x:v>28</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
@@ -1028,10 +1106,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B15" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C15" t="s">
-        <x:v>3</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
@@ -1039,10 +1117,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B16" t="s">
-        <x:v>0</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C16" t="s">
-        <x:v>1</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
@@ -1050,7 +1128,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B17" t="s">
-        <x:v>10</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C17" t="s">
         <x:v>33</x:v>
@@ -1061,10 +1139,153 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B18" t="s">
-        <x:v>34</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C18" t="s">
-        <x:v>2</x:v>
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:3">
+      <x:c r="A19">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B19" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C19" t="s">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:3">
+      <x:c r="A20">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B20" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C20" t="s">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:3">
+      <x:c r="A21">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B21" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C21" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:3">
+      <x:c r="A22">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B22" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C22" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:3">
+      <x:c r="A23">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B23" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C23" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:3">
+      <x:c r="A24">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B24" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C24" t="s">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:3">
+      <x:c r="A25">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B25" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C25" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:3">
+      <x:c r="A26">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B26" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C26" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:3">
+      <x:c r="A27">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B27" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C27" t="s">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:3">
+      <x:c r="A28">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B28" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C28" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:3">
+      <x:c r="A29">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B29" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C29" t="s">
+        <x:v>57</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:3">
+      <x:c r="A30">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B30" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C30" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:3">
+      <x:c r="A31">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B31" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C31" t="s">
+        <x:v>51</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/morpg/morpg/Assets/TableData/Table_Text.xlsx
+++ b/morpg/morpg/Assets/TableData/Table_Text.xlsx
@@ -19,189 +19,339 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="61">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="111">
+  <x:si>
+    <x:t>Hidden001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>???????????????</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hidden002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BultonKajon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gingarsion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>버그리포트 바로가기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IreanSorin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CodeName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GrenFomos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가레멘 투스카 딘</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Necromancer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tartaros</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NarosaFomos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>continue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bugreport</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Summoner</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Alchemist</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Archmage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GaremenTooskaDin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RoutonWinner</x:t>
+  </x:si>
+  <x:si>
+    <x:t>encyclopedia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KaroukWingent</x:t>
+  </x:si>
+  <x:si>
+    <x:t>직업</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도적</x:t>
+  </x:si>
+  <x:si>
+    <x:t>궁수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>페르스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>티모르</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>역사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레디닌</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마법사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>메뉴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>셀레나</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>악마</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Job</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전사</x:t>
+  </x:si>
   <x:si>
     <x:t>레노드</x:t>
   </x:si>
   <x:si>
-    <x:t>continue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>버그리포트 바로가기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bugreport</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CodeName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tartaros</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gingarsion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GrenFomos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NarosaFomos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BultonKajon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IreanSorin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RoutonWinner</x:t>
+    <x:t>저장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도감</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>성직자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로데크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>바드락</x:t>
+  </x:si>
+  <x:si>
+    <x:t>용어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>암살자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>투르카</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타르타로스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Renod</x:t>
+  </x:si>
+  <x:si>
+    <x:t>term</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sandora</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Machine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>load</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kalapok</x:t>
+  </x:si>
+  <x:si>
+    <x:t>newgame</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Korean</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Priest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Archer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나로사 포모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Badrak</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새 시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Perth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라우톤 윈너</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코크루와</x:t>
+  </x:si>
+  <x:si>
+    <x:t>긴가르시온</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Demon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불튼 카존</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불러오기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카루크 뷘젠트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Unknown</x:t>
+  </x:si>
+  <x:si>
+    <x:t>save</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그렌 포모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Teemole</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에를로네</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rogue</x:t>
   </x:si>
   <x:si>
     <x:t>exit</x:t>
   </x:si>
   <x:si>
-    <x:t>새 시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불러오기</x:t>
+    <x:t>option</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ehrlone</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연금술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Warrior</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Comment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>menu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>history</x:t>
   </x:si>
   <x:si>
     <x:t>string</x:t>
   </x:si>
   <x:si>
+    <x:t>Assasin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Human</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cocruwa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rodec</x:t>
+  </x:si>
+  <x:si>
+    <x:t>강령술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소환술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>산도라 태생</x:t>
+  </x:si>
+  <x:si>
+    <x:t>칼라포크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Species</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대마도사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Toorka</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Selena</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Array</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Redinin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타이틀로 이동</x:t>
+  </x:si>
+  <x:si>
     <x:t>Index</x:t>
   </x:si>
   <x:si>
-    <x:t>menu</x:t>
+    <x:t>이레안 소린</x:t>
+  </x:si>
+  <x:si>
+    <x:t>copy</x:t>
   </x:si>
   <x:si>
     <x:t>title</x:t>
   </x:si>
   <x:si>
-    <x:t>copy</x:t>
-  </x:si>
-  <x:si>
     <x:t>이어하기</x:t>
   </x:si>
   <x:si>
-    <x:t>history</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타이틀로 이동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Array</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Comment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>option</x:t>
-  </x:si>
-  <x:si>
-    <x:t>encyclopedia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도감</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>역사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>용어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>저장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>메뉴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>페르스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Perth</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ehrlone</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레디닌</x:t>
-  </x:si>
-  <x:si>
-    <x:t>newgame</x:t>
-  </x:si>
-  <x:si>
-    <x:t>save</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Korean</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Renod</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Redinin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cocruwa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코크루와</x:t>
-  </x:si>
-  <x:si>
-    <x:t>load</x:t>
-  </x:si>
-  <x:si>
-    <x:t>term</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KaroukWingent</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GaremenTooskaDin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가레멘 투스카 딘</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나로사 포모스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그렌 포모스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>긴가르시온</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에를로네</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타르타로스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카루크 뷘젠트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라우톤 윈너</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불튼 카존</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이레안 소린</x:t>
+    <x:t>?????</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -945,7 +1095,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:D31"/>
+  <x:dimension ref="A1:D56"/>
   <x:sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="16.39999999999999857891"/>
   <x:cols>
     <x:col min="1" max="1" width="8.796875" bestFit="1" customWidth="1"/>
@@ -953,31 +1103,31 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D2" s="1"/>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -985,7 +1135,7 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B4" s="1"/>
       <x:c r="C4" s="1"/>
@@ -996,10 +1146,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" t="s">
-        <x:v>40</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C5" t="s">
-        <x:v>13</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
@@ -1007,10 +1157,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" t="s">
-        <x:v>1</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C6" t="s">
-        <x:v>20</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
@@ -1018,10 +1168,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" t="s">
-        <x:v>25</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C7" t="s">
-        <x:v>28</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
@@ -1029,10 +1179,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" t="s">
-        <x:v>12</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C8" t="s">
-        <x:v>32</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
@@ -1040,10 +1190,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B9" t="s">
-        <x:v>41</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C9" t="s">
-        <x:v>34</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
@@ -1051,10 +1201,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B10" t="s">
-        <x:v>47</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C10" t="s">
-        <x:v>14</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
@@ -1062,10 +1212,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B11" t="s">
-        <x:v>19</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C11" t="s">
-        <x:v>31</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
@@ -1073,10 +1223,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B12" t="s">
-        <x:v>17</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C12" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
@@ -1084,10 +1234,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B13" t="s">
-        <x:v>18</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C13" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
@@ -1095,10 +1245,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B14" t="s">
-        <x:v>3</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C14" t="s">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
@@ -1106,10 +1256,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B15" t="s">
-        <x:v>26</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C15" t="s">
-        <x:v>27</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
@@ -1117,10 +1267,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B16" t="s">
-        <x:v>45</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C16" t="s">
-        <x:v>46</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
@@ -1128,10 +1278,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B17" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C17" t="s">
-        <x:v>33</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
@@ -1139,7 +1289,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B18" t="s">
-        <x:v>21</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C18" t="s">
         <x:v>30</x:v>
@@ -1150,10 +1300,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B19" t="s">
-        <x:v>43</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C19" t="s">
-        <x:v>0</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
@@ -1161,10 +1311,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B20" t="s">
-        <x:v>5</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C20" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
@@ -1172,10 +1322,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B21" t="s">
-        <x:v>44</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C21" t="s">
-        <x:v>39</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
@@ -1183,10 +1333,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B22" t="s">
-        <x:v>37</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C22" t="s">
-        <x:v>36</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
@@ -1194,10 +1344,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B23" t="s">
-        <x:v>38</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C23" t="s">
-        <x:v>55</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
@@ -1205,10 +1355,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B24" t="s">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C24" t="s">
-        <x:v>54</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
@@ -1216,10 +1366,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B25" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C25" t="s">
-        <x:v>53</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
@@ -1227,10 +1377,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B26" t="s">
-        <x:v>8</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C26" t="s">
-        <x:v>52</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
@@ -1238,10 +1388,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B27" t="s">
-        <x:v>10</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C27" t="s">
-        <x:v>60</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
@@ -1249,10 +1399,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B28" t="s">
-        <x:v>9</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C28" t="s">
-        <x:v>59</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3">
@@ -1260,10 +1410,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B29" t="s">
-        <x:v>49</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C29" t="s">
-        <x:v>57</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">
@@ -1271,10 +1421,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B30" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C30" t="s">
-        <x:v>58</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
@@ -1282,10 +1432,285 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B31" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C31" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:3">
+      <x:c r="A32">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B32" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C32" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:3">
+      <x:c r="A33">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B33" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C33" t="s">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:3">
+      <x:c r="A34">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B34" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C34" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:3">
+      <x:c r="A35">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B35" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="C35" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:3">
+      <x:c r="A36">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B36" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C36" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:3">
+      <x:c r="A37">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B37" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C37" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:3">
+      <x:c r="A38">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B38" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C38" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:3">
+      <x:c r="A39">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B39" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C39" t="s">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:3">
+      <x:c r="A40">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B40" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C40" t="s">
+        <x:v>96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:3">
+      <x:c r="A41">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B41" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C41" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:3">
+      <x:c r="A42">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B42" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="C42" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:3">
+      <x:c r="A43">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B43" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C43" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:3">
+      <x:c r="A44">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B44" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C44" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:3">
+      <x:c r="A45">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B45" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C45" t="s">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:3">
+      <x:c r="A46">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B46" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C46" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C31" t="s">
+    </x:row>
+    <x:row r="47" spans="1:3">
+      <x:c r="A47">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B47" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C47" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:3">
+      <x:c r="A48">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B48" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C48" t="s">
+        <x:v>94</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:3">
+      <x:c r="A49">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B49" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C49" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:3">
+      <x:c r="A50">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B50" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C50" t="s">
+        <x:v>93</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:3">
+      <x:c r="A51">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B51" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C51" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:3">
+      <x:c r="A52">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B52" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C52" t="s">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:3">
+      <x:c r="A53">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B53" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C53" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:3">
+      <x:c r="A54">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B54" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C54" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:3">
+      <x:c r="A55">
         <x:v>51</x:v>
+      </x:c>
+      <x:c r="B55" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C55" t="s">
+        <x:v>110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:3">
+      <x:c r="A56">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B56" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C56" t="s">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/morpg/morpg/Assets/TableData/Table_Text.xlsx
+++ b/morpg/morpg/Assets/TableData/Table_Text.xlsx
@@ -19,339 +19,345 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="111">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="113">
+  <x:si>
+    <x:t>무직</x:t>
+  </x:si>
+  <x:si>
+    <x:t>궁수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>역사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>셀레나</x:t>
+  </x:si>
+  <x:si>
+    <x:t>악마</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도적</x:t>
+  </x:si>
+  <x:si>
+    <x:t>티모르</x:t>
+  </x:si>
+  <x:si>
+    <x:t>페르스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>메뉴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레디닌</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>직업</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마법사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로데크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>용어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>성직자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>암살자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도감</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레노드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>투르카</x:t>
+  </x:si>
+  <x:si>
+    <x:t>바드락</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Job</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GaremenTooskaDin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>continue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Summoner</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Alchemist</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bugreport</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이어하기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Toorka</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Index</x:t>
+  </x:si>
+  <x:si>
+    <x:t>copy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대마도사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Redinin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타이틀로 이동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이레안 소린</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Selena</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Array</x:t>
+  </x:si>
+  <x:si>
+    <x:t>?????</x:t>
+  </x:si>
+  <x:si>
+    <x:t>버그리포트 바로가기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가레멘 투스카 딘</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gingarsion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CodeName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GrenFomos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hidden002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Necromancer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tartaros</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NarosaFomos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BultonKajon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IreanSorin</x:t>
+  </x:si>
   <x:si>
     <x:t>Hidden001</x:t>
   </x:si>
   <x:si>
+    <x:t>Comment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>menu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그렌 포모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연금술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rogue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Demon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카루크 뷘젠트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>긴가르시온</x:t>
+  </x:si>
+  <x:si>
+    <x:t>exit</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불튼 카존</x:t>
+  </x:si>
+  <x:si>
+    <x:t>save</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에를로네</x:t>
+  </x:si>
+  <x:si>
+    <x:t>option</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Warrior</x:t>
+  </x:si>
+  <x:si>
+    <x:t>history</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불러오기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Teemole</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Assasin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코크루와</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Unknown</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ehrlone</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Human</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cocruwa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소환술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>산도라 태생</x:t>
+  </x:si>
+  <x:si>
+    <x:t>칼라포크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Species</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rodec</x:t>
+  </x:si>
+  <x:si>
+    <x:t>강령술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>newgame</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Priest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나로사 포모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Badrak</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라우톤 윈너</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sandora</x:t>
+  </x:si>
+  <x:si>
+    <x:t>term</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새 시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Renod</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Archer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Perth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Korean</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kalapok</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타르타로스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Machine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>load</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Archmage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>encyclopedia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KaroukWingent</x:t>
+  </x:si>
+  <x:si>
     <x:t>???????????????</x:t>
   </x:si>
   <x:si>
-    <x:t>Hidden002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BultonKajon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gingarsion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>버그리포트 바로가기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IreanSorin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CodeName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GrenFomos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가레멘 투스카 딘</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Necromancer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tartaros</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NarosaFomos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>continue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bugreport</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Summoner</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Alchemist</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Archmage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GaremenTooskaDin</x:t>
-  </x:si>
-  <x:si>
     <x:t>RoutonWinner</x:t>
   </x:si>
   <x:si>
-    <x:t>encyclopedia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KaroukWingent</x:t>
-  </x:si>
-  <x:si>
-    <x:t>직업</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도적</x:t>
-  </x:si>
-  <x:si>
-    <x:t>궁수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>페르스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>티모르</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>역사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레디닌</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마법사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>메뉴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>셀레나</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>악마</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Job</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레노드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>저장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도감</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>성직자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>로데크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>바드락</x:t>
-  </x:si>
-  <x:si>
-    <x:t>용어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>암살자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>투르카</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타르타로스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Renod</x:t>
-  </x:si>
-  <x:si>
-    <x:t>term</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sandora</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Machine</x:t>
-  </x:si>
-  <x:si>
-    <x:t>load</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kalapok</x:t>
-  </x:si>
-  <x:si>
-    <x:t>newgame</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Korean</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Priest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Archer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나로사 포모스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Badrak</x:t>
-  </x:si>
-  <x:si>
-    <x:t>새 시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Perth</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라우톤 윈너</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코크루와</x:t>
-  </x:si>
-  <x:si>
-    <x:t>긴가르시온</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Demon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불튼 카존</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불러오기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카루크 뷘젠트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Unknown</x:t>
-  </x:si>
-  <x:si>
-    <x:t>save</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그렌 포모스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Teemole</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에를로네</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rogue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>exit</x:t>
-  </x:si>
-  <x:si>
-    <x:t>option</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ehrlone</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연금술사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Warrior</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Comment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>menu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>history</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Assasin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Human</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cocruwa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rodec</x:t>
-  </x:si>
-  <x:si>
-    <x:t>강령술사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소환술사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>산도라 태생</x:t>
-  </x:si>
-  <x:si>
-    <x:t>칼라포크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Species</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대마도사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Toorka</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Selena</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Array</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Redinin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타이틀로 이동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Index</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이레안 소린</x:t>
-  </x:si>
-  <x:si>
-    <x:t>copy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이어하기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>?????</x:t>
+    <x:t>notEmployed</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1095,7 +1101,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:D56"/>
+  <x:dimension ref="A1:D57"/>
   <x:sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="16.39999999999999857891"/>
   <x:cols>
     <x:col min="1" max="1" width="8.796875" bestFit="1" customWidth="1"/>
@@ -1103,31 +1109,31 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D2" s="1"/>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -1135,7 +1141,7 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B4" s="1"/>
       <x:c r="C4" s="1"/>
@@ -1146,10 +1152,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" t="s">
-        <x:v>59</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C5" t="s">
-        <x:v>65</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
@@ -1157,10 +1163,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" t="s">
-        <x:v>13</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C6" t="s">
-        <x:v>109</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
@@ -1168,10 +1174,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" t="s">
-        <x:v>81</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C7" t="s">
-        <x:v>33</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
@@ -1179,10 +1185,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" t="s">
-        <x:v>80</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C8" t="s">
-        <x:v>28</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
@@ -1190,10 +1196,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B9" t="s">
-        <x:v>75</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C9" t="s">
-        <x:v>42</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
@@ -1201,10 +1207,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B10" t="s">
-        <x:v>57</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C10" t="s">
-        <x:v>72</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
@@ -1212,10 +1218,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B11" t="s">
-        <x:v>107</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C11" t="s">
-        <x:v>45</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
@@ -1223,10 +1229,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B12" t="s">
-        <x:v>86</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C12" t="s">
-        <x:v>34</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
@@ -1234,10 +1240,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B13" t="s">
-        <x:v>108</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C13" s="2" t="s">
-        <x:v>104</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
@@ -1245,10 +1251,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B14" t="s">
-        <x:v>14</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C14" t="s">
-        <x:v>5</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
@@ -1256,10 +1262,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B15" t="s">
-        <x:v>20</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C15" t="s">
-        <x:v>43</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
@@ -1267,10 +1273,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B16" t="s">
-        <x:v>91</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C16" t="s">
-        <x:v>68</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
@@ -1278,10 +1284,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B17" t="s">
-        <x:v>54</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C17" t="s">
-        <x:v>49</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
@@ -1289,10 +1295,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B18" t="s">
-        <x:v>87</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C18" t="s">
-        <x:v>30</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
@@ -1300,10 +1306,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B19" t="s">
-        <x:v>53</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C19" t="s">
-        <x:v>41</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
@@ -1311,10 +1317,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B20" t="s">
-        <x:v>11</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C20" t="s">
-        <x:v>52</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
@@ -1322,10 +1328,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B21" t="s">
-        <x:v>103</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C21" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
@@ -1333,10 +1339,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B22" t="s">
-        <x:v>66</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C22" t="s">
-        <x:v>26</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
@@ -1344,10 +1350,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B23" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C23" t="s">
-        <x:v>78</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
@@ -1355,10 +1361,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B24" t="s">
-        <x:v>4</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C24" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
@@ -1366,10 +1372,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B25" t="s">
-        <x:v>8</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C25" t="s">
-        <x:v>76</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
@@ -1377,10 +1383,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B26" t="s">
-        <x:v>12</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C26" t="s">
-        <x:v>63</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
@@ -1388,10 +1394,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B27" t="s">
-        <x:v>6</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C27" t="s">
-        <x:v>106</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
@@ -1399,10 +1405,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B28" t="s">
-        <x:v>3</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C28" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3">
@@ -1410,10 +1416,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B29" t="s">
-        <x:v>21</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C29" t="s">
-        <x:v>73</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">
@@ -1421,10 +1427,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B30" t="s">
-        <x:v>19</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C30" t="s">
-        <x:v>67</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
@@ -1432,10 +1438,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B31" t="s">
-        <x:v>18</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C31" t="s">
-        <x:v>9</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:3">
@@ -1443,10 +1449,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B32" t="s">
-        <x:v>90</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C32" t="s">
-        <x:v>38</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:3">
@@ -1454,10 +1460,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B33" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C33" t="s">
-        <x:v>47</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:3">
@@ -1465,10 +1471,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B34" t="s">
-        <x:v>99</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C34" t="s">
-        <x:v>51</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:3">
@@ -1479,7 +1485,7 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="C35" t="s">
-        <x:v>27</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:3">
@@ -1487,10 +1493,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B36" t="s">
-        <x:v>101</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C36" t="s">
-        <x:v>35</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:3">
@@ -1498,10 +1504,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B37" t="s">
-        <x:v>64</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C37" t="s">
-        <x:v>48</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:3">
@@ -1509,10 +1515,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B38" t="s">
-        <x:v>56</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C38" t="s">
-        <x:v>29</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:3">
@@ -1520,10 +1526,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B39" t="s">
-        <x:v>55</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C39" t="s">
-        <x:v>95</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:3">
@@ -1531,10 +1537,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B40" t="s">
-        <x:v>58</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C40" t="s">
-        <x:v>96</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:3">
@@ -1542,10 +1548,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B41" t="s">
-        <x:v>74</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C41" t="s">
-        <x:v>36</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:3">
@@ -1553,10 +1559,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B42" t="s">
-        <x:v>84</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C42" t="s">
-        <x:v>40</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:3">
@@ -1564,10 +1570,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B43" t="s">
-        <x:v>62</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C43" t="s">
-        <x:v>25</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:3">
@@ -1575,10 +1581,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B44" t="s">
-        <x:v>100</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C44" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:3">
@@ -1586,10 +1592,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B45" t="s">
-        <x:v>61</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C45" t="s">
-        <x:v>46</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:3">
@@ -1597,10 +1603,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B46" t="s">
-        <x:v>89</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C46" t="s">
-        <x:v>50</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:3">
@@ -1608,10 +1614,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B47" t="s">
-        <x:v>79</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C47" t="s">
-        <x:v>24</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:3">
@@ -1619,10 +1625,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B48" t="s">
-        <x:v>15</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C48" t="s">
-        <x:v>94</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:3">
@@ -1630,10 +1636,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B49" t="s">
-        <x:v>16</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C49" t="s">
-        <x:v>83</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:3">
@@ -1641,10 +1647,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B50" t="s">
-        <x:v>10</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C50" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:3">
@@ -1652,10 +1658,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B51" t="s">
-        <x:v>70</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C51" t="s">
-        <x:v>37</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:3">
@@ -1663,10 +1669,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B52" t="s">
-        <x:v>17</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C52" t="s">
-        <x:v>98</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:3">
@@ -1674,10 +1680,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B53" t="s">
-        <x:v>97</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C53" t="s">
-        <x:v>23</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:3">
@@ -1685,10 +1691,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B54" t="s">
-        <x:v>39</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C54" t="s">
-        <x:v>22</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:3">
@@ -1696,10 +1702,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B55" t="s">
-        <x:v>0</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C55" t="s">
-        <x:v>110</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:3">
@@ -1707,10 +1713,21 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B56" t="s">
-        <x:v>2</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C56" t="s">
-        <x:v>1</x:v>
+        <x:v>110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:3">
+      <x:c r="A57">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B57" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="C57" t="s">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/morpg/morpg/Assets/TableData/Table_Text.xlsx
+++ b/morpg/morpg/Assets/TableData/Table_Text.xlsx
@@ -19,345 +19,435 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="113">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="143">
+  <x:si>
+    <x:t>반지(좌)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Weapon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Armor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>귀걸이(우)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Boots</x:t>
+  </x:si>
+  <x:si>
+    <x:t>귀걸이(좌)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gloves</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Head</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cloth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Leather</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Plate</x:t>
+  </x:si>
+  <x:si>
+    <x:t>역사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>페르스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>궁수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레노드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레디닌</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장갑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>메뉴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>머리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>성직자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>암살자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장비</x:t>
+  </x:si>
+  <x:si>
+    <x:t>갑옷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>악마</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마법사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도적</x:t>
+  </x:si>
+  <x:si>
+    <x:t>직업</x:t>
+  </x:si>
   <x:si>
     <x:t>무직</x:t>
   </x:si>
   <x:si>
-    <x:t>궁수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>역사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불명</x:t>
+    <x:t>신발</x:t>
   </x:si>
   <x:si>
     <x:t>셀레나</x:t>
   </x:si>
   <x:si>
-    <x:t>악마</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도적</x:t>
+    <x:t>설정</x:t>
   </x:si>
   <x:si>
     <x:t>티모르</x:t>
   </x:si>
   <x:si>
-    <x:t>페르스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>메뉴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레디닌</x:t>
+    <x:t>Job</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로데크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가죽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>투르카</x:t>
+  </x:si>
+  <x:si>
+    <x:t>판금</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도감</x:t>
+  </x:si>
+  <x:si>
+    <x:t>바드락</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목걸이</x:t>
   </x:si>
   <x:si>
     <x:t>종족</x:t>
   </x:si>
   <x:si>
-    <x:t>직업</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마법사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>로데크</x:t>
-  </x:si>
-  <x:si>
     <x:t>용어</x:t>
   </x:si>
   <x:si>
-    <x:t>성직자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>암살자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도감</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레노드</x:t>
-  </x:si>
-  <x:si>
     <x:t>저장</x:t>
   </x:si>
   <x:si>
-    <x:t>투르카</x:t>
-  </x:si>
-  <x:si>
-    <x:t>바드락</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Job</x:t>
+    <x:t>천</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ehrlone</x:t>
+  </x:si>
+  <x:si>
+    <x:t>?????</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카루크 뷘젠트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>긴가르시온</x:t>
+  </x:si>
+  <x:si>
+    <x:t>option</x:t>
+  </x:si>
+  <x:si>
+    <x:t>title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Comment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Index</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Warrior</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Redinin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불튼 카존</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rogue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>copy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그렌 포모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>exit</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연금술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Selena</x:t>
+  </x:si>
+  <x:si>
+    <x:t>save</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불러오기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Toorka</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이레안 소린</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Demon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>반지(우)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>history</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Teemole</x:t>
+  </x:si>
+  <x:si>
+    <x:t>encyclopedia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>???????????????</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RoutonWinner</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KaroukWingent</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RightEarring</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Necklace</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Equipment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LeftRing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Species&amp;Job</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RightRIng</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LeftEarring</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종족&amp;직업</x:t>
   </x:si>
   <x:si>
     <x:t>GaremenTooskaDin</x:t>
   </x:si>
   <x:si>
+    <x:t>나로사 포모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Perth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Korean</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sandora</x:t>
+  </x:si>
+  <x:si>
+    <x:t>칼라포크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Human</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새 시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>강령술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Renod</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Archer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Badrak</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Species</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Machine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>term</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라우톤 윈너</x:t>
+  </x:si>
+  <x:si>
+    <x:t>newgame</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소환술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대마도사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Array</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코크루와</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타이틀로 이동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>산도라 태생</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에를로네</x:t>
+  </x:si>
+  <x:si>
+    <x:t>load</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Priest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rodec</x:t>
+  </x:si>
+  <x:si>
+    <x:t>menu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cocruwa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Unknown</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타르타로스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Assasin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kalapok</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이어하기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NarosaFomos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BultonKajon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>notEmployed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Necromancer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Archmage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CodeName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hidden002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tartaros</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hidden001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IreanSorin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>버그리포트 바로가기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bugreport</x:t>
+  </x:si>
+  <x:si>
     <x:t>continue</x:t>
   </x:si>
   <x:si>
     <x:t>Summoner</x:t>
   </x:si>
   <x:si>
+    <x:t>가레멘 투스카 딘</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gingarsion</x:t>
+  </x:si>
+  <x:si>
     <x:t>Alchemist</x:t>
   </x:si>
   <x:si>
-    <x:t>bugreport</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이어하기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Toorka</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Index</x:t>
-  </x:si>
-  <x:si>
-    <x:t>copy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대마도사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Redinin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타이틀로 이동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이레안 소린</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Selena</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Array</x:t>
-  </x:si>
-  <x:si>
-    <x:t>?????</x:t>
-  </x:si>
-  <x:si>
-    <x:t>버그리포트 바로가기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가레멘 투스카 딘</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gingarsion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CodeName</x:t>
-  </x:si>
-  <x:si>
     <x:t>GrenFomos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hidden002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Necromancer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tartaros</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NarosaFomos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BultonKajon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IreanSorin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hidden001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Comment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>menu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그렌 포모스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연금술사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rogue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Demon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카루크 뷘젠트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>긴가르시온</x:t>
-  </x:si>
-  <x:si>
-    <x:t>exit</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불튼 카존</x:t>
-  </x:si>
-  <x:si>
-    <x:t>save</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에를로네</x:t>
-  </x:si>
-  <x:si>
-    <x:t>option</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Warrior</x:t>
-  </x:si>
-  <x:si>
-    <x:t>history</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불러오기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Teemole</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Assasin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코크루와</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Unknown</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ehrlone</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Human</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cocruwa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소환술사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>산도라 태생</x:t>
-  </x:si>
-  <x:si>
-    <x:t>칼라포크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Species</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rodec</x:t>
-  </x:si>
-  <x:si>
-    <x:t>강령술사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>newgame</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Priest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나로사 포모스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Badrak</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라우톤 윈너</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sandora</x:t>
-  </x:si>
-  <x:si>
-    <x:t>term</x:t>
-  </x:si>
-  <x:si>
-    <x:t>새 시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Renod</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Archer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Perth</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Korean</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kalapok</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타르타로스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Machine</x:t>
-  </x:si>
-  <x:si>
-    <x:t>load</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Archmage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>encyclopedia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KaroukWingent</x:t>
-  </x:si>
-  <x:si>
-    <x:t>???????????????</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RoutonWinner</x:t>
-  </x:si>
-  <x:si>
-    <x:t>notEmployed</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1101,7 +1191,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:D57"/>
+  <x:dimension ref="A1:D72"/>
   <x:sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="16.39999999999999857891"/>
   <x:cols>
     <x:col min="1" max="1" width="8.796875" bestFit="1" customWidth="1"/>
@@ -1109,31 +1199,31 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D2" s="1"/>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -1141,7 +1231,7 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B4" s="1"/>
       <x:c r="C4" s="1"/>
@@ -1152,10 +1242,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" t="s">
-        <x:v>91</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C5" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
@@ -1163,10 +1253,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" t="s">
-        <x:v>32</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C6" t="s">
-        <x:v>36</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
@@ -1174,10 +1264,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" t="s">
-        <x:v>73</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C7" t="s">
-        <x:v>17</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
@@ -1185,10 +1275,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C8" t="s">
-        <x:v>9</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
@@ -1196,10 +1286,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B9" t="s">
-        <x:v>71</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C9" t="s">
-        <x:v>27</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
@@ -1207,10 +1297,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B10" t="s">
-        <x:v>106</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C10" t="s">
-        <x:v>76</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
@@ -1218,10 +1308,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B11" t="s">
-        <x:v>41</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C11" t="s">
-        <x:v>22</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
@@ -1229,10 +1319,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B12" t="s">
-        <x:v>62</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C12" t="s">
-        <x:v>10</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
@@ -1240,10 +1330,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B13" t="s">
-        <x:v>38</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C13" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
@@ -1251,10 +1341,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B14" t="s">
-        <x:v>35</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C14" t="s">
-        <x:v>49</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
@@ -1262,10 +1352,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B15" t="s">
-        <x:v>108</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C15" t="s">
-        <x:v>24</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
@@ -1273,10 +1363,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B16" t="s">
-        <x:v>84</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C16" t="s">
-        <x:v>79</x:v>
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
@@ -1284,10 +1374,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B17" t="s">
-        <x:v>97</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C17" t="s">
-        <x:v>20</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
@@ -1298,7 +1388,7 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="C18" t="s">
-        <x:v>2</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
@@ -1306,10 +1396,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B19" t="s">
-        <x:v>99</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C19" t="s">
-        <x:v>26</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
@@ -1317,10 +1407,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B20" t="s">
-        <x:v>56</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C20" t="s">
-        <x:v>104</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
@@ -1328,10 +1418,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B21" t="s">
-        <x:v>43</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C21" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
@@ -1339,10 +1429,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B22" t="s">
-        <x:v>101</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C22" t="s">
-        <x:v>8</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
@@ -1350,10 +1440,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B23" t="s">
-        <x:v>81</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C23" t="s">
-        <x:v>72</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
@@ -1361,10 +1451,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B24" t="s">
-        <x:v>51</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C24" t="s">
-        <x:v>68</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
@@ -1372,10 +1462,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B25" t="s">
-        <x:v>53</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C25" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
@@ -1383,10 +1473,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B26" t="s">
-        <x:v>57</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C26" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
@@ -1394,10 +1484,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B27" t="s">
-        <x:v>59</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C27" t="s">
-        <x:v>45</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
@@ -1405,10 +1495,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B28" t="s">
-        <x:v>58</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C28" t="s">
-        <x:v>70</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3">
@@ -1416,10 +1506,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B29" t="s">
-        <x:v>109</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C29" t="s">
-        <x:v>67</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">
@@ -1427,10 +1517,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B30" t="s">
-        <x:v>111</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C30" t="s">
-        <x:v>95</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
@@ -1438,10 +1528,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B31" t="s">
-        <x:v>31</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C31" t="s">
-        <x:v>50</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:3">
@@ -1449,10 +1539,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B32" t="s">
-        <x:v>83</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C32" t="s">
-        <x:v>15</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:3">
@@ -1460,10 +1550,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B33" t="s">
-        <x:v>89</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C33" t="s">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:3">
@@ -1471,10 +1561,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B34" t="s">
-        <x:v>39</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C34" t="s">
-        <x:v>28</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:3">
@@ -1482,10 +1572,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B35" t="s">
-        <x:v>77</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C35" t="s">
-        <x:v>7</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:3">
@@ -1493,10 +1583,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B36" t="s">
-        <x:v>46</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C36" t="s">
-        <x:v>4</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:3">
@@ -1504,10 +1594,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B37" t="s">
-        <x:v>94</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C37" t="s">
-        <x:v>29</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:3">
@@ -1515,10 +1605,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B38" t="s">
-        <x:v>105</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C38" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:3">
@@ -1526,10 +1616,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B39" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C39" t="s">
-        <x:v>86</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:3">
@@ -1537,10 +1627,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B40" t="s">
-        <x:v>103</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C40" t="s">
-        <x:v>87</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:3">
@@ -1548,10 +1638,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B41" t="s">
-        <x:v>80</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C41" t="s">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:3">
@@ -1559,7 +1649,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B42" t="s">
-        <x:v>74</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C42" t="s">
         <x:v>18</x:v>
@@ -1570,10 +1660,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B43" t="s">
-        <x:v>100</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C43" t="s">
-        <x:v>1</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:3">
@@ -1581,10 +1671,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B44" t="s">
-        <x:v>37</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C44" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:3">
@@ -1592,10 +1682,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B45" t="s">
-        <x:v>92</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C45" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:3">
@@ -1603,10 +1693,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B46" t="s">
-        <x:v>78</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C46" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:3">
@@ -1614,10 +1704,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B47" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C47" t="s">
-        <x:v>6</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:3">
@@ -1625,10 +1715,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B48" t="s">
-        <x:v>33</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C48" t="s">
-        <x:v>85</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:3">
@@ -1636,10 +1726,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B49" t="s">
-        <x:v>34</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C49" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:3">
@@ -1647,10 +1737,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B50" t="s">
-        <x:v>55</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C50" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:3">
@@ -1658,10 +1748,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B51" t="s">
-        <x:v>66</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C51" t="s">
-        <x:v>5</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:3">
@@ -1669,10 +1759,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B52" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="C52" t="s">
         <x:v>107</x:v>
-      </x:c>
-      <x:c r="C52" t="s">
-        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:3">
@@ -1680,10 +1770,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B53" t="s">
-        <x:v>88</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C53" t="s">
-        <x:v>12</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:3">
@@ -1691,10 +1781,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B54" t="s">
-        <x:v>30</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C54" t="s">
-        <x:v>13</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:3">
@@ -1702,10 +1792,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B55" t="s">
-        <x:v>60</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C55" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:3">
@@ -1713,10 +1803,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B56" t="s">
-        <x:v>54</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C56" t="s">
-        <x:v>110</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:3">
@@ -1724,10 +1814,175 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B57" t="s">
-        <x:v>112</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C57" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:3">
+      <x:c r="A58">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B58" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C58" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:3">
+      <x:c r="A59">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B59" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C59" t="s">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:3">
+      <x:c r="A60">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B60" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C60" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:3">
+      <x:c r="A61">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B61" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C61" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:3">
+      <x:c r="A62">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B62" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C62" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:3">
+      <x:c r="A63">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B63" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C63" t="s">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:3">
+      <x:c r="A64">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B64" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C64" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:3">
+      <x:c r="A65">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B65" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C65" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:3">
+      <x:c r="A66">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B66" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C66" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:3">
+      <x:c r="A67">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B67" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C67" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:3">
+      <x:c r="A68">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B68" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="C68" t="s">
         <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:3">
+      <x:c r="A69">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B69" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C69" t="s">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:3">
+      <x:c r="A70">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B70" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C70" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:3">
+      <x:c r="A71">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B71" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="C71" t="s">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:3">
+      <x:c r="A72">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B72" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C72" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/morpg/morpg/Assets/TableData/Table_Text.xlsx
+++ b/morpg/morpg/Assets/TableData/Table_Text.xlsx
@@ -19,7 +19,202 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="143">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="209">
+  <x:si>
+    <x:t>역세계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초심극점</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NarosaFomos_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BultonKajon_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gingarsion_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NarosaFomos_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IreanSorin_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GrenFomos_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GrenFomos_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BultonKajon_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IreanSorin_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tartaros_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tartaros_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>본세계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제 와서는 이 세상에 절대유일한 '핏빛혈족의 유일한 생존자' 무시무시한 이능력을 지니고 있지만, 그가 지닌 이능력의 정체를 아는 자를 이제는 찾을 수 없다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:현명한 현자. 모든 코크루와 중 유일의 비전투원. 다만 이제는 기억하는 사람도 없는 '본카 일족'의 족장, '짐토'로써 사실상 이 세상의 모든 학문과 기술은 그로부터 비롯된 것이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 불튼이 버금가는 탱킹 능력에 '피를 입는 자'에 버금하는 물리력을 지닌 雷계열 근거리 딜러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GaremenTooskaDin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>평화로운 시기에도 전 세계에 그 개체 수가 5마리를 넘기지 못하던 이 세상 유일의 '초소수종'</x:t>
+  </x:si>
+  <x:si>
+    <x:t>헤디 벤만 오프 모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아키르고 베니아</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 지닌 능력 중 대부분이 상처를 치유하고 아군을 버프, 적을 디버프하는 水계열 후방 서포터.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>term</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Species</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Machine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>산도라 태생</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에를로네</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cocruwa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>load</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Array</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소환술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>newgame</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Priest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>menu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Unknown</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타르타로스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라우톤 윈너</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코크루와</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타이틀로 이동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rodec</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kalapok</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이어하기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Assasin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대마도사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나로사 포모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>강령술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>history</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새 시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종족&amp;직업</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Human</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Badrak</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sandora</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Archer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Demon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Korean</x:t>
+  </x:si>
+  <x:si>
+    <x:t>칼라포크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Renod</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이레안 소린</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Teemole</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Perth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>반지(우)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gloves</x:t>
+  </x:si>
+  <x:si>
+    <x:t>긴가르시온</x:t>
+  </x:si>
   <x:si>
     <x:t>반지(좌)</x:t>
   </x:si>
@@ -27,427 +222,430 @@
     <x:t>Weapon</x:t>
   </x:si>
   <x:si>
+    <x:t>귀걸이(좌)</x:t>
+  </x:si>
+  <x:si>
     <x:t>Armor</x:t>
   </x:si>
   <x:si>
+    <x:t>Boots</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Head</x:t>
+  </x:si>
+  <x:si>
+    <x:t>option</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ehrlone</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Leather</x:t>
+  </x:si>
+  <x:si>
     <x:t>귀걸이(우)</x:t>
   </x:si>
   <x:si>
-    <x:t>Boots</x:t>
-  </x:si>
-  <x:si>
-    <x:t>귀걸이(좌)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gloves</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Head</x:t>
-  </x:si>
-  <x:si>
     <x:t>Cloth</x:t>
   </x:si>
   <x:si>
-    <x:t>Leather</x:t>
-  </x:si>
-  <x:si>
     <x:t>Plate</x:t>
   </x:si>
   <x:si>
+    <x:t>?????</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카루크 뷘젠트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Redinin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Index</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Warrior</x:t>
+  </x:si>
+  <x:si>
+    <x:t>title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rogue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그렌 포모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Comment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>exit</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연금술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>copy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Selena</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불튼 카존</x:t>
+  </x:si>
+  <x:si>
+    <x:t>save</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불러오기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Toorka</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Summoner</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가레멘 투스카 딘</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gingarsion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tartaros</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IreanSorin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hidden002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GrenFomos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Alchemist</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CodeName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bugreport</x:t>
+  </x:si>
+  <x:si>
+    <x:t>버그리포트 바로가기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>continue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hidden001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>직업</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도적</x:t>
+  </x:si>
+  <x:si>
+    <x:t>셀레나</x:t>
+  </x:si>
+  <x:si>
+    <x:t>투르카</x:t>
+  </x:si>
+  <x:si>
+    <x:t>바드락</x:t>
+  </x:si>
+  <x:si>
+    <x:t>판금</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장비</x:t>
+  </x:si>
+  <x:si>
+    <x:t>악마</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도감</x:t>
+  </x:si>
+  <x:si>
+    <x:t>용어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무직</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목걸이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>천</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마법사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가죽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신발</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>암살자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>머리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Job</x:t>
+  </x:si>
+  <x:si>
+    <x:t>티모르</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>갑옷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로데크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>성직자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기계</x:t>
+  </x:si>
+  <x:si>
     <x:t>역사</x:t>
   </x:si>
   <x:si>
     <x:t>불명</x:t>
   </x:si>
   <x:si>
+    <x:t>궁수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레노드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레디닌</x:t>
+  </x:si>
+  <x:si>
     <x:t>페르스</x:t>
   </x:si>
   <x:si>
-    <x:t>궁수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레노드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레디닌</x:t>
+    <x:t>메뉴</x:t>
   </x:si>
   <x:si>
     <x:t>장갑</x:t>
   </x:si>
   <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
     <x:t>전사</x:t>
   </x:si>
   <x:si>
-    <x:t>기계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>메뉴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>머리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>성직자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>암살자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장비</x:t>
-  </x:si>
-  <x:si>
-    <x:t>갑옷</x:t>
-  </x:si>
-  <x:si>
-    <x:t>악마</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마법사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도적</x:t>
-  </x:si>
-  <x:si>
-    <x:t>직업</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무직</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신발</x:t>
-  </x:si>
-  <x:si>
-    <x:t>셀레나</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>티모르</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Job</x:t>
-  </x:si>
-  <x:si>
-    <x:t>로데크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가죽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>투르카</x:t>
-  </x:si>
-  <x:si>
-    <x:t>판금</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도감</x:t>
-  </x:si>
-  <x:si>
-    <x:t>바드락</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>목걸이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>용어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>저장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>천</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ehrlone</x:t>
-  </x:si>
-  <x:si>
-    <x:t>?????</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카루크 뷘젠트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>긴가르시온</x:t>
-  </x:si>
-  <x:si>
-    <x:t>option</x:t>
-  </x:si>
-  <x:si>
-    <x:t>title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Comment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Index</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Warrior</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Redinin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불튼 카존</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rogue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>copy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그렌 포모스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>exit</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연금술사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Selena</x:t>
-  </x:si>
-  <x:si>
-    <x:t>save</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불러오기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Toorka</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이레안 소린</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Demon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>반지(우)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>history</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Teemole</x:t>
+    <x:t>이라모스 강제개폐 사건</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:금속왕. 긴가르시온이 조립한 완전 기계인간, 다만 이 세상에서 유일하게 전신이 '완벽한 신의 금속'으로 이뤄져서 모든 것을 무시할 수준의 방어력을 지니고 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 그가 공격의사를 갖던 말던, 그의 주변에 존재하는 것만으로도 해독이 불가능한 '페이튼'에 중독되어 모든 존재가 소멸한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:유령왕. 태생적으로 '산도라의 후예'인 대마도사였으나, 그의 스승인 '푸 그레이'가 서술한 '초마도의 서'를 이해하여 마법사 중 최강의 존재인 '초마도사'가 되었다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Necklace</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LeftRing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LeftEarring</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Species&amp;Job</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RightRIng</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Equipment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NarosaFomos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BultonKajon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Necromancer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Archmage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>notEmployed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>???????????????</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KaroukWingent</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RightEarring</x:t>
   </x:si>
   <x:si>
     <x:t>encyclopedia</x:t>
   </x:si>
   <x:si>
-    <x:t>???????????????</x:t>
-  </x:si>
-  <x:si>
     <x:t>RoutonWinner</x:t>
   </x:si>
   <x:si>
-    <x:t>KaroukWingent</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RightEarring</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Necklace</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Equipment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LeftRing</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Species&amp;Job</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RightRIng</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LeftEarring</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종족&amp;직업</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GaremenTooskaDin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나로사 포모스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Perth</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Korean</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sandora</x:t>
-  </x:si>
-  <x:si>
-    <x:t>칼라포크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Human</x:t>
-  </x:si>
-  <x:si>
-    <x:t>새 시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>강령술사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Renod</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Archer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Badrak</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Species</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Machine</x:t>
-  </x:si>
-  <x:si>
-    <x:t>term</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라우톤 윈너</x:t>
-  </x:si>
-  <x:si>
-    <x:t>newgame</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소환술사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대마도사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Array</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코크루와</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타이틀로 이동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>산도라 태생</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에를로네</x:t>
-  </x:si>
-  <x:si>
-    <x:t>load</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Priest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rodec</x:t>
-  </x:si>
-  <x:si>
-    <x:t>menu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cocruwa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Unknown</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타르타로스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Assasin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kalapok</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이어하기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NarosaFomos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BultonKajon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>notEmployed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Necromancer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Archmage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CodeName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hidden002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tartaros</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hidden001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IreanSorin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>버그리포트 바로가기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bugreport</x:t>
-  </x:si>
-  <x:si>
-    <x:t>continue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Summoner</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가레멘 투스카 딘</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gingarsion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Alchemist</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GrenFomos</x:t>
+    <x:t>이명:암흑대제. 이 세상에서 유일하게 힘을 비축하는 시간에 비례하여 무한히 강해질 수 있는 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 능력 중 대부분이 공격에 치중된 火계열 중거리 딜러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 자가방어와 자가치유에 치중된 地계열 순수 탱커.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:시간의 마왕. 우리의 세상인 '본세계'와 '역세계'에서도 하나 이상을 찾아볼 수 없는 절대유일의 시간 능력자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GaremenTooskaDin_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GaremenTooskaDin_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KaroukWingent_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KaroukWingent_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RoutonWinner_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RoutonWinner_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Perth_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Redinin_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Redinin_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Renod_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ehrlone_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Renod_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>암흑대제2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 공격보다 정찰에 특화된, 공격력보다는 연타에 치중한 風계열 서포터.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 대장. 전투에 필요한 전반적인 능력을 두루 갖춘, 氷계열 원거리 딜러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그의 일정범위에 존재하는 모든 사물은 점점 느려지기  시작하고, 그 본인은 그 속도만큼 점점 빨라진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:피를 입는 자. '본세계'와 '역세계'를 모두 포함해서도 비슷한 수준의 신체능력을 가진 존재를 찾기 힘들 정도로 압도적인 신체능력을 가지고 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이 세상 모든 것을 중독시키는 '페이튼'에 중독되어 스스로 의사를 갖고 움직이기 시작한 종족 '래머'의 마지막 생존자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종말전쟁</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁 시절, '종족말살정책'으로부터 살아남은 유일한 대지의 종족, '티모르'의 후계자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁 시절, '종족말살정책'으로부터 살아남은 유일한 바다의 종족, '셀레나'의 후계자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁 시절, '종족말살정책'으로부터 살아남은 유일한 창공의 종족, '카루크'의 후계자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써, '태양절맥'을 갖고 태어난 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써, '구음절맥'을 갖고 태어난 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대마도전쟁</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종족전쟁</x:t>
+  </x:si>
+  <x:si>
+    <x:t>위대한 과실</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1191,7 +1389,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:D72"/>
+  <x:dimension ref="A1:D108"/>
   <x:sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="16.39999999999999857891"/>
   <x:cols>
     <x:col min="1" max="1" width="8.796875" bestFit="1" customWidth="1"/>
@@ -1199,31 +1397,31 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D2" s="1"/>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -1231,7 +1429,7 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B4" s="1"/>
       <x:c r="C4" s="1"/>
@@ -1242,10 +1440,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" t="s">
-        <x:v>105</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C5" t="s">
-        <x:v>96</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
@@ -1253,10 +1451,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" t="s">
-        <x:v>137</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C6" t="s">
-        <x:v>124</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
@@ -1264,10 +1462,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" t="s">
-        <x:v>56</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C7" t="s">
-        <x:v>36</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
@@ -1275,10 +1473,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" t="s">
-        <x:v>66</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C8" t="s">
-        <x:v>26</x:v>
+        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
@@ -1286,10 +1484,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B9" t="s">
-        <x:v>69</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C9" t="s">
-        <x:v>50</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
@@ -1297,10 +1495,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B10" t="s">
-        <x:v>114</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C10" t="s">
-        <x:v>70</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
@@ -1308,10 +1506,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B11" t="s">
-        <x:v>64</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C11" t="s">
-        <x:v>43</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
@@ -1319,10 +1517,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B12" t="s">
-        <x:v>117</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C12" t="s">
-        <x:v>20</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
@@ -1330,10 +1528,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B13" t="s">
-        <x:v>57</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C13" s="2" t="s">
-        <x:v>111</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
@@ -1341,10 +1539,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B14" t="s">
-        <x:v>136</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C14" t="s">
-        <x:v>135</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
@@ -1352,10 +1550,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B15" t="s">
-        <x:v>77</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="C15" t="s">
-        <x:v>44</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
@@ -1363,10 +1561,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B16" t="s">
-        <x:v>118</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C16" t="s">
-        <x:v>110</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
@@ -1374,10 +1572,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B17" t="s">
-        <x:v>103</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C17" t="s">
-        <x:v>49</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
@@ -1385,10 +1583,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B18" t="s">
-        <x:v>75</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C18" t="s">
-        <x:v>11</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
@@ -1396,10 +1594,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B19" t="s">
-        <x:v>98</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C19" t="s">
-        <x:v>15</x:v>
+        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
@@ -1407,10 +1605,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B20" t="s">
-        <x:v>132</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C20" t="s">
-        <x:v>120</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
@@ -1418,10 +1616,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B21" t="s">
-        <x:v>61</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C21" t="s">
-        <x:v>16</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
@@ -1429,10 +1627,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B22" t="s">
-        <x:v>91</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C22" t="s">
-        <x:v>13</x:v>
+        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
@@ -1440,10 +1638,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B23" t="s">
-        <x:v>52</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C23" t="s">
-        <x:v>113</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
@@ -1451,10 +1649,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B24" t="s">
-        <x:v>140</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C24" t="s">
-        <x:v>55</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
@@ -1462,10 +1660,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B25" t="s">
-        <x:v>142</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C25" t="s">
-        <x:v>65</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
@@ -1473,10 +1671,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B26" t="s">
-        <x:v>125</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="C26" t="s">
-        <x:v>90</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
@@ -1484,10 +1682,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B27" t="s">
-        <x:v>134</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C27" t="s">
-        <x:v>72</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
@@ -1495,10 +1693,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B28" t="s">
-        <x:v>126</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C28" t="s">
-        <x:v>62</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3">
@@ -1506,10 +1704,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B29" t="s">
-        <x:v>80</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C29" t="s">
-        <x:v>54</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">
@@ -1517,10 +1715,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B30" t="s">
-        <x:v>79</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="C30" t="s">
-        <x:v>104</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
@@ -1528,10 +1726,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B31" t="s">
-        <x:v>89</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C31" t="s">
-        <x:v>139</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:3">
@@ -1539,10 +1737,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B32" t="s">
-        <x:v>95</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C32" t="s">
-        <x:v>22</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:3">
@@ -1550,10 +1748,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B33" t="s">
-        <x:v>116</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C33" t="s">
-        <x:v>39</x:v>
+        <x:v>134</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:3">
@@ -1561,10 +1759,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B34" t="s">
-        <x:v>71</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C34" t="s">
-        <x:v>41</x:v>
+        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:3">
@@ -1572,10 +1770,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B35" t="s">
-        <x:v>76</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C35" t="s">
-        <x:v>37</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:3">
@@ -1583,10 +1781,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B36" t="s">
-        <x:v>68</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C36" t="s">
-        <x:v>35</x:v>
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:3">
@@ -1594,10 +1792,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B37" t="s">
-        <x:v>100</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C37" t="s">
-        <x:v>45</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:3">
@@ -1605,10 +1803,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B38" t="s">
-        <x:v>102</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C38" t="s">
-        <x:v>19</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:3">
@@ -1616,10 +1814,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B39" t="s">
-        <x:v>93</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C39" t="s">
-        <x:v>112</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:3">
@@ -1627,10 +1825,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B40" t="s">
-        <x:v>123</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C40" t="s">
-        <x:v>94</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:3">
@@ -1638,10 +1836,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B41" t="s">
-        <x:v>119</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C41" t="s">
-        <x:v>12</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:3">
@@ -1649,10 +1847,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B42" t="s">
-        <x:v>60</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C42" t="s">
-        <x:v>18</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:3">
@@ -1660,10 +1858,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B43" t="s">
-        <x:v>99</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C43" t="s">
-        <x:v>14</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:3">
@@ -1671,10 +1869,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B44" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C44" t="s">
         <x:v>122</x:v>
-      </x:c>
-      <x:c r="C44" t="s">
-        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:3">
@@ -1682,10 +1880,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B45" t="s">
-        <x:v>115</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C45" t="s">
-        <x:v>24</x:v>
+        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:3">
@@ -1693,10 +1891,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B46" t="s">
-        <x:v>121</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C46" t="s">
-        <x:v>25</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:3">
@@ -1704,10 +1902,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B47" t="s">
-        <x:v>63</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C47" t="s">
-        <x:v>31</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:3">
@@ -1715,10 +1913,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B48" t="s">
-        <x:v>138</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C48" t="s">
-        <x:v>106</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:3">
@@ -1726,10 +1924,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B49" t="s">
-        <x:v>141</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C49" t="s">
-        <x:v>67</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:3">
@@ -1737,10 +1935,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B50" t="s">
-        <x:v>128</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C50" t="s">
-        <x:v>97</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:3">
@@ -1748,10 +1946,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B51" t="s">
-        <x:v>73</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C51" t="s">
-        <x:v>29</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:3">
@@ -1759,10 +1957,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B52" t="s">
-        <x:v>129</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C52" t="s">
-        <x:v>107</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:3">
@@ -1770,10 +1968,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B53" t="s">
-        <x:v>101</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C53" t="s">
-        <x:v>48</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:3">
@@ -1781,10 +1979,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B54" t="s">
-        <x:v>38</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C54" t="s">
-        <x:v>32</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:3">
@@ -1792,10 +1990,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B55" t="s">
-        <x:v>133</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C55" t="s">
-        <x:v>53</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:3">
@@ -1803,10 +2001,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B56" t="s">
-        <x:v>131</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C56" t="s">
-        <x:v>78</x:v>
+        <x:v>163</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:3">
@@ -1814,10 +2012,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B57" t="s">
-        <x:v>127</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C57" t="s">
-        <x:v>33</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:3">
@@ -1825,10 +2023,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B58" t="s">
-        <x:v>83</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C58" t="s">
-        <x:v>27</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:3">
@@ -1836,10 +2034,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B59" t="s">
-        <x:v>85</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C59" t="s">
-        <x:v>88</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:3">
@@ -1847,10 +2045,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B60" t="s">
-        <x:v>8</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C60" t="s">
-        <x:v>51</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:3">
@@ -1858,10 +2056,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B61" t="s">
-        <x:v>9</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C61" t="s">
-        <x:v>40</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:3">
@@ -1869,10 +2067,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B62" t="s">
-        <x:v>10</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C62" t="s">
-        <x:v>42</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:3">
@@ -1880,10 +2078,10 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B63" t="s">
-        <x:v>1</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C63" t="s">
-        <x:v>46</x:v>
+        <x:v>123</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:3">
@@ -1891,10 +2089,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B64" t="s">
-        <x:v>7</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C64" t="s">
-        <x:v>23</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:3">
@@ -1902,10 +2100,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B65" t="s">
-        <x:v>2</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C65" t="s">
-        <x:v>28</x:v>
+        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:3">
@@ -1913,10 +2111,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B66" t="s">
-        <x:v>6</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C66" t="s">
-        <x:v>17</x:v>
+        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:3">
@@ -1924,10 +2122,10 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B67" t="s">
-        <x:v>4</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C67" t="s">
-        <x:v>34</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:3">
@@ -1935,10 +2133,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B68" t="s">
-        <x:v>84</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C68" t="s">
-        <x:v>0</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:3">
@@ -1946,10 +2144,10 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B69" t="s">
-        <x:v>86</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C69" t="s">
-        <x:v>74</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:3">
@@ -1957,10 +2155,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B70" t="s">
-        <x:v>87</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="C70" t="s">
-        <x:v>5</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:3">
@@ -1968,10 +2166,10 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B71" t="s">
-        <x:v>81</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C71" t="s">
-        <x:v>3</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:3">
@@ -1979,11 +2177,383 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B72" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="C72" t="s">
+        <x:v>119</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="1:3">
+      <x:c r="A73">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B73" s="1" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="C73" t="s">
+        <x:v>171</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:3">
+      <x:c r="A74">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B74" s="1" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="C74" t="s">
+        <x:v>197</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:3">
+      <x:c r="A75">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B75" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C75" t="s">
+        <x:v>198</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" spans="1:3">
+      <x:c r="A76">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B76" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C76" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" spans="1:3">
+      <x:c r="A77">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B77" s="1" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="C77" t="s">
+        <x:v>168</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="1:3">
+      <x:c r="A78">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B78" s="1" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="C78" t="s">
+        <x:v>194</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" spans="1:3">
+      <x:c r="A79">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B79" s="1" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="C79" t="s">
+        <x:v>149</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" spans="1:3">
+      <x:c r="A80">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B80" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="C80" t="s">
+        <x:v>151</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" spans="1:3">
+      <x:c r="A81">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B81" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C81" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" spans="1:3">
+      <x:c r="A82">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B82" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C82" t="s">
+        <x:v>169</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" spans="1:3">
+      <x:c r="A83">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B83" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C83" t="s">
+        <x:v>204</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" spans="1:3">
+      <x:c r="A84">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B84" s="1" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C84" t="s">
+        <x:v>196</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" spans="1:3">
+      <x:c r="A85">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B85" s="1" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C85" s="2" t="s">
+        <x:v>205</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" spans="1:3">
+      <x:c r="A86">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="C72" t="s">
-        <x:v>47</x:v>
-      </x:c>
+      <x:c r="B86" s="1" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C86" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" spans="1:3">
+      <x:c r="A87">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B87" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C87" t="s">
+        <x:v>202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" spans="1:3">
+      <x:c r="A88">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B88" s="1" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C88" t="s">
+        <x:v>170</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" spans="1:3">
+      <x:c r="A89">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B89" s="1" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C89" s="2" t="s">
+        <x:v>201</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" spans="1:3">
+      <x:c r="A90">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B90" s="1" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="C90" t="s">
+        <x:v>195</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:3">
+      <x:c r="A91">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B91" s="1" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="C91" s="2" t="s">
+        <x:v>203</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:3">
+      <x:c r="A92">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B92" s="1" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="C92" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="1:3">
+      <x:c r="A93">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B93" s="1" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="C93" s="2" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:3">
+      <x:c r="A94">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B94" s="1" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="C94" t="s">
+        <x:v>150</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:3">
+      <x:c r="A95">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B95" s="1" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="C95" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" spans="1:3">
+      <x:c r="A96">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B96" s="2" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="C96" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:3">
+      <x:c r="A97">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B97" s="2" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="C97" t="s">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:3">
+      <x:c r="A98">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B98" s="2" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="C98" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:3">
+      <x:c r="A99">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B99" s="2" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="C99" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:3">
+      <x:c r="A100">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="B100" s="2" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="C100" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:3">
+      <x:c r="A101">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B101" s="2" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="C101" t="s">
+        <x:v>208</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" spans="1:3">
+      <x:c r="A102">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B102" s="2" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="C102" t="s">
+        <x:v>207</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" spans="1:3">
+      <x:c r="A103">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B103" s="2" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="C103" t="s">
+        <x:v>206</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" spans="1:3">
+      <x:c r="A104">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B104" s="2" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="C104" t="s">
+        <x:v>200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" spans="1:3">
+      <x:c r="A105">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B105" s="2" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="C105" t="s">
+        <x:v>148</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" spans="2:2">
+      <x:c r="B106" s="2"/>
+    </x:row>
+    <x:row r="107" spans="2:2">
+      <x:c r="B107" s="2"/>
+    </x:row>
+    <x:row r="108" spans="2:2">
+      <x:c r="B108" s="2"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51138889789581298828" footer="0.51138889789581298828"/>

--- a/morpg/morpg/Assets/TableData/Table_Text.xlsx
+++ b/morpg/morpg/Assets/TableData/Table_Text.xlsx
@@ -19,633 +19,651 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="209">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="215">
+  <x:si>
+    <x:t>셀레나</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>바드락</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Assassin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제 와서는 이 세상에 절대유일한 '핏빛혈족의 유일한 생존자' 무시무시한 이능력을 지니고 있지만 그가 지닌 이능력의 정체를 아는 자를 이제는 찾을 수 없다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KaroukWingent_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RoutonWinner_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GaremenTooskaDin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KaroukWingent_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RoutonWinner_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마법사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>성직자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>암살자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도적</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Archmage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 능력 중 대부분이 공격에 치중된 火계열 중거리 딜러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 자가방어와 자가치유에 치중된 地계열 순수 탱커.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>평화로운 시기에도 전 세계에 그 개체 수가 5마리를 넘기지 못하던 이 세상 유일의 '초소수종'</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:암흑대제. 이 세상에서 유일하게 힘을 비축하는 시간에 비례하여 무한히 강해질 수 있는 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이 세상 모든 것을 중독시키는 '페이튼'에 중독되어 스스로 의사를 갖고 움직이기 시작한 종족 '래머'의 마지막 생존자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:시간의 마왕. 우리의 세상인 '본세계'와 '역세계'에서도 하나 이상을 찾아볼 수 없는 절대유일의 시간 능력자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 불튼이 버금가는 탱킹 능력에 '피를 입는 자'에 버금하는 물리력을 지닌 雷계열 근거리 딜러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Korean</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코크루와</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이어하기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새 시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종족&amp;직업</x:t>
+  </x:si>
+  <x:si>
+    <x:t>newgame</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나로사 포모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Demon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Renod</x:t>
+  </x:si>
+  <x:si>
+    <x:t>menu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타이틀로 이동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라우톤 윈너</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타르타로스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>history</x:t>
+  </x:si>
+  <x:si>
+    <x:t>load</x:t>
+  </x:si>
+  <x:si>
+    <x:t>term</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cocruwa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Array</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Species</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에를로네</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초심극점</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Perth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>긴가르시온</x:t>
+  </x:si>
+  <x:si>
+    <x:t>반지(우)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Weapon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>반지(좌)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이레안 소린</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gloves</x:t>
+  </x:si>
+  <x:si>
+    <x:t>귀걸이(좌)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Armor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Plate</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ehrlone</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Redinin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Boots</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cloth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Index</x:t>
+  </x:si>
+  <x:si>
+    <x:t>title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>?????</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Leather</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카루크 뷘젠트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>귀걸이(우)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>option</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Head</x:t>
+  </x:si>
+  <x:si>
+    <x:t>copy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그렌 포모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Comment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>exit</x:t>
+  </x:si>
+  <x:si>
+    <x:t>save</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불러오기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>암흑대제2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종말전쟁</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불튼 카존</x:t>
+  </x:si>
+  <x:si>
+    <x:t>헤디 벤만 오프 모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아키르고 베니아</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hidden001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가레멘 투스카 딘</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IreanSorin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gingarsion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GrenFomos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hidden002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CodeName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>버그리포트 바로가기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bugreport</x:t>
+  </x:si>
+  <x:si>
+    <x:t>continue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tartaros</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마왕족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>드래곤</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종족전쟁</x:t>
+  </x:si>
+  <x:si>
+    <x:t>위대한 과실</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대마도전쟁</x:t>
+  </x:si>
+  <x:si>
+    <x:t>encyclopedia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KaroukWingent</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RightEarring</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RoutonWinner</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gingarsion_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BultonKajon_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NarosaFomos_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NarosaFomos_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tartaros_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BultonKajon_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IreanSorin_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GrenFomos_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tartaros_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이라모스 강제개폐 사건</x:t>
+  </x:si>
+  <x:si>
+    <x:t>???????????????</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IreanSorin_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GrenFomos_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로데크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>투르카</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Renod_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Redinin_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Redinin_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ehrlone_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Renod_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>notEmployed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Perth_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:피를 입는 자. '본세계'와 '역세계'를 모두 포함해서도 비슷한 수준의 신체능력을 가진 존재를 찾기 힘들 정도로 압도적인 신체능력을 가지고 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Equipment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RightRIng</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NarosaFomos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LeftRing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Species&amp;Job</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BultonKajon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Necklace</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LeftEarring</x:t>
+  </x:si>
+  <x:si>
+    <x:t>본세계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>판금</x:t>
+  </x:si>
   <x:si>
     <x:t>역세계</x:t>
   </x:si>
   <x:si>
-    <x:t>초심극점</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NarosaFomos_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BultonKajon_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gingarsion_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NarosaFomos_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IreanSorin_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GrenFomos_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GrenFomos_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BultonKajon_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IreanSorin_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tartaros_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tartaros_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>본세계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이제 와서는 이 세상에 절대유일한 '핏빛혈족의 유일한 생존자' 무시무시한 이능력을 지니고 있지만, 그가 지닌 이능력의 정체를 아는 자를 이제는 찾을 수 없다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:현명한 현자. 모든 코크루와 중 유일의 비전투원. 다만 이제는 기억하는 사람도 없는 '본카 일족'의 족장, '짐토'로써 사실상 이 세상의 모든 학문과 기술은 그로부터 비롯된 것이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 불튼이 버금가는 탱킹 능력에 '피를 입는 자'에 버금하는 물리력을 지닌 雷계열 근거리 딜러.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GaremenTooskaDin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>평화로운 시기에도 전 세계에 그 개체 수가 5마리를 넘기지 못하던 이 세상 유일의 '초소수종'</x:t>
-  </x:si>
-  <x:si>
-    <x:t>헤디 벤만 오프 모스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아키르고 베니아</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 지닌 능력 중 대부분이 상처를 치유하고 아군을 버프, 적을 디버프하는 水계열 후방 서포터.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>term</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Species</x:t>
+    <x:t>직업</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도감</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장비</x:t>
+  </x:si>
+  <x:si>
+    <x:t>용어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무직</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>페르스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>메뉴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>역사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Job</x:t>
+  </x:si>
+  <x:si>
+    <x:t>천</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장갑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>머리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레노드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신발</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목걸이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가죽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>갑옷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레디닌</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GaremenTooskaDin_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GaremenTooskaDin_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그의 일정범위에 존재하는 모든 사물은 점점 느려지기  시작하고 그 본인은 그 속도만큼 점점 빨라진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sandora</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kalapok</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Unknown</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Teemole</x:t>
   </x:si>
   <x:si>
     <x:t>Machine</x:t>
   </x:si>
   <x:si>
+    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 대지의 종족 '티모르'의 후계자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 창공의 종족 '카루크'의 후계자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 바다의 종족 '셀레나'의 후계자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Human</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Toorka</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Priest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Warrior</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dragon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Archer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Selena</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Badrak</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rogue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rodec</x:t>
+  </x:si>
+  <x:si>
+    <x:t>티모르</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소환술사</x:t>
+  </x:si>
+  <x:si>
     <x:t>산도라 태생</x:t>
   </x:si>
   <x:si>
-    <x:t>에를로네</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cocruwa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>load</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Array</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소환술사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>newgame</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Priest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>menu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Unknown</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타르타로스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라우톤 윈너</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코크루와</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타이틀로 이동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rodec</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kalapok</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이어하기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Assasin</x:t>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 공격보다 정찰에 특화된 공격력보다는 연타에 치중한 風계열 서포터.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 대장. 전투에 필요한 전반적인 능력을 두루 갖춘 氷계열 원거리 딜러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Necromancer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DemonMage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Summoner</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Alchemist</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:금속왕. 긴가르시온이 조립한 완전 기계인간 다만 이 세상에서 유일하게 전신이 '완벽한 신의 금속'으로 이뤄져서 모든 것을 무시할 수준의 방어력을 지니고 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DemonFighter</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연금술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>궁수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>강령술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마족 마법사</x:t>
   </x:si>
   <x:si>
     <x:t>대마도사</x:t>
   </x:si>
   <x:si>
-    <x:t>나로사 포모스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>강령술사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>history</x:t>
-  </x:si>
-  <x:si>
-    <x:t>새 시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종족&amp;직업</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Human</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Badrak</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sandora</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Archer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Demon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Korean</x:t>
-  </x:si>
-  <x:si>
-    <x:t>칼라포크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Renod</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이레안 소린</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Teemole</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Perth</x:t>
-  </x:si>
-  <x:si>
-    <x:t>반지(우)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gloves</x:t>
-  </x:si>
-  <x:si>
-    <x:t>긴가르시온</x:t>
-  </x:si>
-  <x:si>
-    <x:t>반지(좌)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Weapon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>귀걸이(좌)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Armor</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Boots</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Head</x:t>
-  </x:si>
-  <x:si>
-    <x:t>option</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ehrlone</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Leather</x:t>
-  </x:si>
-  <x:si>
-    <x:t>귀걸이(우)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cloth</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Plate</x:t>
-  </x:si>
-  <x:si>
-    <x:t>?????</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카루크 뷘젠트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Redinin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Index</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Warrior</x:t>
-  </x:si>
-  <x:si>
-    <x:t>title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rogue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그렌 포모스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Comment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>exit</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연금술사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>copy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Selena</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불튼 카존</x:t>
-  </x:si>
-  <x:si>
-    <x:t>save</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불러오기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Toorka</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Summoner</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가레멘 투스카 딘</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gingarsion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tartaros</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IreanSorin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hidden002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GrenFomos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Alchemist</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CodeName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bugreport</x:t>
-  </x:si>
-  <x:si>
-    <x:t>버그리포트 바로가기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>continue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hidden001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>직업</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도적</x:t>
-  </x:si>
-  <x:si>
-    <x:t>셀레나</x:t>
-  </x:si>
-  <x:si>
-    <x:t>투르카</x:t>
-  </x:si>
-  <x:si>
-    <x:t>바드락</x:t>
-  </x:si>
-  <x:si>
-    <x:t>판금</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장비</x:t>
-  </x:si>
-  <x:si>
-    <x:t>악마</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도감</x:t>
-  </x:si>
-  <x:si>
-    <x:t>용어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무직</x:t>
-  </x:si>
-  <x:si>
-    <x:t>목걸이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>저장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>천</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마법사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가죽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신발</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>암살자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>머리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Job</x:t>
-  </x:si>
-  <x:si>
-    <x:t>티모르</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>갑옷</x:t>
-  </x:si>
-  <x:si>
-    <x:t>로데크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>성직자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>역사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>궁수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레노드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레디닌</x:t>
-  </x:si>
-  <x:si>
-    <x:t>페르스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>메뉴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장갑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이라모스 강제개폐 사건</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:금속왕. 긴가르시온이 조립한 완전 기계인간, 다만 이 세상에서 유일하게 전신이 '완벽한 신의 금속'으로 이뤄져서 모든 것을 무시할 수준의 방어력을 지니고 있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 그가 공격의사를 갖던 말던, 그의 주변에 존재하는 것만으로도 해독이 불가능한 '페이튼'에 중독되어 모든 존재가 소멸한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:유령왕. 태생적으로 '산도라의 후예'인 대마도사였으나, 그의 스승인 '푸 그레이'가 서술한 '초마도의 서'를 이해하여 마법사 중 최강의 존재인 '초마도사'가 되었다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Necklace</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LeftRing</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LeftEarring</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Species&amp;Job</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RightRIng</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Equipment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NarosaFomos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BultonKajon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Necromancer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Archmage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>notEmployed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>???????????????</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KaroukWingent</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RightEarring</x:t>
-  </x:si>
-  <x:si>
-    <x:t>encyclopedia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RoutonWinner</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:암흑대제. 이 세상에서 유일하게 힘을 비축하는 시간에 비례하여 무한히 강해질 수 있는 존재.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 능력 중 대부분이 공격에 치중된 火계열 중거리 딜러.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 자가방어와 자가치유에 치중된 地계열 순수 탱커.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:시간의 마왕. 우리의 세상인 '본세계'와 '역세계'에서도 하나 이상을 찾아볼 수 없는 절대유일의 시간 능력자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GaremenTooskaDin_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GaremenTooskaDin_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KaroukWingent_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KaroukWingent_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RoutonWinner_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RoutonWinner_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Perth_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Redinin_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Redinin_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Renod_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ehrlone_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Renod_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>암흑대제2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 공격보다 정찰에 특화된, 공격력보다는 연타에 치중한 風계열 서포터.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 대장. 전투에 필요한 전반적인 능력을 두루 갖춘, 氷계열 원거리 딜러.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그의 일정범위에 존재하는 모든 사물은 점점 느려지기  시작하고, 그 본인은 그 속도만큼 점점 빨라진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:피를 입는 자. '본세계'와 '역세계'를 모두 포함해서도 비슷한 수준의 신체능력을 가진 존재를 찾기 힘들 정도로 압도적인 신체능력을 가지고 있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이 세상 모든 것을 중독시키는 '페이튼'에 중독되어 스스로 의사를 갖고 움직이기 시작한 종족 '래머'의 마지막 생존자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종말전쟁</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁 시절, '종족말살정책'으로부터 살아남은 유일한 대지의 종족, '티모르'의 후계자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁 시절, '종족말살정책'으로부터 살아남은 유일한 바다의 종족, '셀레나'의 후계자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁 시절, '종족말살정책'으로부터 살아남은 유일한 창공의 종족, '카루크'의 후계자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써, '태양절맥'을 갖고 태어난 존재.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써, '구음절맥'을 갖고 태어난 존재.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대마도전쟁</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종족전쟁</x:t>
-  </x:si>
-  <x:si>
-    <x:t>위대한 과실</x:t>
+    <x:t>마족 전사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 지닌 능력 중 대부분이 상처를 치유하고 아군을 버프 적을 디버프하는 水계열 후방 서포터.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:유령왕. 태생적으로 '산도라의 후예'인 대마도사였으나 그의 스승인 '푸 그레이'가 서술한 '초마도의 서'를 이해하여 마법사 중 최강의 존재인 '초마도사'가 되었다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 그가 공격의사를 갖던 말던 그의 주변에 존재하는 것만으로도 해독이 불가능한 '페이튼'에 중독되어 모든 존재가 소멸한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:현명한 현자. 모든 코크루와 중 유일의 비전투원. 다만 이제는 기억하는 사람도 없는 '본카 일족'의 족장 '짐토'로써 사실상 이 세상의 모든 학문과 기술은 그로부터 비롯된 것이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써 '태양절맥'을 갖고 태어난 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써 '구음절맥'을 갖고 태어난 존재.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1389,7 +1407,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:D108"/>
+  <x:dimension ref="A1:D109"/>
   <x:sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="16.39999999999999857891"/>
   <x:cols>
     <x:col min="1" max="1" width="8.796875" bestFit="1" customWidth="1"/>
@@ -1397,31 +1415,31 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D2" s="1"/>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -1429,7 +1447,7 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B4" s="1"/>
       <x:c r="C4" s="1"/>
@@ -1440,10 +1458,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C5" t="s">
-        <x:v>49</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
@@ -1451,10 +1469,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" t="s">
-        <x:v>105</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C6" t="s">
-        <x:v>43</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
@@ -1462,10 +1480,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" t="s">
-        <x:v>71</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C7" t="s">
-        <x:v>127</x:v>
+        <x:v>163</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
@@ -1473,10 +1491,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" t="s">
-        <x:v>86</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C8" t="s">
-        <x:v>132</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
@@ -1484,10 +1502,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B9" t="s">
-        <x:v>91</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C9" t="s">
-        <x:v>120</x:v>
+        <x:v>157</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
@@ -1495,10 +1513,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B10" t="s">
-        <x:v>28</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C10" t="s">
-        <x:v>92</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
@@ -1506,10 +1524,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B11" t="s">
-        <x:v>88</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C11" t="s">
-        <x:v>135</x:v>
+        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
@@ -1517,10 +1535,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B12" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C12" t="s">
-        <x:v>144</x:v>
+        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
@@ -1528,10 +1546,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B13" t="s">
-        <x:v>82</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C13" s="2" t="s">
-        <x:v>40</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
@@ -1539,10 +1557,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B14" t="s">
-        <x:v>103</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C14" t="s">
-        <x:v>104</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
@@ -1550,10 +1568,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B15" t="s">
-        <x:v>166</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C15" t="s">
-        <x:v>116</x:v>
+        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
@@ -1561,10 +1579,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B16" t="s">
-        <x:v>27</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C16" t="s">
-        <x:v>39</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
@@ -1572,10 +1590,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B17" t="s">
-        <x:v>22</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C17" t="s">
-        <x:v>117</x:v>
+        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
@@ -1583,10 +1601,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B18" t="s">
-        <x:v>48</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C18" t="s">
-        <x:v>138</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
@@ -1594,10 +1612,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B19" t="s">
-        <x:v>58</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C19" t="s">
-        <x:v>141</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
@@ -1605,10 +1623,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B20" t="s">
-        <x:v>97</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C20" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
@@ -1616,10 +1634,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B21" t="s">
-        <x:v>79</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C21" t="s">
-        <x:v>142</x:v>
+        <x:v>166</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
@@ -1627,10 +1645,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B22" t="s">
-        <x:v>61</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C22" t="s">
-        <x:v>143</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
@@ -1638,10 +1656,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B23" t="s">
-        <x:v>72</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C23" t="s">
-        <x:v>26</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
@@ -1649,10 +1667,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B24" t="s">
-        <x:v>96</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C24" t="s">
-        <x:v>64</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
@@ -1660,10 +1678,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B25" t="s">
-        <x:v>100</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C25" t="s">
-        <x:v>84</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
@@ -1671,10 +1689,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B26" t="s">
-        <x:v>158</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C26" t="s">
-        <x:v>46</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
@@ -1682,10 +1700,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B27" t="s">
-        <x:v>98</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C27" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
@@ -1693,10 +1711,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B28" t="s">
-        <x:v>159</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C28" t="s">
-        <x:v>90</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3">
@@ -1704,10 +1722,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B29" t="s">
-        <x:v>164</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C29" t="s">
-        <x:v>78</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">
@@ -1715,10 +1733,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B30" t="s">
-        <x:v>167</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C30" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
@@ -1726,10 +1744,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B31" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C31" t="s">
-        <x:v>95</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:3">
@@ -1737,10 +1755,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B32" t="s">
-        <x:v>51</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C32" t="s">
-        <x:v>108</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:3">
@@ -1748,10 +1766,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B33" t="s">
-        <x:v>41</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C33" t="s">
-        <x:v>134</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:3">
@@ -1759,10 +1777,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B34" t="s">
-        <x:v>93</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C34" t="s">
-        <x:v>111</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:3">
@@ -1770,10 +1788,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B35" t="s">
-        <x:v>60</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C35" t="s">
-        <x:v>131</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:3">
@@ -1781,10 +1799,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B36" t="s">
-        <x:v>89</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C36" t="s">
-        <x:v>110</x:v>
+        <x:v>146</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:3">
@@ -1792,10 +1810,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B37" t="s">
-        <x:v>52</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C37" t="s">
-        <x:v>112</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:3">
@@ -1803,10 +1821,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B38" t="s">
-        <x:v>24</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C38" t="s">
-        <x:v>137</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:3">
@@ -1814,10 +1832,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B39" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C39" t="s">
-        <x:v>25</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:3">
@@ -1825,10 +1843,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B40" t="s">
-        <x:v>42</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C40" t="s">
-        <x:v>57</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:3">
@@ -1836,10 +1854,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B41" t="s">
-        <x:v>34</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C41" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:3">
@@ -1847,10 +1865,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B42" t="s">
-        <x:v>81</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C42" t="s">
-        <x:v>147</x:v>
+        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:3">
@@ -1858,10 +1876,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B43" t="s">
-        <x:v>54</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C43" t="s">
-        <x:v>140</x:v>
+        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:3">
@@ -1869,10 +1887,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B44" t="s">
-        <x:v>35</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C44" t="s">
-        <x:v>122</x:v>
+        <x:v>165</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:3">
@@ -1880,10 +1898,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B45" t="s">
-        <x:v>32</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C45" t="s">
-        <x:v>136</x:v>
+        <x:v>153</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:3">
@@ -1891,10 +1909,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B46" t="s">
-        <x:v>44</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C46" t="s">
-        <x:v>128</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:3">
@@ -1902,10 +1920,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B47" t="s">
-        <x:v>83</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C47" t="s">
-        <x:v>109</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:3">
@@ -1913,10 +1931,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B48" t="s">
-        <x:v>94</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C48" t="s">
-        <x:v>30</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:3">
@@ -1924,10 +1942,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B49" t="s">
-        <x:v>101</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C49" t="s">
-        <x:v>87</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:3">
@@ -1935,10 +1953,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B50" t="s">
-        <x:v>160</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C50" t="s">
-        <x:v>47</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:3">
@@ -1946,241 +1964,241 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B51" t="s">
-        <x:v>55</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C51" t="s">
-        <x:v>115</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:3">
       <x:c r="A52">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="B52" t="s">
-        <x:v>161</x:v>
+      <x:c r="B52" s="1" t="s">
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C52" t="s">
-        <x:v>45</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:3">
       <x:c r="A53">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="B53" t="s">
-        <x:v>23</x:v>
+      <x:c r="B53" s="1" t="s">
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C53" t="s">
-        <x:v>124</x:v>
+        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:3">
       <x:c r="A54">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B54" t="s">
+      <x:c r="B54" s="1" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C54" t="s">
         <x:v>130</x:v>
-      </x:c>
-      <x:c r="C54" t="s">
-        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:3">
       <x:c r="A55">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="B55" t="s">
-        <x:v>106</x:v>
+      <x:c r="B55" s="1" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C55" t="s">
-        <x:v>77</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:3">
       <x:c r="A56">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="B56" t="s">
-        <x:v>99</x:v>
+      <x:c r="B56" s="1" t="s">
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C56" t="s">
-        <x:v>163</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:3">
       <x:c r="A57">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="B57" t="s">
-        <x:v>162</x:v>
+      <x:c r="B57" s="1" t="s">
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C57" t="s">
-        <x:v>118</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:3">
       <x:c r="A58">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="B58" t="s">
-        <x:v>157</x:v>
+      <x:c r="B58" s="1" t="s">
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C58" t="s">
-        <x:v>114</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:3">
       <x:c r="A59">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="B59" t="s">
-        <x:v>155</x:v>
+      <x:c r="B59" s="1" t="s">
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C59" t="s">
-        <x:v>50</x:v>
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:3">
       <x:c r="A60">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="B60" t="s">
-        <x:v>75</x:v>
+      <x:c r="B60" s="1" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C60" t="s">
-        <x:v>121</x:v>
+        <x:v>212</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:3">
       <x:c r="A61">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="B61" t="s">
-        <x:v>73</x:v>
+      <x:c r="B61" s="1" t="s">
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C61" t="s">
-        <x:v>125</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:3">
       <x:c r="A62">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="B62" t="s">
-        <x:v>76</x:v>
+      <x:c r="B62" s="1" t="s">
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C62" t="s">
-        <x:v>113</x:v>
+        <x:v>213</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:3">
       <x:c r="A63">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B63" t="s">
-        <x:v>66</x:v>
+      <x:c r="B63" s="1" t="s">
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C63" t="s">
-        <x:v>123</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:3">
       <x:c r="A64">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="B64" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="C64" t="s">
-        <x:v>129</x:v>
+      <x:c r="B64" s="1" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C64" s="2" t="s">
+        <x:v>214</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:3">
       <x:c r="A65">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="B65" t="s">
-        <x:v>68</x:v>
+      <x:c r="B65" s="1" t="s">
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C65" t="s">
-        <x:v>133</x:v>
+        <x:v>209</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:3">
       <x:c r="A66">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="B66" t="s">
-        <x:v>63</x:v>
+      <x:c r="B66" s="1" t="s">
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C66" t="s">
-        <x:v>145</x:v>
+        <x:v>178</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:3">
       <x:c r="A67">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="B67" t="s">
-        <x:v>69</x:v>
+      <x:c r="B67" s="1" t="s">
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C67" t="s">
-        <x:v>126</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:3">
       <x:c r="A68">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="B68" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="C68" t="s">
-        <x:v>65</x:v>
+      <x:c r="B68" s="1" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C68" s="2" t="s">
+        <x:v>176</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:3">
       <x:c r="A69">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="B69" t="s">
-        <x:v>156</x:v>
+      <x:c r="B69" s="1" t="s">
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C69" t="s">
-        <x:v>62</x:v>
+        <x:v>193</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:3">
       <x:c r="A70">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="B70" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="C70" t="s">
-        <x:v>67</x:v>
+      <x:c r="B70" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C70" s="2" t="s">
+        <x:v>177</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:3">
       <x:c r="A71">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="B71" t="s">
-        <x:v>165</x:v>
+      <x:c r="B71" s="1" t="s">
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C71" t="s">
-        <x:v>74</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:3">
       <x:c r="A72">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="B72" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="C72" t="s">
-        <x:v>119</x:v>
+      <x:c r="B72" s="1" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C72" s="2" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:3">
@@ -2188,10 +2206,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="C73" t="s">
-        <x:v>171</x:v>
+        <x:v>211</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:3">
@@ -2199,361 +2217,396 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="C74" t="s">
-        <x:v>197</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:3">
       <x:c r="A75">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="B75" s="1" t="s">
-        <x:v>12</x:v>
+      <x:c r="B75" s="2" t="s">
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C75" t="s">
-        <x:v>198</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:3">
       <x:c r="A76">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="B76" s="1" t="s">
-        <x:v>11</x:v>
+      <x:c r="B76" s="2" t="s">
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C76" t="s">
-        <x:v>14</x:v>
+        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:3">
       <x:c r="A77">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="B77" s="1" t="s">
-        <x:v>185</x:v>
+      <x:c r="B77" s="2" t="s">
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C77" t="s">
-        <x:v>168</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:3">
       <x:c r="A78">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="B78" s="1" t="s">
-        <x:v>186</x:v>
+      <x:c r="B78" s="2" t="s">
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C78" t="s">
-        <x:v>194</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:3">
       <x:c r="A79">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="B79" s="1" t="s">
-        <x:v>184</x:v>
+      <x:c r="B79" s="2" t="s">
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C79" t="s">
-        <x:v>149</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:3">
       <x:c r="A80">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="B80" s="1" t="s">
-        <x:v>191</x:v>
+      <x:c r="B80" s="2" t="s">
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C80" t="s">
-        <x:v>151</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:3">
       <x:c r="A81">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="B81" s="1" t="s">
-        <x:v>4</x:v>
+      <x:c r="B81" s="2" t="s">
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C81" t="s">
-        <x:v>15</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:3">
       <x:c r="A82">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="B82" s="1" t="s">
-        <x:v>7</x:v>
+      <x:c r="B82" s="2" t="s">
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C82" t="s">
-        <x:v>169</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:3">
       <x:c r="A83">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="B83" s="1" t="s">
-        <x:v>8</x:v>
+      <x:c r="B83" s="2" t="s">
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C83" t="s">
-        <x:v>204</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:3">
       <x:c r="A84">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="B84" s="1" t="s">
-        <x:v>2</x:v>
+      <x:c r="B84" s="2" t="s">
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C84" t="s">
-        <x:v>196</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:3">
       <x:c r="A85">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="B85" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C85" s="2" t="s">
-        <x:v>205</x:v>
+      <x:c r="B85" s="2" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="C85" t="s">
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:3">
       <x:c r="A86">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="B86" s="1" t="s">
-        <x:v>6</x:v>
+      <x:c r="B86" s="2" t="s">
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C86" t="s">
-        <x:v>21</x:v>
+        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:3">
       <x:c r="A87">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="B87" s="1" t="s">
-        <x:v>10</x:v>
+      <x:c r="B87" s="2" t="s">
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C87" t="s">
-        <x:v>202</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:3">
       <x:c r="A88">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="B88" s="1" t="s">
-        <x:v>3</x:v>
+      <x:c r="B88" t="s">
+        <x:v>174</x:v>
       </x:c>
       <x:c r="C88" t="s">
-        <x:v>170</x:v>
+        <x:v>190</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:3">
       <x:c r="A89">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="B89" s="1" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C89" s="2" t="s">
-        <x:v>201</x:v>
+      <x:c r="B89" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="C89" t="s">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:3">
       <x:c r="A90">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="B90" s="1" t="s">
-        <x:v>175</x:v>
+      <x:c r="B90" t="s">
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C90" t="s">
-        <x:v>195</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:3">
       <x:c r="A91">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="B91" s="1" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="C91" s="2" t="s">
-        <x:v>203</x:v>
+      <x:c r="B91" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="C91" t="s">
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:3">
       <x:c r="A92">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="B92" s="1" t="s">
-        <x:v>176</x:v>
+      <x:c r="B92" t="s">
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C92" t="s">
-        <x:v>16</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:3">
       <x:c r="A93">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="B93" s="1" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="C93" s="2" t="s">
-        <x:v>18</x:v>
+      <x:c r="B93" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="C93" t="s">
+        <x:v>192</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:3">
       <x:c r="A94">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="B94" s="1" t="s">
-        <x:v>173</x:v>
+      <x:c r="B94" t="s">
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C94" t="s">
-        <x:v>150</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:3">
       <x:c r="A95">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="B95" s="1" t="s">
+      <x:c r="B95" t="s">
         <x:v>172</x:v>
       </x:c>
       <x:c r="C95" t="s">
-        <x:v>199</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:3">
       <x:c r="A96">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="B96" s="2" t="s">
-        <x:v>190</x:v>
+      <x:c r="B96" t="s">
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C96" t="s">
-        <x:v>13</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:3">
       <x:c r="A97">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="B97" s="2" t="s">
-        <x:v>187</x:v>
+      <x:c r="B97" t="s">
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C97" t="s">
-        <x:v>0</x:v>
+        <x:v>146</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:3">
       <x:c r="A98">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="B98" s="2" t="s">
-        <x:v>189</x:v>
+      <x:c r="B98" t="s">
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C98" t="s">
-        <x:v>1</x:v>
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:3">
       <x:c r="A99">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="B99" s="2" t="s">
-        <x:v>178</x:v>
+      <x:c r="B99" t="s">
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C99" t="s">
-        <x:v>19</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:3">
       <x:c r="A100">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="B100" s="2" t="s">
-        <x:v>193</x:v>
+      <x:c r="B100" t="s">
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C100" t="s">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:3">
       <x:c r="A101">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="B101" s="2" t="s">
-        <x:v>182</x:v>
+      <x:c r="B101" t="s">
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C101" t="s">
-        <x:v>208</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:3">
       <x:c r="A102">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="B102" s="2" t="s">
-        <x:v>183</x:v>
+      <x:c r="B102" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C102" t="s">
-        <x:v>207</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:3">
       <x:c r="A103">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="B103" s="2" t="s">
-        <x:v>181</x:v>
+      <x:c r="B103" t="s">
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C103" t="s">
-        <x:v>206</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:3">
       <x:c r="A104">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="B104" s="2" t="s">
-        <x:v>179</x:v>
+      <x:c r="B104" t="s">
+        <x:v>198</x:v>
       </x:c>
       <x:c r="C104" t="s">
-        <x:v>200</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:3">
       <x:c r="A105">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="B105" s="2" t="s">
-        <x:v>180</x:v>
+      <x:c r="B105" t="s">
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C105" t="s">
-        <x:v>148</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="106" spans="2:2">
-      <x:c r="B106" s="2"/>
-    </x:row>
-    <x:row r="107" spans="2:2">
-      <x:c r="B107" s="2"/>
-    </x:row>
-    <x:row r="108" spans="2:2">
-      <x:c r="B108" s="2"/>
+        <x:v>202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" spans="1:3">
+      <x:c r="A106">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B106" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="C106" t="s">
+        <x:v>205</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" spans="1:3">
+      <x:c r="A107">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B107" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="C107" t="s">
+        <x:v>208</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" spans="1:3">
+      <x:c r="A108">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="B108" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="C108" t="s">
+        <x:v>206</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" spans="1:3">
+      <x:c r="A109">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="B109" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C109" t="s">
+        <x:v>207</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51138889789581298828" footer="0.51138889789581298828"/>

--- a/morpg/morpg/Assets/TableData/Table_Text.xlsx
+++ b/morpg/morpg/Assets/TableData/Table_Text.xlsx
@@ -21,649 +21,649 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="215">
   <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 공격보다 정찰에 특화된 공격력보다는 연타에 치중한 風계열 서포터.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 대장. 전투에 필요한 전반적인 능력을 두루 갖춘 氷계열 원거리 딜러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Demon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Korean</x:t>
+  </x:si>
+  <x:si>
+    <x:t>history</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타이틀로 이동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Renod</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타르타로스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나로사 포모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라우톤 윈너</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Array</x:t>
+  </x:si>
+  <x:si>
+    <x:t>menu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>term</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>긴가르시온</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에를로네</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Perth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이어하기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초심극점</x:t>
+  </x:si>
+  <x:si>
+    <x:t>반지(우)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>load</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Species</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cocruwa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Weapon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새 시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종족&amp;직업</x:t>
+  </x:si>
+  <x:si>
+    <x:t>newgame</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gloves</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Armor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ehrlone</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이레안 소린</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Plate</x:t>
+  </x:si>
+  <x:si>
+    <x:t>귀걸이(좌)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>반지(좌)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GaremenTooskaDin_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GaremenTooskaDin_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초월자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>머리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>페르스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마왕족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>성직자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도감</x:t>
+  </x:si>
+  <x:si>
     <x:t>셀레나</x:t>
   </x:si>
   <x:si>
+    <x:t>암살자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>드래곤</x:t>
+  </x:si>
+  <x:si>
     <x:t>마족</x:t>
   </x:si>
   <x:si>
+    <x:t>용어</x:t>
+  </x:si>
+  <x:si>
     <x:t>바드락</x:t>
   </x:si>
   <x:si>
+    <x:t>로데크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>역세계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>직업</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도적</x:t>
+  </x:si>
+  <x:si>
+    <x:t>본세계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무직</x:t>
+  </x:si>
+  <x:si>
+    <x:t>투르카</x:t>
+  </x:si>
+  <x:si>
+    <x:t>역사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Job</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장갑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>판금</x:t>
+  </x:si>
+  <x:si>
+    <x:t>메뉴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마법사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>천</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장비</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>갑옷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>궁수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목걸이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신발</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가죽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레디닌</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>티모르</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레노드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 자가방어와 자가치유에 치중된 地계열 순수 탱커.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 능력 중 대부분이 공격에 치중된 火계열 중거리 딜러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>평화로운 시기에도 전 세계에 그 개체 수가 5마리를 넘기지 못하던 이 세상 유일의 '초소수종'</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:암흑대제. 이 세상에서 유일하게 힘을 비축하는 시간에 비례하여 무한히 강해질 수 있는 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 지닌 능력 중 대부분이 상처를 치유하고 아군을 버프 적을 디버프하는 水계열 후방 서포터.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써 '구음절맥'을 갖고 태어난 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써 '태양절맥'을 갖고 태어난 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그의 일정범위에 존재하는 모든 사물은 점점 느려지기  시작하고 그 본인은 그 속도만큼 점점 빨라진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:금속왕. 긴가르시온이 조립한 완전 기계인간 다만 이 세상에서 유일하게 전신이 '완벽한 신의 금속'으로 이뤄져서 모든 것을 무시할 수준의 방어력을 지니고 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 대지의 종족 '티모르'의 후계자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 바다의 종족 '셀레나'의 후계자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 창공의 종족 '카루크'의 후계자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:시간의 마왕. 우리의 세상인 '본세계'와 '역세계'에서도 하나 이상을 찾아볼 수 없는 절대유일의 시간 능력자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이 세상 모든 것을 중독시키는 '페이튼'에 중독되어 스스로 의사를 갖고 움직이기 시작한 종족 '래머'의 마지막 생존자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:현명한 현자. 모든 코크루와 중 유일의 비전투원. 다만 이제는 기억하는 사람도 없는 '본카 일족'의 족장 '짐토'로써 사실상 이 세상의 모든 학문과 기술은 그로부터 비롯된 것이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:유령왕. 태생적으로 '산도라의 후예'인 대마도사였으나 그의 스승인 '푸 그레이'가 서술한 '초마도의 서'를 이해하여 마법사 중 최강의 존재인 '초마도사'가 되었다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 그가 공격의사를 갖던 말던 그의 주변에 존재하는 것만으로도 해독이 불가능한 '페이튼'에 중독되어 모든 존재가 소멸한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 불튼이 버금가는 탱킹 능력에 '피를 입는 자'에 버금하는 물리력을 지닌 雷계열 근거리 딜러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IreanSorin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>헤디 벤만 오프 모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가레멘 투스카 딘</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hidden001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gingarsion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아키르고 베니아</x:t>
+  </x:si>
+  <x:si>
+    <x:t>continue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tartaros</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hidden002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>버그리포트 바로가기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GrenFomos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CodeName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bugreport</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Redinin_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Redinin_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Renod_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Renod_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ehrlone_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DemonMage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Alchemist</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Summoner</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Necromancer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RightRIng</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Species&amp;Job</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Equipment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LeftRing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Perth_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BultonKajon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NarosaFomos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>notEmployed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Necklace</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LeftEarring</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History_003</x:t>
+  </x:si>
+  <x:si>
     <x:t>Assassin</x:t>
   </x:si>
   <x:si>
+    <x:t>Archmage</x:t>
+  </x:si>
+  <x:si>
     <x:t>이제 와서는 이 세상에 절대유일한 '핏빛혈족의 유일한 생존자' 무시무시한 이능력을 지니고 있지만 그가 지닌 이능력의 정체를 아는 자를 이제는 찾을 수 없다.</x:t>
   </x:si>
   <x:si>
+    <x:t>이명:피를 입는 자. '본세계'와 '역세계'를 모두 포함해서도 비슷한 수준의 신체능력을 가진 존재를 찾기 힘들 정도로 압도적인 신체능력을 가지고 있다.</x:t>
+  </x:si>
+  <x:si>
     <x:t>KaroukWingent_001</x:t>
   </x:si>
   <x:si>
+    <x:t>GaremenTooskaDin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KaroukWingent_002</x:t>
+  </x:si>
+  <x:si>
     <x:t>RoutonWinner_001</x:t>
   </x:si>
   <x:si>
-    <x:t>GaremenTooskaDin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KaroukWingent_002</x:t>
-  </x:si>
-  <x:si>
     <x:t>RoutonWinner_002</x:t>
   </x:si>
   <x:si>
-    <x:t>마법사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>성직자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>암살자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도적</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Archmage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 능력 중 대부분이 공격에 치중된 火계열 중거리 딜러.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 자가방어와 자가치유에 치중된 地계열 순수 탱커.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>평화로운 시기에도 전 세계에 그 개체 수가 5마리를 넘기지 못하던 이 세상 유일의 '초소수종'</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:암흑대제. 이 세상에서 유일하게 힘을 비축하는 시간에 비례하여 무한히 강해질 수 있는 존재.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이 세상 모든 것을 중독시키는 '페이튼'에 중독되어 스스로 의사를 갖고 움직이기 시작한 종족 '래머'의 마지막 생존자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:시간의 마왕. 우리의 세상인 '본세계'와 '역세계'에서도 하나 이상을 찾아볼 수 없는 절대유일의 시간 능력자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 불튼이 버금가는 탱킹 능력에 '피를 입는 자'에 버금하는 물리력을 지닌 雷계열 근거리 딜러.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Korean</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코크루와</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이어하기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>새 시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종족&amp;직업</x:t>
-  </x:si>
-  <x:si>
-    <x:t>newgame</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나로사 포모스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Demon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Renod</x:t>
-  </x:si>
-  <x:si>
-    <x:t>menu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타이틀로 이동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라우톤 윈너</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타르타로스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>history</x:t>
-  </x:si>
-  <x:si>
-    <x:t>load</x:t>
-  </x:si>
-  <x:si>
-    <x:t>term</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cocruwa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Array</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Species</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에를로네</x:t>
-  </x:si>
-  <x:si>
-    <x:t>초심극점</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Perth</x:t>
-  </x:si>
-  <x:si>
-    <x:t>긴가르시온</x:t>
-  </x:si>
-  <x:si>
-    <x:t>반지(우)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Weapon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>반지(좌)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이레안 소린</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gloves</x:t>
-  </x:si>
-  <x:si>
-    <x:t>귀걸이(좌)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Armor</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Plate</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ehrlone</x:t>
+    <x:t>마족 전사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Badrak</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dragon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Teemole</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Machine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Human</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Unknown</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Warrior</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Selena</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rogue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rodec</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소환술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Toorka</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Archer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Priest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연금술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>산도라 태생</x:t>
+  </x:si>
+  <x:si>
+    <x:t>강령술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마족 마법사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대마도사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GrenFomos_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GrenFomos_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NarosaFomos_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tartaros_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BultonKajon_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BultonKajon_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RightEarring</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NarosaFomos_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gingarsion_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IreanSorin_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tartaros_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IreanSorin_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KaroukWingent</x:t>
+  </x:si>
+  <x:si>
+    <x:t>???????????????</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DemonFighter</x:t>
+  </x:si>
+  <x:si>
+    <x:t>encyclopedia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RoutonWinner</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이라모스 강제개폐 사건</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불튼 카존</x:t>
   </x:si>
   <x:si>
     <x:t>Redinin</x:t>
   </x:si>
   <x:si>
+    <x:t>카루크 뷘젠트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>exit</x:t>
+  </x:si>
+  <x:si>
+    <x:t>?????</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종족전쟁</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Comment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>귀걸이(우)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Head</x:t>
+  </x:si>
+  <x:si>
+    <x:t>save</x:t>
+  </x:si>
+  <x:si>
+    <x:t>암흑대제2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>위대한 과실</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그렌 포모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종말전쟁</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sandora</x:t>
+  </x:si>
+  <x:si>
     <x:t>Boots</x:t>
   </x:si>
   <x:si>
+    <x:t>option</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불러오기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대마도전쟁</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Leather</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kalapok</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Index</x:t>
+  </x:si>
+  <x:si>
+    <x:t>title</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cloth</x:t>
   </x:si>
   <x:si>
-    <x:t>Index</x:t>
-  </x:si>
-  <x:si>
-    <x:t>title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>?????</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Leather</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카루크 뷘젠트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>귀걸이(우)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>option</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Head</x:t>
-  </x:si>
-  <x:si>
     <x:t>copy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그렌 포모스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Comment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>exit</x:t>
-  </x:si>
-  <x:si>
-    <x:t>save</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불러오기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>암흑대제2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종말전쟁</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불튼 카존</x:t>
-  </x:si>
-  <x:si>
-    <x:t>헤디 벤만 오프 모스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아키르고 베니아</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hidden001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가레멘 투스카 딘</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IreanSorin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gingarsion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GrenFomos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hidden002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CodeName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>버그리포트 바로가기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bugreport</x:t>
-  </x:si>
-  <x:si>
-    <x:t>continue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tartaros</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마왕족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>드래곤</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종족전쟁</x:t>
-  </x:si>
-  <x:si>
-    <x:t>위대한 과실</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대마도전쟁</x:t>
-  </x:si>
-  <x:si>
-    <x:t>encyclopedia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KaroukWingent</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RightEarring</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RoutonWinner</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gingarsion_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BultonKajon_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NarosaFomos_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NarosaFomos_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tartaros_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BultonKajon_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IreanSorin_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GrenFomos_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tartaros_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이라모스 강제개폐 사건</x:t>
-  </x:si>
-  <x:si>
-    <x:t>???????????????</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IreanSorin_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GrenFomos_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>로데크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>투르카</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Renod_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Redinin_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Redinin_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ehrlone_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Renod_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>notEmployed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Perth_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:피를 입는 자. '본세계'와 '역세계'를 모두 포함해서도 비슷한 수준의 신체능력을 가진 존재를 찾기 힘들 정도로 압도적인 신체능력을 가지고 있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Equipment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RightRIng</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NarosaFomos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LeftRing</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Species&amp;Job</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BultonKajon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Necklace</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LeftEarring</x:t>
-  </x:si>
-  <x:si>
-    <x:t>본세계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>판금</x:t>
-  </x:si>
-  <x:si>
-    <x:t>역세계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>직업</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도감</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장비</x:t>
-  </x:si>
-  <x:si>
-    <x:t>용어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무직</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>페르스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>메뉴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>역사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Job</x:t>
-  </x:si>
-  <x:si>
-    <x:t>천</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장갑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>머리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>저장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레노드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신발</x:t>
-  </x:si>
-  <x:si>
-    <x:t>목걸이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가죽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>갑옷</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레디닌</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GaremenTooskaDin_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GaremenTooskaDin_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그의 일정범위에 존재하는 모든 사물은 점점 느려지기  시작하고 그 본인은 그 속도만큼 점점 빨라진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sandora</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kalapok</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Unknown</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Teemole</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Machine</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 대지의 종족 '티모르'의 후계자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 창공의 종족 '카루크'의 후계자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 바다의 종족 '셀레나'의 후계자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Human</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Toorka</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Priest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Warrior</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Dragon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Archer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Selena</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Badrak</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rogue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rodec</x:t>
-  </x:si>
-  <x:si>
-    <x:t>티모르</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소환술사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>산도라 태생</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 공격보다 정찰에 특화된 공격력보다는 연타에 치중한 風계열 서포터.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 대장. 전투에 필요한 전반적인 능력을 두루 갖춘 氷계열 원거리 딜러.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Necromancer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DemonMage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Summoner</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Alchemist</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:금속왕. 긴가르시온이 조립한 완전 기계인간 다만 이 세상에서 유일하게 전신이 '완벽한 신의 금속'으로 이뤄져서 모든 것을 무시할 수준의 방어력을 지니고 있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DemonFighter</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연금술사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>궁수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>강령술사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마족 마법사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대마도사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마족 전사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 지닌 능력 중 대부분이 상처를 치유하고 아군을 버프 적을 디버프하는 水계열 후방 서포터.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:유령왕. 태생적으로 '산도라의 후예'인 대마도사였으나 그의 스승인 '푸 그레이'가 서술한 '초마도의 서'를 이해하여 마법사 중 최강의 존재인 '초마도사'가 되었다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 그가 공격의사를 갖던 말던 그의 주변에 존재하는 것만으로도 해독이 불가능한 '페이튼'에 중독되어 모든 존재가 소멸한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:현명한 현자. 모든 코크루와 중 유일의 비전투원. 다만 이제는 기억하는 사람도 없는 '본카 일족'의 족장 '짐토'로써 사실상 이 세상의 모든 학문과 기술은 그로부터 비롯된 것이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써 '태양절맥'을 갖고 태어난 존재.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써 '구음절맥'을 갖고 태어난 존재.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1415,31 +1415,31 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D2" s="1"/>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -1447,7 +1447,7 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B4" s="1"/>
       <x:c r="C4" s="1"/>
@@ -1458,10 +1458,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C5" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
@@ -1469,10 +1469,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" t="s">
-        <x:v>86</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C6" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
@@ -1480,10 +1480,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" t="s">
-        <x:v>64</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="C7" t="s">
-        <x:v>163</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
@@ -1491,10 +1491,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" t="s">
-        <x:v>69</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C8" t="s">
-        <x:v>164</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
@@ -1502,10 +1502,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B9" t="s">
-        <x:v>70</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C9" t="s">
-        <x:v>157</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
@@ -1513,10 +1513,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B10" t="s">
-        <x:v>37</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C10" t="s">
-        <x:v>71</x:v>
+        <x:v>207</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
@@ -1524,10 +1524,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B11" t="s">
-        <x:v>66</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="C11" t="s">
-        <x:v>158</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
@@ -1535,10 +1535,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B12" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C12" t="s">
-        <x:v>149</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
@@ -1546,10 +1546,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B13" t="s">
-        <x:v>59</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="C13" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
@@ -1557,10 +1557,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B14" t="s">
-        <x:v>85</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C14" t="s">
-        <x:v>84</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
@@ -1568,10 +1568,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B15" t="s">
-        <x:v>93</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C15" t="s">
-        <x:v>143</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
@@ -1579,10 +1579,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B16" t="s">
-        <x:v>39</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C16" t="s">
-        <x:v>23</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
@@ -1590,10 +1590,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B17" t="s">
-        <x:v>38</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C17" t="s">
-        <x:v>145</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
@@ -1601,10 +1601,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B18" t="s">
-        <x:v>36</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C18" t="s">
-        <x:v>150</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
@@ -1612,10 +1612,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B19" t="s">
-        <x:v>30</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C19" t="s">
-        <x:v>159</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
@@ -1623,10 +1623,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B20" t="s">
-        <x:v>87</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C20" t="s">
-        <x:v>35</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
@@ -1634,10 +1634,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B21" t="s">
-        <x:v>55</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C21" t="s">
-        <x:v>166</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
@@ -1645,10 +1645,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B22" t="s">
-        <x:v>44</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C22" t="s">
-        <x:v>148</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
@@ -1656,10 +1656,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B23" t="s">
-        <x:v>54</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C23" t="s">
-        <x:v>42</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
@@ -1667,10 +1667,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B24" t="s">
-        <x:v>80</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C24" t="s">
-        <x:v>45</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
@@ -1678,10 +1678,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B25" t="s">
-        <x:v>81</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C25" t="s">
-        <x:v>67</x:v>
+        <x:v>202</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
@@ -1689,10 +1689,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B26" t="s">
-        <x:v>133</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C26" t="s">
-        <x:v>28</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
@@ -1700,10 +1700,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B27" t="s">
-        <x:v>79</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C27" t="s">
-        <x:v>49</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
@@ -1711,10 +1711,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B28" t="s">
-        <x:v>136</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C28" t="s">
-        <x:v>74</x:v>
+        <x:v>190</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3">
@@ -1722,10 +1722,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B29" t="s">
-        <x:v>94</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C29" t="s">
-        <x:v>62</x:v>
+        <x:v>192</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">
@@ -1733,10 +1733,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B30" t="s">
-        <x:v>96</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C30" t="s">
-        <x:v>34</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
@@ -1744,10 +1744,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B31" t="s">
-        <x:v>7</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C31" t="s">
-        <x:v>78</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:3">
@@ -1755,10 +1755,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B32" t="s">
-        <x:v>41</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C32" t="s">
-        <x:v>155</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:3">
@@ -1766,10 +1766,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B33" t="s">
-        <x:v>151</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C33" t="s">
-        <x:v>142</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:3">
@@ -1777,10 +1777,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B34" t="s">
-        <x:v>77</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C34" t="s">
-        <x:v>60</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:3">
@@ -1788,10 +1788,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B35" t="s">
-        <x:v>82</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C35" t="s">
-        <x:v>107</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:3">
@@ -1799,10 +1799,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B36" t="s">
-        <x:v>124</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C36" t="s">
-        <x:v>146</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:3">
@@ -1810,10 +1810,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B37" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C37" t="s">
-        <x:v>144</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:3">
@@ -1821,10 +1821,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B38" t="s">
-        <x:v>135</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C38" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:3">
@@ -1832,10 +1832,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B39" t="s">
-        <x:v>57</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="C39" t="s">
-        <x:v>152</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:3">
@@ -1843,10 +1843,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B40" t="s">
-        <x:v>61</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="C40" t="s">
-        <x:v>162</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:3">
@@ -1854,10 +1854,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B41" t="s">
-        <x:v>53</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C41" t="s">
-        <x:v>140</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:3">
@@ -1865,10 +1865,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B42" t="s">
-        <x:v>47</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C42" t="s">
-        <x:v>154</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:3">
@@ -1876,10 +1876,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B43" t="s">
-        <x:v>65</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="C43" t="s">
-        <x:v>156</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:3">
@@ -1887,10 +1887,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B44" t="s">
-        <x:v>52</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C44" t="s">
-        <x:v>165</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:3">
@@ -1898,10 +1898,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B45" t="s">
-        <x:v>50</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C45" t="s">
-        <x:v>153</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:3">
@@ -1909,10 +1909,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B46" t="s">
-        <x:v>56</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C46" t="s">
-        <x:v>160</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:3">
@@ -1920,10 +1920,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B47" t="s">
-        <x:v>134</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C47" t="s">
-        <x:v>48</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:3">
@@ -1931,10 +1931,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B48" t="s">
-        <x:v>132</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C48" t="s">
-        <x:v>46</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:3">
@@ -1942,10 +1942,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B49" t="s">
-        <x:v>138</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C49" t="s">
-        <x:v>51</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:3">
@@ -1953,10 +1953,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B50" t="s">
-        <x:v>95</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C50" t="s">
-        <x:v>63</x:v>
+        <x:v>197</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:3">
@@ -1964,10 +1964,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B51" t="s">
-        <x:v>137</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C51" t="s">
-        <x:v>161</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:3">
@@ -1975,10 +1975,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C52" t="s">
-        <x:v>20</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:3">
@@ -1986,10 +1986,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C53" t="s">
-        <x:v>170</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:3">
@@ -1997,10 +1997,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C54" t="s">
-        <x:v>130</x:v>
+        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:3">
@@ -2008,10 +2008,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C55" t="s">
-        <x:v>4</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:3">
@@ -2019,10 +2019,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C56" t="s">
-        <x:v>18</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:3">
@@ -2030,10 +2030,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C57" t="s">
-        <x:v>72</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:3">
@@ -2041,10 +2041,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C58" t="s">
-        <x:v>200</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:3">
@@ -2052,10 +2052,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C59" t="s">
-        <x:v>210</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:3">
@@ -2063,10 +2063,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C60" t="s">
-        <x:v>212</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:3">
@@ -2074,10 +2074,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="C61" t="s">
-        <x:v>15</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:3">
@@ -2085,10 +2085,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C62" t="s">
-        <x:v>213</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:3">
@@ -2096,10 +2096,10 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C63" t="s">
-        <x:v>194</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:3">
@@ -2107,10 +2107,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="C64" s="2" t="s">
-        <x:v>214</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:3">
@@ -2118,10 +2118,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C65" t="s">
-        <x:v>209</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:3">
@@ -2129,10 +2129,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C66" t="s">
-        <x:v>178</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:3">
@@ -2140,10 +2140,10 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C67" t="s">
-        <x:v>16</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:3">
@@ -2151,10 +2151,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C68" s="2" t="s">
-        <x:v>176</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:3">
@@ -2162,10 +2162,10 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C69" t="s">
-        <x:v>193</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:3">
@@ -2173,10 +2173,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C70" s="2" t="s">
-        <x:v>177</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:3">
@@ -2184,10 +2184,10 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C71" t="s">
-        <x:v>21</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:3">
@@ -2195,10 +2195,10 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C72" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:3">
@@ -2206,10 +2206,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C73" t="s">
-        <x:v>211</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:3">
@@ -2217,10 +2217,10 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>168</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C74" t="s">
-        <x:v>19</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:3">
@@ -2231,7 +2231,7 @@
         <x:v>116</x:v>
       </x:c>
       <x:c r="C75" t="s">
-        <x:v>139</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:3">
@@ -2239,10 +2239,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="B76" s="2" t="s">
-        <x:v>119</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C76" t="s">
-        <x:v>141</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:3">
@@ -2250,10 +2250,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B77" s="2" t="s">
-        <x:v>114</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C77" t="s">
-        <x:v>43</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:3">
@@ -2261,10 +2261,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B78" s="2" t="s">
-        <x:v>125</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C78" t="s">
-        <x:v>75</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:3">
@@ -2272,10 +2272,10 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B79" s="2" t="s">
-        <x:v>121</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C79" t="s">
-        <x:v>76</x:v>
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:3">
@@ -2283,10 +2283,10 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B80" s="2" t="s">
-        <x:v>128</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C80" t="s">
-        <x:v>91</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:3">
@@ -2294,10 +2294,10 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="B81" s="2" t="s">
-        <x:v>123</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C81" t="s">
-        <x:v>90</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:3">
@@ -2305,10 +2305,10 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B82" s="2" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C82" t="s">
-        <x:v>92</x:v>
+        <x:v>208</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:3">
@@ -2316,10 +2316,10 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B83" s="2" t="s">
-        <x:v>126</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C83" t="s">
-        <x:v>73</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:3">
@@ -2327,10 +2327,10 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B84" s="2" t="s">
-        <x:v>122</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C84" t="s">
-        <x:v>106</x:v>
+        <x:v>189</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:3">
@@ -2338,10 +2338,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B85" s="2" t="s">
-        <x:v>179</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C85" t="s">
-        <x:v>110</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:3">
@@ -2349,10 +2349,10 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B86" s="2" t="s">
-        <x:v>189</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C86" t="s">
-        <x:v>111</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:3">
@@ -2360,10 +2360,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B87" s="2" t="s">
-        <x:v>180</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C87" t="s">
-        <x:v>112</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:3">
@@ -2371,10 +2371,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B88" t="s">
-        <x:v>174</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="C88" t="s">
-        <x:v>190</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:3">
@@ -2382,10 +2382,10 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="B89" t="s">
-        <x:v>186</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C89" t="s">
-        <x:v>0</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:3">
@@ -2393,10 +2393,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B90" t="s">
-        <x:v>187</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C90" t="s">
-        <x:v>2</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:3">
@@ -2404,10 +2404,10 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="B91" t="s">
-        <x:v>175</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C91" t="s">
-        <x:v>195</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:3">
@@ -2415,10 +2415,10 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="B92" t="s">
-        <x:v>29</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C92" t="s">
-        <x:v>1</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:3">
@@ -2426,10 +2426,10 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="B93" t="s">
-        <x:v>171</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="C93" t="s">
-        <x:v>192</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:3">
@@ -2437,10 +2437,10 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="B94" t="s">
-        <x:v>183</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C94" t="s">
-        <x:v>89</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:3">
@@ -2448,10 +2448,10 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="B95" t="s">
-        <x:v>172</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="C95" t="s">
-        <x:v>88</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:3">
@@ -2459,10 +2459,10 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="B96" t="s">
-        <x:v>173</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="C96" t="s">
-        <x:v>167</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:3">
@@ -2470,10 +2470,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B97" t="s">
-        <x:v>124</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C97" t="s">
-        <x:v>146</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:3">
@@ -2481,10 +2481,10 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="B98" t="s">
-        <x:v>182</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C98" t="s">
-        <x:v>204</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:3">
@@ -2492,10 +2492,10 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="B99" t="s">
-        <x:v>185</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C99" t="s">
-        <x:v>203</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:3">
@@ -2503,10 +2503,10 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="B100" t="s">
-        <x:v>184</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C100" t="s">
-        <x:v>10</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:3">
@@ -2514,10 +2514,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B101" t="s">
-        <x:v>181</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="C101" t="s">
-        <x:v>11</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:3">
@@ -2525,10 +2525,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="B102" t="s">
-        <x:v>3</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C102" t="s">
-        <x:v>12</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:3">
@@ -2536,10 +2536,10 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="B103" t="s">
-        <x:v>188</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C103" t="s">
-        <x:v>13</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:3">
@@ -2547,10 +2547,10 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="B104" t="s">
-        <x:v>198</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C104" t="s">
-        <x:v>191</x:v>
+        <x:v>163</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:3">
@@ -2558,10 +2558,10 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="B105" t="s">
-        <x:v>199</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C105" t="s">
-        <x:v>202</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:3">
@@ -2569,10 +2569,10 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="B106" t="s">
-        <x:v>196</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C106" t="s">
-        <x:v>205</x:v>
+        <x:v>169</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:3">
@@ -2580,10 +2580,10 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="B107" t="s">
-        <x:v>201</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C107" t="s">
-        <x:v>208</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:3">
@@ -2591,10 +2591,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B108" t="s">
-        <x:v>197</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C108" t="s">
-        <x:v>206</x:v>
+        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:3">
@@ -2602,10 +2602,10 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="B109" t="s">
-        <x:v>14</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C109" t="s">
-        <x:v>207</x:v>
+        <x:v>171</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/morpg/morpg/Assets/TableData/Table_Text.xlsx
+++ b/morpg/morpg/Assets/TableData/Table_Text.xlsx
@@ -19,7 +19,670 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="215">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="255">
+  <x:si>
+    <x:t>Cocruwa001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전 세계에서도 극히 발견하기 어려웠던 과실. 먹는 이의 모든 질병과 상처를 회복해주고, 육체를 가장 건강하던 때로 고정하며 새로운 수명을 하사한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써 '구음절맥'을 갖고 태어난 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써 '태양절맥'을 갖고 태어난 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 그가 공격의사를 갖던 말던 그의 주변에 존재하는 것만으로도 해독이 불가능한 '페이튼'에 중독되어 모든 존재가 소멸한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa013_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa010_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa011_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa010_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa011_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa013_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'본세계' 내에서 최초로 기록된 내전. 이로 인해 '불의 종족' 카르툼이 절멸하였다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa009_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아키르고 베니아</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라우톤</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가레멘</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa007_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GaremenTooskaDin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나로사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라우톤 윈너</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Badrak</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타르타로스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>긴가르시온</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Plate</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ehrlone</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Renod</x:t>
+  </x:si>
+  <x:si>
+    <x:t>load</x:t>
+  </x:si>
+  <x:si>
+    <x:t>귀걸이(좌)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Teemole</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Array</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새 시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gloves</x:t>
+  </x:si>
+  <x:si>
+    <x:t>newgame</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이어하기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dragon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Demon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Weapon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>history</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타이틀로 이동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Korean</x:t>
+  </x:si>
+  <x:si>
+    <x:t>반지(좌)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Species</x:t>
+  </x:si>
+  <x:si>
+    <x:t>반지(우)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>menu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이레안 소린</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Armor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Perth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종족&amp;직업</x:t>
+  </x:si>
+  <x:si>
+    <x:t>term</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에를로네</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cocruwa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마족 전사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나로사 포모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제 와서는 이 세상에 절대유일한 '핏빛혈족의 유일한 생존자' 무시무시한 이능력을 지니고 있지만 그가 지닌 이능력의 정체를 아는 자를 이제는 찾을 수 없다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:피를 입는 자. '본세계'와 '역세계'를 모두 포함해서도 비슷한 수준의 신체능력을 가진 존재를 찾기 힘들 정도로 압도적인 신체능력을 가지고 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RightEarring</x:t>
+  </x:si>
+  <x:si>
+    <x:t>???????????????</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DemonFighter</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RoutonWinner</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KaroukWingent</x:t>
+  </x:si>
+  <x:si>
+    <x:t>encyclopedia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>역세계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa005_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa001_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa006_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term005_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term006_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>헤디 벤만 오프 모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>위대한 과실</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마법의 신, 제샤스 데이틴의 일곱 제자들이 일으킨 내전. 이로 인해 세상의 모든 기록이 소실되어 사실상 모든 것이 초기화되었다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 창공의 종족 '투르카'의 생존자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 바다의 종족 '셀레나'의 생존자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 대지의 종족 '티모르'의 생존저.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 불튼이 버금가는 탱킹 능력에 '피를 입는 자'에 버금하는 물리력을 지닌 雷계열 근거리 딜러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 지닌 능력 중 대부분이 상처를 치유하고 아군을 버프, 적을 디버프하는 水계열 후방 서포터.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:유령왕. 태생적으로 '산도라의 후예'인 대마도사였으나 그의 스승인 '푸 그레이'가 서술한 '초마도의 서'를 이해하여 마법사 중 최강의 존재인 '초마도사'가 되었다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이 세상 모든 것을 중독시키는 '페이튼'에 중독되어 스스로 의사를 갖고 움직이기 시작한 종족 '래머'의 마지막 생존자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:시간의 마왕. 우리의 세상인 '본세계'와 '역세계'에서도 하나 이상을 찾아볼 수 없는 절대유일의 시간 능력자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Assassin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Necklace</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Archmage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LeftEarring</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Equipment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hidden001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bugreport</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gingarsion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가레멘 투스카 딘</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IreanSorin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tartaros</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Summoner</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hidden002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RightRIng</x:t>
+  </x:si>
+  <x:si>
+    <x:t>버그리포트 바로가기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CodeName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>notEmployed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>continue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GrenFomos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LeftRing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Species&amp;Job</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Alchemist</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NarosaFomos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DemonMage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Necromancer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BultonKajon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>역사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>천</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>메뉴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목걸이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>판금</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장갑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가죽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무직</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마법사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>궁수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>티모르</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신발</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>갑옷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>투르카</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레디닌</x:t>
+  </x:si>
+  <x:si>
+    <x:t>용어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초월자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레노드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>바드락</x:t>
+  </x:si>
+  <x:si>
+    <x:t>셀레나</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장비</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로데크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도적</x:t>
+  </x:si>
+  <x:si>
+    <x:t>직업</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Job</x:t>
+  </x:si>
+  <x:si>
+    <x:t>페르스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>드래곤</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도감</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마왕족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>암살자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>머리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>성직자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>귀걸이(우)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Boots</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대마도사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>강령술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>exit</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Redinin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그렌 포모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sandora</x:t>
+  </x:si>
+  <x:si>
+    <x:t>save</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Comment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마족 마법사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rodec</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Human</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Head</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카루크 뷘젠트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>산도라 태생</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불튼 카존</x:t>
+  </x:si>
+  <x:si>
+    <x:t>?????</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소환술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Priest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Machine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Leather</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Index</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불러오기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>copy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Toorka</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Selena</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>option</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cloth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kalapok</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Unknown</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rogue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Warrior</x:t>
+  </x:si>
+  <x:si>
+    <x:t>title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Archer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연금술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그렌</x:t>
+  </x:si>
+  <x:si>
+    <x:t>144년을 주기로 돌아오는 초자연 현상. 이 기간 중에는 성공적인 '이라 모스'의 개폐가 가능해진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa008_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초심극점</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불튼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이레안</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이라 모스 강제 개폐 사건</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'본세계' 내의 다른 10개의 세계와의 연락을 차단했음에도 가장 독자적인 업적을 이룩한 대륙.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:암흑대제. 이 세상에서 유일하게 힘을 비축하는 시간에 비례하여 무한히 강해질 수 있는 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 자가방어와 자가치유에 치중된 地계열 순수 탱커.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 능력 중 대부분이 공격에 치중된 火계열 중거리 딜러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>평화로운 시기에도 전 세계에 그 개체 수가 5마리를 넘기지 못하던 이 세상 유일의 '초소수종'</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>본세계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대마도전쟁</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카루크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:금속왕. 긴가르시온이 조립한 완전 기계인간 다만 이 세상에서 유일하게 전신이 '완벽한 신의 금속'으로 이뤄져서 모든 것을 무시할 수준의 방어력을 지니고 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종족전쟁</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa008_Desc_002</x:t>
+  </x:si>
   <x:si>
     <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 공격보다 정찰에 특화된 공격력보다는 연타에 치중한 風계열 서포터.</x:t>
   </x:si>
@@ -27,643 +690,100 @@
     <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 대장. 전투에 필요한 전반적인 능력을 두루 갖춘 氷계열 원거리 딜러.</x:t>
   </x:si>
   <x:si>
-    <x:t>Demon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Korean</x:t>
-  </x:si>
-  <x:si>
-    <x:t>history</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타이틀로 이동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Renod</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타르타로스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나로사 포모스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라우톤 윈너</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Array</x:t>
-  </x:si>
-  <x:si>
-    <x:t>menu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>term</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>긴가르시온</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에를로네</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Perth</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이어하기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>초심극점</x:t>
-  </x:si>
-  <x:si>
-    <x:t>반지(우)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>load</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Species</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cocruwa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Weapon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>새 시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종족&amp;직업</x:t>
-  </x:si>
-  <x:si>
-    <x:t>newgame</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gloves</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Armor</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ehrlone</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이레안 소린</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Plate</x:t>
-  </x:si>
-  <x:si>
-    <x:t>귀걸이(좌)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>반지(좌)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GaremenTooskaDin_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GaremenTooskaDin_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>초월자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>머리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>페르스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마왕족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>성직자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도감</x:t>
-  </x:si>
-  <x:si>
-    <x:t>셀레나</x:t>
-  </x:si>
-  <x:si>
-    <x:t>암살자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>드래곤</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>용어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>바드락</x:t>
-  </x:si>
-  <x:si>
-    <x:t>로데크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>역세계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>직업</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도적</x:t>
-  </x:si>
-  <x:si>
-    <x:t>본세계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무직</x:t>
-  </x:si>
-  <x:si>
-    <x:t>투르카</x:t>
-  </x:si>
-  <x:si>
-    <x:t>역사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Job</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장갑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>판금</x:t>
-  </x:si>
-  <x:si>
-    <x:t>메뉴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마법사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>천</x:t>
-  </x:si>
-  <x:si>
-    <x:t>저장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장비</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>갑옷</x:t>
-  </x:si>
-  <x:si>
-    <x:t>궁수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>목걸이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신발</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가죽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레디닌</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>티모르</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레노드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 자가방어와 자가치유에 치중된 地계열 순수 탱커.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 능력 중 대부분이 공격에 치중된 火계열 중거리 딜러.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>평화로운 시기에도 전 세계에 그 개체 수가 5마리를 넘기지 못하던 이 세상 유일의 '초소수종'</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:암흑대제. 이 세상에서 유일하게 힘을 비축하는 시간에 비례하여 무한히 강해질 수 있는 존재.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 지닌 능력 중 대부분이 상처를 치유하고 아군을 버프 적을 디버프하는 水계열 후방 서포터.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써 '구음절맥'을 갖고 태어난 존재.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써 '태양절맥'을 갖고 태어난 존재.</x:t>
+    <x:t>종말전쟁</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa009_Desc_002</x:t>
   </x:si>
   <x:si>
     <x:t>그의 일정범위에 존재하는 모든 사물은 점점 느려지기  시작하고 그 본인은 그 속도만큼 점점 빨라진다.</x:t>
   </x:si>
   <x:si>
-    <x:t>이명:금속왕. 긴가르시온이 조립한 완전 기계인간 다만 이 세상에서 유일하게 전신이 '완벽한 신의 금속'으로 이뤄져서 모든 것을 무시할 수준의 방어력을 지니고 있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 대지의 종족 '티모르'의 후계자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 바다의 종족 '셀레나'의 후계자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 창공의 종족 '카루크'의 후계자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:시간의 마왕. 우리의 세상인 '본세계'와 '역세계'에서도 하나 이상을 찾아볼 수 없는 절대유일의 시간 능력자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이 세상 모든 것을 중독시키는 '페이튼'에 중독되어 스스로 의사를 갖고 움직이기 시작한 종족 '래머'의 마지막 생존자.</x:t>
+    <x:t>Cocruwa002_Desc_001</x:t>
   </x:si>
   <x:si>
     <x:t>이명:현명한 현자. 모든 코크루와 중 유일의 비전투원. 다만 이제는 기억하는 사람도 없는 '본카 일족'의 족장 '짐토'로써 사실상 이 세상의 모든 학문과 기술은 그로부터 비롯된 것이다.</x:t>
   </x:si>
   <x:si>
-    <x:t>이명:유령왕. 태생적으로 '산도라의 후예'인 대마도사였으나 그의 스승인 '푸 그레이'가 서술한 '초마도의 서'를 이해하여 마법사 중 최강의 존재인 '초마도사'가 되었다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 그가 공격의사를 갖던 말던 그의 주변에 존재하는 것만으로도 해독이 불가능한 '페이튼'에 중독되어 모든 존재가 소멸한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 불튼이 버금가는 탱킹 능력에 '피를 입는 자'에 버금하는 물리력을 지닌 雷계열 근거리 딜러.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IreanSorin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>헤디 벤만 오프 모스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가레멘 투스카 딘</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hidden001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gingarsion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아키르고 베니아</x:t>
-  </x:si>
-  <x:si>
-    <x:t>continue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tartaros</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hidden002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>버그리포트 바로가기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GrenFomos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CodeName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bugreport</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Redinin_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Redinin_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Renod_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Renod_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ehrlone_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DemonMage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Alchemist</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Summoner</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Necromancer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RightRIng</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Species&amp;Job</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Equipment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LeftRing</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Perth_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BultonKajon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NarosaFomos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>notEmployed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Necklace</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LeftEarring</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Assassin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Archmage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이제 와서는 이 세상에 절대유일한 '핏빛혈족의 유일한 생존자' 무시무시한 이능력을 지니고 있지만 그가 지닌 이능력의 정체를 아는 자를 이제는 찾을 수 없다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:피를 입는 자. '본세계'와 '역세계'를 모두 포함해서도 비슷한 수준의 신체능력을 가진 존재를 찾기 힘들 정도로 압도적인 신체능력을 가지고 있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KaroukWingent_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GaremenTooskaDin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KaroukWingent_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RoutonWinner_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RoutonWinner_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마족 전사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Badrak</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Dragon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Teemole</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Machine</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Human</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Unknown</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Warrior</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Selena</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rogue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rodec</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소환술사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Toorka</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Archer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Priest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연금술사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>산도라 태생</x:t>
-  </x:si>
-  <x:si>
-    <x:t>강령술사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마족 마법사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대마도사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GrenFomos_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GrenFomos_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NarosaFomos_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tartaros_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BultonKajon_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BultonKajon_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RightEarring</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NarosaFomos_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gingarsion_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IreanSorin_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tartaros_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IreanSorin_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KaroukWingent</x:t>
-  </x:si>
-  <x:si>
-    <x:t>???????????????</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DemonFighter</x:t>
-  </x:si>
-  <x:si>
-    <x:t>encyclopedia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RoutonWinner</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이라모스 강제개폐 사건</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불튼 카존</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Redinin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카루크 뷘젠트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>exit</x:t>
-  </x:si>
-  <x:si>
-    <x:t>?????</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종족전쟁</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Comment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>귀걸이(우)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Head</x:t>
-  </x:si>
-  <x:si>
-    <x:t>save</x:t>
-  </x:si>
-  <x:si>
-    <x:t>암흑대제2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>위대한 과실</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그렌 포모스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종말전쟁</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sandora</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Boots</x:t>
-  </x:si>
-  <x:si>
-    <x:t>option</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불러오기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대마도전쟁</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Leather</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kalapok</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Index</x:t>
-  </x:si>
-  <x:si>
-    <x:t>title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cloth</x:t>
-  </x:si>
-  <x:si>
-    <x:t>copy</x:t>
+    <x:t>Cocruwa002_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term006_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term005_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa010_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa005_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa007_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa009_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa008_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa006_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa011_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa013_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Desc_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa007_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'아키르고 베니아'가 아닌 때에 '이라 모스'를 개설한 충격으로 '본세계' 바깥의 세상이 무너져린 사건.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>드래곤을 포함해도 모든 종족 중에서는 물리력 최강의 종족 '바드락'의 생존자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>창조신 'OM'이 창조한 초심극점 너머의 다른 세상.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>창조신 'NM'이 창조한 11개로 겹쳐진 우리의 세상.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'본세계'와 '역세계'를 잇는 유일한 물리적 이동공간.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초심극점을 마주하고 바라보고 있는 다른 세상, '역세계'와의 전쟁.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -726,7 +846,10 @@
       </x:bottom>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="2">
+  <x:cellStyleXfs count="3">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -734,20 +857,23 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="3">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <x:cellXfs count="4">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
-  <x:cellStyles count="2">
+  <x:cellStyles count="3">
     <x:cellStyle name="Normal" xfId="0" builtinId="0" iLevel="0"/>
-    <x:cellStyle name="표준" xfId="1"/>
+    <x:cellStyle name="표준" xfId="2"/>
   </x:cellStyles>
   <x:dxfs count="12">
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -1407,39 +1533,40 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:D109"/>
+  <x:dimension ref="A1:H132"/>
   <x:sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="16.39999999999999857891"/>
   <x:cols>
     <x:col min="1" max="1" width="8.796875" bestFit="1" customWidth="1"/>
+    <x:col min="2" max="2" width="19.73828125" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>211</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D2" s="1"/>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -1447,7 +1574,7 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>196</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B4" s="1"/>
       <x:c r="C4" s="1"/>
@@ -1458,10 +1585,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" t="s">
-        <x:v>26</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C5" t="s">
-        <x:v>24</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
@@ -1472,7 +1599,7 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="C6" t="s">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
@@ -1480,10 +1607,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" t="s">
-        <x:v>206</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C7" t="s">
-        <x:v>80</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
@@ -1491,10 +1618,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" t="s">
-        <x:v>193</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C8" t="s">
-        <x:v>68</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
@@ -1502,10 +1629,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B9" t="s">
-        <x:v>199</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="C9" t="s">
-        <x:v>65</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
@@ -1513,10 +1640,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B10" t="s">
-        <x:v>20</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C10" t="s">
-        <x:v>207</x:v>
+        <x:v>182</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
@@ -1524,10 +1651,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B11" t="s">
-        <x:v>214</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C11" t="s">
-        <x:v>77</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
@@ -1535,10 +1662,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B12" t="s">
-        <x:v>11</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C12" t="s">
-        <x:v>62</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
@@ -1546,10 +1673,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B13" t="s">
-        <x:v>212</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C13" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
@@ -1557,10 +1684,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B14" t="s">
-        <x:v>112</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C14" t="s">
-        <x:v>109</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
@@ -1568,10 +1695,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B15" t="s">
-        <x:v>187</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C15" t="s">
-        <x:v>41</x:v>
+        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
@@ -1579,10 +1706,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B16" t="s">
-        <x:v>22</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C16" t="s">
-        <x:v>36</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
@@ -1590,10 +1717,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B17" t="s">
-        <x:v>12</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C17" t="s">
-        <x:v>46</x:v>
+        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
@@ -1601,10 +1728,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B18" t="s">
-        <x:v>4</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C18" t="s">
-        <x:v>57</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
@@ -1612,10 +1739,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B19" t="s">
-        <x:v>6</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C19" t="s">
-        <x:v>79</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
@@ -1623,10 +1750,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B20" t="s">
-        <x:v>107</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C20" t="s">
-        <x:v>7</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
@@ -1634,10 +1761,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B21" t="s">
-        <x:v>191</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C21" t="s">
-        <x:v>76</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
@@ -1645,10 +1772,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B22" t="s">
-        <x:v>16</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C22" t="s">
-        <x:v>38</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
@@ -1656,10 +1783,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B23" t="s">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C23" t="s">
-        <x:v>15</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
@@ -1667,10 +1794,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B24" t="s">
-        <x:v>104</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C24" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
@@ -1678,10 +1805,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B25" t="s">
-        <x:v>110</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C25" t="s">
-        <x:v>202</x:v>
+        <x:v>165</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
@@ -1689,10 +1816,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B26" t="s">
-        <x:v>136</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C26" t="s">
-        <x:v>8</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
@@ -1700,10 +1827,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B27" t="s">
-        <x:v>100</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C27" t="s">
-        <x:v>30</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
@@ -1711,10 +1838,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B28" t="s">
-        <x:v>135</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C28" t="s">
-        <x:v>190</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3">
@@ -1722,10 +1849,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B29" t="s">
-        <x:v>184</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C29" t="s">
-        <x:v>192</x:v>
+        <x:v>173</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">
@@ -1733,10 +1860,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B30" t="s">
-        <x:v>188</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C30" t="s">
-        <x:v>9</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
@@ -1744,10 +1871,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B31" t="s">
-        <x:v>147</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C31" t="s">
-        <x:v>102</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:3">
@@ -1755,10 +1882,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B32" t="s">
-        <x:v>21</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C32" t="s">
-        <x:v>59</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:3">
@@ -1766,10 +1893,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B33" t="s">
-        <x:v>58</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C33" t="s">
-        <x:v>52</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:3">
@@ -1777,10 +1904,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B34" t="s">
-        <x:v>103</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C34" t="s">
-        <x:v>194</x:v>
+        <x:v>176</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:3">
@@ -1788,10 +1915,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B35" t="s">
-        <x:v>108</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C35" t="s">
-        <x:v>185</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:3">
@@ -1799,10 +1926,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B36" t="s">
-        <x:v>138</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C36" t="s">
-        <x:v>55</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:3">
@@ -1810,10 +1937,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B37" t="s">
-        <x:v>132</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C37" t="s">
-        <x:v>67</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:3">
@@ -1821,10 +1948,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B38" t="s">
-        <x:v>130</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C38" t="s">
-        <x:v>25</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:3">
@@ -1832,10 +1959,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B39" t="s">
-        <x:v>213</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C39" t="s">
-        <x:v>64</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:3">
@@ -1843,10 +1970,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B40" t="s">
-        <x:v>209</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C40" t="s">
-        <x:v>75</x:v>
+        <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:3">
@@ -1854,10 +1981,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B41" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C41" t="s">
-        <x:v>61</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:3">
@@ -1865,10 +1992,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B42" t="s">
-        <x:v>23</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C42" t="s">
-        <x:v>66</x:v>
+        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:3">
@@ -1876,10 +2003,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B43" t="s">
-        <x:v>198</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="C43" t="s">
-        <x:v>37</x:v>
+        <x:v>157</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:3">
@@ -1887,10 +2014,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B44" t="s">
-        <x:v>28</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C44" t="s">
-        <x:v>70</x:v>
+        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:3">
@@ -1898,10 +2025,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B45" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C45" t="s">
-        <x:v>60</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:3">
@@ -1909,10 +2036,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B46" t="s">
-        <x:v>205</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C46" t="s">
-        <x:v>74</x:v>
+        <x:v>134</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:3">
@@ -1920,10 +2047,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B47" t="s">
-        <x:v>133</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C47" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:3">
@@ -1931,10 +2058,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B48" t="s">
-        <x:v>129</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C48" t="s">
-        <x:v>19</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:3">
@@ -1942,10 +2069,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B49" t="s">
-        <x:v>140</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C49" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:3">
@@ -1953,10 +2080,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B50" t="s">
-        <x:v>178</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C50" t="s">
-        <x:v>197</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:3">
@@ -1964,648 +2091,947 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B51" t="s">
-        <x:v>139</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C51" t="s">
-        <x:v>73</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:3">
       <x:c r="A52">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="B52" s="1" t="s">
-        <x:v>115</x:v>
+      <x:c r="B52" s="2" t="s">
+        <x:v>171</x:v>
       </x:c>
       <x:c r="C52" t="s">
-        <x:v>94</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:3">
       <x:c r="A53">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="B53" s="1" t="s">
-        <x:v>117</x:v>
+      <x:c r="B53" s="2" t="s">
+        <x:v>170</x:v>
       </x:c>
       <x:c r="C53" t="s">
-        <x:v>89</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:3">
       <x:c r="A54">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B54" s="1" t="s">
-        <x:v>175</x:v>
+      <x:c r="B54" s="2" t="s">
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C54" t="s">
-        <x:v>145</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:3">
       <x:c r="A55">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="B55" s="1" t="s">
-        <x:v>182</x:v>
+      <x:c r="B55" t="s">
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C55" t="s">
-        <x:v>144</x:v>
+        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:3">
       <x:c r="A56">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="B56" s="1" t="s">
-        <x:v>114</x:v>
+      <x:c r="B56" t="s">
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C56" t="s">
-        <x:v>85</x:v>
+        <x:v>146</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:3">
       <x:c r="A57">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="B57" s="1" t="s">
-        <x:v>113</x:v>
+      <x:c r="B57" t="s">
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C57" t="s">
-        <x:v>200</x:v>
+        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:3">
       <x:c r="A58">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="B58" s="1" t="s">
-        <x:v>134</x:v>
+      <x:c r="B58" t="s">
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C58" t="s">
-        <x:v>90</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:3">
       <x:c r="A59">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="B59" s="1" t="s">
-        <x:v>122</x:v>
+      <x:c r="B59" t="s">
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C59" t="s">
-        <x:v>97</x:v>
+        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:3">
       <x:c r="A60">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="B60" s="1" t="s">
-        <x:v>180</x:v>
+      <x:c r="B60" t="s">
+        <x:v>166</x:v>
       </x:c>
       <x:c r="C60" t="s">
-        <x:v>96</x:v>
+        <x:v>174</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:3">
       <x:c r="A61">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="B61" s="1" t="s">
-        <x:v>172</x:v>
+      <x:c r="B61" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C61" t="s">
-        <x:v>83</x:v>
+        <x:v>153</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:3">
       <x:c r="A62">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="B62" s="1" t="s">
-        <x:v>173</x:v>
+      <x:c r="B62" t="s">
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C62" t="s">
-        <x:v>88</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:3">
       <x:c r="A63">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B63" s="1" t="s">
-        <x:v>179</x:v>
+      <x:c r="B63" t="s">
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C63" t="s">
-        <x:v>1</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:3">
       <x:c r="A64">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="B64" s="1" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="C64" s="2" t="s">
-        <x:v>87</x:v>
+      <x:c r="B64" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C64" t="s">
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:3">
       <x:c r="A65">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="B65" s="1" t="s">
-        <x:v>183</x:v>
+      <x:c r="B65" t="s">
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C65" t="s">
-        <x:v>86</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:3">
       <x:c r="A66">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="B66" s="1" t="s">
-        <x:v>181</x:v>
+      <x:c r="B66" t="s">
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C66" t="s">
-        <x:v>92</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:3">
       <x:c r="A67">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="B67" s="1" t="s">
-        <x:v>177</x:v>
+      <x:c r="B67" t="s">
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C67" t="s">
-        <x:v>82</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:3">
       <x:c r="A68">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="B68" s="1" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="C68" s="2" t="s">
-        <x:v>91</x:v>
+      <x:c r="B68" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="C68" t="s">
+        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:3">
       <x:c r="A69">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="B69" s="1" t="s">
-        <x:v>146</x:v>
+      <x:c r="B69" t="s">
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C69" t="s">
-        <x:v>0</x:v>
+        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:3">
       <x:c r="A70">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="B70" s="1" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="C70" s="2" t="s">
-        <x:v>93</x:v>
+      <x:c r="B70" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="C70" t="s">
+        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:3">
       <x:c r="A71">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="B71" s="1" t="s">
-        <x:v>149</x:v>
+      <x:c r="B71" t="s">
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C71" t="s">
-        <x:v>99</x:v>
+        <x:v>177</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:3">
       <x:c r="A72">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="B72" s="1" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="C72" s="2" t="s">
-        <x:v>84</x:v>
+      <x:c r="B72" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C72" t="s">
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:3">
       <x:c r="A73">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="B73" s="1" t="s">
-        <x:v>35</x:v>
+      <x:c r="B73" t="s">
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C73" t="s">
-        <x:v>98</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:3">
       <x:c r="A74">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="B74" s="1" t="s">
-        <x:v>34</x:v>
+      <x:c r="B74" t="s">
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C74" t="s">
-        <x:v>95</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:3">
       <x:c r="A75">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="B75" s="2" t="s">
-        <x:v>116</x:v>
+      <x:c r="B75" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C75" t="s">
-        <x:v>54</x:v>
+        <x:v>169</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:3">
       <x:c r="A76">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="B76" s="2" t="s">
-        <x:v>121</x:v>
+      <x:c r="B76" t="s">
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C76" t="s">
-        <x:v>49</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="77" spans="1:3">
+        <x:v>161</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" spans="1:8">
       <x:c r="A77">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="B77" s="2" t="s">
-        <x:v>118</x:v>
+      <x:c r="B77" t="s">
+        <x:v>209</x:v>
       </x:c>
       <x:c r="C77" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="78" spans="1:3">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="G77" s="2"/>
+      <x:c r="H77" s="2"/>
+    </x:row>
+    <x:row r="78" spans="1:8">
       <x:c r="A78">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="B78" s="2" t="s">
-        <x:v>131</x:v>
+      <x:c r="B78" t="s">
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C78" t="s">
-        <x:v>101</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="79" spans="1:3">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G78" s="2"/>
+      <x:c r="H78" s="2"/>
+    </x:row>
+    <x:row r="79" spans="1:8">
       <x:c r="A79">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="B79" s="2" t="s">
-        <x:v>123</x:v>
+      <x:c r="B79" t="s">
+        <x:v>236</x:v>
       </x:c>
       <x:c r="C79" t="s">
-        <x:v>105</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="80" spans="1:3">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="G79" s="2"/>
+      <x:c r="H79" s="2"/>
+    </x:row>
+    <x:row r="80" spans="1:8">
       <x:c r="A80">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="B80" s="2" t="s">
-        <x:v>137</x:v>
+      <x:c r="B80" t="s">
+        <x:v>237</x:v>
       </x:c>
       <x:c r="C80" t="s">
-        <x:v>201</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="81" spans="1:3">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="G80" s="2"/>
+      <x:c r="H80" s="2"/>
+    </x:row>
+    <x:row r="81" spans="1:8">
       <x:c r="A81">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="B81" s="2" t="s">
-        <x:v>120</x:v>
+      <x:c r="B81" t="s">
+        <x:v>238</x:v>
       </x:c>
       <x:c r="C81" t="s">
-        <x:v>195</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="82" spans="1:3">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G81" s="2"/>
+      <x:c r="H81" s="2"/>
+    </x:row>
+    <x:row r="82" spans="1:8">
       <x:c r="A82">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="B82" s="2" t="s">
-        <x:v>128</x:v>
+      <x:c r="B82" t="s">
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C82" t="s">
-        <x:v>208</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="83" spans="1:3">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="G82" s="2"/>
+      <x:c r="H82" s="2"/>
+    </x:row>
+    <x:row r="83" spans="1:8">
       <x:c r="A83">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="B83" s="2" t="s">
-        <x:v>141</x:v>
+      <x:c r="B83" t="s">
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C83" t="s">
-        <x:v>203</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="84" spans="1:3">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="G83" s="2"/>
+      <x:c r="H83" s="2"/>
+    </x:row>
+    <x:row r="84" spans="1:8">
       <x:c r="A84">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="B84" s="2" t="s">
-        <x:v>119</x:v>
+      <x:c r="B84" t="s">
+        <x:v>241</x:v>
       </x:c>
       <x:c r="C84" t="s">
-        <x:v>189</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="85" spans="1:3">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G84" s="2"/>
+      <x:c r="H84" s="2"/>
+    </x:row>
+    <x:row r="85" spans="1:8">
       <x:c r="A85">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="B85" s="2" t="s">
-        <x:v>157</x:v>
+      <x:c r="B85" t="s">
+        <x:v>240</x:v>
       </x:c>
       <x:c r="C85" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="86" spans="1:3">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="G85" s="2"/>
+      <x:c r="H85" s="2"/>
+    </x:row>
+    <x:row r="86" spans="1:8">
       <x:c r="A86">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="B86" s="2" t="s">
-        <x:v>162</x:v>
+      <x:c r="B86" t="s">
+        <x:v>235</x:v>
       </x:c>
       <x:c r="C86" t="s">
-        <x:v>48</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="87" spans="1:3">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="G86" s="2"/>
+      <x:c r="H86" s="2"/>
+    </x:row>
+    <x:row r="87" spans="1:8">
       <x:c r="A87">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="B87" s="2" t="s">
-        <x:v>164</x:v>
+      <x:c r="B87" t="s">
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C87" t="s">
-        <x:v>56</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="88" spans="1:3">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="G87" s="2"/>
+      <x:c r="H87" s="2"/>
+    </x:row>
+    <x:row r="88" spans="1:8">
       <x:c r="A88">
         <x:v>84</x:v>
       </x:c>
       <x:c r="B88" t="s">
-        <x:v>154</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="C88" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="89" spans="1:3">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G88" s="2"/>
+      <x:c r="H88" s="2"/>
+    </x:row>
+    <x:row r="89" spans="1:8">
       <x:c r="A89">
         <x:v>85</x:v>
       </x:c>
       <x:c r="B89" t="s">
-        <x:v>160</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="C89" t="s">
-        <x:v>42</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="90" spans="1:3">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G89" s="2"/>
+      <x:c r="H89" s="2"/>
+    </x:row>
+    <x:row r="90" spans="1:8">
       <x:c r="A90">
         <x:v>86</x:v>
       </x:c>
       <x:c r="B90" t="s">
-        <x:v>152</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="C90" t="s">
-        <x:v>47</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="91" spans="1:3">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="G90" s="2"/>
+      <x:c r="H90" s="2"/>
+    </x:row>
+    <x:row r="91" spans="1:8">
       <x:c r="A91">
         <x:v>87</x:v>
       </x:c>
       <x:c r="B91" t="s">
-        <x:v>155</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="C91" t="s">
-        <x:v>69</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="92" spans="1:3">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G91" s="2"/>
+      <x:c r="H91" s="2"/>
+    </x:row>
+    <x:row r="92" spans="1:8">
       <x:c r="A92">
         <x:v>88</x:v>
       </x:c>
       <x:c r="B92" t="s">
-        <x:v>2</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="C92" t="s">
-        <x:v>45</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="93" spans="1:3">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="G92" s="2"/>
+      <x:c r="H92" s="2"/>
+    </x:row>
+    <x:row r="93" spans="1:8">
       <x:c r="A93">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B93" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="C93" t="s">
-        <x:v>168</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="94" spans="1:3">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="C93" s="2" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G93" s="2"/>
+      <x:c r="H93" s="2"/>
+    </x:row>
+    <x:row r="94" spans="1:8">
       <x:c r="A94">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B94" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="C94" t="s">
-        <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="95" spans="1:3">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C94" s="2" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="G94" s="2"/>
+      <x:c r="H94" s="2"/>
+    </x:row>
+    <x:row r="95" spans="1:8">
       <x:c r="A95">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B95" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="C95" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="96" spans="1:3">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="C95" s="2" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="G95" s="2"/>
+      <x:c r="H95" s="2"/>
+    </x:row>
+    <x:row r="96" spans="1:8">
       <x:c r="A96">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B96" t="s">
-        <x:v>158</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="C96" t="s">
-        <x:v>81</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="97" spans="1:3">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="G96" s="2"/>
+      <x:c r="H96" s="2"/>
+    </x:row>
+    <x:row r="97" spans="1:8">
       <x:c r="A97">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B97" t="s">
-        <x:v>138</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C97" t="s">
-        <x:v>55</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="98" spans="1:3">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="G97" s="2"/>
+      <x:c r="H97" s="2"/>
+    </x:row>
+    <x:row r="98" spans="1:8">
       <x:c r="A98">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B98" t="s">
-        <x:v>159</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C98" t="s">
-        <x:v>72</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="99" spans="1:3">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="G98" s="2"/>
+      <x:c r="H98" s="2"/>
+    </x:row>
+    <x:row r="99" spans="1:8">
       <x:c r="A99">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B99" t="s">
-        <x:v>165</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="C99" t="s">
-        <x:v>71</x:v>
-      </x:c>
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="G99" s="2"/>
+      <x:c r="H99" s="2"/>
     </x:row>
     <x:row r="100" spans="1:3">
       <x:c r="A100">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B100" t="s">
-        <x:v>156</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C100" t="s">
-        <x:v>63</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:3">
       <x:c r="A101">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B101" t="s">
-        <x:v>166</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C101" t="s">
-        <x:v>40</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:3">
       <x:c r="A102">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="B102" t="s">
-        <x:v>142</x:v>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B102" s="2" t="s">
+        <x:v>226</x:v>
       </x:c>
       <x:c r="C102" t="s">
-        <x:v>43</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:3">
       <x:c r="A103">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="B103" t="s">
-        <x:v>161</x:v>
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B103" s="2" t="s">
+        <x:v>228</x:v>
       </x:c>
       <x:c r="C103" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:3">
       <x:c r="A104">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="B104" t="s">
-        <x:v>126</x:v>
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B104" s="2" t="s">
+        <x:v>212</x:v>
       </x:c>
       <x:c r="C104" t="s">
-        <x:v>163</x:v>
+        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:3">
       <x:c r="A105">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="B105" t="s">
-        <x:v>125</x:v>
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B105" s="2" t="s">
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C105" t="s">
-        <x:v>167</x:v>
+        <x:v>214</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:3">
       <x:c r="A106">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="B106" t="s">
-        <x:v>127</x:v>
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="B106" s="2" t="s">
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C106" t="s">
-        <x:v>169</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:3">
       <x:c r="A107">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="B107" t="s">
-        <x:v>186</x:v>
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="B107" s="2" t="s">
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C107" t="s">
-        <x:v>151</x:v>
+        <x:v>227</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:3">
       <x:c r="A108">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="B108" t="s">
-        <x:v>124</x:v>
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B108" s="2" t="s">
+        <x:v>248</x:v>
       </x:c>
       <x:c r="C108" t="s">
-        <x:v>170</x:v>
+        <x:v>207</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:3">
       <x:c r="A109">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="B109" t="s">
-        <x:v>143</x:v>
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B109" s="2" t="s">
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C109" t="s">
-        <x:v>171</x:v>
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" spans="1:3">
+      <x:c r="A110">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B110" s="2" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="C110" t="s">
+        <x:v>222</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" spans="1:3">
+      <x:c r="A111">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B111" s="2" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="C111" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" spans="1:3">
+      <x:c r="A112">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="B112" s="2" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C112" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" spans="1:3">
+      <x:c r="A113">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B113" s="2" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="C113" t="s">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" spans="1:3">
+      <x:c r="A114">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="B114" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C114" t="s">
+        <x:v>206</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" spans="1:3">
+      <x:c r="A115">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B115" s="2" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C115" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" spans="1:3">
+      <x:c r="A116">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="B116" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C116" t="s">
+        <x:v>221</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" spans="1:3">
+      <x:c r="A117">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="B117" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C117" t="s">
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" spans="1:3">
+      <x:c r="A118">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B118" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C118" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" spans="1:3">
+      <x:c r="A119">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B119" s="2" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C119" t="s">
+        <x:v>250</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" spans="1:3">
+      <x:c r="A120">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="B120" s="2" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="C120" t="s">
+        <x:v>208</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" spans="1:3">
+      <x:c r="A121">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B121" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C121" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" spans="1:3">
+      <x:c r="A122">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B122" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C122" t="s">
+        <x:v>87</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" spans="1:3">
+      <x:c r="A123">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="B123" s="2" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="C123" t="s">
+        <x:v>252</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" spans="1:3">
+      <x:c r="A124">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="B124" s="2" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C124" t="s">
+        <x:v>251</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" spans="1:3">
+      <x:c r="A125">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="B125" s="2" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C125" s="3" t="s">
+        <x:v>253</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" spans="1:3">
+      <x:c r="A126">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="B126" s="2" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="C126" s="3" t="s">
+        <x:v>204</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" spans="1:3">
+      <x:c r="A127">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="B127" s="2" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C127" t="s">
+        <x:v>197</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" spans="1:3">
+      <x:c r="A128">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="B128" s="2" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C128" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" spans="1:3">
+      <x:c r="A129">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="B129" s="2" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="C129" s="3" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" spans="1:3">
+      <x:c r="A130">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="B130" s="2" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C130" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" spans="1:3">
+      <x:c r="A131">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="B131" s="2" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C131" t="s">
+        <x:v>254</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" spans="1:3">
+      <x:c r="A132">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="B132" s="2" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C132" s="3" t="s">
+        <x:v>249</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/morpg/morpg/Assets/TableData/Table_Text.xlsx
+++ b/morpg/morpg/Assets/TableData/Table_Text.xlsx
@@ -19,771 +19,789 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="255">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="261">
+  <x:si>
+    <x:t>Term007_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa013_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa011_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa010_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa009_Title</x:t>
+  </x:si>
   <x:si>
     <x:t>Cocruwa001_Desc_001</x:t>
   </x:si>
   <x:si>
+    <x:t>Term007_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마법의 신, 제샤스 데이틴의 일곱 제자들이 일으킨 내전. 이로 인해 세상의 모든 기록이 소실되어 사실상 모든 것이 초기화되었다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제 와서는 이 세상에 절대유일한 '핏빛혈족의 유일한 생존자' 무시무시한 이능력을 지니고 있지만 그가 지닌 이능력의 정체를 아는 자를 이제는 찾을 수 없다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:피를 입는 자. '본세계'와 '역세계'를 모두 포함해서도 비슷한 수준의 신체능력을 가진 존재를 찾기 힘들 정도로 압도적인 신체능력을 가지고 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>긴가르시온</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타르타로스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Renod</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Teemole</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새 시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>귀걸이(좌)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>load</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gloves</x:t>
+  </x:si>
+  <x:si>
+    <x:t>newgame</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라우톤 윈너</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ehrlone</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dragon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Demon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Weapon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Array</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이어하기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타이틀로 이동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>history</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Plate</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Korean</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Badrak</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나로사 포모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>반지(우)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>위대한 과실</x:t>
+  </x:si>
+  <x:si>
+    <x:t>menu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>귀걸이(우)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Boots</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Species</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Perth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>반지(좌)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이레안 소린</x:t>
+  </x:si>
+  <x:si>
+    <x:t>term</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종족&amp;직업</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Armor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에를로네</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cocruwa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마족 전사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무직</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마법사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라우톤</x:t>
+  </x:si>
+  <x:si>
+    <x:t>티모르</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신발</x:t>
+  </x:si>
+  <x:si>
+    <x:t>천</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나로사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>판금</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가죽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목걸이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>메뉴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>역사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>역세계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>궁수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장갑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가레멘</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불튼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도적</x:t>
+  </x:si>
+  <x:si>
+    <x:t>직업</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Job</x:t>
+  </x:si>
+  <x:si>
+    <x:t>투르카</x:t>
+  </x:si>
+  <x:si>
+    <x:t>셀레나</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로데크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>드래곤</x:t>
+  </x:si>
+  <x:si>
+    <x:t>갑옷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도감</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레디닌</x:t>
+  </x:si>
+  <x:si>
+    <x:t>암살자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>바드락</x:t>
+  </x:si>
+  <x:si>
+    <x:t>용어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레노드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장비</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마왕족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>머리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그렌</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이레안</x:t>
+  </x:si>
+  <x:si>
+    <x:t>본세계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카루크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초월자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>페르스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>성직자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초심극점을 마주하고 바라보고 있는 다른 세상, '역세계'와의 전쟁.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term007_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:현명한 현자. 모든 코크루와 중 유일의 비전투원. 다만 이제는 기억하는 사람도 없는 '본카 일족'의 족장 '짐토'로써 사실상 이 세상의 모든 학문과 기술은 그로부터 비롯된 것이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'본세계'와 '역세계'를 잇는 유일한 물리적 이동공간.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>창조신 'OM'이 창조한 초심극점 너머의 다른 세상.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>창조신 'NM'이 창조한 11개로 겹쳐진 우리의 세상.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'종말전쟁'이 끝난 이후의 시대가 되며 사실상 유명무실한 용어가 되어 사실상 강력한 힘을 지닌 '초월자'들을 일컫는 용어가 되었다.</x:t>
+  </x:si>
+  <x:si>
     <x:t>전 세계에서도 극히 발견하기 어려웠던 과실. 먹는 이의 모든 질병과 상처를 회복해주고, 육체를 가장 건강하던 때로 고정하며 새로운 수명을 하사한다.</x:t>
   </x:si>
   <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 자가방어와 자가치유에 치중된 地계열 순수 탱커.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>평화로운 시기에도 전 세계에 그 개체 수가 5마리를 넘기지 못하던 이 세상 유일의 '초소수종'</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 능력 중 대부분이 공격에 치중된 火계열 중거리 딜러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'본세계' 내의 다른 10개의 세계와의 연락을 차단했음에도 가장 독자적인 업적을 이룩한 대륙.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:암흑대제. 이 세상에서 유일하게 힘을 비축하는 시간에 비례하여 무한히 강해질 수 있는 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써 '태양절맥'을 갖고 태어난 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>드래곤을 포함해도 모든 종족 중에서는 물리력 최강의 종족 '바드락'의 생존자.</x:t>
+  </x:si>
+  <x:si>
     <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써 '구음절맥'을 갖고 태어난 존재.</x:t>
   </x:si>
   <x:si>
-    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써 '태양절맥'을 갖고 태어난 존재.</x:t>
+    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 창공의 종족 '투르카'의 생존자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 대지의 종족 '티모르'의 생존저.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'본세계' 내에서 최초로 기록된 내전. 이로 인해 '불의 종족' 카르툼이 절멸하였다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 바다의 종족 '셀레나'의 생존자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:금속왕. 긴가르시온이 조립한 완전 기계인간 다만 이 세상에서 유일하게 전신이 '완벽한 신의 금속'으로 이뤄져서 모든 것을 무시할 수준의 방어력을 지니고 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그의 일정범위에 존재하는 모든 사물은 점점 느려지기  시작하고 그 본인은 그 속도만큼 점점 빨라진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>144년을 주기로 돌아오는 초자연 현상. 이 기간 중에는 성공적인 '이라 모스'의 개폐가 가능해진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'아키르고 베니아'가 아닌 때에 '이라 모스'를 개설한 충격으로 '본세계' 바깥의 세상이 무너져린 사건.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term005_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RoutonWinner</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>encyclopedia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KaroukWingent</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이라 모스 강제 개폐 사건</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term006_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>???????????????</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RightEarring</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DemonFighter</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종말전쟁</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종족전쟁</x:t>
+  </x:si>
+  <x:si>
+    <x:t>헤디 벤만 오프 모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Archmage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gingarsion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LeftEarring</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tartaros</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IreanSorin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hidden001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Summoner</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Necklace</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Equipment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bugreport</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Assassin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가레멘 투스카 딘</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 불튼이 버금가는 탱킹 능력에 '피를 입는 자'에 버금하는 물리력을 지닌 雷계열 근거리 딜러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 지닌 능력 중 대부분이 상처를 치유하고 아군을 버프, 적을 디버프하는 水계열 후방 서포터.</x:t>
   </x:si>
   <x:si>
     <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 그가 공격의사를 갖던 말던 그의 주변에 존재하는 것만으로도 해독이 불가능한 '페이튼'에 중독되어 모든 존재가 소멸한다.</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocruwa013_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa010_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa011_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Desc_002</x:t>
+    <x:t>이명:유령왕. 태생적으로 '산도라의 후예'인 대마도사였으나 그의 스승인 '푸 그레이'가 서술한 '초마도의 서'를 이해하여 마법사 중 최강의 존재인 '초마도사'가 되었다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 공격보다 정찰에 특화된 공격력보다는 연타에 치중한 風계열 서포터.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 대장. 전투에 필요한 전반적인 능력을 두루 갖춘 氷계열 원거리 딜러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이 세상 모든 것을 중독시키는 '페이튼'에 중독되어 스스로 의사를 갖고 움직이기 시작한 종족 '래머'의 마지막 생존자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:시간의 마왕. 우리의 세상인 '본세계'와 '역세계'에서도 하나 이상을 찾아볼 수 없는 절대유일의 시간 능력자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아키르고 베니아</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa008_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa001_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa011_Desc_001</x:t>
   </x:si>
   <x:si>
     <x:t>Cocruwa012_Desc_001</x:t>
   </x:si>
   <x:si>
+    <x:t>History003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa013_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa005_Desc_001</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cocruwa010_Desc_001</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocruwa011_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa013_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'본세계' 내에서 최초로 기록된 내전. 이로 인해 '불의 종족' 카르툼이 절멸하였다.</x:t>
+    <x:t>Cocruwa006_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GaremenTooskaDin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa007_Desc_002</x:t>
   </x:si>
   <x:si>
     <x:t>Cocruwa009_Desc_001</x:t>
   </x:si>
   <x:si>
-    <x:t>아키르고 베니아</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa004_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라우톤</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가레멘</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa007_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GaremenTooskaDin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나로사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라우톤 윈너</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Badrak</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타르타로스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>긴가르시온</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Plate</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ehrlone</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Renod</x:t>
-  </x:si>
-  <x:si>
-    <x:t>load</x:t>
-  </x:si>
-  <x:si>
-    <x:t>귀걸이(좌)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Teemole</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Array</x:t>
-  </x:si>
-  <x:si>
-    <x:t>새 시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gloves</x:t>
-  </x:si>
-  <x:si>
-    <x:t>newgame</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이어하기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Dragon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Demon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Weapon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>history</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타이틀로 이동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Korean</x:t>
-  </x:si>
-  <x:si>
-    <x:t>반지(좌)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Species</x:t>
-  </x:si>
-  <x:si>
-    <x:t>반지(우)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>menu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이레안 소린</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Armor</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Perth</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종족&amp;직업</x:t>
-  </x:si>
-  <x:si>
-    <x:t>term</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에를로네</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cocruwa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마족 전사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나로사 포모스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이제 와서는 이 세상에 절대유일한 '핏빛혈족의 유일한 생존자' 무시무시한 이능력을 지니고 있지만 그가 지닌 이능력의 정체를 아는 자를 이제는 찾을 수 없다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:피를 입는 자. '본세계'와 '역세계'를 모두 포함해서도 비슷한 수준의 신체능력을 가진 존재를 찾기 힘들 정도로 압도적인 신체능력을 가지고 있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RightEarring</x:t>
-  </x:si>
-  <x:si>
-    <x:t>???????????????</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DemonFighter</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RoutonWinner</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KaroukWingent</x:t>
-  </x:si>
-  <x:si>
-    <x:t>encyclopedia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>역세계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa005_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa001_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa006_Desc_001</x:t>
+    <x:t>Term002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term006_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term005_Desc_001</x:t>
   </x:si>
   <x:si>
     <x:t>History004_Desc_001</x:t>
   </x:si>
   <x:si>
-    <x:t>Term002_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term005_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History001_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term006_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term003_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History002_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History003_Desc_001</x:t>
+    <x:t>Cloth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kalapok</x:t>
+  </x:si>
+  <x:si>
+    <x:t>?????</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Machine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Priest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불튼 카존</x:t>
+  </x:si>
+  <x:si>
+    <x:t>copy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>산도라 태생</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Warrior</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Leather</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Archer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rogue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연금술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초심극점</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대마도전쟁</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소환술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Unknown</x:t>
+  </x:si>
+  <x:si>
+    <x:t>option</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불러오기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Index</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Selena</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Toorka</x:t>
+  </x:si>
+  <x:si>
+    <x:t>save</x:t>
+  </x:si>
+  <x:si>
+    <x:t>강령술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Comment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그렌 포모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Redinin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Human</x:t>
+  </x:si>
+  <x:si>
+    <x:t>exit</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마족 마법사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rodec</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sandora</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Head</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대마도사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카루크 뷘젠트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RightRIng</x:t>
+  </x:si>
+  <x:si>
+    <x:t>버그리포트 바로가기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CodeName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hidden002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>continue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GrenFomos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DemonMage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LeftRing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Species&amp;Job</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Necromancer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BultonKajon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>notEmployed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NarosaFomos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Alchemist</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa007_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa005_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa010_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa008_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa009_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa008_Desc_001</x:t>
   </x:si>
   <x:si>
     <x:t>Term004_Desc_001</x:t>
   </x:si>
   <x:si>
-    <x:t>헤디 벤만 오프 모스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>위대한 과실</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마법의 신, 제샤스 데이틴의 일곱 제자들이 일으킨 내전. 이로 인해 세상의 모든 기록이 소실되어 사실상 모든 것이 초기화되었다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 창공의 종족 '투르카'의 생존자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 바다의 종족 '셀레나'의 생존자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 대지의 종족 '티모르'의 생존저.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 불튼이 버금가는 탱킹 능력에 '피를 입는 자'에 버금하는 물리력을 지닌 雷계열 근거리 딜러.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 지닌 능력 중 대부분이 상처를 치유하고 아군을 버프, 적을 디버프하는 水계열 후방 서포터.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:유령왕. 태생적으로 '산도라의 후예'인 대마도사였으나 그의 스승인 '푸 그레이'가 서술한 '초마도의 서'를 이해하여 마법사 중 최강의 존재인 '초마도사'가 되었다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이 세상 모든 것을 중독시키는 '페이튼'에 중독되어 스스로 의사를 갖고 움직이기 시작한 종족 '래머'의 마지막 생존자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:시간의 마왕. 우리의 세상인 '본세계'와 '역세계'에서도 하나 이상을 찾아볼 수 없는 절대유일의 시간 능력자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Assassin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Necklace</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Archmage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LeftEarring</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Equipment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hidden001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bugreport</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gingarsion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가레멘 투스카 딘</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IreanSorin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tartaros</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Summoner</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hidden002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RightRIng</x:t>
-  </x:si>
-  <x:si>
-    <x:t>버그리포트 바로가기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CodeName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>notEmployed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>continue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GrenFomos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LeftRing</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Species&amp;Job</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Alchemist</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NarosaFomos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DemonMage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Necromancer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BultonKajon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>역사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>천</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>메뉴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>목걸이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>판금</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장갑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가죽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무직</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마법사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>궁수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>저장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>티모르</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신발</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>갑옷</x:t>
-  </x:si>
-  <x:si>
-    <x:t>투르카</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레디닌</x:t>
-  </x:si>
-  <x:si>
-    <x:t>용어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>초월자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레노드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>바드락</x:t>
-  </x:si>
-  <x:si>
-    <x:t>셀레나</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장비</x:t>
-  </x:si>
-  <x:si>
-    <x:t>로데크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도적</x:t>
-  </x:si>
-  <x:si>
-    <x:t>직업</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Job</x:t>
-  </x:si>
-  <x:si>
-    <x:t>페르스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>드래곤</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도감</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마왕족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>암살자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>머리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>성직자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>귀걸이(우)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Boots</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대마도사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>강령술사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>exit</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Redinin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그렌 포모스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sandora</x:t>
-  </x:si>
-  <x:si>
-    <x:t>save</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Comment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마족 마법사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rodec</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Human</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Head</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카루크 뷘젠트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>산도라 태생</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불튼 카존</x:t>
-  </x:si>
-  <x:si>
-    <x:t>?????</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소환술사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Priest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Machine</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Leather</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Index</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불러오기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>copy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Toorka</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Selena</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>option</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cloth</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kalapok</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Unknown</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rogue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Warrior</x:t>
-  </x:si>
-  <x:si>
-    <x:t>title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Archer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연금술사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그렌</x:t>
-  </x:si>
-  <x:si>
-    <x:t>144년을 주기로 돌아오는 초자연 현상. 이 기간 중에는 성공적인 '이라 모스'의 개폐가 가능해진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa008_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>초심극점</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term001_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불튼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이레안</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이라 모스 강제 개폐 사건</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'본세계' 내의 다른 10개의 세계와의 연락을 차단했음에도 가장 독자적인 업적을 이룩한 대륙.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:암흑대제. 이 세상에서 유일하게 힘을 비축하는 시간에 비례하여 무한히 강해질 수 있는 존재.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 자가방어와 자가치유에 치중된 地계열 순수 탱커.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 능력 중 대부분이 공격에 치중된 火계열 중거리 딜러.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>평화로운 시기에도 전 세계에 그 개체 수가 5마리를 넘기지 못하던 이 세상 유일의 '초소수종'</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa001_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>본세계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대마도전쟁</x:t>
-  </x:si>
-  <x:si>
     <x:t>Cocruwa003_Desc_001</x:t>
   </x:si>
   <x:si>
-    <x:t>카루크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:금속왕. 긴가르시온이 조립한 완전 기계인간 다만 이 세상에서 유일하게 전신이 '완벽한 신의 금속'으로 이뤄져서 모든 것을 무시할 수준의 방어력을 지니고 있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History002_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History001_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History003_Title</x:t>
+    <x:t>Cocruwa002_Desc_002</x:t>
   </x:si>
   <x:si>
     <x:t>History004_Title</x:t>
   </x:si>
   <x:si>
-    <x:t>종족전쟁</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa008_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 공격보다 정찰에 특화된 공격력보다는 연타에 치중한 風계열 서포터.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 대장. 전투에 필요한 전반적인 능력을 두루 갖춘 氷계열 원거리 딜러.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종말전쟁</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa009_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그의 일정범위에 존재하는 모든 사물은 점점 느려지기  시작하고 그 본인은 그 속도만큼 점점 빨라진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa002_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:현명한 현자. 모든 코크루와 중 유일의 비전투원. 다만 이제는 기억하는 사람도 없는 '본카 일족'의 족장 '짐토'로써 사실상 이 세상의 모든 학문과 기술은 그로부터 비롯된 것이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa002_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term006_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term004_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term001_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term003_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term005_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term002_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa010_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa003_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa004_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa005_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa007_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa009_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa008_Title</x:t>
+    <x:t>Cocruwa012_Desc_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa007_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa006_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa011_Title</x:t>
   </x:si>
   <x:si>
     <x:t>Cocruwa002_Title</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocruwa006_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa011_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Title</x:t>
-  </x:si>
-  <x:si>
     <x:t>Cocruwa013_Title</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocruwa012_Desc_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa007_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'아키르고 베니아'가 아닌 때에 '이라 모스'를 개설한 충격으로 '본세계' 바깥의 세상이 무너져린 사건.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>드래곤을 포함해도 모든 종족 중에서는 물리력 최강의 종족 '바드락'의 생존자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>창조신 'OM'이 창조한 초심극점 너머의 다른 세상.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>창조신 'NM'이 창조한 11개로 겹쳐진 우리의 세상.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'본세계'와 '역세계'를 잇는 유일한 물리적 이동공간.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>초심극점을 마주하고 바라보고 있는 다른 세상, '역세계'와의 전쟁.</x:t>
+    <x:t>코크루와</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'본세계' 내에서, '종말전쟁'의 결말을 지켜보던 강력한 존재들을 일컫는 용어.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1533,7 +1551,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:H132"/>
+  <x:dimension ref="A1:H135"/>
   <x:sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="16.39999999999999857891"/>
   <x:cols>
     <x:col min="1" max="1" width="8.796875" bestFit="1" customWidth="1"/>
@@ -1542,31 +1560,31 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>181</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D2" s="1"/>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -1574,7 +1592,7 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>168</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B4" s="1"/>
       <x:c r="C4" s="1"/>
@@ -1585,10 +1603,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" t="s">
-        <x:v>36</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C5" t="s">
-        <x:v>34</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
@@ -1596,10 +1614,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" t="s">
-        <x:v>106</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="C6" t="s">
-        <x:v>37</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
@@ -1607,10 +1625,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" t="s">
-        <x:v>187</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="C7" t="s">
-        <x:v>138</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
@@ -1618,10 +1636,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" t="s">
-        <x:v>163</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="C8" t="s">
-        <x:v>125</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
@@ -1629,10 +1647,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B9" t="s">
-        <x:v>167</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C9" t="s">
-        <x:v>131</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
@@ -1640,10 +1658,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B10" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C10" t="s">
-        <x:v>182</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
@@ -1651,10 +1669,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B11" t="s">
-        <x:v>183</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C11" t="s">
-        <x:v>124</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
@@ -1662,10 +1680,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B12" t="s">
-        <x:v>47</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C12" t="s">
-        <x:v>118</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
@@ -1673,10 +1691,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B13" t="s">
-        <x:v>193</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C13" s="2" t="s">
-        <x:v>42</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
@@ -1684,10 +1702,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B14" t="s">
-        <x:v>95</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C14" t="s">
-        <x:v>103</x:v>
+        <x:v>221</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
@@ -1695,10 +1713,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B15" t="s">
-        <x:v>64</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C15" t="s">
-        <x:v>154</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
@@ -1706,10 +1724,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B16" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C16" t="s">
-        <x:v>142</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
@@ -1717,10 +1735,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B17" t="s">
-        <x:v>52</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C17" t="s">
-        <x:v>141</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
@@ -1728,10 +1746,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B18" t="s">
-        <x:v>41</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C18" t="s">
-        <x:v>115</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
@@ -1739,10 +1757,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B19" t="s">
-        <x:v>28</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C19" t="s">
-        <x:v>144</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
@@ -1750,10 +1768,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B20" t="s">
-        <x:v>99</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C20" t="s">
-        <x:v>24</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
@@ -1761,10 +1779,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B21" t="s">
-        <x:v>164</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="C21" t="s">
-        <x:v>140</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
@@ -1772,10 +1790,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B22" t="s">
-        <x:v>50</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C22" t="s">
-        <x:v>152</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
@@ -1783,10 +1801,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B23" t="s">
-        <x:v>27</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C23" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
@@ -1794,10 +1812,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B24" t="s">
-        <x:v>96</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C24" t="s">
-        <x:v>25</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
@@ -1805,10 +1823,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B25" t="s">
-        <x:v>107</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C25" t="s">
-        <x:v>165</x:v>
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
@@ -1816,10 +1834,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B26" t="s">
-        <x:v>111</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="C26" t="s">
-        <x:v>56</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
@@ -1827,10 +1845,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B27" t="s">
-        <x:v>98</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C27" t="s">
-        <x:v>48</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
@@ -1838,10 +1856,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B28" t="s">
-        <x:v>114</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C28" t="s">
-        <x:v>175</x:v>
+        <x:v>189</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3">
@@ -1849,10 +1867,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B29" t="s">
-        <x:v>63</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C29" t="s">
-        <x:v>173</x:v>
+        <x:v>219</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">
@@ -1860,7 +1878,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B30" t="s">
-        <x:v>62</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C30" t="s">
         <x:v>22</x:v>
@@ -1871,10 +1889,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B31" t="s">
-        <x:v>20</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="C31" t="s">
-        <x:v>97</x:v>
+        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:3">
@@ -1882,10 +1900,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B32" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C32" t="s">
-        <x:v>135</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:3">
@@ -1893,10 +1911,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B33" t="s">
-        <x:v>151</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C33" t="s">
-        <x:v>150</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:3">
@@ -1904,10 +1922,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B34" t="s">
-        <x:v>94</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C34" t="s">
-        <x:v>176</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:3">
@@ -1915,10 +1933,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B35" t="s">
-        <x:v>101</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C35" t="s">
-        <x:v>60</x:v>
+        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:3">
@@ -1926,10 +1944,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B36" t="s">
-        <x:v>105</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="C36" t="s">
-        <x:v>126</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:3">
@@ -1937,10 +1955,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B37" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="C37" t="s">
         <x:v>93</x:v>
-      </x:c>
-      <x:c r="C37" t="s">
-        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:3">
@@ -1948,10 +1966,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B38" t="s">
-        <x:v>109</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="C38" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:3">
@@ -1959,10 +1977,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B39" t="s">
-        <x:v>188</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C39" t="s">
-        <x:v>116</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:3">
@@ -1970,10 +1988,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B40" t="s">
-        <x:v>180</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C40" t="s">
-        <x:v>122</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:3">
@@ -1981,10 +1999,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B41" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C41" t="s">
-        <x:v>120</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:3">
@@ -1992,10 +2010,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B42" t="s">
-        <x:v>40</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C42" t="s">
-        <x:v>132</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:3">
@@ -2003,10 +2021,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B43" t="s">
-        <x:v>172</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C43" t="s">
-        <x:v>157</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:3">
@@ -2014,10 +2032,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B44" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C44" t="s">
-        <x:v>136</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:3">
@@ -2025,10 +2043,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B45" t="s">
-        <x:v>35</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C45" t="s">
-        <x:v>121</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:3">
@@ -2036,10 +2054,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B46" t="s">
-        <x:v>160</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C46" t="s">
-        <x:v>134</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:3">
@@ -2047,10 +2065,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B47" t="s">
-        <x:v>108</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="C47" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:3">
@@ -2058,10 +2076,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B48" t="s">
-        <x:v>102</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C48" t="s">
-        <x:v>46</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:3">
@@ -2069,10 +2087,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B49" t="s">
-        <x:v>92</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C49" t="s">
-        <x:v>30</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:3">
@@ -2080,10 +2098,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B50" t="s">
-        <x:v>59</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C50" t="s">
-        <x:v>159</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:3">
@@ -2091,10 +2109,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B51" t="s">
-        <x:v>90</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C51" t="s">
-        <x:v>119</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:3">
@@ -2102,10 +2120,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B52" s="2" t="s">
-        <x:v>171</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="C52" t="s">
-        <x:v>117</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:3">
@@ -2113,10 +2131,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B53" s="2" t="s">
-        <x:v>170</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C53" t="s">
-        <x:v>148</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:3">
@@ -2124,10 +2142,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B54" s="2" t="s">
-        <x:v>184</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="C54" t="s">
-        <x:v>137</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:3">
@@ -2135,10 +2153,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B55" t="s">
-        <x:v>31</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C55" t="s">
-        <x:v>133</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:3">
@@ -2146,10 +2164,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B56" t="s">
-        <x:v>185</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C56" t="s">
-        <x:v>146</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:3">
@@ -2157,10 +2175,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B57" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C57" t="s">
-        <x:v>145</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:3">
@@ -2168,10 +2186,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B58" t="s">
-        <x:v>179</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C58" t="s">
-        <x:v>128</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:3">
@@ -2179,10 +2197,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B59" t="s">
-        <x:v>39</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C59" t="s">
-        <x:v>143</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:3">
@@ -2190,10 +2208,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B60" t="s">
-        <x:v>166</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="C60" t="s">
-        <x:v>174</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:3">
@@ -2201,10 +2219,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B61" t="s">
-        <x:v>38</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C61" t="s">
-        <x:v>153</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:3">
@@ -2212,10 +2230,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B62" t="s">
-        <x:v>189</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C62" t="s">
-        <x:v>155</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:3">
@@ -2223,10 +2241,10 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B63" t="s">
-        <x:v>190</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C63" t="s">
-        <x:v>139</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:3">
@@ -2234,10 +2252,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B64" t="s">
-        <x:v>105</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="C64" t="s">
-        <x:v>126</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:3">
@@ -2245,10 +2263,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B65" t="s">
-        <x:v>192</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C65" t="s">
-        <x:v>127</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:3">
@@ -2256,10 +2274,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B66" t="s">
-        <x:v>194</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C66" t="s">
-        <x:v>130</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:3">
@@ -2267,10 +2285,10 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B67" t="s">
-        <x:v>186</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C67" t="s">
-        <x:v>129</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:3">
@@ -2278,10 +2296,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B68" t="s">
-        <x:v>178</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C68" t="s">
-        <x:v>158</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:3">
@@ -2289,10 +2307,10 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B69" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="C69" t="s">
         <x:v>89</x:v>
-      </x:c>
-      <x:c r="C69" t="s">
-        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:3">
@@ -2300,10 +2318,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B70" t="s">
-        <x:v>191</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="C70" t="s">
-        <x:v>149</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:3">
@@ -2311,10 +2329,10 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B71" t="s">
-        <x:v>100</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C71" t="s">
-        <x:v>177</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:3">
@@ -2322,10 +2340,10 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B72" t="s">
-        <x:v>110</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C72" t="s">
-        <x:v>195</x:v>
+        <x:v>197</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:3">
@@ -2333,10 +2351,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B73" t="s">
-        <x:v>113</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="C73" t="s">
-        <x:v>162</x:v>
+        <x:v>208</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:3">
@@ -2344,10 +2362,10 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B74" t="s">
-        <x:v>61</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C74" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:3">
@@ -2355,10 +2373,10 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B75" t="s">
-        <x:v>112</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="C75" t="s">
-        <x:v>169</x:v>
+        <x:v>214</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:3">
@@ -2366,10 +2384,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="B76" t="s">
-        <x:v>91</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C76" t="s">
-        <x:v>161</x:v>
+        <x:v>218</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:8">
@@ -2377,10 +2395,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B77" t="s">
-        <x:v>209</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="C77" t="s">
-        <x:v>144</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G77" s="2"/>
       <x:c r="H77" s="2"/>
@@ -2390,10 +2408,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B78" t="s">
-        <x:v>242</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C78" t="s">
-        <x:v>24</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G78" s="2"/>
       <x:c r="H78" s="2"/>
@@ -2403,10 +2421,10 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B79" t="s">
-        <x:v>236</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="C79" t="s">
-        <x:v>140</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="G79" s="2"/>
       <x:c r="H79" s="2"/>
@@ -2416,10 +2434,10 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B80" t="s">
-        <x:v>237</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C80" t="s">
-        <x:v>152</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G80" s="2"/>
       <x:c r="H80" s="2"/>
@@ -2429,10 +2447,10 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="B81" t="s">
-        <x:v>238</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="C81" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G81" s="2"/>
       <x:c r="H81" s="2"/>
@@ -2442,10 +2460,10 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B82" t="s">
-        <x:v>243</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="C82" t="s">
-        <x:v>25</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G82" s="2"/>
       <x:c r="H82" s="2"/>
@@ -2455,10 +2473,10 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B83" t="s">
-        <x:v>239</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="C83" t="s">
-        <x:v>196</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G83" s="2"/>
       <x:c r="H83" s="2"/>
@@ -2468,10 +2486,10 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B84" t="s">
-        <x:v>241</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C84" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G84" s="2"/>
       <x:c r="H84" s="2"/>
@@ -2481,10 +2499,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B85" t="s">
-        <x:v>240</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C85" t="s">
-        <x:v>202</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="G85" s="2"/>
       <x:c r="H85" s="2"/>
@@ -2494,10 +2512,10 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B86" t="s">
-        <x:v>235</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C86" t="s">
-        <x:v>201</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G86" s="2"/>
       <x:c r="H86" s="2"/>
@@ -2507,10 +2525,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B87" t="s">
-        <x:v>244</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C87" t="s">
-        <x:v>213</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="G87" s="2"/>
       <x:c r="H87" s="2"/>
@@ -2520,10 +2538,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B88" t="s">
-        <x:v>245</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C88" t="s">
-        <x:v>17</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G88" s="2"/>
       <x:c r="H88" s="2"/>
@@ -2533,10 +2551,10 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="B89" t="s">
-        <x:v>246</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C89" t="s">
-        <x:v>18</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G89" s="2"/>
       <x:c r="H89" s="2"/>
@@ -2546,10 +2564,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B90" t="s">
-        <x:v>231</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C90" t="s">
-        <x:v>210</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="G90" s="2"/>
       <x:c r="H90" s="2"/>
@@ -2559,10 +2577,10 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="B91" t="s">
-        <x:v>234</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C91" t="s">
-        <x:v>65</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G91" s="2"/>
       <x:c r="H91" s="2"/>
@@ -2572,10 +2590,10 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="B92" t="s">
-        <x:v>232</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C92" t="s">
-        <x:v>199</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="G92" s="2"/>
       <x:c r="H92" s="2"/>
@@ -2585,10 +2603,10 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="B93" t="s">
-        <x:v>230</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C93" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="G93" s="2"/>
       <x:c r="H93" s="2"/>
@@ -2598,10 +2616,10 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="B94" t="s">
-        <x:v>233</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C94" s="2" t="s">
-        <x:v>78</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="G94" s="2"/>
       <x:c r="H94" s="2"/>
@@ -2611,10 +2629,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B95" t="s">
-        <x:v>229</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C95" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G95" s="2"/>
       <x:c r="H95" s="2"/>
@@ -2624,10 +2642,10 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="B96" t="s">
-        <x:v>216</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="C96" t="s">
-        <x:v>219</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="G96" s="2"/>
       <x:c r="H96" s="2"/>
@@ -2637,10 +2655,10 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="B97" t="s">
-        <x:v>215</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C97" t="s">
-        <x:v>211</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="G97" s="2"/>
       <x:c r="H97" s="2"/>
@@ -2650,10 +2668,10 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="B98" t="s">
-        <x:v>217</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="C98" t="s">
-        <x:v>223</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="G98" s="2"/>
       <x:c r="H98" s="2"/>
@@ -2663,10 +2681,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B99" t="s">
-        <x:v>218</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="C99" t="s">
-        <x:v>203</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="G99" s="2"/>
       <x:c r="H99" s="2"/>
@@ -2676,10 +2694,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="B100" t="s">
-        <x:v>0</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C100" t="s">
-        <x:v>88</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:3">
@@ -2687,10 +2705,10 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="B101" t="s">
-        <x:v>67</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C101" t="s">
-        <x:v>225</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:3">
@@ -2698,10 +2716,10 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="B102" s="2" t="s">
-        <x:v>226</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="C102" t="s">
-        <x:v>58</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:3">
@@ -2709,10 +2727,10 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="B103" s="2" t="s">
-        <x:v>228</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C103" t="s">
-        <x:v>57</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:3">
@@ -2720,10 +2738,10 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="B104" s="2" t="s">
-        <x:v>212</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C104" t="s">
-        <x:v>205</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:3">
@@ -2731,10 +2749,10 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="B105" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="C105" t="s">
-        <x:v>214</x:v>
+        <x:v>123</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:3">
@@ -2742,10 +2760,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B106" s="2" t="s">
-        <x:v>66</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="C106" t="s">
-        <x:v>86</x:v>
+        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:3">
@@ -2753,10 +2771,10 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="B107" s="2" t="s">
-        <x:v>68</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C107" t="s">
-        <x:v>227</x:v>
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:3">
@@ -2764,10 +2782,10 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="B108" s="2" t="s">
-        <x:v>248</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C108" t="s">
-        <x:v>207</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:3">
@@ -2775,10 +2793,10 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="B109" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C109" t="s">
-        <x:v>3</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:3">
@@ -2786,10 +2804,10 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="B110" s="2" t="s">
-        <x:v>198</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="C110" t="s">
-        <x:v>222</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:3">
@@ -2797,10 +2815,10 @@
         <x:v>109</x:v>
       </x:c>
       <x:c r="B111" s="2" t="s">
-        <x:v>220</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C111" t="s">
-        <x:v>2</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:3">
@@ -2808,10 +2826,10 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="B112" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C112" t="s">
-        <x:v>85</x:v>
+        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:3">
@@ -2819,10 +2837,10 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="B113" s="2" t="s">
-        <x:v>224</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="C113" t="s">
-        <x:v>82</x:v>
+        <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:3">
@@ -2830,10 +2848,10 @@
         <x:v>112</x:v>
       </x:c>
       <x:c r="B114" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="C114" t="s">
-        <x:v>206</x:v>
+        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:3">
@@ -2841,10 +2859,10 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="B115" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C115" t="s">
-        <x:v>83</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:3">
@@ -2852,10 +2870,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B116" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="C116" t="s">
-        <x:v>221</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:3">
@@ -2863,10 +2881,10 @@
         <x:v>115</x:v>
       </x:c>
       <x:c r="B117" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C117" t="s">
-        <x:v>81</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:3">
@@ -2874,10 +2892,10 @@
         <x:v>116</x:v>
       </x:c>
       <x:c r="B118" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="C118" t="s">
-        <x:v>84</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:3">
@@ -2885,10 +2903,10 @@
         <x:v>117</x:v>
       </x:c>
       <x:c r="B119" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C119" t="s">
-        <x:v>250</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:3">
@@ -2896,10 +2914,10 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="B120" s="2" t="s">
-        <x:v>247</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="C120" t="s">
-        <x:v>208</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:3">
@@ -2907,10 +2925,10 @@
         <x:v>119</x:v>
       </x:c>
       <x:c r="B121" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C121" t="s">
-        <x:v>4</x:v>
+        <x:v>157</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:3">
@@ -2918,10 +2936,10 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="B122" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="C122" t="s">
-        <x:v>87</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:3">
@@ -2929,10 +2947,10 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="B123" s="2" t="s">
-        <x:v>200</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="C123" t="s">
-        <x:v>252</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:3">
@@ -2940,10 +2958,10 @@
         <x:v>122</x:v>
       </x:c>
       <x:c r="B124" s="2" t="s">
-        <x:v>70</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C124" t="s">
-        <x:v>251</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:3">
@@ -2951,10 +2969,10 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="B125" s="2" t="s">
-        <x:v>74</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C125" s="3" t="s">
-        <x:v>253</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:3">
@@ -2962,10 +2980,10 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="B126" s="2" t="s">
-        <x:v>77</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="C126" s="3" t="s">
-        <x:v>204</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:3">
@@ -2973,10 +2991,10 @@
         <x:v>125</x:v>
       </x:c>
       <x:c r="B127" s="2" t="s">
-        <x:v>71</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C127" t="s">
-        <x:v>197</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:3">
@@ -2984,10 +3002,10 @@
         <x:v>126</x:v>
       </x:c>
       <x:c r="B128" s="2" t="s">
-        <x:v>73</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C128" t="s">
-        <x:v>1</x:v>
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:3">
@@ -2995,10 +3013,10 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="B129" s="2" t="s">
-        <x:v>72</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C129" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:3">
@@ -3006,10 +3024,10 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="B130" s="2" t="s">
-        <x:v>75</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C130" t="s">
-        <x:v>80</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:3">
@@ -3017,10 +3035,10 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="B131" s="2" t="s">
-        <x:v>76</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="C131" t="s">
-        <x:v>254</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:3">
@@ -3028,10 +3046,43 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="B132" s="2" t="s">
-        <x:v>69</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C132" s="3" t="s">
-        <x:v>249</x:v>
+        <x:v>126</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" spans="1:3">
+      <x:c r="A133">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="B133" s="2" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C133" t="s">
+        <x:v>259</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" spans="1:3">
+      <x:c r="A134">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B134" s="2" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C134" s="3" t="s">
+        <x:v>260</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" spans="1:3">
+      <x:c r="A135">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="B135" s="2" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C135" s="3" t="s">
+        <x:v>109</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/morpg/morpg/Assets/TableData/Table_Text.xlsx
+++ b/morpg/morpg/Assets/TableData/Table_Text.xlsx
@@ -21,787 +21,787 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="261">
   <x:si>
+    <x:t>Cocruwa013_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa009_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa010_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa005_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa001_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa008_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GaremenTooskaDin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa006_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa011_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마법의 신, 제샤스 데이틴의 일곱 제자들이 일으킨 내전. 이로 인해 세상의 모든 기록이 소실되어 사실상 모든 것이 초기화되었다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제 와서는 이 세상에 절대유일한 '핏빛혈족의 유일한 생존자' 무시무시한 이능력을 지니고 있지만 그가 지닌 이능력의 정체를 아는 자를 이제는 찾을 수 없다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:피를 입는 자. '본세계'와 '역세계'를 모두 포함해서도 비슷한 수준의 신체능력을 가진 존재를 찾기 힘들 정도로 압도적인 신체능력을 가지고 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'본세계'와 '역세계'를 잇는 유일한 물리적 이동공간.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>창조신 'OM'이 창조한 초심극점 너머의 다른 세상.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>창조신 'NM'이 창조한 11개로 겹쳐진 우리의 세상.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rodec</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Unknown</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Human</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sandora</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코크루와</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Redinin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대마도사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>save</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Head</x:t>
+  </x:si>
+  <x:si>
+    <x:t>강령술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Toorka</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마족 마법사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카루크 뷘젠트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Selena</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Index</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rogue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>귀걸이(우)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>menu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>exit</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소환술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Leather</x:t>
+  </x:si>
+  <x:si>
+    <x:t>반지(좌)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불러오기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그렌 포모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Species</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이레안 소린</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대마도전쟁</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cloth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연금술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종족전쟁</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Comment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>option</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초심극점</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cocruwa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kalapok</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마족 전사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>산도라 태생</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Warrior</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Perth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Machine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종족&amp;직업</x:t>
+  </x:si>
+  <x:si>
+    <x:t>title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새 시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Teemole</x:t>
+  </x:si>
+  <x:si>
+    <x:t>load</x:t>
+  </x:si>
+  <x:si>
+    <x:t>귀걸이(좌)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라우톤 윈너</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Renod</x:t>
+  </x:si>
+  <x:si>
+    <x:t>newgame</x:t>
+  </x:si>
+  <x:si>
+    <x:t>긴가르시온</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gloves</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Badrak</x:t>
+  </x:si>
+  <x:si>
+    <x:t>history</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dragon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Demon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Korean</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에를로네</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Priest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Archer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>위대한 과실</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Plate</x:t>
+  </x:si>
+  <x:si>
+    <x:t>반지(우)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Array</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타이틀로 이동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>copy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종말전쟁</x:t>
+  </x:si>
+  <x:si>
+    <x:t>?????</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ehrlone</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타르타로스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나로사 포모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불튼 카존</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Armor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이어하기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Boots</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Weapon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>term</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:금속왕. 긴가르시온이 조립한 완전 기계인간 다만 이 세상에서 유일하게 전신이 '완벽한 신의 금속'으로 이뤄져서 모든 것을 무시할 수준의 방어력을 지니고 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 대장. 전투에 필요한 전반적인 능력을 두루 갖춘 氷계열 원거리 딜러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 공격보다 정찰에 특화된 공격력보다는 연타에 치중한 風계열 서포터.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 지닌 능력 중 대부분이 상처를 치유하고 아군을 버프, 적을 디버프하는 水계열 후방 서포터.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 불튼이 버금가는 탱킹 능력에 '피를 입는 자'에 버금하는 물리력을 지닌 雷계열 근거리 딜러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term007_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:현명한 현자. 모든 코크루와 중 유일의 비전투원. 다만 이제는 기억하는 사람도 없는 '본카 일족'의 족장 '짐토'로써 사실상 이 세상의 모든 학문과 기술은 그로부터 비롯된 것이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무직</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>티모르</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목걸이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마법사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라우톤</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나로사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가레멘</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>역사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>메뉴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>궁수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신발</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장갑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가죽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>판금</x:t>
+  </x:si>
+  <x:si>
+    <x:t>역세계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>천</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Job</x:t>
+  </x:si>
+  <x:si>
+    <x:t>용어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>본세계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레노드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>성직자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초월자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>셀레나</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카루크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>암살자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로데크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>투르카</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레디닌</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>직업</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불튼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도감</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그렌</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도적</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장비</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마왕족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>바드락</x:t>
+  </x:si>
+  <x:si>
+    <x:t>페르스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>갑옷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>드래곤</x:t>
+  </x:si>
+  <x:si>
+    <x:t>머리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이레안</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DemonFighter</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RoutonWinner</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이라 모스 강제 개폐 사건</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term006_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KaroukWingent</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term005_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>???????????????</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RightEarring</x:t>
+  </x:si>
+  <x:si>
+    <x:t>encyclopedia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term003_Title</x:t>
+  </x:si>
+  <x:si>
     <x:t>Term007_Title</x:t>
   </x:si>
   <x:si>
+    <x:t>Term004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전 세계에서도 극히 발견하기 어려웠던 과실. 먹는 이의 모든 질병과 상처를 회복해주고, 육체를 가장 건강하던 때로 고정하며 새로운 수명을 하사한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써 '구음절맥'을 갖고 태어난 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>드래곤을 포함해도 모든 종족 중에서는 물리력 최강의 종족 '바드락'의 생존자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써 '태양절맥'을 갖고 태어난 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'종말전쟁'이 끝난 이후의 시대가 되며 사실상 유명무실한 용어가 되어 사실상 강력한 힘을 지닌 '초월자'들을 일컫는 용어가 되었다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'본세계' 내에서 최초로 기록된 내전. 이로 인해 '불의 종족' 카르툼이 절멸하였다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 바다의 종족 '셀레나'의 생존자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'본세계' 내에서, '종말전쟁'의 결말을 지켜보던 강력한 존재들을 일컫는 용어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 창공의 종족 '투르카'의 생존자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 대지의 종족 '티모르'의 생존저.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 능력 중 대부분이 공격에 치중된 火계열 중거리 딜러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'본세계' 내의 다른 10개의 세계와의 연락을 차단했음에도 가장 독자적인 업적을 이룩한 대륙.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>평화로운 시기에도 전 세계에 그 개체 수가 5마리를 넘기지 못하던 이 세상 유일의 '초소수종'</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:암흑대제. 이 세상에서 유일하게 힘을 비축하는 시간에 비례하여 무한히 강해질 수 있는 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 자가방어와 자가치유에 치중된 地계열 순수 탱커.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:시간의 마왕. 우리의 세상인 '본세계'와 '역세계'에서도 하나 이상을 찾아볼 수 없는 절대유일의 시간 능력자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이 세상 모든 것을 중독시키는 '페이튼'에 중독되어 스스로 의사를 갖고 움직이기 시작한 종족 '래머'의 마지막 생존자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그의 일정범위에 존재하는 모든 사물은 점점 느려지기  시작하고 그 본인은 그 속도만큼 점점 빨라진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'아키르고 베니아'가 아닌 때에 '이라 모스'를 개설한 충격으로 '본세계' 바깥의 세상이 무너져버린 사건.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>144년을 주기로 돌아오는 초자연 현상. 이 기간 중에는 성공적인 '이라 모스'의 개폐가 가능해진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gingarsion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LeftEarring</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Necklace</x:t>
+  </x:si>
+  <x:si>
+    <x:t>버그리포트 바로가기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LeftRing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IreanSorin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>헤디 벤만 오프 모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tartaros</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가레멘 투스카 딘</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Equipment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bugreport</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hidden001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아키르고 베니아</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DemonMage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Archmage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hidden002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Summoner</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Assassin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Species&amp;Job</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RightRIng</x:t>
+  </x:si>
+  <x:si>
+    <x:t>notEmployed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NarosaFomos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GrenFomos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CodeName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>continue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Alchemist</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BultonKajon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Necromancer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term007_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa010_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa013_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 그가 공격의사를 갖던 말던 그의 주변에 존재하는 것만으로도 해독이 불가능한 '페이튼'에 중독되어 모든 존재가 소멸한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:유령왕. 태생적으로 '산도라의 후예'인 대마도사였으나 그의 스승인 '푸 그레이'가 서술한 '초마도의 서'를 이해하여 마법사 중 최강의 존재인 '초마도사'가 되었다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term005_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa006_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term001_Desc_001</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cocruwa012_Desc_002</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocruwa013_Desc_001</x:t>
-  </x:si>
-  <x:si>
     <x:t>Cocruwa011_Desc_002</x:t>
   </x:si>
   <x:si>
+    <x:t>Cocruwa008_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Desc_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa002_Desc_001</x:t>
+  </x:si>
+  <x:si>
     <x:t>History002_Desc_001</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocruwa010_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa009_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa001_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term007_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마법의 신, 제샤스 데이틴의 일곱 제자들이 일으킨 내전. 이로 인해 세상의 모든 기록이 소실되어 사실상 모든 것이 초기화되었다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이제 와서는 이 세상에 절대유일한 '핏빛혈족의 유일한 생존자' 무시무시한 이능력을 지니고 있지만 그가 지닌 이능력의 정체를 아는 자를 이제는 찾을 수 없다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:피를 입는 자. '본세계'와 '역세계'를 모두 포함해서도 비슷한 수준의 신체능력을 가진 존재를 찾기 힘들 정도로 압도적인 신체능력을 가지고 있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>긴가르시온</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타르타로스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Renod</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Teemole</x:t>
-  </x:si>
-  <x:si>
-    <x:t>새 시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>귀걸이(좌)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>load</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gloves</x:t>
-  </x:si>
-  <x:si>
-    <x:t>newgame</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라우톤 윈너</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ehrlone</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Dragon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Demon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Weapon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Array</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이어하기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타이틀로 이동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>history</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Plate</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Korean</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Badrak</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나로사 포모스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>반지(우)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>위대한 과실</x:t>
-  </x:si>
-  <x:si>
-    <x:t>menu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>귀걸이(우)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Boots</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Species</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Perth</x:t>
-  </x:si>
-  <x:si>
-    <x:t>반지(좌)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이레안 소린</x:t>
-  </x:si>
-  <x:si>
-    <x:t>term</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종족&amp;직업</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Armor</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에를로네</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cocruwa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마족 전사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무직</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마법사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>저장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라우톤</x:t>
-  </x:si>
-  <x:si>
-    <x:t>티모르</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신발</x:t>
-  </x:si>
-  <x:si>
-    <x:t>천</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나로사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>판금</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가죽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>목걸이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>메뉴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>역사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>역세계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>궁수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장갑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가레멘</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불튼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도적</x:t>
-  </x:si>
-  <x:si>
-    <x:t>직업</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Job</x:t>
-  </x:si>
-  <x:si>
-    <x:t>투르카</x:t>
-  </x:si>
-  <x:si>
-    <x:t>셀레나</x:t>
-  </x:si>
-  <x:si>
-    <x:t>로데크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>드래곤</x:t>
-  </x:si>
-  <x:si>
-    <x:t>갑옷</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도감</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레디닌</x:t>
-  </x:si>
-  <x:si>
-    <x:t>암살자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>바드락</x:t>
-  </x:si>
-  <x:si>
-    <x:t>용어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레노드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장비</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마왕족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>머리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그렌</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이레안</x:t>
-  </x:si>
-  <x:si>
-    <x:t>본세계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카루크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>초월자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>페르스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>성직자</x:t>
+    <x:t>History004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa009_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa007_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa007_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa005_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa008_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa009_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term006_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa010_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa011_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa002_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa007_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa013_Title</x:t>
   </x:si>
   <x:si>
     <x:t>초심극점을 마주하고 바라보고 있는 다른 세상, '역세계'와의 전쟁.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term007_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:현명한 현자. 모든 코크루와 중 유일의 비전투원. 다만 이제는 기억하는 사람도 없는 '본카 일족'의 족장 '짐토'로써 사실상 이 세상의 모든 학문과 기술은 그로부터 비롯된 것이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'본세계'와 '역세계'를 잇는 유일한 물리적 이동공간.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>창조신 'OM'이 창조한 초심극점 너머의 다른 세상.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>창조신 'NM'이 창조한 11개로 겹쳐진 우리의 세상.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'종말전쟁'이 끝난 이후의 시대가 되며 사실상 유명무실한 용어가 되어 사실상 강력한 힘을 지닌 '초월자'들을 일컫는 용어가 되었다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전 세계에서도 극히 발견하기 어려웠던 과실. 먹는 이의 모든 질병과 상처를 회복해주고, 육체를 가장 건강하던 때로 고정하며 새로운 수명을 하사한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 자가방어와 자가치유에 치중된 地계열 순수 탱커.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>평화로운 시기에도 전 세계에 그 개체 수가 5마리를 넘기지 못하던 이 세상 유일의 '초소수종'</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 능력 중 대부분이 공격에 치중된 火계열 중거리 딜러.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'본세계' 내의 다른 10개의 세계와의 연락을 차단했음에도 가장 독자적인 업적을 이룩한 대륙.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:암흑대제. 이 세상에서 유일하게 힘을 비축하는 시간에 비례하여 무한히 강해질 수 있는 존재.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써 '태양절맥'을 갖고 태어난 존재.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>드래곤을 포함해도 모든 종족 중에서는 물리력 최강의 종족 '바드락'의 생존자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써 '구음절맥'을 갖고 태어난 존재.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 창공의 종족 '투르카'의 생존자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 대지의 종족 '티모르'의 생존저.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'본세계' 내에서 최초로 기록된 내전. 이로 인해 '불의 종족' 카르툼이 절멸하였다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 바다의 종족 '셀레나'의 생존자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:금속왕. 긴가르시온이 조립한 완전 기계인간 다만 이 세상에서 유일하게 전신이 '완벽한 신의 금속'으로 이뤄져서 모든 것을 무시할 수준의 방어력을 지니고 있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그의 일정범위에 존재하는 모든 사물은 점점 느려지기  시작하고 그 본인은 그 속도만큼 점점 빨라진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>144년을 주기로 돌아오는 초자연 현상. 이 기간 중에는 성공적인 '이라 모스'의 개폐가 가능해진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'아키르고 베니아'가 아닌 때에 '이라 모스'를 개설한 충격으로 '본세계' 바깥의 세상이 무너져린 사건.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term005_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term002_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RoutonWinner</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term004_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term001_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>encyclopedia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KaroukWingent</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이라 모스 강제 개폐 사건</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term006_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>???????????????</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RightEarring</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DemonFighter</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term003_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종말전쟁</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종족전쟁</x:t>
-  </x:si>
-  <x:si>
-    <x:t>헤디 벤만 오프 모스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Archmage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gingarsion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LeftEarring</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tartaros</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IreanSorin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hidden001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Summoner</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Necklace</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Equipment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bugreport</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Assassin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가레멘 투스카 딘</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 불튼이 버금가는 탱킹 능력에 '피를 입는 자'에 버금하는 물리력을 지닌 雷계열 근거리 딜러.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 지닌 능력 중 대부분이 상처를 치유하고 아군을 버프, 적을 디버프하는 水계열 후방 서포터.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 그가 공격의사를 갖던 말던 그의 주변에 존재하는 것만으로도 해독이 불가능한 '페이튼'에 중독되어 모든 존재가 소멸한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:유령왕. 태생적으로 '산도라의 후예'인 대마도사였으나 그의 스승인 '푸 그레이'가 서술한 '초마도의 서'를 이해하여 마법사 중 최강의 존재인 '초마도사'가 되었다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 공격보다 정찰에 특화된 공격력보다는 연타에 치중한 風계열 서포터.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 대장. 전투에 필요한 전반적인 능력을 두루 갖춘 氷계열 원거리 딜러.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이 세상 모든 것을 중독시키는 '페이튼'에 중독되어 스스로 의사를 갖고 움직이기 시작한 종족 '래머'의 마지막 생존자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:시간의 마왕. 우리의 세상인 '본세계'와 '역세계'에서도 하나 이상을 찾아볼 수 없는 절대유일의 시간 능력자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아키르고 베니아</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa008_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa001_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa011_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History003_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa013_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa004_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa005_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa010_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa006_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GaremenTooskaDin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa007_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa009_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term002_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term006_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term003_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History001_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term005_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History004_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cloth</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kalapok</x:t>
-  </x:si>
-  <x:si>
-    <x:t>?????</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Machine</x:t>
-  </x:si>
-  <x:si>
-    <x:t>title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Priest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불튼 카존</x:t>
-  </x:si>
-  <x:si>
-    <x:t>copy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>산도라 태생</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Warrior</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Leather</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Archer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rogue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연금술사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>초심극점</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대마도전쟁</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소환술사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Unknown</x:t>
-  </x:si>
-  <x:si>
-    <x:t>option</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불러오기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Index</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Selena</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Toorka</x:t>
-  </x:si>
-  <x:si>
-    <x:t>save</x:t>
-  </x:si>
-  <x:si>
-    <x:t>강령술사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Comment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그렌 포모스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Redinin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Human</x:t>
-  </x:si>
-  <x:si>
-    <x:t>exit</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마족 마법사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rodec</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sandora</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Head</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대마도사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카루크 뷘젠트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RightRIng</x:t>
-  </x:si>
-  <x:si>
-    <x:t>버그리포트 바로가기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CodeName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hidden002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>continue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GrenFomos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DemonMage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LeftRing</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Species&amp;Job</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Necromancer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BultonKajon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>notEmployed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NarosaFomos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Alchemist</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa003_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa007_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa005_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa001_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term001_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa010_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History003_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History001_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa004_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa008_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History002_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa009_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa002_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa008_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term004_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa003_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa002_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History004_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Desc_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa007_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa006_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa011_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa002_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa013_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코크루와</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'본세계' 내에서, '종말전쟁'의 결말을 지켜보던 강력한 존재들을 일컫는 용어.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -875,7 +875,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="4">
+  <x:cellXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
@@ -886,6 +886,9 @@
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
@@ -1551,7 +1554,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:H135"/>
+  <x:dimension ref="A1:N135"/>
   <x:sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="16.39999999999999857891"/>
   <x:cols>
     <x:col min="1" max="1" width="8.796875" bestFit="1" customWidth="1"/>
@@ -1560,31 +1563,31 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>204</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>222</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D2" s="1"/>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -1592,7 +1595,7 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B4" s="1"/>
       <x:c r="C4" s="1"/>
@@ -1603,10 +1606,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" t="s">
-        <x:v>21</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C5" t="s">
-        <x:v>16</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
@@ -1614,10 +1617,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" t="s">
-        <x:v>224</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="C6" t="s">
-        <x:v>28</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
@@ -1625,10 +1628,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" t="s">
-        <x:v>202</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C7" t="s">
-        <x:v>86</x:v>
+        <x:v>146</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
@@ -1636,10 +1639,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" t="s">
-        <x:v>213</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C8" t="s">
-        <x:v>51</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
@@ -1647,10 +1650,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B9" t="s">
-        <x:v>207</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C9" t="s">
-        <x:v>58</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
@@ -1658,10 +1661,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B10" t="s">
-        <x:v>18</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C10" t="s">
-        <x:v>203</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
@@ -1669,10 +1672,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B11" t="s">
-        <x:v>190</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C11" t="s">
-        <x:v>50</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
@@ -1680,10 +1683,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B12" t="s">
-        <x:v>37</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C12" t="s">
-        <x:v>68</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
@@ -1691,10 +1694,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B13" t="s">
-        <x:v>187</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C13" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
@@ -1702,10 +1705,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B14" t="s">
-        <x:v>152</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="C14" t="s">
-        <x:v>221</x:v>
+        <x:v>193</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
@@ -1713,10 +1716,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B15" t="s">
-        <x:v>132</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="C15" t="s">
-        <x:v>87</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
@@ -1724,10 +1727,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B16" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C16" t="s">
-        <x:v>100</x:v>
+        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
@@ -1735,10 +1738,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B17" t="s">
-        <x:v>44</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C17" t="s">
-        <x:v>91</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
@@ -1746,10 +1749,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B18" t="s">
-        <x:v>30</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C18" t="s">
-        <x:v>69</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
@@ -1757,10 +1760,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B19" t="s">
-        <x:v>14</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C19" t="s">
-        <x:v>92</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
@@ -1768,10 +1771,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B20" t="s">
-        <x:v>146</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="C20" t="s">
-        <x:v>13</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
@@ -1779,10 +1782,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B21" t="s">
-        <x:v>211</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C21" t="s">
-        <x:v>88</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
@@ -1790,10 +1793,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B22" t="s">
-        <x:v>41</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C22" t="s">
-        <x:v>101</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
@@ -1801,10 +1804,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B23" t="s">
-        <x:v>23</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C23" t="s">
-        <x:v>47</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
@@ -1812,10 +1815,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B24" t="s">
-        <x:v>144</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C24" t="s">
-        <x:v>12</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
@@ -1823,10 +1826,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B25" t="s">
-        <x:v>225</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="C25" t="s">
-        <x:v>210</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
@@ -1834,10 +1837,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B26" t="s">
-        <x:v>232</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="C26" t="s">
-        <x:v>34</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
@@ -1845,7 +1848,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B27" t="s">
-        <x:v>147</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C27" t="s">
         <x:v>43</x:v>
@@ -1856,10 +1859,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B28" t="s">
-        <x:v>230</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="C28" t="s">
-        <x:v>189</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3">
@@ -1867,10 +1870,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B29" t="s">
-        <x:v>133</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C29" t="s">
-        <x:v>219</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">
@@ -1878,10 +1881,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B30" t="s">
-        <x:v>129</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="C30" t="s">
-        <x:v>22</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
@@ -1889,10 +1892,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B31" t="s">
-        <x:v>174</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C31" t="s">
-        <x:v>154</x:v>
+        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:3">
@@ -1900,10 +1903,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B32" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C32" t="s">
-        <x:v>54</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:3">
@@ -1911,10 +1914,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B33" t="s">
-        <x:v>80</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C33" t="s">
-        <x:v>79</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:3">
@@ -1922,10 +1925,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B34" t="s">
-        <x:v>148</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C34" t="s">
-        <x:v>185</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:3">
@@ -1933,10 +1936,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B35" t="s">
-        <x:v>223</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C35" t="s">
-        <x:v>136</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:3">
@@ -1944,10 +1947,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B36" t="s">
-        <x:v>231</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="C36" t="s">
-        <x:v>52</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:3">
@@ -1955,10 +1958,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B37" t="s">
-        <x:v>151</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C37" t="s">
-        <x:v>93</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:3">
@@ -1966,10 +1969,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B38" t="s">
-        <x:v>228</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="C38" t="s">
-        <x:v>45</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:3">
@@ -1977,10 +1980,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B39" t="s">
-        <x:v>183</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C39" t="s">
-        <x:v>63</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:3">
@@ -1988,10 +1991,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B40" t="s">
-        <x:v>194</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C40" t="s">
-        <x:v>66</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:3">
@@ -1999,10 +2002,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B41" t="s">
-        <x:v>31</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C41" t="s">
-        <x:v>65</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:3">
@@ -2010,10 +2013,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B42" t="s">
-        <x:v>26</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C42" t="s">
-        <x:v>59</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:3">
@@ -2021,10 +2024,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B43" t="s">
-        <x:v>217</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C43" t="s">
-        <x:v>95</x:v>
+        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:3">
@@ -2032,10 +2035,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B44" t="s">
-        <x:v>46</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C44" t="s">
-        <x:v>85</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:3">
@@ -2043,10 +2046,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B45" t="s">
-        <x:v>20</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C45" t="s">
-        <x:v>72</x:v>
+        <x:v>123</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:3">
@@ -2054,10 +2057,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B46" t="s">
-        <x:v>39</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C46" t="s">
-        <x:v>62</x:v>
+        <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:3">
@@ -2065,10 +2068,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B47" t="s">
-        <x:v>227</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C47" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:3">
@@ -2076,10 +2079,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B48" t="s">
-        <x:v>220</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="C48" t="s">
-        <x:v>35</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:3">
@@ -2087,10 +2090,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B49" t="s">
-        <x:v>145</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C49" t="s">
-        <x:v>17</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:3">
@@ -2098,10 +2101,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B50" t="s">
-        <x:v>137</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C50" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:3">
@@ -2109,10 +2112,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B51" t="s">
-        <x:v>150</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C51" t="s">
-        <x:v>67</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:3">
@@ -2120,10 +2123,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B52" s="2" t="s">
-        <x:v>212</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C52" t="s">
-        <x:v>57</x:v>
+        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:3">
@@ -2131,10 +2134,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B53" s="2" t="s">
-        <x:v>215</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C53" t="s">
-        <x:v>83</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:3">
@@ -2142,10 +2145,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B54" s="2" t="s">
-        <x:v>206</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C54" t="s">
-        <x:v>81</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:3">
@@ -2153,10 +2156,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B55" t="s">
-        <x:v>15</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C55" t="s">
-        <x:v>61</x:v>
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:3">
@@ -2164,10 +2167,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B56" t="s">
-        <x:v>205</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C56" t="s">
-        <x:v>82</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:3">
@@ -2175,10 +2178,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B57" t="s">
-        <x:v>33</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C57" t="s">
-        <x:v>90</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:3">
@@ -2186,10 +2189,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B58" t="s">
-        <x:v>186</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C58" t="s">
-        <x:v>56</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:3">
@@ -2197,10 +2200,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B59" t="s">
-        <x:v>25</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C59" t="s">
-        <x:v>75</x:v>
+        <x:v>134</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:3">
@@ -2208,10 +2211,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B60" t="s">
-        <x:v>216</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C60" t="s">
-        <x:v>191</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:3">
@@ -2219,10 +2222,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B61" t="s">
-        <x:v>24</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C61" t="s">
-        <x:v>84</x:v>
+        <x:v>153</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:3">
@@ -2230,10 +2233,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B62" t="s">
-        <x:v>184</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C62" t="s">
-        <x:v>94</x:v>
+        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:3">
@@ -2241,10 +2244,10 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B63" t="s">
-        <x:v>201</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C63" t="s">
-        <x:v>76</x:v>
+        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:3">
@@ -2252,10 +2255,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B64" t="s">
-        <x:v>231</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="C64" t="s">
-        <x:v>52</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:3">
@@ -2263,10 +2266,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B65" t="s">
-        <x:v>193</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C65" t="s">
-        <x:v>53</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:3">
@@ -2274,10 +2277,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B66" t="s">
-        <x:v>195</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C66" t="s">
-        <x:v>71</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:3">
@@ -2285,10 +2288,10 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B67" t="s">
-        <x:v>192</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C67" t="s">
-        <x:v>55</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:3">
@@ -2296,10 +2299,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B68" t="s">
-        <x:v>188</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C68" t="s">
-        <x:v>102</x:v>
+        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:3">
@@ -2307,10 +2310,10 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B69" t="s">
-        <x:v>153</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C69" t="s">
-        <x:v>89</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:3">
@@ -2318,10 +2321,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B70" t="s">
-        <x:v>196</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C70" t="s">
-        <x:v>78</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:3">
@@ -2329,10 +2332,10 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B71" t="s">
-        <x:v>149</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="C71" t="s">
-        <x:v>200</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:3">
@@ -2340,10 +2343,10 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B72" t="s">
-        <x:v>233</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C72" t="s">
-        <x:v>197</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:3">
@@ -2351,10 +2354,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B73" t="s">
-        <x:v>229</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C73" t="s">
-        <x:v>208</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:3">
@@ -2362,10 +2365,10 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B74" t="s">
-        <x:v>138</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C74" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:3">
@@ -2373,10 +2376,10 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B75" t="s">
-        <x:v>226</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C75" t="s">
-        <x:v>214</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:3">
@@ -2384,10 +2387,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="B76" t="s">
-        <x:v>143</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="C76" t="s">
-        <x:v>218</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:8">
@@ -2395,10 +2398,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B77" t="s">
-        <x:v>237</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C77" t="s">
-        <x:v>92</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G77" s="2"/>
       <x:c r="H77" s="2"/>
@@ -2408,10 +2411,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B78" t="s">
-        <x:v>257</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="C78" t="s">
-        <x:v>13</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="G78" s="2"/>
       <x:c r="H78" s="2"/>
@@ -2421,10 +2424,10 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B79" t="s">
-        <x:v>234</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="C79" t="s">
-        <x:v>88</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="G79" s="2"/>
       <x:c r="H79" s="2"/>
@@ -2434,10 +2437,10 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B80" t="s">
-        <x:v>242</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="C80" t="s">
-        <x:v>101</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="G80" s="2"/>
       <x:c r="H80" s="2"/>
@@ -2447,10 +2450,10 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="B81" t="s">
-        <x:v>236</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="C81" t="s">
-        <x:v>47</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="G81" s="2"/>
       <x:c r="H81" s="2"/>
@@ -2460,10 +2463,10 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B82" t="s">
-        <x:v>255</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C82" t="s">
-        <x:v>12</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="G82" s="2"/>
       <x:c r="H82" s="2"/>
@@ -2473,10 +2476,10 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B83" t="s">
-        <x:v>235</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C83" t="s">
-        <x:v>96</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="G83" s="2"/>
       <x:c r="H83" s="2"/>
@@ -2486,10 +2489,10 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B84" t="s">
-        <x:v>164</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C84" t="s">
-        <x:v>64</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G84" s="2"/>
       <x:c r="H84" s="2"/>
@@ -2499,10 +2502,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B85" t="s">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C85" t="s">
-        <x:v>97</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="G85" s="2"/>
       <x:c r="H85" s="2"/>
@@ -2512,10 +2515,10 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B86" t="s">
-        <x:v>239</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="C86" t="s">
-        <x:v>77</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="G86" s="2"/>
       <x:c r="H86" s="2"/>
@@ -2525,10 +2528,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B87" t="s">
-        <x:v>256</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="C87" t="s">
-        <x:v>99</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="G87" s="2"/>
       <x:c r="H87" s="2"/>
@@ -2538,10 +2541,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B88" t="s">
-        <x:v>254</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="C88" t="s">
-        <x:v>60</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="G88" s="2"/>
       <x:c r="H88" s="2"/>
@@ -2551,10 +2554,10 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="B89" t="s">
-        <x:v>258</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="C89" t="s">
-        <x:v>73</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="G89" s="2"/>
       <x:c r="H89" s="2"/>
@@ -2564,10 +2567,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B90" t="s">
-        <x:v>131</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C90" t="s">
-        <x:v>98</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="G90" s="2"/>
       <x:c r="H90" s="2"/>
@@ -2577,10 +2580,10 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="B91" t="s">
-        <x:v>128</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C91" t="s">
-        <x:v>70</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="G91" s="2"/>
       <x:c r="H91" s="2"/>
@@ -2590,10 +2593,10 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="B92" t="s">
-        <x:v>139</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="C92" t="s">
-        <x:v>198</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G92" s="2"/>
       <x:c r="H92" s="2"/>
@@ -2603,10 +2606,10 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="B93" t="s">
-        <x:v>130</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="C93" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="G93" s="2"/>
       <x:c r="H93" s="2"/>
@@ -2616,10 +2619,10 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="B94" t="s">
-        <x:v>127</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C94" s="2" t="s">
-        <x:v>142</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="G94" s="2"/>
       <x:c r="H94" s="2"/>
@@ -2629,10 +2632,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B95" t="s">
-        <x:v>135</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C95" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="G95" s="2"/>
       <x:c r="H95" s="2"/>
@@ -2642,10 +2645,10 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="B96" t="s">
-        <x:v>241</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C96" t="s">
-        <x:v>141</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G96" s="2"/>
       <x:c r="H96" s="2"/>
@@ -2655,10 +2658,10 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="B97" t="s">
-        <x:v>244</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C97" t="s">
-        <x:v>199</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="G97" s="2"/>
       <x:c r="H97" s="2"/>
@@ -2668,10 +2671,10 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="B98" t="s">
-        <x:v>240</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="C98" t="s">
-        <x:v>140</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="G98" s="2"/>
       <x:c r="H98" s="2"/>
@@ -2681,10 +2684,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B99" t="s">
-        <x:v>251</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C99" t="s">
-        <x:v>134</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="G99" s="2"/>
       <x:c r="H99" s="2"/>
@@ -2694,10 +2697,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="B100" t="s">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C100" t="s">
-        <x:v>162</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:3">
@@ -2705,10 +2708,10 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="B101" t="s">
-        <x:v>165</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C101" t="s">
-        <x:v>124</x:v>
+        <x:v>187</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:3">
@@ -2716,10 +2719,10 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="B102" s="2" t="s">
-        <x:v>246</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="C102" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:3">
@@ -2727,10 +2730,10 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="B103" s="2" t="s">
-        <x:v>250</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C103" t="s">
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:3">
@@ -2738,10 +2741,10 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="B104" s="2" t="s">
-        <x:v>249</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="C104" t="s">
-        <x:v>115</x:v>
+        <x:v>183</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:3">
@@ -2749,10 +2752,10 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="B105" s="2" t="s">
-        <x:v>170</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C105" t="s">
-        <x:v>123</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:3">
@@ -2760,10 +2763,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B106" s="2" t="s">
-        <x:v>171</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C106" t="s">
-        <x:v>158</x:v>
+        <x:v>222</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:3">
@@ -2771,10 +2774,10 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="B107" s="2" t="s">
-        <x:v>173</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C107" t="s">
-        <x:v>105</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:3">
@@ -2782,10 +2785,10 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="B108" s="2" t="s">
-        <x:v>253</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C108" t="s">
-        <x:v>113</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:3">
@@ -2793,10 +2796,10 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="B109" s="2" t="s">
-        <x:v>175</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C109" t="s">
-        <x:v>116</x:v>
+        <x:v>173</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:3">
@@ -2804,10 +2807,10 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="B110" s="2" t="s">
-        <x:v>247</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="C110" t="s">
-        <x:v>160</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:3">
@@ -2815,10 +2818,10 @@
         <x:v>109</x:v>
       </x:c>
       <x:c r="B111" s="2" t="s">
-        <x:v>243</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C111" t="s">
-        <x:v>118</x:v>
+        <x:v>171</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:3">
@@ -2826,10 +2829,10 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="B112" s="2" t="s">
-        <x:v>176</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="C112" t="s">
-        <x:v>156</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:3">
@@ -2837,10 +2840,10 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="B113" s="2" t="s">
-        <x:v>245</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="C113" t="s">
-        <x:v>122</x:v>
+        <x:v>176</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:3">
@@ -2848,10 +2851,10 @@
         <x:v>112</x:v>
       </x:c>
       <x:c r="B114" s="2" t="s">
-        <x:v>172</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C114" t="s">
-        <x:v>111</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:3">
@@ -2859,10 +2862,10 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="B115" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="C115" t="s">
-        <x:v>120</x:v>
+        <x:v>179</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:3">
@@ -2870,10 +2873,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B116" s="2" t="s">
-        <x:v>166</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C116" t="s">
-        <x:v>159</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:3">
@@ -2881,10 +2884,10 @@
         <x:v>115</x:v>
       </x:c>
       <x:c r="B117" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="C117" t="s">
-        <x:v>119</x:v>
+        <x:v>178</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:3">
@@ -2892,10 +2895,10 @@
         <x:v>116</x:v>
       </x:c>
       <x:c r="B118" s="2" t="s">
-        <x:v>167</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C118" t="s">
-        <x:v>155</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:3">
@@ -2903,10 +2906,10 @@
         <x:v>117</x:v>
       </x:c>
       <x:c r="B119" s="2" t="s">
-        <x:v>1</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="C119" t="s">
-        <x:v>117</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:3">
@@ -2914,10 +2917,10 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="B120" s="2" t="s">
-        <x:v>252</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="C120" t="s">
-        <x:v>112</x:v>
+        <x:v>182</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:3">
@@ -2925,10 +2928,10 @@
         <x:v>119</x:v>
       </x:c>
       <x:c r="B121" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C121" t="s">
-        <x:v>157</x:v>
+        <x:v>221</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:3">
@@ -2936,10 +2939,10 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="B122" s="2" t="s">
-        <x:v>169</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C122" t="s">
-        <x:v>161</x:v>
+        <x:v>186</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:3">
@@ -2947,10 +2950,10 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="B123" s="2" t="s">
-        <x:v>238</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="C123" t="s">
-        <x:v>108</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:3">
@@ -2958,43 +2961,45 @@
         <x:v>122</x:v>
       </x:c>
       <x:c r="B124" s="2" t="s">
-        <x:v>177</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="C124" t="s">
-        <x:v>107</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="125" spans="1:3">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" spans="1:14">
       <x:c r="A125">
         <x:v>123</x:v>
       </x:c>
       <x:c r="B125" s="2" t="s">
-        <x:v>179</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C125" s="3" t="s">
-        <x:v>106</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="126" spans="1:3">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="N125" s="4"/>
+    </x:row>
+    <x:row r="126" spans="1:14">
       <x:c r="A126">
         <x:v>124</x:v>
       </x:c>
       <x:c r="B126" s="2" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="C126" s="3" t="s">
-        <x:v>114</x:v>
-      </x:c>
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="C126" s="2" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="N126" s="2"/>
     </x:row>
     <x:row r="127" spans="1:3">
       <x:c r="A127">
         <x:v>125</x:v>
       </x:c>
       <x:c r="B127" s="2" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="C127" s="4" t="s">
         <x:v>181</x:v>
-      </x:c>
-      <x:c r="C127" t="s">
-        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:3">
@@ -3002,10 +3007,10 @@
         <x:v>126</x:v>
       </x:c>
       <x:c r="B128" s="2" t="s">
-        <x:v>178</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C128" t="s">
-        <x:v>110</x:v>
+        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:3">
@@ -3013,10 +3018,10 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="B129" s="2" t="s">
-        <x:v>180</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="C129" s="3" t="s">
-        <x:v>121</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:3">
@@ -3024,10 +3029,10 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="B130" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C130" t="s">
-        <x:v>9</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:3">
@@ -3035,10 +3040,10 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="B131" s="2" t="s">
-        <x:v>168</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C131" t="s">
-        <x:v>103</x:v>
+        <x:v>260</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:3">
@@ -3046,10 +3051,10 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="B132" s="2" t="s">
-        <x:v>182</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="C132" s="3" t="s">
-        <x:v>126</x:v>
+        <x:v>188</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:3">
@@ -3057,10 +3062,10 @@
         <x:v>131</x:v>
       </x:c>
       <x:c r="B133" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="C133" t="s">
-        <x:v>259</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:3">
@@ -3068,10 +3073,10 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="B134" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="C134" s="3" t="s">
-        <x:v>260</x:v>
+        <x:v>177</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:3">
@@ -3079,10 +3084,10 @@
         <x:v>133</x:v>
       </x:c>
       <x:c r="B135" s="2" t="s">
-        <x:v>104</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C135" s="3" t="s">
-        <x:v>109</x:v>
+        <x:v>174</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/morpg/morpg/Assets/TableData/Table_Text.xlsx
+++ b/morpg/morpg/Assets/TableData/Table_Text.xlsx
@@ -19,7 +19,391 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="261">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="267">
+  <x:si>
+    <x:t>전 세계에서도 극히 발견하기 어려웠던 과실. 먹는 이의 모든 질병과 상처를 회복해주고, 육체를 가장 건강하던 때로 고정하며 새로운 수명을 하사한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마법의 신, 제샤스 데이틴의 일곱 제자들이 일으킨 내전. 이로 인해 세상의 모든 기록이 소실되어 사실상 모든 것이 초기화되었다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초심극점을 마주하고 바라보고 있는 다른 세상, '역세계'와의 전쟁.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>원래라면 죽었을 때 다시 되살아나지만, 죽을 경우 다시는 되살아나지 못하는 것을 조건으로 강력한 힘을 얻어 그의 희생으로 '종말전쟁'에서 승리할 수 있었다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>티모르</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라우톤</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>궁수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나로사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신발</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장갑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>천</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무직</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마법사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가레멘</x:t>
+  </x:si>
+  <x:si>
+    <x:t>판금</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목걸이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>역사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Job</x:t>
+  </x:si>
+  <x:si>
+    <x:t>메뉴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가죽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>역세계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도감</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레노드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레디닌</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장비</x:t>
+  </x:si>
+  <x:si>
+    <x:t>암살자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로데크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>투르카</x:t>
+  </x:si>
+  <x:si>
+    <x:t>직업</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그렌</x:t>
+  </x:si>
+  <x:si>
+    <x:t>용어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>성직자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불튼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마왕족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>드래곤</x:t>
+  </x:si>
+  <x:si>
+    <x:t>페르스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>갑옷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>본세계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도적</x:t>
+  </x:si>
+  <x:si>
+    <x:t>머리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카루크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>바드락</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이레안</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초월자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>셀레나</x:t>
+  </x:si>
+  <x:si>
+    <x:t>창조신 'OM'이 창조한 초심극점 너머의 다른 세상.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>창조신 'NM'이 창조한 11개로 겹쳐진 우리의 세상.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'본세계'와 '역세계'를 잇는 유일한 물리적 이동공간.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa014_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제 와서는 이 세상에 절대유일한 '핏빛혈족의 유일한 생존자' 무시무시한 이능력을 지니고 있지만 그가 지닌 이능력의 정체를 아는 자를 이제는 찾을 수 없다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:피를 입는 자. '본세계'와 '역세계'를 모두 포함해서도 비슷한 수준의 신체능력을 가진 존재를 찾기 힘들 정도로 압도적인 신체능력을 가지고 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa014_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 자가방어와 자가치유에 치중된 地계열 순수 탱커.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 능력 중 대부분이 공격에 치중된 火계열 중거리 딜러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'본세계' 내의 다른 10개의 세계와의 연락을 차단했음에도 가장 독자적인 업적을 이룩한 대륙.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>평화로운 시기에도 전 세계에 그 개체 수가 5마리를 넘기지 못하던 이 세상 유일의 '초소수종'</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:암흑대제. 이 세상에서 유일하게 힘을 비축하는 시간에 비례하여 무한히 강해질 수 있는 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 공격보다 정찰에 특화된 공격력보다는 연타에 치중한 風계열 서포터.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 대장. 전투에 필요한 전반적인 능력을 두루 갖춘 氷계열 원거리 딜러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 창공의 종족 '투르카'의 생존자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 바다의 종족 '셀레나'의 생존자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'본세계' 내에서, '종말전쟁'의 결말을 지켜보던 강력한 존재들을 일컫는 용어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 대지의 종족 '티모르'의 생존저.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'본세계' 내에서 최초로 기록된 내전. 이로 인해 '불의 종족' 카르툼이 절멸하였다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세이렌 알트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>드래곤을 포함해도 모든 종족 중에서는 물리력 최강의 종족 '바드락'의 생존자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써 '태양절맥'을 갖고 태어난 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써 '구음절맥'을 갖고 태어난 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'종말전쟁'이 끝난 이후의 시대가 되며 사실상 유명무실한 용어가 되어 사실상 강력한 힘을 지닌 '초월자'들을 일컫는 용어가 되었다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:금속왕. 긴가르시온이 조립한 완전 기계인간 다만 이 세상에서 유일하게 전신이 '완벽한 신의 금속'으로 이뤄져서 모든 것을 무시할 수준의 방어력을 지니고 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:시간의 마왕. 우리의 세상인 '본세계'와 '역세계'에서도 하나 이상을 찾아볼 수 없는 절대유일의 시간 능력자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이 세상 모든 것을 중독시키는 '페이튼'에 중독되어 스스로 의사를 갖고 움직이기 시작한 종족 '래머'의 마지막 생존자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 지닌 능력 중 대부분이 상처를 치유하고 아군을 버프, 적을 디버프하는 水계열 후방 서포터.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 불튼이 버금가는 탱킹 능력에 '피를 입는 자'에 버금하는 물리력을 지닌 雷계열 근거리 딜러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'아키르고 베니아'가 아닌 때에 '이라 모스'를 개설한 충격으로 '본세계' 바깥의 세상이 무너져버린 사건.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그의 일정범위에 존재하는 모든 사물은 점점 느려지기  시작하고 그 본인은 그 속도만큼 점점 빨라진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>144년을 주기로 돌아오는 초자연 현상. 이 기간 중에는 성공적인 '이라 모스'의 개폐가 가능해진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Archmage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Assassin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아키르고 베니아</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DemonMage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Species&amp;Job</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RightRIng</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Summoner</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hidden002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa005_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa009_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa007_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa009_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa010_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa008_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa011_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term006_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa008_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa013_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa007_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Desc_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa007_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa002_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Desc_002</x:t>
+  </x:si>
   <x:si>
     <x:t>Cocruwa013_Desc_002</x:t>
   </x:si>
@@ -33,6 +417,18 @@
     <x:t>Cocruwa005_Desc_001</x:t>
   </x:si>
   <x:si>
+    <x:t>Cocruwa001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa011_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa004_Desc_001</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cocruwa001_Desc_002</x:t>
   </x:si>
   <x:si>
@@ -42,108 +438,99 @@
     <x:t>GaremenTooskaDin</x:t>
   </x:si>
   <x:si>
-    <x:t>History003_Desc_001</x:t>
-  </x:si>
-  <x:si>
     <x:t>Cocruwa006_Desc_001</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocruwa004_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa001_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa011_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마법의 신, 제샤스 데이틴의 일곱 제자들이 일으킨 내전. 이로 인해 세상의 모든 기록이 소실되어 사실상 모든 것이 초기화되었다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이제 와서는 이 세상에 절대유일한 '핏빛혈족의 유일한 생존자' 무시무시한 이능력을 지니고 있지만 그가 지닌 이능력의 정체를 아는 자를 이제는 찾을 수 없다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:피를 입는 자. '본세계'와 '역세계'를 모두 포함해서도 비슷한 수준의 신체능력을 가진 존재를 찾기 힘들 정도로 압도적인 신체능력을 가지고 있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'본세계'와 '역세계'를 잇는 유일한 물리적 이동공간.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>창조신 'OM'이 창조한 초심극점 너머의 다른 세상.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>창조신 'NM'이 창조한 11개로 겹쳐진 우리의 세상.</x:t>
+    <x:t>이명:현명한 현자. 모든 코크루와 중 유일의 비전투원. 다만 이제는 기억하는 사람도 없는 '본카 일족'의 족장 '짐토'로써 사실상 이 세상의 모든 학문과 기술은 그로부터 비롯된 것이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:유령왕. 태생적으로 '산도라의 후예'인 대마도사였으나 그의 스승인 '푸 그레이'가 서술한 '초마도의 서'를 이해하여 마법사 중 최강의 존재인 '초마도사'가 되었다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 그가 공격의사를 갖던 말던 그의 주변에 존재하는 것만으로도 해독이 불가능한 '페이튼'에 중독되어 모든 존재가 소멸한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sandora</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Human</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코크루와</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Redinin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>강령술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>save</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Unknown</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Head</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마족 마법사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카루크 뷘젠트</x:t>
   </x:si>
   <x:si>
     <x:t>Rodec</x:t>
   </x:si>
   <x:si>
-    <x:t>Unknown</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Human</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sandora</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코크루와</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Redinin</x:t>
-  </x:si>
-  <x:si>
     <x:t>대마도사</x:t>
   </x:si>
   <x:si>
-    <x:t>save</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Head</x:t>
-  </x:si>
-  <x:si>
-    <x:t>강령술사</x:t>
-  </x:si>
-  <x:si>
     <x:t>Toorka</x:t>
   </x:si>
   <x:si>
-    <x:t>마족 마법사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카루크 뷘젠트</x:t>
+    <x:t>대마도전쟁</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소환술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cloth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불러오기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연금술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종족전쟁</x:t>
+  </x:si>
+  <x:si>
+    <x:t>반지(좌)</x:t>
   </x:si>
   <x:si>
     <x:t>Selena</x:t>
   </x:si>
   <x:si>
+    <x:t>Rogue</x:t>
+  </x:si>
+  <x:si>
     <x:t>Index</x:t>
   </x:si>
   <x:si>
-    <x:t>Rogue</x:t>
+    <x:t>exit</x:t>
+  </x:si>
+  <x:si>
+    <x:t>menu</x:t>
   </x:si>
   <x:si>
     <x:t>귀걸이(우)</x:t>
   </x:si>
   <x:si>
-    <x:t>menu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>exit</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소환술사</x:t>
-  </x:si>
-  <x:si>
     <x:t>Leather</x:t>
   </x:si>
   <x:si>
-    <x:t>반지(좌)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불러오기</x:t>
-  </x:si>
-  <x:si>
     <x:t>그렌 포모스</x:t>
   </x:si>
   <x:si>
@@ -153,442 +540,223 @@
     <x:t>이레안 소린</x:t>
   </x:si>
   <x:si>
-    <x:t>대마도전쟁</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cloth</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연금술사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종족전쟁</x:t>
+    <x:t>Cocruwa012_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa010_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa006_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term007_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term005_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa013_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term007_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa011_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이어하기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>term</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Boots</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Weapon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Armor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>귀걸이(좌)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>load</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라우톤 윈너</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Renod</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Badrak</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에를로네</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Array</x:t>
+  </x:si>
+  <x:si>
+    <x:t>?????</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타르타로스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Demon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불튼 카존</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Korean</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Priest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종말전쟁</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Archer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>긴가르시온</x:t>
+  </x:si>
+  <x:si>
+    <x:t>history</x:t>
+  </x:si>
+  <x:si>
+    <x:t>newgame</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타이틀로 이동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gloves</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Plate</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dragon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>반지(우)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>copy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>위대한 과실</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ehrlone</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나로사 포모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새 시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종족&amp;직업</x:t>
+  </x:si>
+  <x:si>
+    <x:t>산도라 태생</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Perth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초심극점</x:t>
+  </x:si>
+  <x:si>
+    <x:t>option</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cocruwa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Teemole</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kalapok</x:t>
   </x:si>
   <x:si>
     <x:t>Comment</x:t>
   </x:si>
   <x:si>
-    <x:t>option</x:t>
-  </x:si>
-  <x:si>
-    <x:t>초심극점</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cocruwa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kalapok</x:t>
-  </x:si>
-  <x:si>
     <x:t>마족 전사</x:t>
   </x:si>
   <x:si>
-    <x:t>산도라 태생</x:t>
-  </x:si>
-  <x:si>
     <x:t>Warrior</x:t>
   </x:si>
   <x:si>
-    <x:t>Perth</x:t>
-  </x:si>
-  <x:si>
     <x:t>Machine</x:t>
   </x:si>
   <x:si>
-    <x:t>종족&amp;직업</x:t>
-  </x:si>
-  <x:si>
     <x:t>title</x:t>
   </x:si>
   <x:si>
-    <x:t>새 시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Teemole</x:t>
-  </x:si>
-  <x:si>
-    <x:t>load</x:t>
-  </x:si>
-  <x:si>
-    <x:t>귀걸이(좌)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라우톤 윈너</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Renod</x:t>
-  </x:si>
-  <x:si>
-    <x:t>newgame</x:t>
-  </x:si>
-  <x:si>
-    <x:t>긴가르시온</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gloves</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Badrak</x:t>
-  </x:si>
-  <x:si>
-    <x:t>history</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Dragon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Demon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Korean</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에를로네</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Priest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Archer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>위대한 과실</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Plate</x:t>
-  </x:si>
-  <x:si>
-    <x:t>반지(우)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Array</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타이틀로 이동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>copy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종말전쟁</x:t>
-  </x:si>
-  <x:si>
-    <x:t>?????</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ehrlone</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타르타로스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나로사 포모스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불튼 카존</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Armor</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이어하기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Boots</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Weapon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>term</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:금속왕. 긴가르시온이 조립한 완전 기계인간 다만 이 세상에서 유일하게 전신이 '완벽한 신의 금속'으로 이뤄져서 모든 것을 무시할 수준의 방어력을 지니고 있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 대장. 전투에 필요한 전반적인 능력을 두루 갖춘 氷계열 원거리 딜러.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 공격보다 정찰에 특화된 공격력보다는 연타에 치중한 風계열 서포터.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 지닌 능력 중 대부분이 상처를 치유하고 아군을 버프, 적을 디버프하는 水계열 후방 서포터.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 불튼이 버금가는 탱킹 능력에 '피를 입는 자'에 버금하는 물리력을 지닌 雷계열 근거리 딜러.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term007_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:현명한 현자. 모든 코크루와 중 유일의 비전투원. 다만 이제는 기억하는 사람도 없는 '본카 일족'의 족장 '짐토'로써 사실상 이 세상의 모든 학문과 기술은 그로부터 비롯된 것이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무직</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>티모르</x:t>
-  </x:si>
-  <x:si>
-    <x:t>목걸이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마법사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라우톤</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나로사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가레멘</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>역사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>저장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>메뉴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>궁수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신발</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장갑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가죽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>판금</x:t>
-  </x:si>
-  <x:si>
-    <x:t>역세계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>천</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Job</x:t>
-  </x:si>
-  <x:si>
-    <x:t>용어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>본세계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레노드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>성직자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>초월자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>셀레나</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카루크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>암살자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>로데크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>투르카</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레디닌</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>직업</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불튼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도감</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그렌</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도적</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장비</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마왕족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>바드락</x:t>
-  </x:si>
-  <x:si>
-    <x:t>페르스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>갑옷</x:t>
-  </x:si>
-  <x:si>
-    <x:t>드래곤</x:t>
-  </x:si>
-  <x:si>
-    <x:t>머리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이레안</x:t>
+    <x:t>???????????????</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term004_Title</x:t>
   </x:si>
   <x:si>
     <x:t>DemonFighter</x:t>
   </x:si>
   <x:si>
+    <x:t>encyclopedia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term005_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term006_Title</x:t>
+  </x:si>
+  <x:si>
     <x:t>Term001_Title</x:t>
   </x:si>
   <x:si>
     <x:t>RoutonWinner</x:t>
   </x:si>
   <x:si>
-    <x:t>Term002_Title</x:t>
+    <x:t>RightEarring</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term007_Title</x:t>
   </x:si>
   <x:si>
     <x:t>이라 모스 강제 개폐 사건</x:t>
   </x:si>
   <x:si>
-    <x:t>Term006_Title</x:t>
-  </x:si>
-  <x:si>
     <x:t>KaroukWingent</x:t>
   </x:si>
   <x:si>
-    <x:t>Term005_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>???????????????</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RightEarring</x:t>
-  </x:si>
-  <x:si>
-    <x:t>encyclopedia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term003_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term007_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term004_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전 세계에서도 극히 발견하기 어려웠던 과실. 먹는 이의 모든 질병과 상처를 회복해주고, 육체를 가장 건강하던 때로 고정하며 새로운 수명을 하사한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써 '구음절맥'을 갖고 태어난 존재.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>드래곤을 포함해도 모든 종족 중에서는 물리력 최강의 종족 '바드락'의 생존자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써 '태양절맥'을 갖고 태어난 존재.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'종말전쟁'이 끝난 이후의 시대가 되며 사실상 유명무실한 용어가 되어 사실상 강력한 힘을 지닌 '초월자'들을 일컫는 용어가 되었다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'본세계' 내에서 최초로 기록된 내전. 이로 인해 '불의 종족' 카르툼이 절멸하였다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 바다의 종족 '셀레나'의 생존자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'본세계' 내에서, '종말전쟁'의 결말을 지켜보던 강력한 존재들을 일컫는 용어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 창공의 종족 '투르카'의 생존자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 대지의 종족 '티모르'의 생존저.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 능력 중 대부분이 공격에 치중된 火계열 중거리 딜러.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'본세계' 내의 다른 10개의 세계와의 연락을 차단했음에도 가장 독자적인 업적을 이룩한 대륙.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>평화로운 시기에도 전 세계에 그 개체 수가 5마리를 넘기지 못하던 이 세상 유일의 '초소수종'</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:암흑대제. 이 세상에서 유일하게 힘을 비축하는 시간에 비례하여 무한히 강해질 수 있는 존재.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 자가방어와 자가치유에 치중된 地계열 순수 탱커.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:시간의 마왕. 우리의 세상인 '본세계'와 '역세계'에서도 하나 이상을 찾아볼 수 없는 절대유일의 시간 능력자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이 세상 모든 것을 중독시키는 '페이튼'에 중독되어 스스로 의사를 갖고 움직이기 시작한 종족 '래머'의 마지막 생존자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그의 일정범위에 존재하는 모든 사물은 점점 느려지기  시작하고 그 본인은 그 속도만큼 점점 빨라진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'아키르고 베니아'가 아닌 때에 '이라 모스'를 개설한 충격으로 '본세계' 바깥의 세상이 무너져버린 사건.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>144년을 주기로 돌아오는 초자연 현상. 이 기간 중에는 성공적인 '이라 모스'의 개폐가 가능해진다.</x:t>
+    <x:t>IreanSorin</x:t>
   </x:si>
   <x:si>
     <x:t>Gingarsion</x:t>
@@ -597,211 +765,61 @@
     <x:t>LeftEarring</x:t>
   </x:si>
   <x:si>
+    <x:t>LeftRing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tartaros</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bugreport</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hidden001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>버그리포트 바로가기</x:t>
+  </x:si>
+  <x:si>
     <x:t>Necklace</x:t>
   </x:si>
   <x:si>
-    <x:t>버그리포트 바로가기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LeftRing</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IreanSorin</x:t>
-  </x:si>
-  <x:si>
     <x:t>헤디 벤만 오프 모스</x:t>
   </x:si>
   <x:si>
-    <x:t>Tartaros</x:t>
-  </x:si>
-  <x:si>
     <x:t>가레멘 투스카 딘</x:t>
   </x:si>
   <x:si>
     <x:t>Equipment</x:t>
   </x:si>
   <x:si>
-    <x:t>bugreport</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hidden001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아키르고 베니아</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DemonMage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Archmage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hidden002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Summoner</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Assassin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Species&amp;Job</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RightRIng</x:t>
+    <x:t>Alchemist</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GrenFomos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>continue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NarosaFomos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CodeName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Necromancer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BultonKajon</x:t>
   </x:si>
   <x:si>
     <x:t>notEmployed</x:t>
   </x:si>
   <x:si>
-    <x:t>NarosaFomos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GrenFomos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CodeName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>continue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Alchemist</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BultonKajon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Necromancer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term007_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa010_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa013_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 그가 공격의사를 갖던 말던 그의 주변에 존재하는 것만으로도 해독이 불가능한 '페이튼'에 중독되어 모든 존재가 소멸한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:유령왕. 태생적으로 '산도라의 후예'인 대마도사였으나 그의 스승인 '푸 그레이'가 서술한 '초마도의 서'를 이해하여 마법사 중 최강의 존재인 '초마도사'가 되었다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term005_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa006_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term001_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa011_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa008_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa003_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa002_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term003_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History003_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Desc_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History001_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa004_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa002_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History002_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History004_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa009_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa007_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History001_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa007_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa005_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa008_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa009_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term002_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term006_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History002_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa010_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa011_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa001_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term004_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa003_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa002_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History004_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa007_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa013_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>초심극점을 마주하고 바라보고 있는 다른 세상, '역세계'와의 전쟁.</x:t>
+    <x:t>이명:죽어도 되살아나는 자. 역사상 최초의 '초월자'이자 무한하게 강해지는 '암흑대제'의 원형.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa014_Title</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1554,7 +1572,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:N135"/>
+  <x:dimension ref="A1:N138"/>
   <x:sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="16.39999999999999857891"/>
   <x:cols>
     <x:col min="1" max="1" width="8.796875" bestFit="1" customWidth="1"/>
@@ -1563,31 +1581,31 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="D1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>213</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="D2" s="1"/>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -1595,7 +1613,7 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B4" s="1"/>
       <x:c r="C4" s="1"/>
@@ -1606,10 +1624,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" t="s">
-        <x:v>68</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="C5" t="s">
-        <x:v>61</x:v>
+        <x:v>216</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
@@ -1617,10 +1635,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" t="s">
-        <x:v>214</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="C6" t="s">
-        <x:v>92</x:v>
+        <x:v>183</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
@@ -1628,10 +1646,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" t="s">
-        <x:v>49</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="C7" t="s">
-        <x:v>146</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
@@ -1639,10 +1657,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" t="s">
-        <x:v>36</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="C8" t="s">
-        <x:v>108</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
@@ -1650,10 +1668,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B9" t="s">
-        <x:v>25</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C9" t="s">
-        <x:v>118</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
@@ -1661,10 +1679,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B10" t="s">
-        <x:v>63</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C10" t="s">
-        <x:v>40</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
@@ -1672,10 +1690,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B11" t="s">
-        <x:v>84</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="C11" t="s">
-        <x:v>115</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
@@ -1683,10 +1701,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B12" t="s">
-        <x:v>35</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="C12" t="s">
-        <x:v>119</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
@@ -1694,10 +1712,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B13" t="s">
-        <x:v>60</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C13" s="2" t="s">
-        <x:v>83</x:v>
+        <x:v>207</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
@@ -1705,10 +1723,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B14" t="s">
-        <x:v>200</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C14" t="s">
-        <x:v>193</x:v>
+        <x:v>252</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
@@ -1716,10 +1734,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B15" t="s">
-        <x:v>166</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="C15" t="s">
-        <x:v>144</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
@@ -1727,10 +1745,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B16" t="s">
-        <x:v>51</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C16" t="s">
-        <x:v>133</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
@@ -1738,10 +1756,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B17" t="s">
-        <x:v>95</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C17" t="s">
-        <x:v>129</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
@@ -1749,10 +1767,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B18" t="s">
-        <x:v>72</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C18" t="s">
-        <x:v>117</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
@@ -1760,10 +1778,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B19" t="s">
-        <x:v>67</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C19" t="s">
-        <x:v>131</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
@@ -1771,10 +1789,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B20" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="C20" t="s">
         <x:v>197</x:v>
-      </x:c>
-      <x:c r="C20" t="s">
-        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
@@ -1782,10 +1800,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B21" t="s">
-        <x:v>23</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C21" t="s">
-        <x:v>140</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
@@ -1793,10 +1811,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B22" t="s">
-        <x:v>57</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="C22" t="s">
-        <x:v>151</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
@@ -1804,10 +1822,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B23" t="s">
-        <x:v>87</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="C23" t="s">
-        <x:v>76</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
@@ -1815,10 +1833,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B24" t="s">
-        <x:v>190</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="C24" t="s">
-        <x:v>69</x:v>
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
@@ -1826,10 +1844,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B25" t="s">
-        <x:v>212</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C25" t="s">
-        <x:v>41</x:v>
+        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
@@ -1837,10 +1855,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B26" t="s">
-        <x:v>211</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C26" t="s">
-        <x:v>89</x:v>
+        <x:v>215</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
@@ -1848,10 +1866,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B27" t="s">
-        <x:v>195</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="C27" t="s">
-        <x:v>43</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
@@ -1859,10 +1877,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B28" t="s">
-        <x:v>216</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="C28" t="s">
-        <x:v>90</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3">
@@ -1870,10 +1888,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B29" t="s">
-        <x:v>162</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C29" t="s">
-        <x:v>30</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">
@@ -1881,10 +1899,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B30" t="s">
-        <x:v>158</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C30" t="s">
-        <x:v>66</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
@@ -1892,10 +1910,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B31" t="s">
-        <x:v>6</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C31" t="s">
-        <x:v>198</x:v>
+        <x:v>255</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:3">
@@ -1903,10 +1921,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B32" t="s">
-        <x:v>42</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="C32" t="s">
-        <x:v>116</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:3">
@@ -1914,10 +1932,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B33" t="s">
-        <x:v>128</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C33" t="s">
-        <x:v>142</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:3">
@@ -1925,10 +1943,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B34" t="s">
-        <x:v>201</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="C34" t="s">
-        <x:v>86</x:v>
+        <x:v>196</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:3">
@@ -1936,10 +1954,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B35" t="s">
-        <x:v>205</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C35" t="s">
-        <x:v>164</x:v>
+        <x:v>231</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:3">
@@ -1947,10 +1965,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B36" t="s">
-        <x:v>210</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="C36" t="s">
-        <x:v>103</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:3">
@@ -1958,10 +1976,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B37" t="s">
-        <x:v>199</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C37" t="s">
-        <x:v>148</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:3">
@@ -1969,10 +1987,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B38" t="s">
-        <x:v>208</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C38" t="s">
-        <x:v>59</x:v>
+        <x:v>217</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:3">
@@ -1980,10 +1998,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B39" t="s">
-        <x:v>45</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="C39" t="s">
-        <x:v>127</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:3">
@@ -1991,10 +2009,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B40" t="s">
-        <x:v>38</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="C40" t="s">
-        <x:v>124</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:3">
@@ -2002,10 +2020,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B41" t="s">
-        <x:v>80</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="C41" t="s">
-        <x:v>125</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:3">
@@ -2013,10 +2031,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B42" t="s">
-        <x:v>94</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C42" t="s">
-        <x:v>104</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:3">
@@ -2024,10 +2042,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B43" t="s">
-        <x:v>26</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C43" t="s">
-        <x:v>154</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:3">
@@ -2035,10 +2053,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B44" t="s">
-        <x:v>91</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C44" t="s">
-        <x:v>152</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:3">
@@ -2046,10 +2064,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B45" t="s">
-        <x:v>70</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="C45" t="s">
-        <x:v>123</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:3">
@@ -2057,10 +2075,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B46" t="s">
-        <x:v>93</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C46" t="s">
-        <x:v>122</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:3">
@@ -2068,10 +2086,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B47" t="s">
-        <x:v>194</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="C47" t="s">
-        <x:v>39</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:3">
@@ -2079,10 +2097,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B48" t="s">
-        <x:v>209</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C48" t="s">
-        <x:v>81</x:v>
+        <x:v>211</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:3">
@@ -2090,10 +2108,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B49" t="s">
-        <x:v>191</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="C49" t="s">
-        <x:v>64</x:v>
+        <x:v>188</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:3">
@@ -2101,10 +2119,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B50" t="s">
-        <x:v>165</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="C50" t="s">
-        <x:v>34</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:3">
@@ -2112,10 +2130,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B51" t="s">
-        <x:v>192</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C51" t="s">
-        <x:v>106</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:3">
@@ -2123,10 +2141,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B52" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C52" t="s">
-        <x:v>111</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:3">
@@ -2134,10 +2152,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B53" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C53" t="s">
-        <x:v>138</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:3">
@@ -2145,10 +2163,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B54" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C54" t="s">
-        <x:v>139</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:3">
@@ -2156,10 +2174,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B55" t="s">
-        <x:v>62</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="C55" t="s">
-        <x:v>105</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:3">
@@ -2167,10 +2185,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B56" t="s">
-        <x:v>31</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C56" t="s">
-        <x:v>135</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:3">
@@ -2178,10 +2196,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B57" t="s">
-        <x:v>71</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C57" t="s">
-        <x:v>150</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:3">
@@ -2189,10 +2207,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B58" t="s">
-        <x:v>58</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="C58" t="s">
-        <x:v>114</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:3">
@@ -2200,10 +2218,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B59" t="s">
-        <x:v>74</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="C59" t="s">
-        <x:v>134</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:3">
@@ -2211,10 +2229,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B60" t="s">
-        <x:v>21</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C60" t="s">
-        <x:v>55</x:v>
+        <x:v>218</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:3">
@@ -2222,10 +2240,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B61" t="s">
-        <x:v>73</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="C61" t="s">
-        <x:v>153</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:3">
@@ -2233,10 +2251,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B62" t="s">
-        <x:v>53</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C62" t="s">
-        <x:v>149</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:3">
@@ -2244,10 +2262,10 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B63" t="s">
-        <x:v>19</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C63" t="s">
-        <x:v>141</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:3">
@@ -2255,10 +2273,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B64" t="s">
-        <x:v>210</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="C64" t="s">
-        <x:v>103</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:3">
@@ -2266,10 +2284,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B65" t="s">
-        <x:v>56</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="C65" t="s">
-        <x:v>120</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:3">
@@ -2277,10 +2295,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B66" t="s">
-        <x:v>78</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C66" t="s">
-        <x:v>121</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:3">
@@ -2288,10 +2306,10 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B67" t="s">
-        <x:v>52</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C67" t="s">
-        <x:v>107</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:3">
@@ -2299,10 +2317,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B68" t="s">
-        <x:v>77</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C68" t="s">
-        <x:v>132</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:3">
@@ -2310,10 +2328,10 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B69" t="s">
-        <x:v>207</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C69" t="s">
-        <x:v>137</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:3">
@@ -2321,10 +2339,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B70" t="s">
-        <x:v>33</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C70" t="s">
-        <x:v>147</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:3">
@@ -2332,10 +2350,10 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B71" t="s">
-        <x:v>206</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C71" t="s">
-        <x:v>37</x:v>
+        <x:v>157</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:3">
@@ -2343,10 +2361,10 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B72" t="s">
-        <x:v>215</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C72" t="s">
-        <x:v>46</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:3">
@@ -2354,10 +2372,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B73" t="s">
-        <x:v>217</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C73" t="s">
-        <x:v>27</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:3">
@@ -2365,10 +2383,10 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B74" t="s">
-        <x:v>156</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C74" t="s">
-        <x:v>54</x:v>
+        <x:v>227</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:3">
@@ -2376,10 +2394,10 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B75" t="s">
-        <x:v>203</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C75" t="s">
-        <x:v>29</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:3">
@@ -2387,10 +2405,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="B76" t="s">
-        <x:v>204</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C76" t="s">
-        <x:v>24</x:v>
+        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:8">
@@ -2398,10 +2416,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B77" t="s">
-        <x:v>253</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C77" t="s">
-        <x:v>131</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G77" s="2"/>
       <x:c r="H77" s="2"/>
@@ -2411,10 +2429,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B78" t="s">
-        <x:v>232</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C78" t="s">
-        <x:v>88</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="G78" s="2"/>
       <x:c r="H78" s="2"/>
@@ -2424,10 +2442,10 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B79" t="s">
-        <x:v>231</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C79" t="s">
-        <x:v>140</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G79" s="2"/>
       <x:c r="H79" s="2"/>
@@ -2437,10 +2455,10 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B80" t="s">
-        <x:v>237</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C80" t="s">
-        <x:v>151</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G80" s="2"/>
       <x:c r="H80" s="2"/>
@@ -2450,10 +2468,10 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="B81" t="s">
-        <x:v>245</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C81" t="s">
-        <x:v>76</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="G81" s="2"/>
       <x:c r="H81" s="2"/>
@@ -2463,10 +2481,10 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B82" t="s">
-        <x:v>225</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C82" t="s">
-        <x:v>69</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="G82" s="2"/>
       <x:c r="H82" s="2"/>
@@ -2476,10 +2494,10 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B83" t="s">
-        <x:v>258</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C83" t="s">
-        <x:v>145</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G83" s="2"/>
       <x:c r="H83" s="2"/>
@@ -2489,10 +2507,10 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B84" t="s">
-        <x:v>5</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C84" t="s">
-        <x:v>112</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G84" s="2"/>
       <x:c r="H84" s="2"/>
@@ -2502,10 +2520,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B85" t="s">
-        <x:v>1</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C85" t="s">
-        <x:v>155</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G85" s="2"/>
       <x:c r="H85" s="2"/>
@@ -2515,10 +2533,10 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B86" t="s">
-        <x:v>251</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C86" t="s">
-        <x:v>143</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G86" s="2"/>
       <x:c r="H86" s="2"/>
@@ -2528,10 +2546,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B87" t="s">
-        <x:v>252</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C87" t="s">
-        <x:v>136</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G87" s="2"/>
       <x:c r="H87" s="2"/>
@@ -2541,10 +2559,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B88" t="s">
-        <x:v>226</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C88" t="s">
-        <x:v>110</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G88" s="2"/>
       <x:c r="H88" s="2"/>
@@ -2554,10 +2572,10 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="B89" t="s">
-        <x:v>259</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C89" t="s">
-        <x:v>113</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G89" s="2"/>
       <x:c r="H89" s="2"/>
@@ -2567,10 +2585,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B90" t="s">
-        <x:v>157</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="C90" t="s">
-        <x:v>130</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G90" s="2"/>
       <x:c r="H90" s="2"/>
@@ -2580,10 +2598,10 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="B91" t="s">
-        <x:v>159</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="C91" t="s">
-        <x:v>126</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G91" s="2"/>
       <x:c r="H91" s="2"/>
@@ -2593,10 +2611,10 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="B92" t="s">
-        <x:v>167</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="C92" t="s">
-        <x:v>50</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="G92" s="2"/>
       <x:c r="H92" s="2"/>
@@ -2606,10 +2624,10 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="B93" t="s">
-        <x:v>169</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="C93" s="2" t="s">
-        <x:v>202</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="G93" s="2"/>
       <x:c r="H93" s="2"/>
@@ -2619,10 +2637,10 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="B94" t="s">
-        <x:v>163</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="C94" s="2" t="s">
-        <x:v>196</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="G94" s="2"/>
       <x:c r="H94" s="2"/>
@@ -2632,10 +2650,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B95" t="s">
-        <x:v>161</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="C95" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="G95" s="2"/>
       <x:c r="H95" s="2"/>
@@ -2645,10 +2663,10 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="B96" t="s">
-        <x:v>243</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C96" t="s">
-        <x:v>47</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G96" s="2"/>
       <x:c r="H96" s="2"/>
@@ -2658,10 +2676,10 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="B97" t="s">
-        <x:v>250</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C97" t="s">
-        <x:v>44</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="G97" s="2"/>
       <x:c r="H97" s="2"/>
@@ -2671,10 +2689,10 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="B98" t="s">
-        <x:v>234</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C98" t="s">
-        <x:v>85</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="G98" s="2"/>
       <x:c r="H98" s="2"/>
@@ -2684,10 +2702,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B99" t="s">
-        <x:v>257</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C99" t="s">
-        <x:v>160</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="G99" s="2"/>
       <x:c r="H99" s="2"/>
@@ -2697,10 +2715,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="B100" t="s">
-        <x:v>10</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C100" t="s">
-        <x:v>185</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:3">
@@ -2708,10 +2726,10 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="B101" t="s">
-        <x:v>4</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C101" t="s">
-        <x:v>187</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:3">
@@ -2719,10 +2737,10 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="B102" s="2" t="s">
-        <x:v>238</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C102" t="s">
-        <x:v>14</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:3">
@@ -2730,10 +2748,10 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="B103" s="2" t="s">
-        <x:v>256</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C103" t="s">
-        <x:v>13</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:3">
@@ -2741,10 +2759,10 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="B104" s="2" t="s">
-        <x:v>255</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C104" t="s">
-        <x:v>183</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:3">
@@ -2752,10 +2770,10 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="B105" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C105" t="s">
-        <x:v>96</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:3">
@@ -2763,10 +2781,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B106" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C106" t="s">
-        <x:v>222</x:v>
+        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:3">
@@ -2774,10 +2792,10 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="B107" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C107" t="s">
-        <x:v>102</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:3">
@@ -2785,10 +2803,10 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="B108" s="2" t="s">
-        <x:v>242</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C108" t="s">
-        <x:v>180</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:3">
@@ -2796,10 +2814,10 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="B109" s="2" t="s">
-        <x:v>244</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C109" t="s">
-        <x:v>173</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:3">
@@ -2807,10 +2825,10 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="B110" s="2" t="s">
-        <x:v>246</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C110" t="s">
-        <x:v>97</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:3">
@@ -2818,10 +2836,10 @@
         <x:v>109</x:v>
       </x:c>
       <x:c r="B111" s="2" t="s">
-        <x:v>230</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C111" t="s">
-        <x:v>171</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:3">
@@ -2829,10 +2847,10 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="B112" s="2" t="s">
-        <x:v>247</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C112" t="s">
-        <x:v>99</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:3">
@@ -2840,10 +2858,10 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="B113" s="2" t="s">
-        <x:v>241</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C113" t="s">
-        <x:v>176</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:3">
@@ -2851,10 +2869,10 @@
         <x:v>112</x:v>
       </x:c>
       <x:c r="B114" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C114" t="s">
-        <x:v>184</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:3">
@@ -2862,10 +2880,10 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="B115" s="2" t="s">
-        <x:v>219</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C115" t="s">
-        <x:v>179</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:3">
@@ -2873,10 +2891,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B116" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C116" t="s">
-        <x:v>98</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:3">
@@ -2884,10 +2902,10 @@
         <x:v>115</x:v>
       </x:c>
       <x:c r="B117" s="2" t="s">
-        <x:v>229</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C117" t="s">
-        <x:v>178</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:3">
@@ -2895,10 +2913,10 @@
         <x:v>116</x:v>
       </x:c>
       <x:c r="B118" s="2" t="s">
-        <x:v>223</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C118" t="s">
-        <x:v>100</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:3">
@@ -2906,10 +2924,10 @@
         <x:v>117</x:v>
       </x:c>
       <x:c r="B119" s="2" t="s">
-        <x:v>228</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C119" t="s">
-        <x:v>172</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:3">
@@ -2917,10 +2935,10 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="B120" s="2" t="s">
-        <x:v>235</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C120" t="s">
-        <x:v>182</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:3">
@@ -2928,10 +2946,10 @@
         <x:v>119</x:v>
       </x:c>
       <x:c r="B121" s="2" t="s">
-        <x:v>220</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C121" t="s">
-        <x:v>221</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:3">
@@ -2939,10 +2957,10 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="B122" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C122" t="s">
-        <x:v>186</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:3">
@@ -2950,10 +2968,10 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="B123" s="2" t="s">
-        <x:v>227</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="C123" t="s">
-        <x:v>17</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:3">
@@ -2961,10 +2979,10 @@
         <x:v>122</x:v>
       </x:c>
       <x:c r="B124" s="2" t="s">
-        <x:v>248</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C124" t="s">
-        <x:v>16</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:14">
@@ -2972,10 +2990,10 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="B125" s="2" t="s">
-        <x:v>233</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C125" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N125" s="4"/>
     </x:row>
@@ -2984,10 +3002,10 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="B126" s="2" t="s">
-        <x:v>254</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C126" s="2" t="s">
-        <x:v>189</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="N126" s="2"/>
     </x:row>
@@ -2996,10 +3014,10 @@
         <x:v>125</x:v>
       </x:c>
       <x:c r="B127" s="2" t="s">
-        <x:v>224</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C127" s="4" t="s">
-        <x:v>181</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:3">
@@ -3007,10 +3025,10 @@
         <x:v>126</x:v>
       </x:c>
       <x:c r="B128" s="2" t="s">
-        <x:v>249</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C128" t="s">
-        <x:v>170</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:3">
@@ -3018,10 +3036,10 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="B129" s="2" t="s">
-        <x:v>236</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C129" s="3" t="s">
-        <x:v>175</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:3">
@@ -3029,10 +3047,10 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="B130" s="2" t="s">
-        <x:v>239</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C130" t="s">
-        <x:v>12</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:3">
@@ -3040,10 +3058,10 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="B131" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C131" t="s">
-        <x:v>260</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:3">
@@ -3051,10 +3069,10 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="B132" s="2" t="s">
-        <x:v>240</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C132" s="3" t="s">
-        <x:v>188</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:3">
@@ -3062,10 +3080,10 @@
         <x:v>131</x:v>
       </x:c>
       <x:c r="B133" s="2" t="s">
-        <x:v>168</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C133" t="s">
-        <x:v>22</x:v>
+        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:3">
@@ -3073,10 +3091,10 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="B134" s="2" t="s">
-        <x:v>218</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C134" s="3" t="s">
-        <x:v>177</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:3">
@@ -3084,10 +3102,43 @@
         <x:v>133</x:v>
       </x:c>
       <x:c r="B135" s="2" t="s">
-        <x:v>101</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C135" s="3" t="s">
-        <x:v>174</x:v>
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" spans="1:3">
+      <x:c r="A136">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="B136" s="2" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C136" t="s">
+        <x:v>265</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" spans="1:3">
+      <x:c r="A137">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B137" s="2" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="C137" t="s">
+        <x:v>76</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" spans="1:3">
+      <x:c r="A138">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="B138" s="2" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C138" t="s">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/morpg/morpg/Assets/TableData/Table_Text.xlsx
+++ b/morpg/morpg/Assets/TableData/Table_Text.xlsx
@@ -19,807 +19,867 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="267">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="287">
+  <x:si>
+    <x:t>Term004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term006_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RightEarring</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DemonFighter</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>???????????????</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KaroukWingent</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RoutonWinner</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term005_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term007_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이라 모스 강제 개폐 사건</x:t>
+  </x:si>
+  <x:si>
+    <x:t>encyclopedia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 바다의 종족 '셀레나'의 생존자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'본세계' 내에서, '종말전쟁'의 결말을 지켜보던 강력한 존재들을 일컫는 용어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 창공의 종족 '투르카'의 생존자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'본세계' 내에서 최초로 기록된 내전. 이로 인해 '불의 종족' 카르툼이 절멸하였다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 대지의 종족 '티모르'의 생존저.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써 '구음절맥'을 갖고 태어난 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>드래곤을 포함해도 모든 종족 중에서는 물리력 최강의 종족 '바드락'의 생존자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써 '태양절맥'을 갖고 태어난 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>흉켈링</x:t>
+  </x:si>
+  <x:si>
+    <x:t>늑대신이라 불리는 자. '짐토'가 '위대한 과실'의 생산 원리를 알아내고 그것을 독점하기 전까지, 사실상 유일한 '위대한 과실'의 유통을 담당했다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:금속왕. 긴가르시온이 조립한 완전 기계인간 다만 이 세상에서 유일하게 전신이 '완벽한 신의 금속'으로 이뤄져서 모든 것을 무시할 수준의 방어력을 지니고 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마법의 신, 제샤스 데이틴의 일곱 제자들이 일으킨 내전. 이로 인해 세상의 모든 기록이 소실되어 사실상 모든 것이 초기화되었다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 불튼이 버금가는 탱킹 능력에 '피를 입는 자'에 버금하는 물리력을 지닌 雷계열 근거리 딜러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 지닌 능력 중 대부분이 상처를 치유하고 아군을 버프, 적을 디버프하는 水계열 후방 서포터.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:시간의 마왕. 우리의 세상인 '본세계'와 '역세계'에서도 하나 이상을 찾아볼 수 없는 절대유일의 시간 능력자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이 세상 모든 것을 중독시키는 '페이튼'에 중독되어 스스로 의사를 갖고 움직이기 시작한 종족 '래머'의 마지막 생존자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>menu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소환술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Human</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세이렌 알트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Leather</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카루크 뷘젠트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cloth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Unknown</x:t>
+  </x:si>
+  <x:si>
+    <x:t>exit</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Index</x:t>
+  </x:si>
+  <x:si>
+    <x:t>save</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Head</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대마도사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대마도전쟁</x:t>
+  </x:si>
+  <x:si>
+    <x:t>귀걸이(우)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불러오기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종족전쟁</x:t>
+  </x:si>
+  <x:si>
+    <x:t>강령술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코크루와</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rodec</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Toorka</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sandora</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이어하기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>?????</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종말전쟁</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Selena</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Redinin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dragon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>load</x:t>
+  </x:si>
+  <x:si>
+    <x:t>귀걸이(좌)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연금술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>term</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Badrak</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Array</x:t>
+  </x:si>
+  <x:si>
+    <x:t>newgame</x:t>
+  </x:si>
+  <x:si>
+    <x:t>반지(좌)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그렌 포모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gloves</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타이틀로 이동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Korean</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타르타로스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마족 마법사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Demon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>긴가르시온</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rogue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Archer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Plate</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Armor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Renod</x:t>
+  </x:si>
+  <x:si>
+    <x:t>반지(우)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Priest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이레안 소린</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Species</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Comment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Boots</x:t>
+  </x:si>
+  <x:si>
+    <x:t>위대한 과실</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Warrior</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초심극점</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마족 전사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나로사 포모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>option</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Weapon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>copy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ehrlone</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라우톤 윈너</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종족&amp;직업</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cocruwa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Teemole</x:t>
+  </x:si>
+  <x:si>
+    <x:t>history</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Machine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에를로네</x:t>
+  </x:si>
+  <x:si>
+    <x:t>title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Perth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>산도라 태생</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불튼 카존</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새 시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kalapok</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초심극점을 마주하고 바라보고 있는 다른 세상, '역세계'와의 전쟁.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>판금</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마법사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카루크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도적</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레노드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목걸이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라우톤</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Job</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무직</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신발</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>암살자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>천</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인물</x:t>
+  </x:si>
+  <x:si>
+    <x:t>궁수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>티모르</x:t>
+  </x:si>
+  <x:si>
+    <x:t>본세계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불튼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로데크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>페르스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나로사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장갑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가레멘</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>머리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도감</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>용어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>드래곤</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초월자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장비</x:t>
+  </x:si>
+  <x:si>
+    <x:t>셀레나</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>성직자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>직업</x:t>
+  </x:si>
+  <x:si>
+    <x:t>투르카</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레디닌</x:t>
+  </x:si>
+  <x:si>
+    <x:t>갑옷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>바드락</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가죽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>역세계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이레안</x:t>
+  </x:si>
+  <x:si>
+    <x:t>역사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마왕족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그렌</x:t>
+  </x:si>
+  <x:si>
+    <x:t>메뉴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자기 자신의 직계자손에 한정하여, 자신의 기억과 인격을 전달하는 '전생술'을 개발한 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>창조신 'OM'이 창조한 초심극점 너머의 다른 세상.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'본세계'와 '역세계'를 잇는 유일한 물리적 이동공간.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>창조신 'NM'이 창조한 11개로 겹쳐진 우리의 세상.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>평화로운 시기에도 전 세계에 그 개체 수가 5마리를 넘기지 못하던 이 세상 유일의 '초소수종'</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:죽어도 되살아나는 자. 역사상 최초의 '초월자'이자 무한하게 강해지는 '암흑대제'의 원형.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 자가방어와 자가치유에 치중된 地계열 순수 탱커.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 능력 중 대부분이 공격에 치중된 火계열 중거리 딜러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:암흑대제. 이 세상에서 유일하게 힘을 비축하는 시간에 비례하여 무한히 강해질 수 있는 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'본세계' 내의 다른 10개의 세계와의 연락을 차단했음에도 가장 독자적인 업적을 이룩한 대륙.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그의 일정범위에 존재하는 모든 사물은 점점 느려지기  시작하고 그 본인은 그 속도만큼 점점 빨라진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'아키르고 베니아'가 아닌 때에 '이라 모스'를 개설한 충격으로 '본세계' 바깥의 세상이 무너져버린 사건.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>144년을 주기로 돌아오는 초자연 현상. 이 기간 중에는 성공적인 '이라 모스'의 개폐가 가능해진다.</x:t>
+  </x:si>
   <x:si>
     <x:t>전 세계에서도 극히 발견하기 어려웠던 과실. 먹는 이의 모든 질병과 상처를 회복해주고, 육체를 가장 건강하던 때로 고정하며 새로운 수명을 하사한다.</x:t>
   </x:si>
   <x:si>
-    <x:t>마법의 신, 제샤스 데이틴의 일곱 제자들이 일으킨 내전. 이로 인해 세상의 모든 기록이 소실되어 사실상 모든 것이 초기화되었다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>초심극점을 마주하고 바라보고 있는 다른 세상, '역세계'와의 전쟁.</x:t>
+    <x:t>'종말전쟁'이 끝난 이후의 시대가 되며 사실상 유명무실한 용어가 되어 사실상 강력한 힘을 지닌 '초월자'들을 일컫는 용어가 되었다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 공격보다 정찰에 특화된 공격력보다는 연타에 치중한 風계열 서포터.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 대장. 전투에 필요한 전반적인 능력을 두루 갖춘 氷계열 원거리 딜러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa005_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa001_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa011_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa013_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa010_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa006_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa013_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa014_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa002_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa011_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa011_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GaremenTooskaDin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa009_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa008_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term007_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa007_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term006_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa006_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term007_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa010_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa010_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term005_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa013_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa014_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa005_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa009_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa009_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa014_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa008_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa008_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa007_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa007_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Desc_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:현명한 현자. 모든 코크루와 중 유일의 비전투원. 다만 이제는 기억하는 사람도 없는 '본카 일족'의 족장 '짐토'로써 사실상 이 세상의 모든 학문과 기술은 그로부터 비롯된 것이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:유령왕. 태생적으로 '산도라의 후예'인 대마도사였으나 그의 스승인 '푸 그레이'가 서술한 '초마도의 서'를 이해하여 마법사 중 최강의 존재인 '초마도사'가 되었다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 그가 공격의사를 갖던 말던 그의 주변에 존재하는 것만으로도 해독이 불가능한 '페이튼'에 중독되어 모든 존재가 소멸한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제 와서는 이 세상에 절대유일한 '핏빛혈족의 유일한 생존자' 무시무시한 이능력을 지니고 있지만 그가 지닌 이능력의 정체를 아는 자를 이제는 찾을 수 없다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:피를 입는 자. '본세계'와 '역세계'를 모두 포함해서도 비슷한 수준의 신체능력을 가진 존재를 찾기 힘들 정도로 압도적인 신체능력을 가지고 있다.</x:t>
   </x:si>
   <x:si>
     <x:t>원래라면 죽었을 때 다시 되살아나지만, 죽을 경우 다시는 되살아나지 못하는 것을 조건으로 강력한 힘을 얻어 그의 희생으로 '종말전쟁'에서 승리할 수 있었다.</x:t>
   </x:si>
   <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>티모르</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라우톤</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>궁수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나로사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신발</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장갑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>천</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무직</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마법사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가레멘</x:t>
-  </x:si>
-  <x:si>
-    <x:t>판금</x:t>
-  </x:si>
-  <x:si>
-    <x:t>목걸이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>역사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Job</x:t>
-  </x:si>
-  <x:si>
-    <x:t>메뉴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가죽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>역세계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>저장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도감</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레노드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레디닌</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장비</x:t>
-  </x:si>
-  <x:si>
-    <x:t>암살자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>로데크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>투르카</x:t>
-  </x:si>
-  <x:si>
-    <x:t>직업</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그렌</x:t>
-  </x:si>
-  <x:si>
-    <x:t>용어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>성직자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불튼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마왕족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>드래곤</x:t>
-  </x:si>
-  <x:si>
-    <x:t>페르스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>갑옷</x:t>
-  </x:si>
-  <x:si>
-    <x:t>본세계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도적</x:t>
-  </x:si>
-  <x:si>
-    <x:t>머리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카루크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>바드락</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이레안</x:t>
-  </x:si>
-  <x:si>
-    <x:t>초월자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>셀레나</x:t>
-  </x:si>
-  <x:si>
-    <x:t>창조신 'OM'이 창조한 초심극점 너머의 다른 세상.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>창조신 'NM'이 창조한 11개로 겹쳐진 우리의 세상.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'본세계'와 '역세계'를 잇는 유일한 물리적 이동공간.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa014_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이제 와서는 이 세상에 절대유일한 '핏빛혈족의 유일한 생존자' 무시무시한 이능력을 지니고 있지만 그가 지닌 이능력의 정체를 아는 자를 이제는 찾을 수 없다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:피를 입는 자. '본세계'와 '역세계'를 모두 포함해서도 비슷한 수준의 신체능력을 가진 존재를 찾기 힘들 정도로 압도적인 신체능력을 가지고 있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa014_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 자가방어와 자가치유에 치중된 地계열 순수 탱커.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 능력 중 대부분이 공격에 치중된 火계열 중거리 딜러.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'본세계' 내의 다른 10개의 세계와의 연락을 차단했음에도 가장 독자적인 업적을 이룩한 대륙.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>평화로운 시기에도 전 세계에 그 개체 수가 5마리를 넘기지 못하던 이 세상 유일의 '초소수종'</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:암흑대제. 이 세상에서 유일하게 힘을 비축하는 시간에 비례하여 무한히 강해질 수 있는 존재.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 공격보다 정찰에 특화된 공격력보다는 연타에 치중한 風계열 서포터.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 대장. 전투에 필요한 전반적인 능력을 두루 갖춘 氷계열 원거리 딜러.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 창공의 종족 '투르카'의 생존자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 바다의 종족 '셀레나'의 생존자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'본세계' 내에서, '종말전쟁'의 결말을 지켜보던 강력한 존재들을 일컫는 용어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 대지의 종족 '티모르'의 생존저.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'본세계' 내에서 최초로 기록된 내전. 이로 인해 '불의 종족' 카르툼이 절멸하였다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>세이렌 알트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>드래곤을 포함해도 모든 종족 중에서는 물리력 최강의 종족 '바드락'의 생존자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써 '태양절맥'을 갖고 태어난 존재.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써 '구음절맥'을 갖고 태어난 존재.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'종말전쟁'이 끝난 이후의 시대가 되며 사실상 유명무실한 용어가 되어 사실상 강력한 힘을 지닌 '초월자'들을 일컫는 용어가 되었다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:금속왕. 긴가르시온이 조립한 완전 기계인간 다만 이 세상에서 유일하게 전신이 '완벽한 신의 금속'으로 이뤄져서 모든 것을 무시할 수준의 방어력을 지니고 있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:시간의 마왕. 우리의 세상인 '본세계'와 '역세계'에서도 하나 이상을 찾아볼 수 없는 절대유일의 시간 능력자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이 세상 모든 것을 중독시키는 '페이튼'에 중독되어 스스로 의사를 갖고 움직이기 시작한 종족 '래머'의 마지막 생존자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 지닌 능력 중 대부분이 상처를 치유하고 아군을 버프, 적을 디버프하는 水계열 후방 서포터.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 불튼이 버금가는 탱킹 능력에 '피를 입는 자'에 버금하는 물리력을 지닌 雷계열 근거리 딜러.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'아키르고 베니아'가 아닌 때에 '이라 모스'를 개설한 충격으로 '본세계' 바깥의 세상이 무너져버린 사건.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그의 일정범위에 존재하는 모든 사물은 점점 느려지기  시작하고 그 본인은 그 속도만큼 점점 빨라진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>144년을 주기로 돌아오는 초자연 현상. 이 기간 중에는 성공적인 '이라 모스'의 개폐가 가능해진다.</x:t>
+    <x:t>Character003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hidden002</x:t>
   </x:si>
   <x:si>
     <x:t>Archmage</x:t>
   </x:si>
   <x:si>
+    <x:t>아키르고 베니아</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GrenFomos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Summoner</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gingarsion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DemonMage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>버그리포트 바로가기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Alchemist</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LeftEarring</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RightRIng</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Necklace</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bugreport</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tartaros</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Species&amp;Job</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IreanSorin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>헤디 벤만 오프 모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hidden001</x:t>
+  </x:si>
+  <x:si>
     <x:t>Assassin</x:t>
   </x:si>
   <x:si>
-    <x:t>아키르고 베니아</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DemonMage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Species&amp;Job</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RightRIng</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Summoner</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hidden002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History001_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History004_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa005_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History002_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa009_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History003_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa001_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa002_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa003_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term003_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa007_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa009_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa010_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History002_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa002_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa008_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa011_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term006_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa003_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term004_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa008_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa013_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History004_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa007_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History001_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Desc_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa007_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa004_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa002_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term002_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa013_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa009_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa010_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa005_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa001_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa011_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History003_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa004_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa001_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa008_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GaremenTooskaDin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa006_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:현명한 현자. 모든 코크루와 중 유일의 비전투원. 다만 이제는 기억하는 사람도 없는 '본카 일족'의 족장 '짐토'로써 사실상 이 세상의 모든 학문과 기술은 그로부터 비롯된 것이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:유령왕. 태생적으로 '산도라의 후예'인 대마도사였으나 그의 스승인 '푸 그레이'가 서술한 '초마도의 서'를 이해하여 마법사 중 최강의 존재인 '초마도사'가 되었다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 그가 공격의사를 갖던 말던 그의 주변에 존재하는 것만으로도 해독이 불가능한 '페이튼'에 중독되어 모든 존재가 소멸한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sandora</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Human</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코크루와</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Redinin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>강령술사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>save</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Unknown</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Head</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마족 마법사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카루크 뷘젠트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rodec</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대마도사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Toorka</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대마도전쟁</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소환술사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cloth</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불러오기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연금술사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종족전쟁</x:t>
-  </x:si>
-  <x:si>
-    <x:t>반지(좌)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Selena</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rogue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Index</x:t>
-  </x:si>
-  <x:si>
-    <x:t>exit</x:t>
-  </x:si>
-  <x:si>
-    <x:t>menu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>귀걸이(우)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Leather</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그렌 포모스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Species</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이레안 소린</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term001_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa010_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa006_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term007_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term005_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa013_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term007_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa011_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이어하기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>term</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Boots</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Weapon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Armor</x:t>
-  </x:si>
-  <x:si>
-    <x:t>귀걸이(좌)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>load</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라우톤 윈너</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Renod</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Badrak</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에를로네</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Array</x:t>
-  </x:si>
-  <x:si>
-    <x:t>?????</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타르타로스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Demon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불튼 카존</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Korean</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Priest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종말전쟁</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Archer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>긴가르시온</x:t>
-  </x:si>
-  <x:si>
-    <x:t>history</x:t>
-  </x:si>
-  <x:si>
-    <x:t>newgame</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타이틀로 이동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gloves</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Plate</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Dragon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>반지(우)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>copy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>위대한 과실</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ehrlone</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나로사 포모스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>새 시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종족&amp;직업</x:t>
-  </x:si>
-  <x:si>
-    <x:t>산도라 태생</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Perth</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>초심극점</x:t>
-  </x:si>
-  <x:si>
-    <x:t>option</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cocruwa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Teemole</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kalapok</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Comment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마족 전사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Warrior</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Machine</x:t>
-  </x:si>
-  <x:si>
-    <x:t>title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>???????????????</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term004_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DemonFighter</x:t>
-  </x:si>
-  <x:si>
-    <x:t>encyclopedia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term005_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term002_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term006_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term001_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RoutonWinner</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RightEarring</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term003_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term007_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이라 모스 강제 개폐 사건</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KaroukWingent</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IreanSorin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gingarsion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LeftEarring</x:t>
+    <x:t>continue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BultonKajon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>notEmployed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가레멘 투스카 딘</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CodeName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Equipment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Necromancer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NarosaFomos</x:t>
   </x:si>
   <x:si>
     <x:t>LeftRing</x:t>
   </x:si>
   <x:si>
-    <x:t>Tartaros</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bugreport</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hidden001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>버그리포트 바로가기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Necklace</x:t>
-  </x:si>
-  <x:si>
-    <x:t>헤디 벤만 오프 모스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가레멘 투스카 딘</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Equipment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Alchemist</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GrenFomos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>continue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NarosaFomos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CodeName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Necromancer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BultonKajon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>notEmployed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:죽어도 되살아나는 자. 역사상 최초의 '초월자'이자 무한하게 강해지는 '암흑대제'의 원형.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa014_Title</x:t>
+    <x:t>백랑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>샤이나 반 고드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">역사에 기록될 정도로 강한 힘을 지닌, 무한히 강해질 수 있는 능력을 지닌 9성 대장, '암흑대제'의 영부인. </x:t>
+  </x:si>
+  <x:si>
+    <x:t>화룡왕이라 불리는 자. 악신룡 '지크리피언'에게 육체는 소멸 당하고, 육체가 아닌 정신만으로 살아있는 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character002_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>올베인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'헤디 벤만 오프 모스' 출신, 역사상 가장 위대한 무인이라 불리는 자.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1572,7 +1632,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:N138"/>
+  <x:dimension ref="A1:N150"/>
   <x:sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="16.39999999999999857891"/>
   <x:cols>
     <x:col min="1" max="1" width="8.796875" bestFit="1" customWidth="1"/>
@@ -1581,31 +1641,31 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>190</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>190</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>261</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>200</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D2" s="1"/>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -1613,7 +1673,7 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>226</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B4" s="1"/>
       <x:c r="C4" s="1"/>
@@ -1624,10 +1684,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" t="s">
-        <x:v>206</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C5" t="s">
-        <x:v>216</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
@@ -1635,10 +1695,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" t="s">
-        <x:v>259</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C6" t="s">
-        <x:v>183</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
@@ -1646,10 +1706,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" t="s">
-        <x:v>222</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C7" t="s">
-        <x:v>43</x:v>
+        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
@@ -1657,10 +1717,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" t="s">
-        <x:v>166</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C8" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
@@ -1668,10 +1728,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B9" t="s">
-        <x:v>148</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C9" t="s">
-        <x:v>29</x:v>
+        <x:v>134</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
@@ -1679,10 +1739,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B10" t="s">
-        <x:v>189</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C10" t="s">
-        <x:v>159</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
@@ -1690,10 +1750,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B11" t="s">
-        <x:v>212</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C11" t="s">
-        <x:v>13</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
@@ -1701,10 +1761,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B12" t="s">
-        <x:v>167</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C12" t="s">
-        <x:v>25</x:v>
+        <x:v>165</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
@@ -1712,10 +1772,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B13" t="s">
-        <x:v>230</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C13" s="2" t="s">
-        <x:v>207</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
@@ -1723,10 +1783,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B14" t="s">
-        <x:v>250</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C14" t="s">
-        <x:v>252</x:v>
+        <x:v>257</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
@@ -1734,10 +1794,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B15" t="s">
-        <x:v>234</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C15" t="s">
-        <x:v>30</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
@@ -1745,10 +1805,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B16" t="s">
-        <x:v>223</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C16" t="s">
-        <x:v>55</x:v>
+        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
@@ -1756,10 +1816,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B17" t="s">
-        <x:v>184</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C17" t="s">
-        <x:v>39</x:v>
+        <x:v>146</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
@@ -1767,10 +1827,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B18" t="s">
-        <x:v>205</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C18" t="s">
-        <x:v>21</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
@@ -1778,10 +1838,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B19" t="s">
-        <x:v>192</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C19" t="s">
-        <x:v>31</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
@@ -1789,10 +1849,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B20" t="s">
-        <x:v>249</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="C20" t="s">
-        <x:v>197</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
@@ -1800,10 +1860,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B21" t="s">
-        <x:v>146</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C21" t="s">
-        <x:v>32</x:v>
+        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
@@ -1811,10 +1871,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B22" t="s">
-        <x:v>219</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C22" t="s">
-        <x:v>45</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
@@ -1822,10 +1882,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B23" t="s">
-        <x:v>214</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C23" t="s">
-        <x:v>194</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
@@ -1833,10 +1893,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B24" t="s">
-        <x:v>246</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="C24" t="s">
-        <x:v>204</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
@@ -1844,10 +1904,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B25" t="s">
-        <x:v>258</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C25" t="s">
-        <x:v>170</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
@@ -1855,10 +1915,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B26" t="s">
-        <x:v>260</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="C26" t="s">
-        <x:v>215</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
@@ -1866,10 +1926,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B27" t="s">
-        <x:v>245</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="C27" t="s">
-        <x:v>172</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
@@ -1877,10 +1937,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B28" t="s">
-        <x:v>263</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="C28" t="s">
-        <x:v>199</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3">
@@ -1888,10 +1948,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B29" t="s">
-        <x:v>244</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C29" t="s">
-        <x:v>152</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">
@@ -1899,10 +1959,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B30" t="s">
-        <x:v>239</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C30" t="s">
-        <x:v>191</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
@@ -1910,10 +1970,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B31" t="s">
-        <x:v>138</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C31" t="s">
-        <x:v>255</x:v>
+        <x:v>272</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:3">
@@ -1921,10 +1981,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B32" t="s">
-        <x:v>171</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C32" t="s">
-        <x:v>28</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:3">
@@ -1932,10 +1992,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B33" t="s">
-        <x:v>24</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C33" t="s">
-        <x:v>37</x:v>
+        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:3">
@@ -1943,10 +2003,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B34" t="s">
-        <x:v>251</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C34" t="s">
-        <x:v>196</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:3">
@@ -1954,10 +2014,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B35" t="s">
-        <x:v>96</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C35" t="s">
-        <x:v>231</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:3">
@@ -1965,10 +2025,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B36" t="s">
-        <x:v>264</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="C36" t="s">
-        <x:v>16</x:v>
+        <x:v>123</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:3">
@@ -1976,10 +2036,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B37" t="s">
-        <x:v>256</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C37" t="s">
-        <x:v>33</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:3">
@@ -1987,10 +2047,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B38" t="s">
-        <x:v>93</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="C38" t="s">
-        <x:v>217</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:3">
@@ -1998,10 +2058,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B39" t="s">
-        <x:v>158</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C39" t="s">
-        <x:v>15</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:3">
@@ -2009,10 +2069,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B40" t="s">
-        <x:v>169</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C40" t="s">
-        <x:v>26</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:3">
@@ -2020,10 +2080,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B41" t="s">
-        <x:v>209</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C41" t="s">
-        <x:v>19</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:3">
@@ -2031,10 +2091,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B42" t="s">
-        <x:v>186</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C42" t="s">
-        <x:v>11</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:3">
@@ -2042,10 +2102,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B43" t="s">
-        <x:v>150</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C43" t="s">
-        <x:v>51</x:v>
+        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:3">
@@ -2053,10 +2113,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B44" t="s">
-        <x:v>187</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C44" t="s">
-        <x:v>46</x:v>
+        <x:v>157</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:3">
@@ -2064,10 +2124,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B45" t="s">
-        <x:v>208</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C45" t="s">
-        <x:v>14</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:3">
@@ -2075,10 +2135,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B46" t="s">
-        <x:v>185</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C46" t="s">
-        <x:v>12</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:3">
@@ -2086,10 +2146,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B47" t="s">
-        <x:v>248</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="C47" t="s">
-        <x:v>162</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:3">
@@ -2097,10 +2157,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B48" t="s">
-        <x:v>94</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C48" t="s">
-        <x:v>211</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:3">
@@ -2108,10 +2168,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B49" t="s">
-        <x:v>247</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="C49" t="s">
-        <x:v>188</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:3">
@@ -2119,10 +2179,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B50" t="s">
-        <x:v>240</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C50" t="s">
-        <x:v>168</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:3">
@@ -2130,10 +2190,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B51" t="s">
-        <x:v>253</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="C51" t="s">
-        <x:v>20</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:3">
@@ -2141,10 +2201,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B52" s="2" t="s">
-        <x:v>144</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C52" t="s">
-        <x:v>23</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:3">
@@ -2152,10 +2212,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B53" s="2" t="s">
-        <x:v>153</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C53" t="s">
-        <x:v>35</x:v>
+        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:3">
@@ -2163,10 +2223,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B54" s="2" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C54" t="s">
         <x:v>155</x:v>
-      </x:c>
-      <x:c r="C54" t="s">
-        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:3">
@@ -2174,10 +2234,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B55" t="s">
-        <x:v>224</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C55" t="s">
-        <x:v>5</x:v>
+        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:3">
@@ -2185,10 +2245,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B56" t="s">
-        <x:v>163</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C56" t="s">
-        <x:v>56</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:3">
@@ -2196,10 +2256,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B57" t="s">
-        <x:v>193</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C57" t="s">
-        <x:v>53</x:v>
+        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:3">
@@ -2207,10 +2267,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B58" t="s">
-        <x:v>229</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C58" t="s">
-        <x:v>7</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:3">
@@ -2218,10 +2278,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B59" t="s">
-        <x:v>198</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C59" t="s">
-        <x:v>49</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:3">
@@ -2229,10 +2289,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B60" t="s">
-        <x:v>143</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C60" t="s">
-        <x:v>218</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:3">
@@ -2240,10 +2300,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B61" t="s">
-        <x:v>210</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C61" t="s">
-        <x:v>44</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:3">
@@ -2251,10 +2311,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B62" t="s">
-        <x:v>225</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C62" t="s">
-        <x:v>42</x:v>
+        <x:v>163</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:3">
@@ -2262,10 +2322,10 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B63" t="s">
-        <x:v>149</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C63" t="s">
-        <x:v>48</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:3">
@@ -2273,10 +2333,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B64" t="s">
-        <x:v>264</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="C64" t="s">
-        <x:v>16</x:v>
+        <x:v>123</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:3">
@@ -2284,10 +2344,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B65" t="s">
-        <x:v>228</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C65" t="s">
-        <x:v>8</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:3">
@@ -2295,10 +2355,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B66" t="s">
-        <x:v>203</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C66" t="s">
-        <x:v>9</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:3">
@@ -2306,10 +2366,10 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B67" t="s">
-        <x:v>220</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C67" t="s">
-        <x:v>17</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:3">
@@ -2317,10 +2377,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B68" t="s">
-        <x:v>201</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C68" t="s">
-        <x:v>40</x:v>
+        <x:v>153</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:3">
@@ -2328,10 +2388,10 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B69" t="s">
-        <x:v>90</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C69" t="s">
-        <x:v>34</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:3">
@@ -2339,10 +2399,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B70" t="s">
-        <x:v>164</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C70" t="s">
-        <x:v>50</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:3">
@@ -2350,10 +2410,10 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B71" t="s">
-        <x:v>95</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C71" t="s">
-        <x:v>157</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:3">
@@ -2361,10 +2421,10 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B72" t="s">
-        <x:v>257</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C72" t="s">
-        <x:v>160</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:3">
@@ -2372,10 +2432,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B73" t="s">
-        <x:v>262</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="C73" t="s">
-        <x:v>147</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:3">
@@ -2383,10 +2443,10 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B74" t="s">
-        <x:v>233</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C74" t="s">
-        <x:v>227</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:3">
@@ -2394,10 +2454,10 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B75" t="s">
-        <x:v>92</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C75" t="s">
-        <x:v>151</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:3">
@@ -2405,10 +2465,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="B76" t="s">
-        <x:v>89</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="C76" t="s">
-        <x:v>154</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:8">
@@ -2416,10 +2476,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B77" t="s">
-        <x:v>103</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="C77" t="s">
-        <x:v>31</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="G77" s="2"/>
       <x:c r="H77" s="2"/>
@@ -2429,10 +2489,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B78" t="s">
-        <x:v>111</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C78" t="s">
-        <x:v>197</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="G78" s="2"/>
       <x:c r="H78" s="2"/>
@@ -2442,10 +2502,10 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B79" t="s">
-        <x:v>105</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C79" t="s">
-        <x:v>32</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="G79" s="2"/>
       <x:c r="H79" s="2"/>
@@ -2455,10 +2515,10 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B80" t="s">
-        <x:v>124</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="C80" t="s">
-        <x:v>45</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="G80" s="2"/>
       <x:c r="H80" s="2"/>
@@ -2468,10 +2528,10 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="B81" t="s">
-        <x:v>99</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C81" t="s">
-        <x:v>194</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="G81" s="2"/>
       <x:c r="H81" s="2"/>
@@ -2481,10 +2541,10 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B82" t="s">
-        <x:v>176</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="C82" t="s">
-        <x:v>204</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G82" s="2"/>
       <x:c r="H82" s="2"/>
@@ -2494,10 +2554,10 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B83" t="s">
-        <x:v>120</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="C83" t="s">
-        <x:v>38</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="G83" s="2"/>
       <x:c r="H83" s="2"/>
@@ -2507,10 +2567,10 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B84" t="s">
-        <x:v>137</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="C84" t="s">
-        <x:v>10</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="G84" s="2"/>
       <x:c r="H84" s="2"/>
@@ -2520,10 +2580,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B85" t="s">
-        <x:v>129</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C85" t="s">
-        <x:v>54</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G85" s="2"/>
       <x:c r="H85" s="2"/>
@@ -2533,10 +2593,10 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B86" t="s">
-        <x:v>109</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C86" t="s">
-        <x:v>41</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="G86" s="2"/>
       <x:c r="H86" s="2"/>
@@ -2546,10 +2606,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B87" t="s">
-        <x:v>113</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="C87" t="s">
-        <x:v>52</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="G87" s="2"/>
       <x:c r="H87" s="2"/>
@@ -2559,10 +2619,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B88" t="s">
-        <x:v>173</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="C88" t="s">
-        <x:v>6</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G88" s="2"/>
       <x:c r="H88" s="2"/>
@@ -2572,10 +2632,10 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="B89" t="s">
-        <x:v>118</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C89" t="s">
-        <x:v>18</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="G89" s="2"/>
       <x:c r="H89" s="2"/>
@@ -2585,10 +2645,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B90" t="s">
-        <x:v>238</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C90" t="s">
-        <x:v>47</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="G90" s="2"/>
       <x:c r="H90" s="2"/>
@@ -2598,10 +2658,10 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="B91" t="s">
-        <x:v>236</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C91" t="s">
-        <x:v>27</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="G91" s="2"/>
       <x:c r="H91" s="2"/>
@@ -2611,10 +2671,10 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="B92" t="s">
-        <x:v>241</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C92" t="s">
-        <x:v>221</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G92" s="2"/>
       <x:c r="H92" s="2"/>
@@ -2624,10 +2684,10 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="B93" t="s">
-        <x:v>232</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C93" s="2" t="s">
-        <x:v>91</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="G93" s="2"/>
       <x:c r="H93" s="2"/>
@@ -2637,10 +2697,10 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="B94" t="s">
-        <x:v>235</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C94" s="2" t="s">
-        <x:v>254</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="G94" s="2"/>
       <x:c r="H94" s="2"/>
@@ -2650,10 +2710,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B95" t="s">
-        <x:v>237</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C95" s="2" t="s">
-        <x:v>213</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="G95" s="2"/>
       <x:c r="H95" s="2"/>
@@ -2663,10 +2723,10 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="B96" t="s">
-        <x:v>121</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="C96" t="s">
-        <x:v>161</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G96" s="2"/>
       <x:c r="H96" s="2"/>
@@ -2676,10 +2736,10 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="B97" t="s">
-        <x:v>100</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="C97" t="s">
-        <x:v>156</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G97" s="2"/>
       <x:c r="H97" s="2"/>
@@ -2689,10 +2749,10 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="B98" t="s">
-        <x:v>102</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C98" t="s">
-        <x:v>202</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G98" s="2"/>
       <x:c r="H98" s="2"/>
@@ -2702,10 +2762,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B99" t="s">
-        <x:v>119</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C99" t="s">
-        <x:v>243</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G99" s="2"/>
       <x:c r="H99" s="2"/>
@@ -2715,10 +2775,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="B100" t="s">
-        <x:v>132</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C100" t="s">
-        <x:v>82</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:3">
@@ -2726,10 +2786,10 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="B101" t="s">
-        <x:v>136</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C101" t="s">
-        <x:v>87</x:v>
+        <x:v>178</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:3">
@@ -2737,10 +2797,10 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="B102" s="2" t="s">
-        <x:v>104</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="C102" t="s">
-        <x:v>62</x:v>
+        <x:v>247</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:3">
@@ -2748,10 +2808,10 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="B103" s="2" t="s">
-        <x:v>125</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="C103" t="s">
-        <x:v>61</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:3">
@@ -2759,10 +2819,10 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="B104" s="2" t="s">
-        <x:v>115</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="C104" t="s">
-        <x:v>68</x:v>
+        <x:v>176</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:3">
@@ -2770,10 +2830,10 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="B105" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="C105" t="s">
-        <x:v>81</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:3">
@@ -2781,10 +2841,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B106" s="2" t="s">
-        <x:v>131</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C106" t="s">
-        <x:v>141</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:3">
@@ -2792,10 +2852,10 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="B107" s="2" t="s">
-        <x:v>139</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C107" t="s">
-        <x:v>140</x:v>
+        <x:v>243</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:3">
@@ -2803,10 +2863,10 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="B108" s="2" t="s">
-        <x:v>123</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="C108" t="s">
-        <x:v>65</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:3">
@@ -2814,10 +2874,10 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="B109" s="2" t="s">
-        <x:v>107</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="C109" t="s">
-        <x:v>78</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:3">
@@ -2825,10 +2885,10 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="B110" s="2" t="s">
-        <x:v>117</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="C110" t="s">
-        <x:v>70</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:3">
@@ -2836,10 +2896,10 @@
         <x:v>109</x:v>
       </x:c>
       <x:c r="B111" s="2" t="s">
-        <x:v>112</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="C111" t="s">
-        <x:v>79</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:3">
@@ -2847,10 +2907,10 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="B112" s="2" t="s">
-        <x:v>108</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="C112" t="s">
-        <x:v>84</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:3">
@@ -2858,10 +2918,10 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="B113" s="2" t="s">
-        <x:v>101</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C113" t="s">
-        <x:v>72</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:3">
@@ -2869,10 +2929,10 @@
         <x:v>112</x:v>
       </x:c>
       <x:c r="B114" s="2" t="s">
-        <x:v>130</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C114" t="s">
-        <x:v>64</x:v>
+        <x:v>174</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:3">
@@ -2880,10 +2940,10 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="B115" s="2" t="s">
-        <x:v>175</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="C115" t="s">
-        <x:v>74</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:3">
@@ -2891,10 +2951,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B116" s="2" t="s">
-        <x:v>133</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C116" t="s">
-        <x:v>69</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:3">
@@ -2902,10 +2962,10 @@
         <x:v>115</x:v>
       </x:c>
       <x:c r="B117" s="2" t="s">
-        <x:v>181</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C117" t="s">
-        <x:v>71</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:3">
@@ -2913,10 +2973,10 @@
         <x:v>116</x:v>
       </x:c>
       <x:c r="B118" s="2" t="s">
-        <x:v>182</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="C118" t="s">
-        <x:v>85</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:3">
@@ -2924,10 +2984,10 @@
         <x:v>117</x:v>
       </x:c>
       <x:c r="B119" s="2" t="s">
-        <x:v>127</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C119" t="s">
-        <x:v>77</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:3">
@@ -2935,10 +2995,10 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="B120" s="2" t="s">
-        <x:v>122</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="C120" t="s">
-        <x:v>67</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:3">
@@ -2946,10 +3006,10 @@
         <x:v>119</x:v>
       </x:c>
       <x:c r="B121" s="2" t="s">
-        <x:v>179</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C121" t="s">
-        <x:v>142</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:3">
@@ -2957,10 +3017,10 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="B122" s="2" t="s">
-        <x:v>128</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C122" t="s">
-        <x:v>83</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:3">
@@ -2968,10 +3028,10 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="B123" s="2" t="s">
-        <x:v>174</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="C123" t="s">
-        <x:v>58</x:v>
+        <x:v>171</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:3">
@@ -2979,10 +3039,10 @@
         <x:v>122</x:v>
       </x:c>
       <x:c r="B124" s="2" t="s">
-        <x:v>126</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C124" t="s">
-        <x:v>57</x:v>
+        <x:v>169</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:14">
@@ -2990,10 +3050,10 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="B125" s="2" t="s">
-        <x:v>106</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="C125" s="3" t="s">
-        <x:v>59</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="N125" s="4"/>
     </x:row>
@@ -3002,10 +3062,10 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="B126" s="2" t="s">
-        <x:v>116</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C126" s="2" t="s">
-        <x:v>88</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="N126" s="2"/>
     </x:row>
@@ -3014,10 +3074,10 @@
         <x:v>125</x:v>
       </x:c>
       <x:c r="B127" s="2" t="s">
-        <x:v>178</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="C127" s="4" t="s">
-        <x:v>66</x:v>
+        <x:v>177</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:3">
@@ -3025,10 +3085,10 @@
         <x:v>126</x:v>
       </x:c>
       <x:c r="B128" s="2" t="s">
-        <x:v>114</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="C128" t="s">
-        <x:v>0</x:v>
+        <x:v>181</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:3">
@@ -3036,10 +3096,10 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="B129" s="2" t="s">
-        <x:v>97</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="C129" s="3" t="s">
-        <x:v>75</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:3">
@@ -3047,10 +3107,10 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="B130" s="2" t="s">
-        <x:v>110</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="C130" t="s">
-        <x:v>1</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:3">
@@ -3058,10 +3118,10 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="B131" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="C131" t="s">
-        <x:v>2</x:v>
+        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:3">
@@ -3069,10 +3129,10 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="B132" s="2" t="s">
-        <x:v>98</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="C132" s="3" t="s">
-        <x:v>86</x:v>
+        <x:v>179</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:3">
@@ -3080,10 +3140,10 @@
         <x:v>131</x:v>
       </x:c>
       <x:c r="B133" s="2" t="s">
-        <x:v>242</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C133" t="s">
-        <x:v>145</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:3">
@@ -3091,10 +3151,10 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="B134" s="2" t="s">
-        <x:v>180</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C134" s="3" t="s">
-        <x:v>73</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:3">
@@ -3102,10 +3162,10 @@
         <x:v>133</x:v>
       </x:c>
       <x:c r="B135" s="2" t="s">
-        <x:v>177</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="C135" s="3" t="s">
-        <x:v>80</x:v>
+        <x:v>182</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:3">
@@ -3113,10 +3173,10 @@
         <x:v>134</x:v>
       </x:c>
       <x:c r="B136" s="2" t="s">
-        <x:v>60</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="C136" t="s">
-        <x:v>265</x:v>
+        <x:v>173</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:3">
@@ -3124,10 +3184,10 @@
         <x:v>135</x:v>
       </x:c>
       <x:c r="B137" s="2" t="s">
-        <x:v>266</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C137" t="s">
-        <x:v>76</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:3">
@@ -3135,11 +3195,127 @@
         <x:v>136</x:v>
       </x:c>
       <x:c r="B138" s="2" t="s">
-        <x:v>63</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="C138" t="s">
-        <x:v>3</x:v>
-      </x:c>
+        <x:v>248</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" spans="1:3">
+      <x:c r="A139">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B139" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C139" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" spans="1:3">
+      <x:c r="A140">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="B140" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="C140" t="s">
+        <x:v>279</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" spans="1:3">
+      <x:c r="A141">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="B141" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="C141" t="s">
+        <x:v>281</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142" spans="1:3">
+      <x:c r="A142">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="B142" s="2" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="C142" t="s">
+        <x:v>278</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" spans="1:3">
+      <x:c r="A143">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="B143" s="2" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="C143" s="3" t="s">
+        <x:v>286</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" spans="1:3">
+      <x:c r="A144">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="B144" s="2" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="C144" t="s">
+        <x:v>167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" spans="1:3">
+      <x:c r="A145">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="B145" s="2" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="C145" t="s">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" spans="1:3">
+      <x:c r="A146">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="B146" s="2" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="C146" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" spans="1:3">
+      <x:c r="A147">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="B147" s="2" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="C147" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" spans="1:3">
+      <x:c r="A148">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="B148" s="2" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C148" t="s">
+        <x:v>282</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" spans="2:2">
+      <x:c r="B149" s="2"/>
+    </x:row>
+    <x:row r="150" spans="2:2">
+      <x:c r="B150" s="2"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51138889789581298828" footer="0.51138889789581298828"/>

--- a/morpg/morpg/Assets/TableData/Table_Text.xlsx
+++ b/morpg/morpg/Assets/TableData/Table_Text.xlsx
@@ -21,865 +21,865 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="287">
   <x:si>
+    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 대지의 종족 '티모르'의 생존저.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 바다의 종족 '셀레나'의 생존자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'본세계' 내에서, '종말전쟁'의 결말을 지켜보던 강력한 존재들을 일컫는 용어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 창공의 종족 '투르카'의 생존자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'본세계' 내에서 최초로 기록된 내전. 이로 인해 '불의 종족' 카르툼이 절멸하였다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>드래곤을 포함해도 모든 종족 중에서는 물리력 최강의 종족 '바드락'의 생존자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'헤디 벤만 오프 모스' 출신, 역사상 가장 위대한 무인이라 불리는 자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써 '태양절맥'을 갖고 태어난 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써 '구음절맥'을 갖고 태어난 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term006_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term005_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>encyclopedia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이라 모스 강제 개폐 사건</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KaroukWingent</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DemonFighter</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RoutonWinner</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RightEarring</x:t>
+  </x:si>
+  <x:si>
+    <x:t>???????????????</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term007_Title</x:t>
+  </x:si>
+  <x:si>
     <x:t>Term004_Title</x:t>
   </x:si>
   <x:si>
-    <x:t>Term003_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term006_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RightEarring</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DemonFighter</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term002_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>???????????????</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KaroukWingent</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RoutonWinner</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term005_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term001_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term007_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이라 모스 강제 개폐 사건</x:t>
-  </x:si>
-  <x:si>
-    <x:t>encyclopedia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 바다의 종족 '셀레나'의 생존자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'본세계' 내에서, '종말전쟁'의 결말을 지켜보던 강력한 존재들을 일컫는 용어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 창공의 종족 '투르카'의 생존자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'본세계' 내에서 최초로 기록된 내전. 이로 인해 '불의 종족' 카르툼이 절멸하였다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 대지의 종족 '티모르'의 생존저.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써 '구음절맥'을 갖고 태어난 존재.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>드래곤을 포함해도 모든 종족 중에서는 물리력 최강의 종족 '바드락'의 생존자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써 '태양절맥'을 갖고 태어난 존재.</x:t>
+    <x:t>Character001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Desc_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마법의 신, 제샤스 데이틴의 일곱 제자들이 일으킨 내전. 이로 인해 세상의 모든 기록이 소실되어 사실상 모든 것이 초기화되었다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자기 자신의 직계자손에 한정하여, 자신의 기억과 인격을 전달하는 '전생술'을 개발한 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 불튼이 버금가는 탱킹 능력에 '피를 입는 자'에 버금하는 물리력을 지닌 雷계열 근거리 딜러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 지닌 능력 중 대부분이 상처를 치유하고 아군을 버프, 적을 디버프하는 水계열 후방 서포터.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초심극점을 마주하고 바라보고 있는 다른 세상, '역세계'와의 전쟁.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'아키르고 베니아'가 아닌 때에 '이라 모스'를 개설한 충격으로 '본세계' 바깥의 세상이 무너져버린 사건.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>144년을 주기로 돌아오는 초자연 현상. 이 기간 중에는 성공적인 '이라 모스'의 개폐가 가능해진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그의 일정범위에 존재하는 모든 사물은 점점 느려지기  시작하고 그 본인은 그 속도만큼 점점 빨라진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History</x:t>
+  </x:si>
+  <x:si>
+    <x:t>창조신 'NM'이 창조한 11개로 겹쳐진 우리의 세상.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'본세계'와 '역세계'를 잇는 유일한 물리적 이동공간.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>창조신 'OM'이 창조한 초심극점 너머의 다른 세상.</x:t>
   </x:si>
   <x:si>
     <x:t>Character004_Desc_001</x:t>
   </x:si>
   <x:si>
+    <x:t>Character001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character002_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'종말전쟁'이 끝난 이후의 시대가 되며 사실상 유명무실한 용어가 되어 사실상 강력한 힘을 지닌 '초월자'들을 일컫는 용어가 되었다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>늑대신이라 불리는 자. '짐토'가 '위대한 과실'의 생산 원리를 알아내고 그것을 독점하기 전까지, 사실상 유일한 '위대한 과실'의 유통을 담당했다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전 세계에서도 극히 발견하기 어려웠던 과실. 먹는 이의 모든 질병과 상처를 회복해주고, 육체를 가장 건강하던 때로 고정하며 새로운 수명을 하사한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 능력 중 대부분이 공격에 치중된 火계열 중거리 딜러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:죽어도 되살아나는 자. 역사상 최초의 '초월자'이자 무한하게 강해지는 '암흑대제'의 원형.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>평화로운 시기에도 전 세계에 그 개체 수가 5마리를 넘기지 못하던 이 세상 유일의 '초소수종'</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 자가방어와 자가치유에 치중된 地계열 순수 탱커.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:암흑대제. 이 세상에서 유일하게 힘을 비축하는 시간에 비례하여 무한히 강해질 수 있는 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'본세계' 내의 다른 10개의 세계와의 연락을 차단했음에도 가장 독자적인 업적을 이룩한 대륙.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:금속왕. 긴가르시온이 조립한 완전 기계인간 다만 이 세상에서 유일하게 전신이 '완벽한 신의 금속'으로 이뤄져서 모든 것을 무시할 수준의 방어력을 지니고 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa007_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa010_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa005_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa006_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa014_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa011_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa013_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa013_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa001_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa009_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa010_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa008_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa006_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa013_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa005_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa009_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa002_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa010_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term007_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term007_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa014_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa011_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa007_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa009_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa014_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa011_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GaremenTooskaDin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term006_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term005_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa007_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa008_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa008_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:시간의 마왕. 우리의 세상인 '본세계'와 '역세계'에서도 하나 이상을 찾아볼 수 없는 절대유일의 시간 능력자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이 세상 모든 것을 중독시키는 '페이튼'에 중독되어 스스로 의사를 갖고 움직이기 시작한 종족 '래머'의 마지막 생존자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>샤이나 반 고드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LeftRing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NarosaFomos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 공격보다 정찰에 특화된 공격력보다는 연타에 치중한 風계열 서포터.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 대장. 전투에 필요한 전반적인 능력을 두루 갖춘 氷계열 원거리 딜러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화룡왕이라 불리는 자. 악신룡 '지크리피언'에게 육체는 소멸 당하고, 육체가 아닌 정신만으로 살아있는 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">역사에 기록될 정도로 강한 힘을 지닌, 무한히 강해질 수 있는 능력을 지닌 9성 대장, '암흑대제'의 영부인. </x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:유령왕. 태생적으로 '산도라의 후예'인 대마도사였으나 그의 스승인 '푸 그레이'가 서술한 '초마도의 서'를 이해하여 마법사 중 최강의 존재인 '초마도사'가 되었다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 그가 공격의사를 갖던 말던 그의 주변에 존재하는 것만으로도 해독이 불가능한 '페이튼'에 중독되어 모든 존재가 소멸한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gingarsion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Archmage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아키르고 베니아</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GrenFomos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hidden002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Summoner</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DemonMage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>버그리포트 바로가기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LeftEarring</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Alchemist</x:t>
+  </x:si>
+  <x:si>
+    <x:t>notEmployed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RightRIng</x:t>
+  </x:si>
+  <x:si>
+    <x:t>헤디 벤만 오프 모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bugreport</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hidden001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>continue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IreanSorin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가레멘 투스카 딘</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Assassin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CodeName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Equipment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Necromancer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Species&amp;Job</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Necklace</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tartaros</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BultonKajon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:현명한 현자. 모든 코크루와 중 유일의 비전투원. 다만 이제는 기억하는 사람도 없는 '본카 일족'의 족장 '짐토'로써 사실상 이 세상의 모든 학문과 기술은 그로부터 비롯된 것이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제 와서는 이 세상에 절대유일한 '핏빛혈족의 유일한 생존자' 무시무시한 이능력을 지니고 있지만 그가 지닌 이능력의 정체를 아는 자를 이제는 찾을 수 없다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:피를 입는 자. '본세계'와 '역세계'를 모두 포함해서도 비슷한 수준의 신체능력을 가진 존재를 찾기 힘들 정도로 압도적인 신체능력을 가지고 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>원래라면 죽었을 때 다시 되살아나지만, 죽을 경우 다시는 되살아나지 못하는 것을 조건으로 강력한 힘을 얻어 그의 희생으로 '종말전쟁'에서 승리할 수 있었다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소환술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>menu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Human</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종족전쟁</x:t>
+  </x:si>
+  <x:si>
+    <x:t>귀걸이(우)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rodec</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종말전쟁</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세이렌 알트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카루크 뷘젠트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불러오기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이어하기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>?????</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코크루와</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Selena</x:t>
+  </x:si>
+  <x:si>
+    <x:t>load</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dragon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Head</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Leather</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대마도사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Toorka</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Index</x:t>
+  </x:si>
+  <x:si>
+    <x:t>save</x:t>
+  </x:si>
+  <x:si>
+    <x:t>강령술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cloth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sandora</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Redinin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>exit</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Unknown</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대마도전쟁</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>newgame</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Korean</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Renod</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Priest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타르타로스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Species</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Boots</x:t>
+  </x:si>
+  <x:si>
+    <x:t>위대한 과실</x:t>
+  </x:si>
+  <x:si>
+    <x:t>반지(좌)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Demon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Archer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Array</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Plate</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마족 마법사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Badrak</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Comment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Warrior</x:t>
+  </x:si>
+  <x:si>
+    <x:t>귀걸이(좌)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>긴가르시온</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초심극점</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마족 전사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나로사 포모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gloves</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rogue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그렌 포모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Armor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타이틀로 이동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연금술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>반지(우)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이레안 소린</x:t>
+  </x:si>
+  <x:si>
+    <x:t>option</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라우톤 윈너</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Machine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새 시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에를로네</x:t>
+  </x:si>
+  <x:si>
+    <x:t>copy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종족&amp;직업</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Perth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Teemole</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ehrlone</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Weapon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kalapok</x:t>
+  </x:si>
+  <x:si>
+    <x:t>산도라 태생</x:t>
+  </x:si>
+  <x:si>
+    <x:t>title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불튼 카존</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카루크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도적</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종료</x:t>
+  </x:si>
+  <x:si>
     <x:t>흉켈링</x:t>
   </x:si>
   <x:si>
-    <x:t>늑대신이라 불리는 자. '짐토'가 '위대한 과실'의 생산 원리를 알아내고 그것을 독점하기 전까지, 사실상 유일한 '위대한 과실'의 유통을 담당했다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:금속왕. 긴가르시온이 조립한 완전 기계인간 다만 이 세상에서 유일하게 전신이 '완벽한 신의 금속'으로 이뤄져서 모든 것을 무시할 수준의 방어력을 지니고 있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마법의 신, 제샤스 데이틴의 일곱 제자들이 일으킨 내전. 이로 인해 세상의 모든 기록이 소실되어 사실상 모든 것이 초기화되었다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 불튼이 버금가는 탱킹 능력에 '피를 입는 자'에 버금하는 물리력을 지닌 雷계열 근거리 딜러.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 지닌 능력 중 대부분이 상처를 치유하고 아군을 버프, 적을 디버프하는 水계열 후방 서포터.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:시간의 마왕. 우리의 세상인 '본세계'와 '역세계'에서도 하나 이상을 찾아볼 수 없는 절대유일의 시간 능력자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이 세상 모든 것을 중독시키는 '페이튼'에 중독되어 스스로 의사를 갖고 움직이기 시작한 종족 '래머'의 마지막 생존자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>menu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소환술사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Human</x:t>
-  </x:si>
-  <x:si>
-    <x:t>세이렌 알트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Leather</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카루크 뷘젠트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cloth</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Unknown</x:t>
-  </x:si>
-  <x:si>
-    <x:t>exit</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Index</x:t>
-  </x:si>
-  <x:si>
-    <x:t>save</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Head</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대마도사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대마도전쟁</x:t>
-  </x:si>
-  <x:si>
-    <x:t>귀걸이(우)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불러오기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종족전쟁</x:t>
-  </x:si>
-  <x:si>
-    <x:t>강령술사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코크루와</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rodec</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Toorka</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sandora</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이어하기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>?????</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종말전쟁</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Selena</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Redinin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Dragon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>load</x:t>
-  </x:si>
-  <x:si>
-    <x:t>귀걸이(좌)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연금술사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>term</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Badrak</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Array</x:t>
-  </x:si>
-  <x:si>
-    <x:t>newgame</x:t>
-  </x:si>
-  <x:si>
-    <x:t>반지(좌)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그렌 포모스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gloves</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타이틀로 이동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Korean</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타르타로스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마족 마법사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Demon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>긴가르시온</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rogue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Archer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Plate</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Armor</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Renod</x:t>
-  </x:si>
-  <x:si>
-    <x:t>반지(우)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Priest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이레안 소린</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Species</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Comment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Boots</x:t>
-  </x:si>
-  <x:si>
-    <x:t>위대한 과실</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Warrior</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>초심극점</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마족 전사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나로사 포모스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>option</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Weapon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>copy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ehrlone</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라우톤 윈너</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종족&amp;직업</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cocruwa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Teemole</x:t>
-  </x:si>
-  <x:si>
-    <x:t>history</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Machine</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에를로네</x:t>
-  </x:si>
-  <x:si>
-    <x:t>title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Perth</x:t>
-  </x:si>
-  <x:si>
-    <x:t>산도라 태생</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불튼 카존</x:t>
-  </x:si>
-  <x:si>
-    <x:t>새 시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kalapok</x:t>
-  </x:si>
-  <x:si>
-    <x:t>초심극점을 마주하고 바라보고 있는 다른 세상, '역세계'와의 전쟁.</x:t>
-  </x:si>
-  <x:si>
     <x:t>판금</x:t>
   </x:si>
   <x:si>
     <x:t>마법사</x:t>
   </x:si>
   <x:si>
-    <x:t>카루크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도적</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종료</x:t>
-  </x:si>
-  <x:si>
     <x:t>레노드</x:t>
   </x:si>
   <x:si>
+    <x:t>기계</x:t>
+  </x:si>
+  <x:si>
     <x:t>int</x:t>
   </x:si>
   <x:si>
-    <x:t>기계</x:t>
+    <x:t>라우톤</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나로사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>암살자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도감</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로데크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>드래곤</x:t>
+  </x:si>
+  <x:si>
+    <x:t>티모르</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>페르스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>머리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가레멘</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장비</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인물</x:t>
+  </x:si>
+  <x:si>
+    <x:t>궁수</x:t>
   </x:si>
   <x:si>
     <x:t>목걸이</x:t>
   </x:si>
   <x:si>
-    <x:t>라우톤</x:t>
+    <x:t>무기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불튼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무직</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장갑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>용어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>셀레나</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>본세계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초월자</x:t>
   </x:si>
   <x:si>
     <x:t>Job</x:t>
   </x:si>
   <x:si>
-    <x:t>무직</x:t>
-  </x:si>
-  <x:si>
     <x:t>신발</x:t>
   </x:si>
   <x:si>
-    <x:t>인간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>암살자</x:t>
-  </x:si>
-  <x:si>
     <x:t>천</x:t>
   </x:si>
   <x:si>
-    <x:t>인물</x:t>
-  </x:si>
-  <x:si>
-    <x:t>궁수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>티모르</x:t>
-  </x:si>
-  <x:si>
-    <x:t>본세계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>저장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불튼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>로데크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>페르스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나로사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장갑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가레멘</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>머리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도감</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>용어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>드래곤</x:t>
-  </x:si>
-  <x:si>
-    <x:t>초월자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장비</x:t>
-  </x:si>
-  <x:si>
-    <x:t>셀레나</x:t>
+    <x:t>마왕족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>투르카</x:t>
+  </x:si>
+  <x:si>
+    <x:t>올베인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>바드락</x:t>
+  </x:si>
+  <x:si>
+    <x:t>직업</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가죽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>성직자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>역사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>백랑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이레안</x:t>
+  </x:si>
+  <x:si>
+    <x:t>메뉴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그렌</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레디닌</x:t>
+  </x:si>
+  <x:si>
+    <x:t>갑옷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>역세계</x:t>
   </x:si>
   <x:si>
     <x:t>마족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>성직자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>직업</x:t>
-  </x:si>
-  <x:si>
-    <x:t>투르카</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레디닌</x:t>
-  </x:si>
-  <x:si>
-    <x:t>갑옷</x:t>
-  </x:si>
-  <x:si>
-    <x:t>바드락</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가죽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>역세계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이레안</x:t>
-  </x:si>
-  <x:si>
-    <x:t>역사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마왕족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그렌</x:t>
-  </x:si>
-  <x:si>
-    <x:t>메뉴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character004_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자기 자신의 직계자손에 한정하여, 자신의 기억과 인격을 전달하는 '전생술'을 개발한 존재.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character001_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>창조신 'OM'이 창조한 초심극점 너머의 다른 세상.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'본세계'와 '역세계'를 잇는 유일한 물리적 이동공간.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>창조신 'NM'이 창조한 11개로 겹쳐진 우리의 세상.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>평화로운 시기에도 전 세계에 그 개체 수가 5마리를 넘기지 못하던 이 세상 유일의 '초소수종'</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:죽어도 되살아나는 자. 역사상 최초의 '초월자'이자 무한하게 강해지는 '암흑대제'의 원형.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 자가방어와 자가치유에 치중된 地계열 순수 탱커.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 능력 중 대부분이 공격에 치중된 火계열 중거리 딜러.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:암흑대제. 이 세상에서 유일하게 힘을 비축하는 시간에 비례하여 무한히 강해질 수 있는 존재.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'본세계' 내의 다른 10개의 세계와의 연락을 차단했음에도 가장 독자적인 업적을 이룩한 대륙.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그의 일정범위에 존재하는 모든 사물은 점점 느려지기  시작하고 그 본인은 그 속도만큼 점점 빨라진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'아키르고 베니아'가 아닌 때에 '이라 모스'를 개설한 충격으로 '본세계' 바깥의 세상이 무너져버린 사건.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>144년을 주기로 돌아오는 초자연 현상. 이 기간 중에는 성공적인 '이라 모스'의 개폐가 가능해진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전 세계에서도 극히 발견하기 어려웠던 과실. 먹는 이의 모든 질병과 상처를 회복해주고, 육체를 가장 건강하던 때로 고정하며 새로운 수명을 하사한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'종말전쟁'이 끝난 이후의 시대가 되며 사실상 유명무실한 용어가 되어 사실상 강력한 힘을 지닌 '초월자'들을 일컫는 용어가 되었다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character002_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 공격보다 정찰에 특화된 공격력보다는 연타에 치중한 風계열 서포터.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 대장. 전투에 필요한 전반적인 능력을 두루 갖춘 氷계열 원거리 딜러.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa005_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa001_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa011_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa001_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa013_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa010_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa006_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa013_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa014_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa004_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa002_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa011_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa011_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GaremenTooskaDin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History001_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa009_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa008_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa003_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term007_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa004_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa007_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term006_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa006_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History003_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term007_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa010_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa010_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term001_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term002_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term005_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History004_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa013_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History003_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa014_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa005_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa001_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa009_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa009_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa014_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History001_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa008_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa002_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History002_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa002_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History004_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa003_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa008_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa007_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa007_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term003_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term004_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History002_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Desc_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character001_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:현명한 현자. 모든 코크루와 중 유일의 비전투원. 다만 이제는 기억하는 사람도 없는 '본카 일족'의 족장 '짐토'로써 사실상 이 세상의 모든 학문과 기술은 그로부터 비롯된 것이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:유령왕. 태생적으로 '산도라의 후예'인 대마도사였으나 그의 스승인 '푸 그레이'가 서술한 '초마도의 서'를 이해하여 마법사 중 최강의 존재인 '초마도사'가 되었다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 그가 공격의사를 갖던 말던 그의 주변에 존재하는 것만으로도 해독이 불가능한 '페이튼'에 중독되어 모든 존재가 소멸한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이제 와서는 이 세상에 절대유일한 '핏빛혈족의 유일한 생존자' 무시무시한 이능력을 지니고 있지만 그가 지닌 이능력의 정체를 아는 자를 이제는 찾을 수 없다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:피를 입는 자. '본세계'와 '역세계'를 모두 포함해서도 비슷한 수준의 신체능력을 가진 존재를 찾기 힘들 정도로 압도적인 신체능력을 가지고 있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>원래라면 죽었을 때 다시 되살아나지만, 죽을 경우 다시는 되살아나지 못하는 것을 조건으로 강력한 힘을 얻어 그의 희생으로 '종말전쟁'에서 승리할 수 있었다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character003_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hidden002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Archmage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아키르고 베니아</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GrenFomos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Summoner</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gingarsion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DemonMage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>버그리포트 바로가기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Alchemist</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LeftEarring</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RightRIng</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Necklace</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bugreport</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tartaros</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Species&amp;Job</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IreanSorin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>헤디 벤만 오프 모스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hidden001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Assassin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>continue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BultonKajon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>notEmployed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가레멘 투스카 딘</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CodeName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Equipment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Necromancer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NarosaFomos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LeftRing</x:t>
-  </x:si>
-  <x:si>
-    <x:t>백랑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>샤이나 반 고드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character003_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">역사에 기록될 정도로 강한 힘을 지닌, 무한히 강해질 수 있는 능력을 지닌 9성 대장, '암흑대제'의 영부인. </x:t>
-  </x:si>
-  <x:si>
-    <x:t>화룡왕이라 불리는 자. 악신룡 '지크리피언'에게 육체는 소멸 당하고, 육체가 아닌 정신만으로 살아있는 존재.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character002_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character002_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>올베인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'헤디 벤만 오프 모스' 출신, 역사상 가장 위대한 무인이라 불리는 자.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1641,31 +1641,31 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>273</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="D2" s="1"/>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -1673,7 +1673,7 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="B4" s="1"/>
       <x:c r="C4" s="1"/>
@@ -1684,10 +1684,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" t="s">
-        <x:v>66</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C5" t="s">
-        <x:v>109</x:v>
+        <x:v>217</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
@@ -1695,10 +1695,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" t="s">
-        <x:v>269</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C6" t="s">
-        <x:v>54</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
@@ -1706,10 +1706,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" t="s">
-        <x:v>93</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="C7" t="s">
-        <x:v>145</x:v>
+        <x:v>241</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
@@ -1717,10 +1717,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" t="s">
-        <x:v>40</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C8" t="s">
-        <x:v>116</x:v>
+        <x:v>232</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
@@ -1728,10 +1728,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B9" t="s">
-        <x:v>42</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C9" t="s">
-        <x:v>134</x:v>
+        <x:v>243</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
@@ -1739,10 +1739,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B10" t="s">
-        <x:v>60</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="C10" t="s">
-        <x:v>47</x:v>
+        <x:v>163</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
@@ -1750,10 +1750,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B11" t="s">
-        <x:v>96</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="C11" t="s">
-        <x:v>131</x:v>
+        <x:v>264</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
@@ -1761,10 +1761,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B12" t="s">
-        <x:v>32</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C12" t="s">
-        <x:v>165</x:v>
+        <x:v>281</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
@@ -1772,10 +1772,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B13" t="s">
-        <x:v>105</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="C13" s="2" t="s">
-        <x:v>70</x:v>
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
@@ -1783,10 +1783,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B14" t="s">
-        <x:v>262</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C14" t="s">
-        <x:v>257</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
@@ -1794,10 +1794,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B15" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C15" t="s">
-        <x:v>144</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
@@ -1805,10 +1805,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B16" t="s">
-        <x:v>100</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C16" t="s">
-        <x:v>149</x:v>
+        <x:v>267</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
@@ -1816,10 +1816,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B17" t="s">
-        <x:v>63</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C17" t="s">
-        <x:v>146</x:v>
+        <x:v>262</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
@@ -1827,10 +1827,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B18" t="s">
-        <x:v>102</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C18" t="s">
-        <x:v>162</x:v>
+        <x:v>278</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
@@ -1838,10 +1838,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B19" t="s">
-        <x:v>80</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C19" t="s">
-        <x:v>117</x:v>
+        <x:v>236</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
@@ -1849,10 +1849,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B20" t="s">
-        <x:v>263</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C20" t="s">
-        <x:v>72</x:v>
+        <x:v>188</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
@@ -1860,10 +1860,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B21" t="s">
-        <x:v>58</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C21" t="s">
-        <x:v>156</x:v>
+        <x:v>283</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
@@ -1871,10 +1871,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B22" t="s">
-        <x:v>106</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C22" t="s">
-        <x:v>137</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
@@ -1882,10 +1882,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B23" t="s">
-        <x:v>97</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C23" t="s">
-        <x:v>104</x:v>
+        <x:v>218</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
@@ -1893,10 +1893,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B24" t="s">
-        <x:v>255</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C24" t="s">
-        <x:v>75</x:v>
+        <x:v>202</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
@@ -1904,10 +1904,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B25" t="s">
-        <x:v>253</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C25" t="s">
-        <x:v>68</x:v>
+        <x:v>208</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
@@ -1915,10 +1915,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B26" t="s">
-        <x:v>276</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C26" t="s">
-        <x:v>92</x:v>
+        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
@@ -1926,10 +1926,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B27" t="s">
-        <x:v>265</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C27" t="s">
-        <x:v>83</x:v>
+        <x:v>213</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
@@ -1937,10 +1937,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B28" t="s">
-        <x:v>270</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C28" t="s">
-        <x:v>108</x:v>
+        <x:v>229</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3">
@@ -1948,10 +1948,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B29" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C29" t="s">
-        <x:v>37</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">
@@ -1959,10 +1959,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B30" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C30" t="s">
-        <x:v>98</x:v>
+        <x:v>215</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
@@ -1970,10 +1970,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B31" t="s">
-        <x:v>201</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C31" t="s">
-        <x:v>272</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:3">
@@ -1981,10 +1981,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B32" t="s">
-        <x:v>84</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C32" t="s">
-        <x:v>147</x:v>
+        <x:v>266</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:3">
@@ -1992,10 +1992,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B33" t="s">
-        <x:v>122</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C33" t="s">
-        <x:v>154</x:v>
+        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:3">
@@ -2003,10 +2003,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B34" t="s">
-        <x:v>267</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C34" t="s">
-        <x:v>55</x:v>
+        <x:v>165</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:3">
@@ -2014,10 +2014,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B35" t="s">
-        <x:v>250</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C35" t="s">
-        <x:v>6</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:3">
@@ -2025,10 +2025,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B36" t="s">
-        <x:v>271</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C36" t="s">
-        <x:v>123</x:v>
+        <x:v>260</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:3">
@@ -2036,10 +2036,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B37" t="s">
-        <x:v>274</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C37" t="s">
-        <x:v>150</x:v>
+        <x:v>254</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:3">
@@ -2047,10 +2047,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B38" t="s">
-        <x:v>264</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C38" t="s">
-        <x:v>99</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:3">
@@ -2058,10 +2058,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B39" t="s">
-        <x:v>38</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C39" t="s">
-        <x:v>127</x:v>
+        <x:v>270</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:3">
@@ -2069,10 +2069,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B40" t="s">
-        <x:v>36</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="C40" t="s">
-        <x:v>159</x:v>
+        <x:v>276</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:3">
@@ -2080,10 +2080,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B41" t="s">
-        <x:v>78</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="C41" t="s">
-        <x:v>112</x:v>
+        <x:v>234</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:3">
@@ -2091,10 +2091,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B42" t="s">
-        <x:v>94</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="C42" t="s">
-        <x:v>130</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:3">
@@ -2102,10 +2102,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B43" t="s">
-        <x:v>43</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="C43" t="s">
-        <x:v>143</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:3">
@@ -2113,10 +2113,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B44" t="s">
-        <x:v>79</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="C44" t="s">
-        <x:v>157</x:v>
+        <x:v>284</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:3">
@@ -2124,10 +2124,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B45" t="s">
-        <x:v>69</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="C45" t="s">
-        <x:v>140</x:v>
+        <x:v>261</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:3">
@@ -2135,10 +2135,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B46" t="s">
-        <x:v>86</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C46" t="s">
-        <x:v>124</x:v>
+        <x:v>269</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:3">
@@ -2146,10 +2146,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B47" t="s">
-        <x:v>277</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C47" t="s">
-        <x:v>67</x:v>
+        <x:v>192</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:3">
@@ -2157,10 +2157,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B48" t="s">
-        <x:v>260</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C48" t="s">
-        <x:v>81</x:v>
+        <x:v>212</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:3">
@@ -2168,10 +2168,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B49" t="s">
-        <x:v>259</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C49" t="s">
-        <x:v>61</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:3">
@@ -2179,10 +2179,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B50" t="s">
-        <x:v>3</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C50" t="s">
-        <x:v>46</x:v>
+        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:3">
@@ -2190,10 +2190,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B51" t="s">
-        <x:v>261</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C51" t="s">
-        <x:v>120</x:v>
+        <x:v>257</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:3">
@@ -2201,10 +2201,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B52" s="2" t="s">
-        <x:v>34</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C52" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:3">
@@ -2212,10 +2212,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B53" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C53" t="s">
-        <x:v>136</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:3">
@@ -2223,10 +2223,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B54" s="2" t="s">
-        <x:v>52</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C54" t="s">
-        <x:v>155</x:v>
+        <x:v>272</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:3">
@@ -2234,10 +2234,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B55" t="s">
-        <x:v>101</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="C55" t="s">
-        <x:v>132</x:v>
+        <x:v>247</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:3">
@@ -2245,10 +2245,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B56" t="s">
-        <x:v>57</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="C56" t="s">
-        <x:v>151</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:3">
@@ -2256,10 +2256,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B57" t="s">
-        <x:v>64</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="C57" t="s">
-        <x:v>158</x:v>
+        <x:v>274</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:3">
@@ -2267,10 +2267,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B58" t="s">
-        <x:v>103</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="C58" t="s">
-        <x:v>119</x:v>
+        <x:v>237</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:3">
@@ -2278,10 +2278,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B59" t="s">
-        <x:v>74</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C59" t="s">
-        <x:v>152</x:v>
+        <x:v>286</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:3">
@@ -2289,10 +2289,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B60" t="s">
-        <x:v>53</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C60" t="s">
-        <x:v>107</x:v>
+        <x:v>227</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:3">
@@ -2300,10 +2300,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B61" t="s">
-        <x:v>59</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="C61" t="s">
-        <x:v>148</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:3">
@@ -2311,10 +2311,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B62" t="s">
-        <x:v>110</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="C62" t="s">
-        <x:v>163</x:v>
+        <x:v>271</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:3">
@@ -2322,10 +2322,10 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B63" t="s">
-        <x:v>39</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C63" t="s">
-        <x:v>142</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:3">
@@ -2333,10 +2333,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B64" t="s">
-        <x:v>271</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C64" t="s">
-        <x:v>123</x:v>
+        <x:v>260</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:3">
@@ -2344,10 +2344,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B65" t="s">
-        <x:v>88</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="C65" t="s">
-        <x:v>139</x:v>
+        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:3">
@@ -2355,10 +2355,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B66" t="s">
-        <x:v>77</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C66" t="s">
-        <x:v>129</x:v>
+        <x:v>256</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:3">
@@ -2366,10 +2366,10 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B67" t="s">
-        <x:v>89</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C67" t="s">
-        <x:v>113</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:3">
@@ -2377,10 +2377,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B68" t="s">
-        <x:v>82</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C68" t="s">
-        <x:v>153</x:v>
+        <x:v>277</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:3">
@@ -2388,10 +2388,10 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B69" t="s">
-        <x:v>268</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C69" t="s">
-        <x:v>126</x:v>
+        <x:v>242</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:3">
@@ -2399,10 +2399,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B70" t="s">
-        <x:v>76</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C70" t="s">
-        <x:v>115</x:v>
+        <x:v>231</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:3">
@@ -2410,10 +2410,10 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B71" t="s">
-        <x:v>254</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C71" t="s">
-        <x:v>33</x:v>
+        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:3">
@@ -2421,10 +2421,10 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B72" t="s">
-        <x:v>258</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C72" t="s">
-        <x:v>62</x:v>
+        <x:v>211</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:3">
@@ -2432,10 +2432,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B73" t="s">
-        <x:v>275</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C73" t="s">
-        <x:v>49</x:v>
+        <x:v>176</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:3">
@@ -2443,10 +2443,10 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B74" t="s">
-        <x:v>4</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C74" t="s">
-        <x:v>91</x:v>
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:3">
@@ -2454,10 +2454,10 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B75" t="s">
-        <x:v>256</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C75" t="s">
-        <x:v>73</x:v>
+        <x:v>197</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:3">
@@ -2465,10 +2465,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="B76" t="s">
-        <x:v>251</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C76" t="s">
-        <x:v>44</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:8">
@@ -2476,10 +2476,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B77" t="s">
-        <x:v>224</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C77" t="s">
-        <x:v>117</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="G77" s="2"/>
       <x:c r="H77" s="2"/>
@@ -2489,10 +2489,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B78" t="s">
-        <x:v>230</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C78" t="s">
-        <x:v>72</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="G78" s="2"/>
       <x:c r="H78" s="2"/>
@@ -2502,10 +2502,10 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B79" t="s">
-        <x:v>205</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C79" t="s">
-        <x:v>156</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="G79" s="2"/>
       <x:c r="H79" s="2"/>
@@ -2515,10 +2515,10 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B80" t="s">
-        <x:v>196</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C80" t="s">
-        <x:v>137</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G80" s="2"/>
       <x:c r="H80" s="2"/>
@@ -2528,10 +2528,10 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="B81" t="s">
-        <x:v>223</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C81" t="s">
-        <x:v>104</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="G81" s="2"/>
       <x:c r="H81" s="2"/>
@@ -2541,10 +2541,10 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B82" t="s">
-        <x:v>211</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C82" t="s">
-        <x:v>75</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="G82" s="2"/>
       <x:c r="H82" s="2"/>
@@ -2554,10 +2554,10 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B83" t="s">
-        <x:v>209</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C83" t="s">
-        <x:v>164</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="G83" s="2"/>
       <x:c r="H83" s="2"/>
@@ -2567,10 +2567,10 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B84" t="s">
-        <x:v>204</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C84" t="s">
-        <x:v>138</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="G84" s="2"/>
       <x:c r="H84" s="2"/>
@@ -2580,10 +2580,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B85" t="s">
-        <x:v>203</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C85" t="s">
-        <x:v>161</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="G85" s="2"/>
       <x:c r="H85" s="2"/>
@@ -2593,10 +2593,10 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B86" t="s">
-        <x:v>215</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C86" t="s">
-        <x:v>135</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="G86" s="2"/>
       <x:c r="H86" s="2"/>
@@ -2606,10 +2606,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B87" t="s">
-        <x:v>200</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C87" t="s">
-        <x:v>114</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="G87" s="2"/>
       <x:c r="H87" s="2"/>
@@ -2619,10 +2619,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B88" t="s">
-        <x:v>206</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C88" t="s">
-        <x:v>121</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="G88" s="2"/>
       <x:c r="H88" s="2"/>
@@ -2632,10 +2632,10 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="B89" t="s">
-        <x:v>220</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C89" t="s">
-        <x:v>141</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="G89" s="2"/>
       <x:c r="H89" s="2"/>
@@ -2645,10 +2645,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B90" t="s">
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C90" t="s">
-        <x:v>133</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="G90" s="2"/>
       <x:c r="H90" s="2"/>
@@ -2658,10 +2658,10 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="B91" t="s">
-        <x:v>5</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C91" t="s">
-        <x:v>160</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="G91" s="2"/>
       <x:c r="H91" s="2"/>
@@ -2671,10 +2671,10 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="B92" t="s">
-        <x:v>1</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C92" t="s">
-        <x:v>90</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="G92" s="2"/>
       <x:c r="H92" s="2"/>
@@ -2684,10 +2684,10 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="B93" t="s">
-        <x:v>0</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C93" s="2" t="s">
-        <x:v>252</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="G93" s="2"/>
       <x:c r="H93" s="2"/>
@@ -2697,10 +2697,10 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="B94" t="s">
-        <x:v>9</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C94" s="2" t="s">
-        <x:v>266</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="G94" s="2"/>
       <x:c r="H94" s="2"/>
@@ -2710,10 +2710,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B95" t="s">
-        <x:v>2</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C95" s="2" t="s">
-        <x:v>87</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="G95" s="2"/>
       <x:c r="H95" s="2"/>
@@ -2723,10 +2723,10 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="B96" t="s">
-        <x:v>202</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C96" t="s">
-        <x:v>48</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="G96" s="2"/>
       <x:c r="H96" s="2"/>
@@ -2736,10 +2736,10 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="B97" t="s">
-        <x:v>231</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C97" t="s">
-        <x:v>45</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="G97" s="2"/>
       <x:c r="H97" s="2"/>
@@ -2749,10 +2749,10 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="B98" t="s">
-        <x:v>221</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C98" t="s">
-        <x:v>56</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="G98" s="2"/>
       <x:c r="H98" s="2"/>
@@ -2762,10 +2762,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B99" t="s">
-        <x:v>233</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C99" t="s">
-        <x:v>12</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G99" s="2"/>
       <x:c r="H99" s="2"/>
@@ -2775,10 +2775,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="B100" t="s">
-        <x:v>189</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C100" t="s">
-        <x:v>30</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:3">
@@ -2786,10 +2786,10 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="B101" t="s">
-        <x:v>187</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C101" t="s">
-        <x:v>178</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:3">
@@ -2797,10 +2797,10 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="B102" s="2" t="s">
-        <x:v>232</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C102" t="s">
-        <x:v>247</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:3">
@@ -2808,10 +2808,10 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="B103" s="2" t="s">
-        <x:v>197</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C103" t="s">
-        <x:v>246</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:3">
@@ -2819,10 +2819,10 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="B104" s="2" t="s">
-        <x:v>234</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C104" t="s">
-        <x:v>176</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:3">
@@ -2830,10 +2830,10 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="B105" s="2" t="s">
-        <x:v>208</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C105" t="s">
-        <x:v>25</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:3">
@@ -2841,10 +2841,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B106" s="2" t="s">
-        <x:v>186</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C106" t="s">
-        <x:v>244</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:3">
@@ -2852,10 +2852,10 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="B107" s="2" t="s">
-        <x:v>193</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C107" t="s">
-        <x:v>243</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:3">
@@ -2863,10 +2863,10 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="B108" s="2" t="s">
-        <x:v>236</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C108" t="s">
-        <x:v>175</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:3">
@@ -2874,10 +2874,10 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="B109" s="2" t="s">
-        <x:v>237</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C109" t="s">
-        <x:v>21</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:3">
@@ -2885,10 +2885,10 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="B110" s="2" t="s">
-        <x:v>235</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C110" t="s">
-        <x:v>185</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:3">
@@ -2896,10 +2896,10 @@
         <x:v>109</x:v>
       </x:c>
       <x:c r="B111" s="2" t="s">
-        <x:v>229</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C111" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:3">
@@ -2907,10 +2907,10 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="B112" s="2" t="s">
-        <x:v>226</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C112" t="s">
-        <x:v>29</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:3">
@@ -2918,10 +2918,10 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="B113" s="2" t="s">
-        <x:v>225</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C113" t="s">
-        <x:v>14</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:3">
@@ -2929,10 +2929,10 @@
         <x:v>112</x:v>
       </x:c>
       <x:c r="B114" s="2" t="s">
-        <x:v>191</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C114" t="s">
-        <x:v>174</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:3">
@@ -2940,10 +2940,10 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="B115" s="2" t="s">
-        <x:v>214</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C115" t="s">
-        <x:v>18</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:3">
@@ -2951,10 +2951,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B116" s="2" t="s">
-        <x:v>199</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C116" t="s">
-        <x:v>184</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:3">
@@ -2962,10 +2962,10 @@
         <x:v>115</x:v>
       </x:c>
       <x:c r="B117" s="2" t="s">
-        <x:v>188</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C117" t="s">
-        <x:v>16</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:3">
@@ -2973,10 +2973,10 @@
         <x:v>116</x:v>
       </x:c>
       <x:c r="B118" s="2" t="s">
-        <x:v>198</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C118" t="s">
-        <x:v>28</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:3">
@@ -2984,10 +2984,10 @@
         <x:v>117</x:v>
       </x:c>
       <x:c r="B119" s="2" t="s">
-        <x:v>192</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C119" t="s">
-        <x:v>20</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:3">
@@ -2995,10 +2995,10 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="B120" s="2" t="s">
-        <x:v>241</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C120" t="s">
-        <x:v>172</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:3">
@@ -3006,10 +3006,10 @@
         <x:v>119</x:v>
       </x:c>
       <x:c r="B121" s="2" t="s">
-        <x:v>194</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C121" t="s">
-        <x:v>245</x:v>
+        <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:3">
@@ -3017,10 +3017,10 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="B122" s="2" t="s">
-        <x:v>190</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C122" t="s">
-        <x:v>31</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:3">
@@ -3028,10 +3028,10 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="B123" s="2" t="s">
-        <x:v>216</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C123" t="s">
-        <x:v>171</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:3">
@@ -3039,10 +3039,10 @@
         <x:v>122</x:v>
       </x:c>
       <x:c r="B124" s="2" t="s">
-        <x:v>217</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C124" t="s">
-        <x:v>169</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:14">
@@ -3050,10 +3050,10 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="B125" s="2" t="s">
-        <x:v>238</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C125" s="3" t="s">
-        <x:v>170</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="N125" s="4"/>
     </x:row>
@@ -3062,10 +3062,10 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="B126" s="2" t="s">
-        <x:v>239</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C126" s="2" t="s">
-        <x:v>180</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="N126" s="2"/>
     </x:row>
@@ -3074,10 +3074,10 @@
         <x:v>125</x:v>
       </x:c>
       <x:c r="B127" s="2" t="s">
-        <x:v>218</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C127" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:3">
@@ -3085,10 +3085,10 @@
         <x:v>126</x:v>
       </x:c>
       <x:c r="B128" s="2" t="s">
-        <x:v>210</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C128" t="s">
-        <x:v>181</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:3">
@@ -3096,10 +3096,10 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="B129" s="2" t="s">
-        <x:v>228</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C129" s="3" t="s">
-        <x:v>17</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:3">
@@ -3107,10 +3107,10 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="B130" s="2" t="s">
-        <x:v>240</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C130" t="s">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:3">
@@ -3118,10 +3118,10 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="B131" s="2" t="s">
-        <x:v>212</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C131" t="s">
-        <x:v>111</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:3">
@@ -3129,10 +3129,10 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="B132" s="2" t="s">
-        <x:v>219</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C132" s="3" t="s">
-        <x:v>179</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:3">
@@ -3140,10 +3140,10 @@
         <x:v>131</x:v>
       </x:c>
       <x:c r="B133" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C133" t="s">
-        <x:v>50</x:v>
+        <x:v>166</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:3">
@@ -3151,10 +3151,10 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="B134" s="2" t="s">
-        <x:v>207</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C134" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:3">
@@ -3162,10 +3162,10 @@
         <x:v>133</x:v>
       </x:c>
       <x:c r="B135" s="2" t="s">
-        <x:v>213</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C135" s="3" t="s">
-        <x:v>182</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:3">
@@ -3173,10 +3173,10 @@
         <x:v>134</x:v>
       </x:c>
       <x:c r="B136" s="2" t="s">
-        <x:v>222</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C136" t="s">
-        <x:v>173</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:3">
@@ -3184,10 +3184,10 @@
         <x:v>135</x:v>
       </x:c>
       <x:c r="B137" s="2" t="s">
-        <x:v>195</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C137" t="s">
-        <x:v>35</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:3">
@@ -3195,10 +3195,10 @@
         <x:v>136</x:v>
       </x:c>
       <x:c r="B138" s="2" t="s">
-        <x:v>227</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C138" t="s">
-        <x:v>248</x:v>
+        <x:v>153</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:3">
@@ -3206,10 +3206,10 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="B139" t="s">
-        <x:v>27</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C139" t="s">
-        <x:v>128</x:v>
+        <x:v>255</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:3">
@@ -3217,10 +3217,10 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="B140" t="s">
-        <x:v>242</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C140" t="s">
-        <x:v>279</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:3">
@@ -3228,10 +3228,10 @@
         <x:v>139</x:v>
       </x:c>
       <x:c r="B141" t="s">
-        <x:v>168</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C141" t="s">
-        <x:v>281</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:3">
@@ -3239,10 +3239,10 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="B142" s="2" t="s">
-        <x:v>283</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C142" t="s">
-        <x:v>278</x:v>
+        <x:v>279</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:3">
@@ -3250,10 +3250,10 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="B143" s="2" t="s">
-        <x:v>183</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C143" s="3" t="s">
-        <x:v>286</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:3">
@@ -3261,10 +3261,10 @@
         <x:v>142</x:v>
       </x:c>
       <x:c r="B144" s="2" t="s">
-        <x:v>284</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C144" t="s">
-        <x:v>167</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:3">
@@ -3272,10 +3272,10 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="B145" s="2" t="s">
-        <x:v>280</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C145" t="s">
-        <x:v>285</x:v>
+        <x:v>273</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:3">
@@ -3283,10 +3283,10 @@
         <x:v>144</x:v>
       </x:c>
       <x:c r="B146" s="2" t="s">
-        <x:v>249</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C146" t="s">
-        <x:v>24</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:3">
@@ -3294,10 +3294,10 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="B147" s="2" t="s">
-        <x:v>166</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C147" t="s">
-        <x:v>23</x:v>
+        <x:v>233</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:3">
@@ -3305,10 +3305,10 @@
         <x:v>146</x:v>
       </x:c>
       <x:c r="B148" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C148" t="s">
-        <x:v>282</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="2:2">

--- a/morpg/morpg/Assets/TableData/Table_Text.xlsx
+++ b/morpg/morpg/Assets/TableData/Table_Text.xlsx
@@ -19,342 +19,750 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="287">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="293">
+  <x:si>
+    <x:t>Etc003_Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써 '구음절맥'을 갖고 태어난 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써 '태양절맥'을 갖고 태어난 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'헤디 벤만 오프 모스' 출신, 역사상 가장 위대한 무인이라 불리는 자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>드래곤을 포함해도 모든 종족 중에서는 물리력 최강의 종족 '바드락'의 생존자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 불튼이 버금가는 탱킹 능력에 '피를 입는 자'에 버금하는 물리력을 지닌 雷계열 근거리 딜러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 지닌 능력 중 대부분이 상처를 치유하고 아군을 버프, 적을 디버프하는 水계열 후방 서포터.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>144년을 주기로 돌아오는 초자연 현상. 이 기간 중에는 성공적인 '이라 모스'의 개폐가 가능해진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'아키르고 베니아'가 아닌 때에 '이라 모스'를 개설한 충격으로 '본세계' 바깥의 세상이 무너져버린 사건.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그의 일정범위에 존재하는 모든 사물은 점점 느려지기  시작하고 그 본인은 그 속도만큼 점점 빨라진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>창조신 'NM'이 창조한 11개로 겹쳐진 우리의 세상.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>창조신 'OM'이 창조한 초심극점 너머의 다른 세상.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'본세계'와 '역세계'를 잇는 유일한 물리적 이동공간.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초심극점을 마주하고 바라보고 있는 다른 세상, '역세계'와의 전쟁.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Desc_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa006_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa007_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa009_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa005_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa014_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa011_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa013_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa013_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa001_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa010_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa009_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa013_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa010_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa008_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa006_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa005_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa002_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa014_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term007_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa014_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa011_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa011_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term007_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GaremenTooskaDin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa008_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term005_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa007_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa009_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa007_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term006_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa008_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa010_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Etc004_Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character002_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소환술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종족전쟁</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Human</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rodec</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세이렌 알트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종말전쟁</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카루크 뷘젠트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>menu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dragon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불러오기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Leather</x:t>
+  </x:si>
+  <x:si>
+    <x:t>save</x:t>
+  </x:si>
+  <x:si>
+    <x:t>강령술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Index</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Toorka</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cloth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이어하기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>load</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코크루와</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sandora</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대마도사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Selena</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Head</x:t>
+  </x:si>
+  <x:si>
+    <x:t>?????</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Plate</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Badrak</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Priest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Species</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Demon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Korean</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Archer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Comment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마족 전사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>exit</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초심극점</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gloves</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마족 마법사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rogue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그렌 포모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나로사 포모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Armor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Boots</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Warrior</x:t>
+  </x:si>
+  <x:si>
+    <x:t>newgame</x:t>
+  </x:si>
+  <x:si>
+    <x:t>위대한 과실</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Array</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Renod</x:t>
+  </x:si>
+  <x:si>
+    <x:t>긴가르시온</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Redinin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타르타로스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대마도전쟁</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Unknown</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이레안 소린</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라우톤 윈너</x:t>
+  </x:si>
+  <x:si>
+    <x:t>copy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종족&amp;직업</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타이틀로 이동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연금술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>option</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Machine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새 시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에를로네</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Weapon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kalapok</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Perth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>산도라 태생</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Teemole</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ehrlone</x:t>
+  </x:si>
+  <x:si>
+    <x:t>title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불튼 카존</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마법의 신, 제샤스 데이틴의 일곱 제자들이 일으킨 내전. 이로 인해 세상의 모든 기록이 소실되어 사실상 모든 것이 초기화되었다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>encyclopedia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KaroukWingent</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>???????????????</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term007_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term006_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DemonFighter</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term005_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이라 모스 강제 개폐 사건</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RoutonWinner</x:t>
+  </x:si>
+  <x:si>
+    <x:t>역사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>올베인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이레안</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레디닌</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가죽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>갑옷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>백랑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>바드락</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그렌</x:t>
+  </x:si>
+  <x:si>
+    <x:t>메뉴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>성직자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>직업</x:t>
+  </x:si>
+  <x:si>
+    <x:t>역세계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>흉켈링</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카루크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레노드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>판금</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라우톤</x:t>
+  </x:si>
+  <x:si>
+    <x:t>암살자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나로사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도감</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마법사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도적</x:t>
+  </x:si>
+  <x:si>
+    <x:t>머리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>드래곤</x:t>
+  </x:si>
+  <x:si>
+    <x:t>페르스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가레멘</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>티모르</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로데크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>용어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무직</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불튼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>셀레나</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장갑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장비</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>궁수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목걸이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인물</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초월자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>본세계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신발</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마왕족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Job</x:t>
+  </x:si>
+  <x:si>
+    <x:t>천</x:t>
+  </x:si>
+  <x:si>
+    <x:t>투르카</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Etc002_Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:금속왕. 긴가르시온이 조립한 완전 기계인간 다만 이 세상에서 유일하게 전신이 '완벽한 신의 금속'으로 이뤄져서 모든 것을 무시할 수준의 방어력을 지니고 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>늑대신이라 불리는 자. '짐토'가 '위대한 과실'의 생산 원리를 알아내고 그것을 독점하기 전까지, 사실상 유일한 '위대한 과실'의 유통을 담당했다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전 세계에서도 극히 발견하기 어려웠던 과실. 먹는 이의 모든 질병과 상처를 회복해주고, 육체를 가장 건강하던 때로 고정하며 새로운 수명을 하사한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:죽어도 되살아나는 자. 역사상 최초의 '초월자'이자 무한하게 강해지는 '암흑대제'의 원형.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 능력 중 대부분이 공격에 치중된 火계열 중거리 딜러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>평화로운 시기에도 전 세계에 그 개체 수가 5마리를 넘기지 못하던 이 세상 유일의 '초소수종'</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 자가방어와 자가치유에 치중된 地계열 순수 탱커.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:암흑대제. 이 세상에서 유일하게 힘을 비축하는 시간에 비례하여 무한히 강해질 수 있는 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'본세계' 내의 다른 10개의 세계와의 연락을 차단했음에도 가장 독자적인 업적을 이룩한 대륙.</x:t>
+  </x:si>
   <x:si>
     <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 대지의 종족 '티모르'의 생존저.</x:t>
   </x:si>
   <x:si>
+    <x:t>'본세계' 내에서, '종말전쟁'의 결말을 지켜보던 강력한 존재들을 일컫는 용어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'본세계' 내에서 최초로 기록된 내전. 이로 인해 '불의 종족' 카르툼이 절멸하였다.</x:t>
+  </x:si>
+  <x:si>
     <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 바다의 종족 '셀레나'의 생존자.</x:t>
   </x:si>
   <x:si>
-    <x:t>'본세계' 내에서, '종말전쟁'의 결말을 지켜보던 강력한 존재들을 일컫는 용어.</x:t>
-  </x:si>
-  <x:si>
     <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 창공의 종족 '투르카'의 생존자.</x:t>
   </x:si>
   <x:si>
-    <x:t>'본세계' 내에서 최초로 기록된 내전. 이로 인해 '불의 종족' 카르툼이 절멸하였다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>드래곤을 포함해도 모든 종족 중에서는 물리력 최강의 종족 '바드락'의 생존자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'헤디 벤만 오프 모스' 출신, 역사상 가장 위대한 무인이라 불리는 자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써 '태양절맥'을 갖고 태어난 존재.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써 '구음절맥'을 갖고 태어난 존재.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term003_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term006_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term005_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term001_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term002_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>encyclopedia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이라 모스 강제 개폐 사건</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KaroukWingent</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DemonFighter</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RoutonWinner</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RightEarring</x:t>
-  </x:si>
-  <x:si>
-    <x:t>???????????????</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term007_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term004_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character001_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character003_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character002_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Desc_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term003_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term004_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History002_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마법의 신, 제샤스 데이틴의 일곱 제자들이 일으킨 내전. 이로 인해 세상의 모든 기록이 소실되어 사실상 모든 것이 초기화되었다.</x:t>
-  </x:si>
-  <x:si>
     <x:t>자기 자신의 직계자손에 한정하여, 자신의 기억과 인격을 전달하는 '전생술'을 개발한 존재.</x:t>
   </x:si>
   <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 불튼이 버금가는 탱킹 능력에 '피를 입는 자'에 버금하는 물리력을 지닌 雷계열 근거리 딜러.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 지닌 능력 중 대부분이 상처를 치유하고 아군을 버프, 적을 디버프하는 水계열 후방 서포터.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>초심극점을 마주하고 바라보고 있는 다른 세상, '역세계'와의 전쟁.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'아키르고 베니아'가 아닌 때에 '이라 모스'를 개설한 충격으로 '본세계' 바깥의 세상이 무너져버린 사건.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>144년을 주기로 돌아오는 초자연 현상. 이 기간 중에는 성공적인 '이라 모스'의 개폐가 가능해진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그의 일정범위에 존재하는 모든 사물은 점점 느려지기  시작하고 그 본인은 그 속도만큼 점점 빨라진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History</x:t>
-  </x:si>
-  <x:si>
-    <x:t>창조신 'NM'이 창조한 11개로 겹쳐진 우리의 세상.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'본세계'와 '역세계'를 잇는 유일한 물리적 이동공간.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>창조신 'OM'이 창조한 초심극점 너머의 다른 세상.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character004_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character001_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character002_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character003_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character002_Desc_002</x:t>
-  </x:si>
-  <x:si>
     <x:t>'종말전쟁'이 끝난 이후의 시대가 되며 사실상 유명무실한 용어가 되어 사실상 강력한 힘을 지닌 '초월자'들을 일컫는 용어가 되었다.</x:t>
   </x:si>
   <x:si>
-    <x:t>늑대신이라 불리는 자. '짐토'가 '위대한 과실'의 생산 원리를 알아내고 그것을 독점하기 전까지, 사실상 유일한 '위대한 과실'의 유통을 담당했다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전 세계에서도 극히 발견하기 어려웠던 과실. 먹는 이의 모든 질병과 상처를 회복해주고, 육체를 가장 건강하던 때로 고정하며 새로운 수명을 하사한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 능력 중 대부분이 공격에 치중된 火계열 중거리 딜러.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:죽어도 되살아나는 자. 역사상 최초의 '초월자'이자 무한하게 강해지는 '암흑대제'의 원형.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>평화로운 시기에도 전 세계에 그 개체 수가 5마리를 넘기지 못하던 이 세상 유일의 '초소수종'</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 자가방어와 자가치유에 치중된 地계열 순수 탱커.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:암흑대제. 이 세상에서 유일하게 힘을 비축하는 시간에 비례하여 무한히 강해질 수 있는 존재.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'본세계' 내의 다른 10개의 세계와의 연락을 차단했음에도 가장 독자적인 업적을 이룩한 대륙.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:금속왕. 긴가르시온이 조립한 완전 기계인간 다만 이 세상에서 유일하게 전신이 '완벽한 신의 금속'으로 이뤄져서 모든 것을 무시할 수준의 방어력을 지니고 있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa007_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa010_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa001_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa005_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa006_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa014_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa011_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character004_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa013_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa013_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa001_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa009_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa010_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History004_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa008_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa006_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa003_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa013_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa005_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa009_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa002_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa010_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa001_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term007_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term007_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa014_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History003_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa011_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa007_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History003_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa009_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa014_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa011_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa004_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa004_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GaremenTooskaDin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History001_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term001_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term006_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term002_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term005_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History001_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa007_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa008_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History002_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa003_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa002_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa002_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa008_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History004_Title</x:t>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 그가 공격의사를 갖던 말던 그의 주변에 존재하는 것만으로도 해독이 불가능한 '페이튼'에 중독되어 모든 존재가 소멸한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:유령왕. 태생적으로 '산도라의 후예'인 대마도사였으나 그의 스승인 '푸 그레이'가 서술한 '초마도의 서'를 이해하여 마법사 중 최강의 존재인 '초마도사'가 되었다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>원래라면 죽었을 때 다시 되살아나지만, 죽을 경우 다시는 되살아나지 못하는 것을 조건으로 강력한 힘을 얻어 그의 희생으로 '종말전쟁'에서 승리할 수 있었다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제 와서는 이 세상에 절대유일한 '핏빛혈족의 유일한 생존자' 무시무시한 이능력을 지니고 있지만 그가 지닌 이능력의 정체를 아는 자를 이제는 찾을 수 없다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:피를 입는 자. '본세계'와 '역세계'를 모두 포함해서도 비슷한 수준의 신체능력을 가진 존재를 찾기 힘들 정도로 압도적인 신체능력을 가지고 있다.</x:t>
   </x:si>
   <x:si>
     <x:t>이명:시간의 마왕. 우리의 세상인 '본세계'와 '역세계'에서도 하나 이상을 찾아볼 수 없는 절대유일의 시간 능력자.</x:t>
@@ -363,31 +771,46 @@
     <x:t>이 세상 모든 것을 중독시키는 '페이튼'에 중독되어 스스로 의사를 갖고 움직이기 시작한 종족 '래머'의 마지막 생존자.</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">역사에 기록될 정도로 강한 힘을 지닌, 무한히 강해질 수 있는 능력을 지닌 9성 대장, '암흑대제'의 영부인. </x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 공격보다 정찰에 특화된 공격력보다는 연타에 치중한 風계열 서포터.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화룡왕이라 불리는 자. 악신룡 '지크리피언'에게 육체는 소멸 당하고, 육체가 아닌 정신만으로 살아있는 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 대장. 전투에 필요한 전반적인 능력을 두루 갖춘 氷계열 원거리 딜러.</x:t>
+  </x:si>
+  <x:si>
     <x:t>샤이나 반 고드</x:t>
   </x:si>
   <x:si>
-    <x:t>LeftRing</x:t>
+    <x:t>DemonMage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>버그리포트 바로가기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Alchemist</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아키르고 베니아</x:t>
   </x:si>
   <x:si>
     <x:t>NarosaFomos</x:t>
   </x:si>
   <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 공격보다 정찰에 특화된 공격력보다는 연타에 치중한 風계열 서포터.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 대장. 전투에 필요한 전반적인 능력을 두루 갖춘 氷계열 원거리 딜러.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화룡왕이라 불리는 자. 악신룡 '지크리피언'에게 육체는 소멸 당하고, 육체가 아닌 정신만으로 살아있는 존재.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">역사에 기록될 정도로 강한 힘을 지닌, 무한히 강해질 수 있는 능력을 지닌 9성 대장, '암흑대제'의 영부인. </x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:유령왕. 태생적으로 '산도라의 후예'인 대마도사였으나 그의 스승인 '푸 그레이'가 서술한 '초마도의 서'를 이해하여 마법사 중 최강의 존재인 '초마도사'가 되었다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 그가 공격의사를 갖던 말던 그의 주변에 존재하는 것만으로도 해독이 불가능한 '페이튼'에 중독되어 모든 존재가 소멸한다.</x:t>
+    <x:t>Hidden002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>notEmployed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GrenFomos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Summoner</x:t>
   </x:si>
   <x:si>
     <x:t>Gingarsion</x:t>
@@ -396,34 +819,16 @@
     <x:t>Archmage</x:t>
   </x:si>
   <x:si>
-    <x:t>아키르고 베니아</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GrenFomos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hidden002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Summoner</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DemonMage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>버그리포트 바로가기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LeftEarring</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Alchemist</x:t>
-  </x:si>
-  <x:si>
-    <x:t>notEmployed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RightRIng</x:t>
+    <x:t>Tartaros</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CodeName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Equipment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Necklace</x:t>
   </x:si>
   <x:si>
     <x:t>헤디 벤만 오프 모스</x:t>
@@ -432,454 +837,67 @@
     <x:t>bugreport</x:t>
   </x:si>
   <x:si>
+    <x:t>Assassin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가레멘 투스카 딘</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BultonKajon</x:t>
+  </x:si>
+  <x:si>
     <x:t>Hidden001</x:t>
   </x:si>
   <x:si>
+    <x:t>Species&amp;Job</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character</x:t>
+  </x:si>
+  <x:si>
     <x:t>continue</x:t>
   </x:si>
   <x:si>
+    <x:t>Necromancer</x:t>
+  </x:si>
+  <x:si>
     <x:t>IreanSorin</x:t>
   </x:si>
   <x:si>
-    <x:t>가레멘 투스카 딘</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Assassin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CodeName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Equipment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Necromancer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Species&amp;Job</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Necklace</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tartaros</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BultonKajon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character</x:t>
-  </x:si>
-  <x:si>
     <x:t>이명:현명한 현자. 모든 코크루와 중 유일의 비전투원. 다만 이제는 기억하는 사람도 없는 '본카 일족'의 족장 '짐토'로써 사실상 이 세상의 모든 학문과 기술은 그로부터 비롯된 것이다.</x:t>
   </x:si>
   <x:si>
-    <x:t>이제 와서는 이 세상에 절대유일한 '핏빛혈족의 유일한 생존자' 무시무시한 이능력을 지니고 있지만 그가 지닌 이능력의 정체를 아는 자를 이제는 찾을 수 없다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:피를 입는 자. '본세계'와 '역세계'를 모두 포함해서도 비슷한 수준의 신체능력을 가진 존재를 찾기 힘들 정도로 압도적인 신체능력을 가지고 있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>원래라면 죽었을 때 다시 되살아나지만, 죽을 경우 다시는 되살아나지 못하는 것을 조건으로 강력한 힘을 얻어 그의 희생으로 '종말전쟁'에서 승리할 수 있었다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소환술사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>menu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Human</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종족전쟁</x:t>
-  </x:si>
-  <x:si>
-    <x:t>귀걸이(우)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rodec</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종말전쟁</x:t>
-  </x:si>
-  <x:si>
-    <x:t>세이렌 알트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카루크 뷘젠트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불러오기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이어하기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>?????</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코크루와</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Selena</x:t>
-  </x:si>
-  <x:si>
-    <x:t>load</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Dragon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Head</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Leather</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대마도사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Toorka</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Index</x:t>
-  </x:si>
-  <x:si>
-    <x:t>save</x:t>
-  </x:si>
-  <x:si>
-    <x:t>강령술사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cloth</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sandora</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Redinin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>exit</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Unknown</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대마도전쟁</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>newgame</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Korean</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Renod</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Priest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타르타로스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Species</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Boots</x:t>
-  </x:si>
-  <x:si>
-    <x:t>위대한 과실</x:t>
-  </x:si>
-  <x:si>
-    <x:t>반지(좌)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Demon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Archer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Array</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Plate</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마족 마법사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Badrak</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Comment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Warrior</x:t>
-  </x:si>
-  <x:si>
-    <x:t>귀걸이(좌)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>긴가르시온</x:t>
-  </x:si>
-  <x:si>
-    <x:t>초심극점</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마족 전사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나로사 포모스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gloves</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rogue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그렌 포모스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Armor</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타이틀로 이동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연금술사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>반지(우)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이레안 소린</x:t>
-  </x:si>
-  <x:si>
-    <x:t>option</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라우톤 윈너</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Machine</x:t>
-  </x:si>
-  <x:si>
-    <x:t>새 시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에를로네</x:t>
-  </x:si>
-  <x:si>
-    <x:t>copy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종족&amp;직업</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Perth</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Teemole</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ehrlone</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Weapon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kalapok</x:t>
-  </x:si>
-  <x:si>
-    <x:t>산도라 태생</x:t>
-  </x:si>
-  <x:si>
-    <x:t>title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불튼 카존</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카루크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도적</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>흉켈링</x:t>
-  </x:si>
-  <x:si>
-    <x:t>판금</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마법사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레노드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라우톤</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나로사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>암살자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>저장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도감</x:t>
-  </x:si>
-  <x:si>
-    <x:t>로데크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>드래곤</x:t>
-  </x:si>
-  <x:si>
-    <x:t>티모르</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>페르스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>머리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가레멘</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장비</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인물</x:t>
-  </x:si>
-  <x:si>
-    <x:t>궁수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>목걸이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불튼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무직</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장갑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>용어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>셀레나</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>본세계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>초월자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Job</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신발</x:t>
-  </x:si>
-  <x:si>
-    <x:t>천</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마왕족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>투르카</x:t>
-  </x:si>
-  <x:si>
-    <x:t>올베인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>바드락</x:t>
-  </x:si>
-  <x:si>
-    <x:t>직업</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가죽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>성직자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>역사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>백랑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이레안</x:t>
-  </x:si>
-  <x:si>
-    <x:t>메뉴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그렌</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레디닌</x:t>
-  </x:si>
-  <x:si>
-    <x:t>갑옷</x:t>
-  </x:si>
-  <x:si>
-    <x:t>역세계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마족</x:t>
+    <x:t>Etc001_Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Etc005_Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ring</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Earring</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잡템005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잡템001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>반지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>귀걸이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잡템003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잡템004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잡템002</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1632,7 +1650,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:N150"/>
+  <x:dimension ref="A1:N151"/>
   <x:sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="16.39999999999999857891"/>
   <x:cols>
     <x:col min="1" max="1" width="8.796875" bestFit="1" customWidth="1"/>
@@ -1641,31 +1659,31 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="1" t="s">
-        <x:v>238</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>225</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>225</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>174</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D2" s="1"/>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -1673,7 +1691,7 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B4" s="1"/>
       <x:c r="C4" s="1"/>
@@ -1684,10 +1702,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" t="s">
-        <x:v>184</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C5" t="s">
-        <x:v>217</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
@@ -1695,10 +1713,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" t="s">
-        <x:v>138</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="C6" t="s">
-        <x:v>164</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
@@ -1706,10 +1724,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" t="s">
-        <x:v>214</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C7" t="s">
-        <x:v>241</x:v>
+        <x:v>188</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
@@ -1717,10 +1735,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" t="s">
-        <x:v>180</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C8" t="s">
-        <x:v>232</x:v>
+        <x:v>183</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
@@ -1728,10 +1746,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B9" t="s">
-        <x:v>175</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C9" t="s">
-        <x:v>243</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
@@ -1739,10 +1757,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B10" t="s">
-        <x:v>168</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C10" t="s">
-        <x:v>163</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
@@ -1750,10 +1768,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B11" t="s">
-        <x:v>219</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C11" t="s">
-        <x:v>264</x:v>
+        <x:v>216</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
@@ -1761,10 +1779,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B12" t="s">
-        <x:v>155</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C12" t="s">
-        <x:v>281</x:v>
+        <x:v>178</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
@@ -1772,10 +1790,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B13" t="s">
-        <x:v>228</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C13" s="2" t="s">
-        <x:v>210</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
@@ -1783,10 +1801,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B14" t="s">
-        <x:v>136</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="C14" t="s">
-        <x:v>130</x:v>
+        <x:v>256</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
@@ -1794,10 +1812,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B15" t="s">
-        <x:v>15</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C15" t="s">
-        <x:v>244</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
@@ -1805,10 +1823,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B16" t="s">
-        <x:v>31</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C16" t="s">
-        <x:v>267</x:v>
+        <x:v>218</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
@@ -1816,10 +1834,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B17" t="s">
-        <x:v>9</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C17" t="s">
-        <x:v>262</x:v>
+        <x:v>207</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
@@ -1827,10 +1845,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B18" t="s">
-        <x:v>40</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C18" t="s">
-        <x:v>278</x:v>
+        <x:v>169</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
@@ -1838,10 +1856,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B19" t="s">
-        <x:v>186</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C19" t="s">
-        <x:v>236</x:v>
+        <x:v>189</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
@@ -1849,10 +1867,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B20" t="s">
-        <x:v>147</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="C20" t="s">
-        <x:v>188</x:v>
+        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
@@ -1860,10 +1878,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B21" t="s">
-        <x:v>179</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C21" t="s">
-        <x:v>283</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
@@ -1871,10 +1889,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B22" t="s">
-        <x:v>221</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C22" t="s">
-        <x:v>249</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
@@ -1882,10 +1900,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B23" t="s">
-        <x:v>223</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C23" t="s">
-        <x:v>218</x:v>
+        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
@@ -1893,10 +1911,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B24" t="s">
-        <x:v>123</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="C24" t="s">
-        <x:v>202</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
@@ -1904,10 +1922,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B25" t="s">
-        <x:v>126</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C25" t="s">
-        <x:v>208</x:v>
+        <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
@@ -1915,10 +1933,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B26" t="s">
-        <x:v>116</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="C26" t="s">
-        <x:v>205</x:v>
+        <x:v>123</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
@@ -1926,10 +1944,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B27" t="s">
-        <x:v>139</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="C27" t="s">
-        <x:v>213</x:v>
+        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
@@ -1937,10 +1955,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B28" t="s">
-        <x:v>148</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C28" t="s">
-        <x:v>229</x:v>
+        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3">
@@ -1948,10 +1966,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B29" t="s">
-        <x:v>17</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="C29" t="s">
-        <x:v>162</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">
@@ -1959,10 +1977,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B30" t="s">
-        <x:v>19</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="C30" t="s">
-        <x:v>215</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
@@ -1970,10 +1988,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B31" t="s">
-        <x:v>97</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C31" t="s">
-        <x:v>140</x:v>
+        <x:v>273</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:3">
@@ -1981,10 +1999,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B32" t="s">
-        <x:v>189</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C32" t="s">
-        <x:v>266</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:3">
@@ -1992,10 +2010,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B33" t="s">
-        <x:v>268</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C33" t="s">
-        <x:v>275</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:3">
@@ -2003,10 +2021,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B34" t="s">
-        <x:v>137</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="C34" t="s">
-        <x:v>165</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:3">
@@ -2014,10 +2032,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B35" t="s">
-        <x:v>127</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C35" t="s">
-        <x:v>21</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:3">
@@ -2025,10 +2043,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B36" t="s">
-        <x:v>133</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="C36" t="s">
-        <x:v>260</x:v>
+        <x:v>208</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:3">
@@ -2036,10 +2054,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B37" t="s">
-        <x:v>143</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C37" t="s">
-        <x:v>254</x:v>
+        <x:v>212</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:3">
@@ -2047,10 +2065,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B38" t="s">
-        <x:v>145</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="C38" t="s">
-        <x:v>220</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:3">
@@ -2058,10 +2076,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B39" t="s">
-        <x:v>177</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C39" t="s">
-        <x:v>270</x:v>
+        <x:v>224</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:3">
@@ -2069,10 +2087,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B40" t="s">
-        <x:v>171</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C40" t="s">
-        <x:v>276</x:v>
+        <x:v>173</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:3">
@@ -2080,10 +2098,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B41" t="s">
-        <x:v>196</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C41" t="s">
-        <x:v>234</x:v>
+        <x:v>190</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:3">
@@ -2091,10 +2109,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B42" t="s">
-        <x:v>224</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C42" t="s">
-        <x:v>258</x:v>
+        <x:v>213</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:3">
@@ -2102,10 +2120,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B43" t="s">
-        <x:v>170</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C43" t="s">
-        <x:v>251</x:v>
+        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:3">
@@ -2113,10 +2131,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B44" t="s">
-        <x:v>209</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C44" t="s">
-        <x:v>284</x:v>
+        <x:v>174</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:3">
@@ -2124,10 +2142,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B45" t="s">
-        <x:v>206</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C45" t="s">
-        <x:v>261</x:v>
+        <x:v>211</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:3">
@@ -2135,10 +2153,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B46" t="s">
-        <x:v>190</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C46" t="s">
-        <x:v>269</x:v>
+        <x:v>221</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:3">
@@ -2146,10 +2164,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B47" t="s">
-        <x:v>115</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="C47" t="s">
-        <x:v>192</x:v>
+        <x:v>288</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:3">
@@ -2157,10 +2175,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B48" t="s">
-        <x:v>134</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="C48" t="s">
-        <x:v>212</x:v>
+        <x:v>289</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:3">
@@ -2168,32 +2186,32 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B49" t="s">
-        <x:v>131</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C49" t="s">
-        <x:v>201</x:v>
+        <x:v>215</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:3">
       <x:c r="A50">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="B50" t="s">
-        <x:v>20</x:v>
+      <x:c r="B50" s="2" t="s">
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C50" t="s">
-        <x:v>158</x:v>
+        <x:v>206</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:3">
       <x:c r="A51">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="B51" t="s">
-        <x:v>146</x:v>
+      <x:c r="B51" s="2" t="s">
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C51" t="s">
-        <x:v>257</x:v>
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:3">
@@ -2201,32 +2219,32 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B52" s="2" t="s">
-        <x:v>156</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C52" t="s">
-        <x:v>252</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:3">
       <x:c r="A53">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="B53" s="2" t="s">
-        <x:v>159</x:v>
+      <x:c r="B53" t="s">
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C53" t="s">
-        <x:v>245</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:3">
       <x:c r="A54">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B54" s="2" t="s">
-        <x:v>173</x:v>
+      <x:c r="B54" t="s">
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C54" t="s">
-        <x:v>272</x:v>
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:3">
@@ -2234,10 +2252,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B55" t="s">
-        <x:v>222</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C55" t="s">
-        <x:v>247</x:v>
+        <x:v>176</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:3">
@@ -2245,10 +2263,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B56" t="s">
-        <x:v>167</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C56" t="s">
-        <x:v>263</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:3">
@@ -2256,10 +2274,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B57" t="s">
-        <x:v>198</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C57" t="s">
-        <x:v>274</x:v>
+        <x:v>182</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:3">
@@ -2267,10 +2285,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B58" t="s">
-        <x:v>216</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C58" t="s">
-        <x:v>237</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:3">
@@ -2278,10 +2296,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B59" t="s">
-        <x:v>193</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C59" t="s">
-        <x:v>286</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:3">
@@ -2289,10 +2307,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B60" t="s">
-        <x:v>178</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C60" t="s">
-        <x:v>227</x:v>
+        <x:v>222</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:3">
@@ -2300,10 +2318,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B61" t="s">
-        <x:v>169</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C61" t="s">
-        <x:v>246</x:v>
+        <x:v>202</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:3">
@@ -2311,10 +2329,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B62" t="s">
-        <x:v>226</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="C62" t="s">
-        <x:v>271</x:v>
+        <x:v>208</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:3">
@@ -2322,10 +2340,10 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B63" t="s">
-        <x:v>181</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C63" t="s">
-        <x:v>250</x:v>
+        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:3">
@@ -2333,10 +2351,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B64" t="s">
-        <x:v>133</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C64" t="s">
-        <x:v>260</x:v>
+        <x:v>214</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:3">
@@ -2344,10 +2362,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B65" t="s">
-        <x:v>200</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C65" t="s">
-        <x:v>248</x:v>
+        <x:v>196</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:3">
@@ -2355,10 +2373,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B66" t="s">
-        <x:v>194</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C66" t="s">
-        <x:v>256</x:v>
+        <x:v>179</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:3">
@@ -2366,10 +2384,10 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B67" t="s">
-        <x:v>183</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="C67" t="s">
-        <x:v>235</x:v>
+        <x:v>192</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:3">
@@ -2377,10 +2395,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B68" t="s">
-        <x:v>187</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C68" t="s">
-        <x:v>277</x:v>
+        <x:v>197</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:3">
@@ -2388,10 +2406,10 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B69" t="s">
-        <x:v>141</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="C69" t="s">
-        <x:v>242</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:3">
@@ -2399,10 +2417,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B70" t="s">
-        <x:v>207</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C70" t="s">
-        <x:v>231</x:v>
+        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:3">
@@ -2410,10 +2428,10 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B71" t="s">
-        <x:v>128</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="C71" t="s">
-        <x:v>154</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:3">
@@ -2421,10 +2439,10 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B72" t="s">
-        <x:v>132</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C72" t="s">
-        <x:v>211</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:3">
@@ -2432,10 +2450,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B73" t="s">
-        <x:v>144</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="C73" t="s">
-        <x:v>176</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:3">
@@ -2443,43 +2461,47 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B74" t="s">
-        <x:v>18</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="C74" t="s">
-        <x:v>204</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="75" spans="1:3">
+        <x:v>103</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:8">
       <x:c r="A75">
         <x:v>71</x:v>
       </x:c>
       <x:c r="B75" t="s">
-        <x:v>129</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C75" t="s">
-        <x:v>197</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="76" spans="1:3">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="G75" s="2"/>
+      <x:c r="H75" s="2"/>
+    </x:row>
+    <x:row r="76" spans="1:8">
       <x:c r="A76">
         <x:v>72</x:v>
       </x:c>
       <x:c r="B76" t="s">
-        <x:v>124</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C76" t="s">
-        <x:v>172</x:v>
-      </x:c>
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="G76" s="2"/>
+      <x:c r="H76" s="2"/>
     </x:row>
     <x:row r="77" spans="1:8">
       <x:c r="A77">
         <x:v>73</x:v>
       </x:c>
       <x:c r="B77" t="s">
-        <x:v>83</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C77" t="s">
-        <x:v>236</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="G77" s="2"/>
       <x:c r="H77" s="2"/>
@@ -2489,10 +2511,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B78" t="s">
-        <x:v>108</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C78" t="s">
-        <x:v>188</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="G78" s="2"/>
       <x:c r="H78" s="2"/>
@@ -2502,10 +2524,10 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B79" t="s">
-        <x:v>76</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C79" t="s">
-        <x:v>283</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="G79" s="2"/>
       <x:c r="H79" s="2"/>
@@ -2515,10 +2537,10 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B80" t="s">
-        <x:v>96</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C80" t="s">
-        <x:v>249</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G80" s="2"/>
       <x:c r="H80" s="2"/>
@@ -2528,10 +2550,10 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="B81" t="s">
-        <x:v>78</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C81" t="s">
-        <x:v>218</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="G81" s="2"/>
       <x:c r="H81" s="2"/>
@@ -2541,10 +2563,10 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B82" t="s">
-        <x:v>75</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C82" t="s">
-        <x:v>202</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="G82" s="2"/>
       <x:c r="H82" s="2"/>
@@ -2554,10 +2576,10 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B83" t="s">
-        <x:v>90</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C83" t="s">
-        <x:v>282</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="G83" s="2"/>
       <x:c r="H83" s="2"/>
@@ -2567,10 +2589,10 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B84" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C84" t="s">
-        <x:v>240</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="G84" s="2"/>
       <x:c r="H84" s="2"/>
@@ -2580,10 +2602,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B85" t="s">
-        <x:v>71</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C85" t="s">
-        <x:v>280</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="G85" s="2"/>
       <x:c r="H85" s="2"/>
@@ -2593,10 +2615,10 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B86" t="s">
-        <x:v>81</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C86" t="s">
-        <x:v>259</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="G86" s="2"/>
       <x:c r="H86" s="2"/>
@@ -2606,10 +2628,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B87" t="s">
-        <x:v>94</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C87" t="s">
-        <x:v>230</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="G87" s="2"/>
       <x:c r="H87" s="2"/>
@@ -2619,10 +2641,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B88" t="s">
-        <x:v>87</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C88" t="s">
-        <x:v>239</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="G88" s="2"/>
       <x:c r="H88" s="2"/>
@@ -2632,10 +2654,10 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="B89" t="s">
-        <x:v>77</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="C89" t="s">
-        <x:v>253</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="G89" s="2"/>
       <x:c r="H89" s="2"/>
@@ -2645,10 +2667,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B90" t="s">
-        <x:v>13</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C90" t="s">
-        <x:v>265</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="G90" s="2"/>
       <x:c r="H90" s="2"/>
@@ -2658,10 +2680,10 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="B91" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C91" t="s">
-        <x:v>285</x:v>
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C91" s="2" t="s">
+        <x:v>258</x:v>
       </x:c>
       <x:c r="G91" s="2"/>
       <x:c r="H91" s="2"/>
@@ -2671,651 +2693,674 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="B92" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C92" t="s">
-        <x:v>203</x:v>
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="C92" s="2" t="s">
+        <x:v>270</x:v>
       </x:c>
       <x:c r="G92" s="2"/>
       <x:c r="H92" s="2"/>
     </x:row>
     <x:row r="93" spans="1:8">
       <x:c r="A93">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B93" t="s">
-        <x:v>23</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C93" s="2" t="s">
-        <x:v>125</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="G93" s="2"/>
       <x:c r="H93" s="2"/>
     </x:row>
     <x:row r="94" spans="1:8">
       <x:c r="A94">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B94" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C94" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C94" t="s">
+        <x:v>82</x:v>
       </x:c>
       <x:c r="G94" s="2"/>
       <x:c r="H94" s="2"/>
     </x:row>
     <x:row r="95" spans="1:8">
       <x:c r="A95">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B95" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C95" s="2" t="s">
-        <x:v>191</x:v>
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C95" t="s">
+        <x:v>134</x:v>
       </x:c>
       <x:c r="G95" s="2"/>
       <x:c r="H95" s="2"/>
     </x:row>
     <x:row r="96" spans="1:8">
       <x:c r="A96">
-        <x:v>94</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B96" t="s">
-        <x:v>98</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C96" t="s">
-        <x:v>157</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="G96" s="2"/>
       <x:c r="H96" s="2"/>
     </x:row>
     <x:row r="97" spans="1:8">
       <x:c r="A97">
-        <x:v>95</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B97" t="s">
-        <x:v>106</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C97" t="s">
-        <x:v>182</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="G97" s="2"/>
       <x:c r="H97" s="2"/>
     </x:row>
-    <x:row r="98" spans="1:8">
+    <x:row r="98" spans="1:3">
       <x:c r="A98">
-        <x:v>96</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B98" t="s">
-        <x:v>91</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C98" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="G98" s="2"/>
-      <x:c r="H98" s="2"/>
-    </x:row>
-    <x:row r="99" spans="1:8">
+        <x:v>248</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:3">
       <x:c r="A99">
-        <x:v>97</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B99" t="s">
-        <x:v>111</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C99" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G99" s="2"/>
-      <x:c r="H99" s="2"/>
+        <x:v>9</x:v>
+      </x:c>
     </x:row>
     <x:row r="100" spans="1:3">
       <x:c r="A100">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="B100" t="s">
-        <x:v>61</x:v>
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="B100" s="2" t="s">
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C100" t="s">
-        <x:v>112</x:v>
+        <x:v>247</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:3">
       <x:c r="A101">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="B101" t="s">
-        <x:v>70</x:v>
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B101" s="2" t="s">
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C101" t="s">
-        <x:v>39</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:3">
       <x:c r="A102">
-        <x:v>100</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B102" s="2" t="s">
-        <x:v>109</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C102" t="s">
-        <x:v>152</x:v>
+        <x:v>234</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:3">
       <x:c r="A103">
-        <x:v>101</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B103" s="2" t="s">
-        <x:v>80</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C103" t="s">
-        <x:v>151</x:v>
+        <x:v>227</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:3">
       <x:c r="A104">
-        <x:v>102</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B104" s="2" t="s">
-        <x:v>107</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C104" t="s">
-        <x:v>56</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:3">
       <x:c r="A105">
-        <x:v>103</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B105" s="2" t="s">
-        <x:v>95</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C105" t="s">
-        <x:v>58</x:v>
+        <x:v>281</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:3">
       <x:c r="A106">
-        <x:v>104</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B106" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C106" t="s">
-        <x:v>121</x:v>
+        <x:v>231</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:3">
       <x:c r="A107">
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B107" s="2" t="s">
-        <x:v>63</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C107" t="s">
-        <x:v>150</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:3">
       <x:c r="A108">
-        <x:v>106</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B108" s="2" t="s">
-        <x:v>104</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C108" t="s">
-        <x:v>52</x:v>
+        <x:v>253</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:3">
       <x:c r="A109">
-        <x:v>107</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B109" s="2" t="s">
-        <x:v>59</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C109" t="s">
-        <x:v>7</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:3">
       <x:c r="A110">
-        <x:v>108</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B110" s="2" t="s">
-        <x:v>110</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C110" t="s">
-        <x:v>118</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:3">
       <x:c r="A111">
-        <x:v>109</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B111" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C111" t="s">
-        <x:v>8</x:v>
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:3">
       <x:c r="A112">
-        <x:v>110</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B112" s="2" t="s">
-        <x:v>92</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C112" t="s">
-        <x:v>35</x:v>
+        <x:v>233</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:3">
       <x:c r="A113">
-        <x:v>111</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B113" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C113" t="s">
-        <x:v>1</x:v>
+        <x:v>236</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:3">
       <x:c r="A114">
-        <x:v>112</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B114" s="2" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C114" t="s">
-        <x:v>55</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:3">
       <x:c r="A115">
-        <x:v>113</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B115" s="2" t="s">
-        <x:v>72</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C115" t="s">
-        <x:v>0</x:v>
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:3">
       <x:c r="A116">
-        <x:v>114</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B116" s="2" t="s">
-        <x:v>89</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C116" t="s">
-        <x:v>117</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:3">
       <x:c r="A117">
-        <x:v>115</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B117" s="2" t="s">
-        <x:v>66</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C117" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:3">
       <x:c r="A118">
-        <x:v>116</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B118" s="2" t="s">
-        <x:v>82</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C118" t="s">
-        <x:v>34</x:v>
+        <x:v>232</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:3">
       <x:c r="A119">
-        <x:v>117</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B119" s="2" t="s">
-        <x:v>64</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C119" t="s">
-        <x:v>5</x:v>
+        <x:v>243</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:3">
       <x:c r="A120">
-        <x:v>118</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B120" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C120" t="s">
-        <x:v>54</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:3">
       <x:c r="A121">
-        <x:v>119</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B121" s="2" t="s">
-        <x:v>68</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C121" t="s">
-        <x:v>122</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:3">
       <x:c r="A122">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="B122" s="2" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C122" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" spans="1:14">
+      <x:c r="A123">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B123" s="2" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C123" s="3" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="N123" s="4"/>
+    </x:row>
+    <x:row r="124" spans="1:14">
+      <x:c r="A124">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="B122" s="2" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C122" t="s">
-        <x:v>113</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="123" spans="1:3">
-      <x:c r="A123">
+      <x:c r="B124" s="2" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C124" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N124" s="2"/>
+    </x:row>
+    <x:row r="125" spans="1:3">
+      <x:c r="A125">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="B123" s="2" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C123" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="124" spans="1:3">
-      <x:c r="A124">
+      <x:c r="B125" s="2" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C125" s="4" t="s">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" spans="1:3">
+      <x:c r="A126">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="B124" s="2" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C124" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="125" spans="1:14">
-      <x:c r="A125">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="B125" s="2" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C125" s="3" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="N125" s="4"/>
-    </x:row>
-    <x:row r="126" spans="1:14">
-      <x:c r="A126">
-        <x:v>124</x:v>
-      </x:c>
       <x:c r="B126" s="2" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C126" s="2" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="N126" s="2"/>
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C126" t="s">
+        <x:v>229</x:v>
+      </x:c>
     </x:row>
     <x:row r="127" spans="1:3">
       <x:c r="A127">
-        <x:v>125</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B127" s="2" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="C127" s="4" t="s">
-        <x:v>57</x:v>
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C127" s="3" t="s">
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:3">
       <x:c r="A128">
-        <x:v>126</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B128" s="2" t="s">
-        <x:v>100</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C128" t="s">
-        <x:v>51</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:3">
       <x:c r="A129">
-        <x:v>127</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B129" s="2" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="C129" s="3" t="s">
-        <x:v>4</x:v>
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C129" t="s">
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:3">
       <x:c r="A130">
-        <x:v>128</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B130" s="2" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C130" t="s">
-        <x:v>32</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C130" s="3" t="s">
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:3">
       <x:c r="A131">
-        <x:v>129</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B131" s="2" t="s">
-        <x:v>88</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C131" t="s">
-        <x:v>36</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:3">
       <x:c r="A132">
-        <x:v>130</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B132" s="2" t="s">
-        <x:v>73</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C132" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>237</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:3">
       <x:c r="A133">
-        <x:v>131</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B133" s="2" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C133" t="s">
-        <x:v>166</x:v>
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C133" s="3" t="s">
+        <x:v>242</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:3">
       <x:c r="A134">
-        <x:v>132</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B134" s="2" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="C134" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C134" t="s">
+        <x:v>230</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:3">
       <x:c r="A135">
-        <x:v>133</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B135" s="2" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="C135" s="3" t="s">
-        <x:v>49</x:v>
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C135" t="s">
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:3">
       <x:c r="A136">
-        <x:v>134</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B136" s="2" t="s">
-        <x:v>86</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C136" t="s">
-        <x:v>53</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:3">
       <x:c r="A137">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="B137" s="2" t="s">
-        <x:v>65</x:v>
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="B137" t="s">
+        <x:v>277</x:v>
       </x:c>
       <x:c r="C137" t="s">
-        <x:v>161</x:v>
+        <x:v>217</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:3">
       <x:c r="A138">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="B138" s="2" t="s">
-        <x:v>93</x:v>
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="B138" t="s">
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C138" t="s">
-        <x:v>153</x:v>
+        <x:v>254</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:3">
       <x:c r="A139">
-        <x:v>137</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B139" t="s">
-        <x:v>149</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C139" t="s">
-        <x:v>255</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:3">
       <x:c r="A140">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="B140" t="s">
-        <x:v>24</x:v>
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="B140" s="2" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C140" t="s">
-        <x:v>114</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:3">
       <x:c r="A141">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="B141" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C141" t="s">
-        <x:v>120</x:v>
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B141" s="2" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C141" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:3">
       <x:c r="A142">
-        <x:v>140</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B142" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C142" t="s">
-        <x:v>279</x:v>
+        <x:v>241</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:3">
       <x:c r="A143">
-        <x:v>141</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B143" s="2" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C143" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C143" t="s">
+        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:3">
       <x:c r="A144">
-        <x:v>142</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B144" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C144" t="s">
-        <x:v>33</x:v>
+        <x:v>228</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:3">
       <x:c r="A145">
-        <x:v>143</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B145" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C145" t="s">
-        <x:v>273</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:3">
       <x:c r="A146">
-        <x:v>144</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B146" s="2" t="s">
-        <x:v>47</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C146" t="s">
-        <x:v>50</x:v>
+        <x:v>252</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:3">
       <x:c r="A147">
-        <x:v>145</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B147" s="2" t="s">
-        <x:v>67</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="C147" t="s">
-        <x:v>233</x:v>
+        <x:v>287</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:3">
       <x:c r="A148">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="B148" s="2" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="C148" t="s">
+        <x:v>292</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" spans="1:3">
+      <x:c r="A149">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="B149" s="2" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C149" t="s">
+        <x:v>290</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" spans="1:3">
+      <x:c r="A150">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="B148" s="2" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C148" t="s">
-        <x:v>119</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="149" spans="2:2">
-      <x:c r="B149" s="2"/>
-    </x:row>
-    <x:row r="150" spans="2:2">
-      <x:c r="B150" s="2"/>
+      <x:c r="B150" s="2" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C150" t="s">
+        <x:v>291</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" spans="1:3">
+      <x:c r="A151">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="B151" s="2" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="C151" t="s">
+        <x:v>286</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51138889789581298828" footer="0.51138889789581298828"/>

--- a/morpg/morpg/Assets/TableData/Table_Text.xlsx
+++ b/morpg/morpg/Assets/TableData/Table_Text.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fileVersion appName="HCell" lastEdited="12.0" lowestEdited="12.0" rupBuild="0.4426"/>
+  <x:fileVersion appName="HCell" lastEdited="12.0" lowestEdited="12.0" rupBuild="0.4547"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
@@ -19,885 +19,903 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="293">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="299">
+  <x:si>
+    <x:t>전체</x:t>
+  </x:si>
+  <x:si>
+    <x:t>늑대신이라 불리는 자. '짐토'가 '위대한 과실'의 생산 원리를 알아내고 그것을 독점하기 전까지, 사실상 유일한 '위대한 과실'의 유통을 담당했다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전 세계에서도 극히 발견하기 어려웠던 과실. 먹는 이의 모든 질병과 상처를 회복해주고, 육체를 가장 건강하던 때로 고정하며 새로운 수명을 하사한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:현명한 현자. 모든 코크루와 중 유일의 비전투원. 다만 이제는 기억하는 사람도 없는 '본카 일족'의 족장 '짐토'로써 사실상 이 세상의 모든 학문과 기술은 그로부터 비롯된 것이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 그가 공격의사를 갖던 말던 그의 주변에 존재하는 것만으로도 해독이 불가능한 '페이튼'에 중독되어 모든 존재가 소멸한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:유령왕. 태생적으로 '산도라의 후예'인 대마도사였으나 그의 스승인 '푸 그레이'가 서술한 '초마도의 서'를 이해하여 마법사 중 최강의 존재인 '초마도사'가 되었다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마법의 신, 제샤스 데이틴의 일곱 제자들이 일으킨 내전. 이로 인해 세상의 모든 기록이 소실되어 사실상 모든 것이 초기화되었다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">역사에 기록될 정도로 강한 힘을 지닌, 무한히 강해질 수 있는 능력을 지닌 9성 대장, '암흑대제'의 영부인. </x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 공격보다 정찰에 특화된 공격력보다는 연타에 치중한 風계열 서포터.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:금속왕. 긴가르시온이 조립한 완전 기계인간 다만 이 세상에서 유일하게 전신이 '완벽한 신의 금속'으로 이뤄져서 모든 것을 무시할 수준의 방어력을 지니고 있다.</x:t>
+  </x:si>
   <x:si>
     <x:t>Etc003_Name</x:t>
   </x:si>
   <x:si>
+    <x:t>Etc004_Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DemonMage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Etc002_Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>샤이나 반 고드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Equipment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NarosaFomos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tartaros</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Necklace</x:t>
+  </x:si>
+  <x:si>
+    <x:t>헤디 벤만 오프 모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>버그리포트 바로가기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Alchemist</x:t>
+  </x:si>
+  <x:si>
+    <x:t>notEmployed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gingarsion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CodeName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GrenFomos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bugreport</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Summoner</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Archmage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hidden002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아키르고 베니아</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hidden001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Assassin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Necromancer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Species&amp;Job</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Etc005_Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BultonKajon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가레멘 투스카 딘</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IreanSorin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>continue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Etc001_Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 불튼이 버금가는 탱킹 능력에 '피를 입는 자'에 버금하는 물리력을 지닌 雷계열 근거리 딜러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 지닌 능력 중 대부분이 상처를 치유하고 아군을 버프, 적을 디버프하는 水계열 후방 서포터.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초심극점을 마주하고 바라보고 있는 다른 세상, '역세계'와의 전쟁.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>144년을 주기로 돌아오는 초자연 현상. 이 기간 중에는 성공적인 '이라 모스'의 개폐가 가능해진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그의 일정범위에 존재하는 모든 사물은 점점 느려지기  시작하고 그 본인은 그 속도만큼 점점 빨라진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'아키르고 베니아'가 아닌 때에 '이라 모스'를 개설한 충격으로 '본세계' 바깥의 세상이 무너져버린 사건.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Etc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>재료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>암살자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>메뉴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>역사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나로사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>바드락</x:t>
+  </x:si>
+  <x:si>
+    <x:t>성직자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>역세계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가죽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이레안</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그렌</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레디닌</x:t>
+  </x:si>
+  <x:si>
+    <x:t>백랑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>직업</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>흉켈링</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카루크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>갑옷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라우톤</x:t>
+  </x:si>
+  <x:si>
+    <x:t>판금</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레노드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>올베인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신발</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>천</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마왕족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도감</x:t>
+  </x:si>
+  <x:si>
+    <x:t>드래곤</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초월자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>본세계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Job</x:t>
+  </x:si>
+  <x:si>
+    <x:t>투르카</x:t>
+  </x:si>
+  <x:si>
+    <x:t>용어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장갑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가레멘</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인물</x:t>
+  </x:si>
+  <x:si>
+    <x:t>페르스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무직</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로데크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>셀레나</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불튼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장비</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>티모르</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도적</x:t>
+  </x:si>
+  <x:si>
+    <x:t>머리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마법사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>궁수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목걸이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>반지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>귀걸이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소모품</x:t>
+  </x:si>
+  <x:si>
+    <x:t>All</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Desc_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa006_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa010_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa005_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa005_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa009_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa010_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa002_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa011_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa014_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa014_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term007_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa007_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa001_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa013_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa009_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa008_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa014_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa013_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa013_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa006_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa008_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GaremenTooskaDin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term006_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa007_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa007_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa011_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa008_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa011_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term007_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa009_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa010_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term005_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화룡왕이라 불리는 자. 악신룡 '지크리피언'에게 육체는 소멸 당하고, 육체가 아닌 정신만으로 살아있는 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 대장. 전투에 필요한 전반적인 능력을 두루 갖춘 氷계열 원거리 딜러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종족전쟁</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이어하기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sandora</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대마도사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종말전쟁</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Index</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rodec</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Selena</x:t>
+  </x:si>
+  <x:si>
+    <x:t>?????</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세이렌 알트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>menu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카루크 뷘젠트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Toorka</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cloth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dragon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Leather</x:t>
+  </x:si>
+  <x:si>
+    <x:t>강령술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소환술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>load</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Head</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코크루와</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Plate</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Human</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불러오기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>save</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대마도전쟁</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Boots</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Badrak</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나로사 포모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Armor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Warrior</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Demon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gloves</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Korean</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그렌 포모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Renod</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Species</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Unknown</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Redinin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라우톤 윈너</x:t>
+  </x:si>
+  <x:si>
+    <x:t>copy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>긴가르시온</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rogue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Comment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Archer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이레안 소린</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초심극점</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종족&amp;직업</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마족 마법사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>exit</x:t>
+  </x:si>
+  <x:si>
+    <x:t>위대한 과실</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Priest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>newgame</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Array</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마족 전사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타르타로스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>option</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Teemole</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잡템003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타이틀로 이동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Machine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새 시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잡템004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Earring</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연금술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kalapok</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Perth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에를로네</x:t>
+  </x:si>
+  <x:si>
+    <x:t>title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ring</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잡템001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불튼 카존</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잡템002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Weapon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잡템005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ehrlone</x:t>
+  </x:si>
+  <x:si>
+    <x:t>산도라 태생</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Consume</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자기 자신의 직계자손에 한정하여, 자신의 기억과 인격을 전달하는 '전생술'을 개발한 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 대지의 종족 '티모르'의 생존저.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'본세계' 내에서 최초로 기록된 내전. 이로 인해 '불의 종족' 카르툼이 절멸하였다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 창공의 종족 '투르카'의 생존자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'본세계' 내에서, '종말전쟁'의 결말을 지켜보던 강력한 존재들을 일컫는 용어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 바다의 종족 '셀레나'의 생존자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:죽어도 되살아나는 자. 역사상 최초의 '초월자'이자 무한하게 강해지는 '암흑대제'의 원형.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:암흑대제. 이 세상에서 유일하게 힘을 비축하는 시간에 비례하여 무한히 강해질 수 있는 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>평화로운 시기에도 전 세계에 그 개체 수가 5마리를 넘기지 못하던 이 세상 유일의 '초소수종'</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 자가방어와 자가치유에 치중된 地계열 순수 탱커.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 능력 중 대부분이 공격에 치중된 火계열 중거리 딜러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'본세계' 내의 다른 10개의 세계와의 연락을 차단했음에도 가장 독자적인 업적을 이룩한 대륙.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RoutonWinner</x:t>
+  </x:si>
+  <x:si>
+    <x:t>???????????????</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term006_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term007_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term005_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이라 모스 강제 개폐 사건</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>encyclopedia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KaroukWingent</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DemonFighter</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써 '태양절맥'을 갖고 태어난 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'헤디 벤만 오프 모스' 출신, 역사상 가장 위대한 무인이라 불리는 자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>드래곤을 포함해도 모든 종족 중에서는 물리력 최강의 종족 '바드락'의 생존자.</x:t>
+  </x:si>
+  <x:si>
     <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써 '구음절맥'을 갖고 태어난 존재.</x:t>
   </x:si>
   <x:si>
-    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써 '태양절맥'을 갖고 태어난 존재.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'헤디 벤만 오프 모스' 출신, 역사상 가장 위대한 무인이라 불리는 자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>드래곤을 포함해도 모든 종족 중에서는 물리력 최강의 종족 '바드락'의 생존자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 불튼이 버금가는 탱킹 능력에 '피를 입는 자'에 버금하는 물리력을 지닌 雷계열 근거리 딜러.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 지닌 능력 중 대부분이 상처를 치유하고 아군을 버프, 적을 디버프하는 水계열 후방 서포터.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>144년을 주기로 돌아오는 초자연 현상. 이 기간 중에는 성공적인 '이라 모스'의 개폐가 가능해진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'아키르고 베니아'가 아닌 때에 '이라 모스'를 개설한 충격으로 '본세계' 바깥의 세상이 무너져버린 사건.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그의 일정범위에 존재하는 모든 사물은 점점 느려지기  시작하고 그 본인은 그 속도만큼 점점 빨라진다.</x:t>
+    <x:t>'종말전쟁'이 끝난 이후의 시대가 되며 사실상 유명무실한 용어가 되어 사실상 강력한 힘을 지닌 '초월자'들을 일컫는 용어가 되었다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character002_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character003_Desc_001</x:t>
   </x:si>
   <x:si>
     <x:t>창조신 'NM'이 창조한 11개로 겹쳐진 우리의 세상.</x:t>
   </x:si>
   <x:si>
+    <x:t>'본세계'와 '역세계'를 잇는 유일한 물리적 이동공간.</x:t>
+  </x:si>
+  <x:si>
     <x:t>창조신 'OM'이 창조한 초심극점 너머의 다른 세상.</x:t>
   </x:si>
   <x:si>
-    <x:t>'본세계'와 '역세계'를 잇는 유일한 물리적 이동공간.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>초심극점을 마주하고 바라보고 있는 다른 세상, '역세계'와의 전쟁.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Desc_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character002_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character001_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character003_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa006_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character004_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa007_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa009_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History004_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa003_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa005_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term004_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa014_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa011_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa013_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa013_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa001_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa010_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa009_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term003_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa013_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa010_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa008_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa001_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa006_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa005_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History002_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term002_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa002_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa014_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History003_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term007_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa014_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa011_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa011_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa004_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa003_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History003_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term007_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GaremenTooskaDin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa008_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History001_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term005_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History004_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa002_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa001_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History001_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term001_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa007_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa009_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa002_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa007_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term006_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa008_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History002_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa010_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa004_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Etc004_Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character004_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character001_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character003_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character002_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character002_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소환술사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종족전쟁</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Human</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rodec</x:t>
-  </x:si>
-  <x:si>
-    <x:t>세이렌 알트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종말전쟁</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카루크 뷘젠트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>menu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Dragon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불러오기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Leather</x:t>
-  </x:si>
-  <x:si>
-    <x:t>save</x:t>
-  </x:si>
-  <x:si>
-    <x:t>강령술사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Index</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Toorka</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cloth</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이어하기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>load</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코크루와</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sandora</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대마도사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Selena</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Head</x:t>
-  </x:si>
-  <x:si>
-    <x:t>?????</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Plate</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Badrak</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Priest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Species</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Demon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Korean</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Archer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Comment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마족 전사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>exit</x:t>
-  </x:si>
-  <x:si>
-    <x:t>초심극점</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gloves</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마족 마법사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rogue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그렌 포모스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나로사 포모스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Armor</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Boots</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Warrior</x:t>
-  </x:si>
-  <x:si>
-    <x:t>newgame</x:t>
-  </x:si>
-  <x:si>
-    <x:t>위대한 과실</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Array</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Renod</x:t>
-  </x:si>
-  <x:si>
-    <x:t>긴가르시온</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Redinin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타르타로스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대마도전쟁</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Unknown</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이레안 소린</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라우톤 윈너</x:t>
-  </x:si>
-  <x:si>
-    <x:t>copy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종족&amp;직업</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타이틀로 이동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연금술사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>option</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Machine</x:t>
-  </x:si>
-  <x:si>
-    <x:t>새 시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에를로네</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Weapon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kalapok</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Perth</x:t>
-  </x:si>
-  <x:si>
-    <x:t>산도라 태생</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Teemole</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ehrlone</x:t>
-  </x:si>
-  <x:si>
-    <x:t>title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불튼 카존</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마법의 신, 제샤스 데이틴의 일곱 제자들이 일으킨 내전. 이로 인해 세상의 모든 기록이 소실되어 사실상 모든 것이 초기화되었다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term004_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>encyclopedia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KaroukWingent</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term003_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>???????????????</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term007_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term006_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term001_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DemonFighter</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term005_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term002_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이라 모스 강제 개폐 사건</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RoutonWinner</x:t>
-  </x:si>
-  <x:si>
-    <x:t>역사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>올베인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이레안</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레디닌</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가죽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>갑옷</x:t>
-  </x:si>
-  <x:si>
-    <x:t>백랑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>바드락</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그렌</x:t>
-  </x:si>
-  <x:si>
-    <x:t>메뉴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>성직자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>직업</x:t>
-  </x:si>
-  <x:si>
-    <x:t>역세계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>흉켈링</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카루크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레노드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>판금</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라우톤</x:t>
-  </x:si>
-  <x:si>
-    <x:t>암살자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나로사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>저장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도감</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마법사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도적</x:t>
-  </x:si>
-  <x:si>
-    <x:t>머리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>드래곤</x:t>
-  </x:si>
-  <x:si>
-    <x:t>페르스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가레멘</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>티모르</x:t>
-  </x:si>
-  <x:si>
-    <x:t>로데크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>용어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무직</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불튼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>셀레나</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장갑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장비</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>궁수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>목걸이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인물</x:t>
-  </x:si>
-  <x:si>
-    <x:t>초월자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>본세계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신발</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마왕족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Job</x:t>
-  </x:si>
-  <x:si>
-    <x:t>천</x:t>
-  </x:si>
-  <x:si>
-    <x:t>투르카</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Etc002_Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:금속왕. 긴가르시온이 조립한 완전 기계인간 다만 이 세상에서 유일하게 전신이 '완벽한 신의 금속'으로 이뤄져서 모든 것을 무시할 수준의 방어력을 지니고 있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>늑대신이라 불리는 자. '짐토'가 '위대한 과실'의 생산 원리를 알아내고 그것을 독점하기 전까지, 사실상 유일한 '위대한 과실'의 유통을 담당했다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전 세계에서도 극히 발견하기 어려웠던 과실. 먹는 이의 모든 질병과 상처를 회복해주고, 육체를 가장 건강하던 때로 고정하며 새로운 수명을 하사한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:죽어도 되살아나는 자. 역사상 최초의 '초월자'이자 무한하게 강해지는 '암흑대제'의 원형.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 능력 중 대부분이 공격에 치중된 火계열 중거리 딜러.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>평화로운 시기에도 전 세계에 그 개체 수가 5마리를 넘기지 못하던 이 세상 유일의 '초소수종'</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 자가방어와 자가치유에 치중된 地계열 순수 탱커.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:암흑대제. 이 세상에서 유일하게 힘을 비축하는 시간에 비례하여 무한히 강해질 수 있는 존재.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'본세계' 내의 다른 10개의 세계와의 연락을 차단했음에도 가장 독자적인 업적을 이룩한 대륙.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 대지의 종족 '티모르'의 생존저.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'본세계' 내에서, '종말전쟁'의 결말을 지켜보던 강력한 존재들을 일컫는 용어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'본세계' 내에서 최초로 기록된 내전. 이로 인해 '불의 종족' 카르툼이 절멸하였다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 바다의 종족 '셀레나'의 생존자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 창공의 종족 '투르카'의 생존자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자기 자신의 직계자손에 한정하여, 자신의 기억과 인격을 전달하는 '전생술'을 개발한 존재.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'종말전쟁'이 끝난 이후의 시대가 되며 사실상 유명무실한 용어가 되어 사실상 강력한 힘을 지닌 '초월자'들을 일컫는 용어가 되었다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 그가 공격의사를 갖던 말던 그의 주변에 존재하는 것만으로도 해독이 불가능한 '페이튼'에 중독되어 모든 존재가 소멸한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:유령왕. 태생적으로 '산도라의 후예'인 대마도사였으나 그의 스승인 '푸 그레이'가 서술한 '초마도의 서'를 이해하여 마법사 중 최강의 존재인 '초마도사'가 되었다.</x:t>
+    <x:t>이명:시간의 마왕. 우리의 세상인 '본세계'와 '역세계'에서도 하나 이상을 찾아볼 수 없는 절대유일의 시간 능력자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이 세상 모든 것을 중독시키는 '페이튼'에 중독되어 스스로 의사를 갖고 움직이기 시작한 종족 '래머'의 마지막 생존자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:피를 입는 자. '본세계'와 '역세계'를 모두 포함해서도 비슷한 수준의 신체능력을 가진 존재를 찾기 힘들 정도로 압도적인 신체능력을 가지고 있다.</x:t>
   </x:si>
   <x:si>
     <x:t>원래라면 죽었을 때 다시 되살아나지만, 죽을 경우 다시는 되살아나지 못하는 것을 조건으로 강력한 힘을 얻어 그의 희생으로 '종말전쟁'에서 승리할 수 있었다.</x:t>
   </x:si>
   <x:si>
     <x:t>이제 와서는 이 세상에 절대유일한 '핏빛혈족의 유일한 생존자' 무시무시한 이능력을 지니고 있지만 그가 지닌 이능력의 정체를 아는 자를 이제는 찾을 수 없다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:피를 입는 자. '본세계'와 '역세계'를 모두 포함해서도 비슷한 수준의 신체능력을 가진 존재를 찾기 힘들 정도로 압도적인 신체능력을 가지고 있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:시간의 마왕. 우리의 세상인 '본세계'와 '역세계'에서도 하나 이상을 찾아볼 수 없는 절대유일의 시간 능력자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이 세상 모든 것을 중독시키는 '페이튼'에 중독되어 스스로 의사를 갖고 움직이기 시작한 종족 '래머'의 마지막 생존자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">역사에 기록될 정도로 강한 힘을 지닌, 무한히 강해질 수 있는 능력을 지닌 9성 대장, '암흑대제'의 영부인. </x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 공격보다 정찰에 특화된 공격력보다는 연타에 치중한 風계열 서포터.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화룡왕이라 불리는 자. 악신룡 '지크리피언'에게 육체는 소멸 당하고, 육체가 아닌 정신만으로 살아있는 존재.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 대장. 전투에 필요한 전반적인 능력을 두루 갖춘 氷계열 원거리 딜러.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>샤이나 반 고드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DemonMage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>버그리포트 바로가기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Alchemist</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아키르고 베니아</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NarosaFomos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hidden002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>notEmployed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GrenFomos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Summoner</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gingarsion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Archmage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tartaros</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CodeName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Equipment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Necklace</x:t>
-  </x:si>
-  <x:si>
-    <x:t>헤디 벤만 오프 모스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bugreport</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Assassin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가레멘 투스카 딘</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BultonKajon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hidden001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Species&amp;Job</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character</x:t>
-  </x:si>
-  <x:si>
-    <x:t>continue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Necromancer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IreanSorin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:현명한 현자. 모든 코크루와 중 유일의 비전투원. 다만 이제는 기억하는 사람도 없는 '본카 일족'의 족장 '짐토'로써 사실상 이 세상의 모든 학문과 기술은 그로부터 비롯된 것이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Etc001_Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Etc005_Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ring</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Earring</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잡템005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잡템001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>반지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>귀걸이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잡템003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잡템004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잡템002</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1650,7 +1668,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:N151"/>
+  <x:dimension ref="A1:N155"/>
   <x:sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="16.39999999999999857891"/>
   <x:cols>
     <x:col min="1" max="1" width="8.796875" bestFit="1" customWidth="1"/>
@@ -1659,31 +1677,31 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="D1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>267</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="D2" s="1"/>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -1691,7 +1709,7 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B4" s="1"/>
       <x:c r="C4" s="1"/>
@@ -1702,10 +1720,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" t="s">
-        <x:v>127</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="C5" t="s">
-        <x:v>144</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
@@ -1713,10 +1731,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" t="s">
-        <x:v>278</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C6" t="s">
-        <x:v>99</x:v>
+        <x:v>174</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
@@ -1724,10 +1742,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" t="s">
-        <x:v>142</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C7" t="s">
-        <x:v>188</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
@@ -1735,10 +1753,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" t="s">
-        <x:v>117</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="C8" t="s">
-        <x:v>183</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
@@ -1746,10 +1764,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B9" t="s">
-        <x:v>94</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C9" t="s">
-        <x:v>194</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
@@ -1757,10 +1775,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B10" t="s">
-        <x:v>100</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C10" t="s">
-        <x:v>92</x:v>
+        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
@@ -1768,10 +1786,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B11" t="s">
-        <x:v>138</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C11" t="s">
-        <x:v>216</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
@@ -1779,10 +1797,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B12" t="s">
-        <x:v>89</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C12" t="s">
-        <x:v>178</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
@@ -1790,10 +1808,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B13" t="s">
-        <x:v>153</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="C13" s="2" t="s">
-        <x:v>140</x:v>
+        <x:v>236</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
@@ -1801,10 +1819,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B14" t="s">
-        <x:v>271</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C14" t="s">
-        <x:v>256</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
@@ -1812,10 +1830,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B15" t="s">
-        <x:v>157</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="C15" t="s">
-        <x:v>195</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
@@ -1823,10 +1841,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B16" t="s">
-        <x:v>84</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C16" t="s">
-        <x:v>218</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
@@ -1834,10 +1852,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B17" t="s">
-        <x:v>80</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="C17" t="s">
-        <x:v>207</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
@@ -1845,10 +1863,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B18" t="s">
-        <x:v>90</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C18" t="s">
-        <x:v>169</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
@@ -1856,10 +1874,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B19" t="s">
-        <x:v>130</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="C19" t="s">
-        <x:v>189</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
@@ -1867,10 +1885,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B20" t="s">
-        <x:v>266</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C20" t="s">
-        <x:v>133</x:v>
+        <x:v>232</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
@@ -1878,10 +1896,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B21" t="s">
-        <x:v>132</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C21" t="s">
-        <x:v>172</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
@@ -1889,10 +1907,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B22" t="s">
-        <x:v>149</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C22" t="s">
-        <x:v>200</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
@@ -1900,10 +1918,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B23" t="s">
-        <x:v>152</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C23" t="s">
-        <x:v>145</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
@@ -1911,10 +1929,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B24" t="s">
-        <x:v>264</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C24" t="s">
-        <x:v>131</x:v>
+        <x:v>218</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
@@ -1922,10 +1940,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B25" t="s">
-        <x:v>262</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C25" t="s">
-        <x:v>122</x:v>
+        <x:v>211</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
@@ -1933,10 +1951,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B26" t="s">
-        <x:v>259</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C26" t="s">
-        <x:v>123</x:v>
+        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
@@ -1944,10 +1962,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B27" t="s">
-        <x:v>280</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C27" t="s">
-        <x:v>136</x:v>
+        <x:v>222</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
@@ -1955,10 +1973,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B28" t="s">
-        <x:v>274</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C28" t="s">
-        <x:v>154</x:v>
+        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3">
@@ -1966,10 +1984,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B29" t="s">
-        <x:v>158</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="C29" t="s">
-        <x:v>88</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">
@@ -1977,10 +1995,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B30" t="s">
-        <x:v>168</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C30" t="s">
-        <x:v>137</x:v>
+        <x:v>216</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
@@ -1988,10 +2006,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B31" t="s">
-        <x:v>54</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C31" t="s">
-        <x:v>273</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:3">
@@ -1999,10 +2017,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B32" t="s">
-        <x:v>111</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="C32" t="s">
-        <x:v>220</x:v>
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:3">
@@ -2010,10 +2028,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B33" t="s">
-        <x:v>223</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C33" t="s">
-        <x:v>180</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:3">
@@ -2021,10 +2039,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B34" t="s">
-        <x:v>275</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C34" t="s">
-        <x:v>106</x:v>
+        <x:v>182</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:3">
@@ -2032,10 +2050,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B35" t="s">
-        <x:v>260</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C35" t="s">
-        <x:v>160</x:v>
+        <x:v>269</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:3">
@@ -2043,10 +2061,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B36" t="s">
-        <x:v>261</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C36" t="s">
-        <x:v>208</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:3">
@@ -2054,10 +2072,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B37" t="s">
-        <x:v>268</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C37" t="s">
-        <x:v>212</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:3">
@@ -2065,10 +2083,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B38" t="s">
-        <x:v>276</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C38" t="s">
-        <x:v>139</x:v>
+        <x:v>224</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:3">
@@ -2076,10 +2094,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B39" t="s">
-        <x:v>98</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C39" t="s">
-        <x:v>224</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:3">
@@ -2087,10 +2105,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B40" t="s">
-        <x:v>93</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C40" t="s">
-        <x:v>173</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:3">
@@ -2098,10 +2116,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B41" t="s">
-        <x:v>107</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="C41" t="s">
-        <x:v>190</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:3">
@@ -2109,10 +2127,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B42" t="s">
-        <x:v>146</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="C42" t="s">
-        <x:v>213</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:3">
@@ -2120,10 +2138,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B43" t="s">
-        <x:v>105</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C43" t="s">
-        <x:v>198</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:3">
@@ -2131,10 +2149,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B44" t="s">
-        <x:v>124</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="C44" t="s">
-        <x:v>174</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:3">
@@ -2142,10 +2160,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B45" t="s">
-        <x:v>119</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="C45" t="s">
-        <x:v>211</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:3">
@@ -2153,10 +2171,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B46" t="s">
-        <x:v>125</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="C46" t="s">
-        <x:v>221</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:3">
@@ -2164,10 +2182,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B47" t="s">
-        <x:v>284</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="C47" t="s">
-        <x:v>288</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:3">
@@ -2175,10 +2193,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B48" t="s">
-        <x:v>285</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="C48" t="s">
-        <x:v>289</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:3">
@@ -2186,10 +2204,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B49" t="s">
-        <x:v>269</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C49" t="s">
-        <x:v>215</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:3">
@@ -2197,10 +2215,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B50" s="2" t="s">
-        <x:v>83</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="C50" t="s">
-        <x:v>206</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:3">
@@ -2208,10 +2226,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B51" s="2" t="s">
-        <x:v>85</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C51" t="s">
-        <x:v>204</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:3">
@@ -2219,10 +2237,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B52" s="2" t="s">
-        <x:v>97</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C52" t="s">
-        <x:v>225</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:3">
@@ -2230,10 +2248,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B53" t="s">
-        <x:v>151</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="C53" t="s">
-        <x:v>203</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:3">
@@ -2241,10 +2259,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B54" t="s">
-        <x:v>104</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C54" t="s">
-        <x:v>210</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:3">
@@ -2252,10 +2270,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B55" t="s">
-        <x:v>108</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="C55" t="s">
-        <x:v>176</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:3">
@@ -2263,10 +2281,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B56" t="s">
-        <x:v>143</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="C56" t="s">
-        <x:v>185</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:3">
@@ -2274,10 +2292,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B57" t="s">
-        <x:v>112</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="C57" t="s">
-        <x:v>182</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:3">
@@ -2285,10 +2303,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B58" t="s">
-        <x:v>102</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C58" t="s">
-        <x:v>150</x:v>
+        <x:v>254</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:3">
@@ -2296,10 +2314,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B59" t="s">
-        <x:v>91</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C59" t="s">
-        <x:v>199</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:3">
@@ -2307,10 +2325,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B60" t="s">
-        <x:v>148</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C60" t="s">
-        <x:v>222</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:3">
@@ -2318,10 +2336,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B61" t="s">
-        <x:v>135</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="C61" t="s">
-        <x:v>202</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:3">
@@ -2329,10 +2347,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B62" t="s">
-        <x:v>261</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C62" t="s">
-        <x:v>208</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:3">
@@ -2340,10 +2358,10 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B63" t="s">
-        <x:v>126</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C63" t="s">
-        <x:v>205</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:3">
@@ -2351,10 +2369,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B64" t="s">
-        <x:v>114</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C64" t="s">
-        <x:v>214</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:3">
@@ -2362,10 +2380,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B65" t="s">
-        <x:v>110</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C65" t="s">
-        <x:v>196</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:3">
@@ -2373,10 +2391,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B66" t="s">
-        <x:v>109</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="C66" t="s">
-        <x:v>179</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:3">
@@ -2384,10 +2402,10 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B67" t="s">
-        <x:v>272</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C67" t="s">
-        <x:v>192</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:3">
@@ -2395,10 +2413,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B68" t="s">
-        <x:v>121</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="C68" t="s">
-        <x:v>197</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:3">
@@ -2406,10 +2424,10 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B69" t="s">
-        <x:v>263</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C69" t="s">
-        <x:v>81</x:v>
+        <x:v>192</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:3">
@@ -2417,10 +2435,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B70" t="s">
-        <x:v>257</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C70" t="s">
-        <x:v>141</x:v>
+        <x:v>241</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:3">
@@ -2428,10 +2446,10 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B71" t="s">
-        <x:v>279</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C71" t="s">
-        <x:v>95</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:3">
@@ -2439,10 +2457,10 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B72" t="s">
-        <x:v>164</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="C72" t="s">
-        <x:v>116</x:v>
+        <x:v>231</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:3">
@@ -2450,10 +2468,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B73" t="s">
-        <x:v>255</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C73" t="s">
-        <x:v>120</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:3">
@@ -2461,10 +2479,10 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B74" t="s">
-        <x:v>265</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C74" t="s">
-        <x:v>103</x:v>
+        <x:v>176</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:8">
@@ -2472,10 +2490,10 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B75" t="s">
-        <x:v>60</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="C75" t="s">
-        <x:v>189</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="G75" s="2"/>
       <x:c r="H75" s="2"/>
@@ -2485,10 +2503,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="B76" t="s">
-        <x:v>65</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C76" t="s">
-        <x:v>133</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="G76" s="2"/>
       <x:c r="H76" s="2"/>
@@ -2498,10 +2516,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B77" t="s">
-        <x:v>23</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C77" t="s">
-        <x:v>172</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G77" s="2"/>
       <x:c r="H77" s="2"/>
@@ -2511,10 +2529,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B78" t="s">
-        <x:v>73</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C78" t="s">
-        <x:v>200</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G78" s="2"/>
       <x:c r="H78" s="2"/>
@@ -2524,10 +2542,10 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B79" t="s">
-        <x:v>40</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C79" t="s">
-        <x:v>145</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="G79" s="2"/>
       <x:c r="H79" s="2"/>
@@ -2537,10 +2555,10 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B80" t="s">
-        <x:v>39</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C80" t="s">
-        <x:v>131</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="G80" s="2"/>
       <x:c r="H80" s="2"/>
@@ -2550,10 +2568,10 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="B81" t="s">
-        <x:v>63</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C81" t="s">
-        <x:v>177</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G81" s="2"/>
       <x:c r="H81" s="2"/>
@@ -2563,10 +2581,10 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B82" t="s">
-        <x:v>37</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C82" t="s">
-        <x:v>193</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G82" s="2"/>
       <x:c r="H82" s="2"/>
@@ -2576,10 +2594,10 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B83" t="s">
-        <x:v>32</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C83" t="s">
-        <x:v>171</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G83" s="2"/>
       <x:c r="H83" s="2"/>
@@ -2589,10 +2607,10 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B84" t="s">
-        <x:v>72</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C84" t="s">
-        <x:v>209</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="G84" s="2"/>
       <x:c r="H84" s="2"/>
@@ -2602,10 +2620,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B85" t="s">
-        <x:v>49</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C85" t="s">
-        <x:v>187</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="G85" s="2"/>
       <x:c r="H85" s="2"/>
@@ -2615,10 +2633,10 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B86" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="C86" t="s">
         <x:v>70</x:v>
-      </x:c>
-      <x:c r="C86" t="s">
-        <x:v>191</x:v>
       </x:c>
       <x:c r="G86" s="2"/>
       <x:c r="H86" s="2"/>
@@ -2628,10 +2646,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B87" t="s">
-        <x:v>29</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C87" t="s">
-        <x:v>201</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G87" s="2"/>
       <x:c r="H87" s="2"/>
@@ -2641,10 +2659,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B88" t="s">
-        <x:v>163</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="C88" t="s">
-        <x:v>219</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="G88" s="2"/>
       <x:c r="H88" s="2"/>
@@ -2654,10 +2672,10 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="B89" t="s">
-        <x:v>166</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="C89" t="s">
-        <x:v>181</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G89" s="2"/>
       <x:c r="H89" s="2"/>
@@ -2667,10 +2685,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B90" t="s">
-        <x:v>159</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="C90" t="s">
-        <x:v>118</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="G90" s="2"/>
       <x:c r="H90" s="2"/>
@@ -2680,10 +2698,10 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="B91" t="s">
-        <x:v>156</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C91" s="2" t="s">
-        <x:v>258</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="G91" s="2"/>
       <x:c r="H91" s="2"/>
@@ -2693,10 +2711,10 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="B92" t="s">
-        <x:v>165</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="C92" s="2" t="s">
-        <x:v>270</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G92" s="2"/>
       <x:c r="H92" s="2"/>
@@ -2706,10 +2724,10 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="B93" t="s">
-        <x:v>162</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="C93" s="2" t="s">
-        <x:v>128</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="G93" s="2"/>
       <x:c r="H93" s="2"/>
@@ -2719,10 +2737,10 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="B94" t="s">
-        <x:v>56</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C94" t="s">
-        <x:v>82</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="G94" s="2"/>
       <x:c r="H94" s="2"/>
@@ -2732,10 +2750,10 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="B95" t="s">
-        <x:v>71</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="C95" t="s">
-        <x:v>134</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="G95" s="2"/>
       <x:c r="H95" s="2"/>
@@ -2745,10 +2763,10 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="B96" t="s">
-        <x:v>45</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C96" t="s">
-        <x:v>87</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="G96" s="2"/>
       <x:c r="H96" s="2"/>
@@ -2758,10 +2776,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B97" t="s">
-        <x:v>58</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="C97" t="s">
-        <x:v>167</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G97" s="2"/>
       <x:c r="H97" s="2"/>
@@ -2771,10 +2789,10 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="B98" t="s">
-        <x:v>38</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C98" t="s">
-        <x:v>248</x:v>
+        <x:v>294</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:3">
@@ -2782,10 +2800,10 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="B99" t="s">
-        <x:v>30</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C99" t="s">
-        <x:v>9</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:3">
@@ -2793,10 +2811,10 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="B100" s="2" t="s">
-        <x:v>59</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C100" t="s">
-        <x:v>247</x:v>
+        <x:v>296</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:3">
@@ -2804,10 +2822,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B101" s="2" t="s">
-        <x:v>43</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C101" t="s">
-        <x:v>246</x:v>
+        <x:v>298</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:3">
@@ -2815,10 +2833,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="B102" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C102" t="s">
-        <x:v>234</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:3">
@@ -2826,10 +2844,10 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="B103" s="2" t="s">
-        <x:v>50</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="C103" t="s">
-        <x:v>227</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:3">
@@ -2837,10 +2855,10 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="B104" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C104" t="s">
-        <x:v>244</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:3">
@@ -2848,10 +2866,10 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="B105" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C105" t="s">
-        <x:v>281</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:3">
@@ -2859,10 +2877,10 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="B106" s="2" t="s">
-        <x:v>66</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C106" t="s">
-        <x:v>231</x:v>
+        <x:v>266</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:3">
@@ -2870,10 +2888,10 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="B107" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C107" t="s">
-        <x:v>2</x:v>
+        <x:v>281</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:3">
@@ -2881,10 +2899,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B108" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C108" t="s">
-        <x:v>253</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:3">
@@ -2892,10 +2910,10 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="B109" s="2" t="s">
-        <x:v>69</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C109" t="s">
-        <x:v>1</x:v>
+        <x:v>284</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:3">
@@ -2903,10 +2921,10 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="B110" s="2" t="s">
-        <x:v>64</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C110" t="s">
-        <x:v>6</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:3">
@@ -2914,10 +2932,10 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="B111" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C111" t="s">
-        <x:v>239</x:v>
+        <x:v>261</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:3">
@@ -2925,10 +2943,10 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="B112" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C112" t="s">
-        <x:v>233</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:3">
@@ -2936,10 +2954,10 @@
         <x:v>109</x:v>
       </x:c>
       <x:c r="B113" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C113" t="s">
-        <x:v>236</x:v>
+        <x:v>257</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:3">
@@ -2947,10 +2965,10 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="B114" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C114" t="s">
-        <x:v>251</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:3">
@@ -2958,10 +2976,10 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="B115" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C115" t="s">
-        <x:v>240</x:v>
+        <x:v>259</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:3">
@@ -2969,10 +2987,10 @@
         <x:v>112</x:v>
       </x:c>
       <x:c r="B116" s="2" t="s">
-        <x:v>67</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C116" t="s">
-        <x:v>5</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:3">
@@ -2980,10 +2998,10 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="B117" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C117" t="s">
-        <x:v>4</x:v>
+        <x:v>283</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:3">
@@ -2991,10 +3009,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B118" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C118" t="s">
-        <x:v>232</x:v>
+        <x:v>264</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:3">
@@ -3002,10 +3020,10 @@
         <x:v>115</x:v>
       </x:c>
       <x:c r="B119" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C119" t="s">
-        <x:v>243</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:3">
@@ -3013,10 +3031,10 @@
         <x:v>116</x:v>
       </x:c>
       <x:c r="B120" s="2" t="s">
-        <x:v>34</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C120" t="s">
-        <x:v>249</x:v>
+        <x:v>295</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:3">
@@ -3024,10 +3042,10 @@
         <x:v>117</x:v>
       </x:c>
       <x:c r="B121" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C121" t="s">
-        <x:v>10</x:v>
+        <x:v>291</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:3">
@@ -3035,10 +3053,10 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="B122" s="2" t="s">
-        <x:v>42</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C122" t="s">
-        <x:v>11</x:v>
+        <x:v>293</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:14">
@@ -3046,10 +3064,10 @@
         <x:v>119</x:v>
       </x:c>
       <x:c r="B123" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C123" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="N123" s="4"/>
     </x:row>
@@ -3058,10 +3076,10 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="B124" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C124" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="N124" s="2"/>
     </x:row>
@@ -3070,10 +3088,10 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="B125" s="2" t="s">
-        <x:v>57</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="C125" s="4" t="s">
-        <x:v>235</x:v>
+        <x:v>267</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:3">
@@ -3081,10 +3099,10 @@
         <x:v>122</x:v>
       </x:c>
       <x:c r="B126" s="2" t="s">
-        <x:v>68</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C126" t="s">
-        <x:v>229</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:3">
@@ -3092,10 +3110,10 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="B127" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C127" s="3" t="s">
-        <x:v>238</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:3">
@@ -3103,10 +3121,10 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="B128" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C128" t="s">
-        <x:v>155</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:3">
@@ -3114,10 +3132,10 @@
         <x:v>125</x:v>
       </x:c>
       <x:c r="B129" s="2" t="s">
-        <x:v>52</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="C129" t="s">
-        <x:v>13</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:3">
@@ -3125,10 +3143,10 @@
         <x:v>126</x:v>
       </x:c>
       <x:c r="B130" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C130" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:3">
@@ -3136,10 +3154,10 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="B131" s="2" t="s">
-        <x:v>161</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="C131" t="s">
-        <x:v>101</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:3">
@@ -3147,10 +3165,10 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="B132" s="2" t="s">
-        <x:v>46</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C132" s="3" t="s">
-        <x:v>237</x:v>
+        <x:v>260</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:3">
@@ -3158,10 +3176,10 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="B133" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C133" s="3" t="s">
-        <x:v>242</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:3">
@@ -3169,10 +3187,10 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="B134" s="2" t="s">
-        <x:v>47</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C134" t="s">
-        <x:v>230</x:v>
+        <x:v>262</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:3">
@@ -3180,10 +3198,10 @@
         <x:v>131</x:v>
       </x:c>
       <x:c r="B135" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C135" t="s">
-        <x:v>86</x:v>
+        <x:v>183</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:3">
@@ -3191,10 +3209,10 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="B136" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C136" t="s">
-        <x:v>245</x:v>
+        <x:v>297</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:3">
@@ -3202,10 +3220,10 @@
         <x:v>133</x:v>
       </x:c>
       <x:c r="B137" t="s">
-        <x:v>277</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C137" t="s">
-        <x:v>217</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:3">
@@ -3213,10 +3231,10 @@
         <x:v>134</x:v>
       </x:c>
       <x:c r="B138" t="s">
-        <x:v>16</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C138" t="s">
-        <x:v>254</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:3">
@@ -3224,10 +3242,10 @@
         <x:v>135</x:v>
       </x:c>
       <x:c r="B139" t="s">
-        <x:v>76</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="C139" t="s">
-        <x:v>250</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:3">
@@ -3235,10 +3253,10 @@
         <x:v>136</x:v>
       </x:c>
       <x:c r="B140" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C140" t="s">
-        <x:v>175</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:3">
@@ -3246,10 +3264,10 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="B141" s="2" t="s">
-        <x:v>78</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="C141" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>282</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:3">
@@ -3257,10 +3275,10 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="B142" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="C142" t="s">
-        <x:v>241</x:v>
+        <x:v>256</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:3">
@@ -3268,10 +3286,10 @@
         <x:v>139</x:v>
       </x:c>
       <x:c r="B143" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C143" t="s">
-        <x:v>170</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:3">
@@ -3279,10 +3297,10 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="B144" s="2" t="s">
-        <x:v>77</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="C144" t="s">
-        <x:v>228</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:3">
@@ -3290,10 +3308,10 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="B145" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C145" t="s">
-        <x:v>184</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:3">
@@ -3301,10 +3319,10 @@
         <x:v>142</x:v>
       </x:c>
       <x:c r="B146" s="2" t="s">
-        <x:v>75</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="C146" t="s">
-        <x:v>252</x:v>
+        <x:v>171</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:3">
@@ -3312,10 +3330,10 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="B147" s="2" t="s">
-        <x:v>282</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C147" t="s">
-        <x:v>287</x:v>
+        <x:v>247</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:3">
@@ -3323,10 +3341,10 @@
         <x:v>144</x:v>
       </x:c>
       <x:c r="B148" s="2" t="s">
-        <x:v>226</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C148" t="s">
-        <x:v>292</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:3">
@@ -3334,10 +3352,10 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="B149" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C149" t="s">
-        <x:v>290</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:3">
@@ -3345,10 +3363,10 @@
         <x:v>146</x:v>
       </x:c>
       <x:c r="B150" s="2" t="s">
-        <x:v>74</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C150" t="s">
-        <x:v>291</x:v>
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:3">
@@ -3356,10 +3374,54 @@
         <x:v>147</x:v>
       </x:c>
       <x:c r="B151" s="2" t="s">
-        <x:v>283</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C151" t="s">
-        <x:v>286</x:v>
+        <x:v>252</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" spans="1:3">
+      <x:c r="A152">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="B152" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="C152" t="s">
+        <x:v>109</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" spans="1:3">
+      <x:c r="A153">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="B153" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C153" t="s">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" spans="1:3">
+      <x:c r="A154">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="B154" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C154" t="s">
+        <x:v>49</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" spans="1:3">
+      <x:c r="A155">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="B155" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C155" t="s">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/morpg/morpg/Assets/TableData/Table_Text.xlsx
+++ b/morpg/morpg/Assets/TableData/Table_Text.xlsx
@@ -19,903 +19,909 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="299">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="301">
+  <x:si>
+    <x:t>144년을 주기로 돌아오는 초자연 현상. 이 기간 중에는 성공적인 '이라 모스'의 개폐가 가능해진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그의 일정범위에 존재하는 모든 사물은 점점 느려지기  시작하고 그 본인은 그 속도만큼 점점 빨라진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>늑대신이라 불리는 자. '짐토'가 '위대한 과실'의 생산 원리를 알아내고 그것을 독점하기 전까지, 사실상 유일한 '위대한 과실'의 유통을 담당했다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전 세계에서도 극히 발견하기 어려웠던 과실. 먹는 이의 모든 질병과 상처를 회복해주고, 육체를 가장 건강하던 때로 고정하며 새로운 수명을 하사한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Desc_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa006_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa005_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa010_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa010_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa005_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa002_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa009_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa006_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa008_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa009_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GaremenTooskaDin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa013_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa001_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term007_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term006_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa007_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa007_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa013_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa011_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa014_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa011_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa013_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa014_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa007_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa008_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa014_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term005_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa009_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa010_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term007_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa011_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa008_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Etc002_Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DemonMage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Equipment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Etc004_Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>샤이나 반 고드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NarosaFomos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tartaros</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Necklace</x:t>
+  </x:si>
+  <x:si>
+    <x:t>헤디 벤만 오프 모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>버그리포트 바로가기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Etc003_Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Necromancer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hidden002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Assassin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hidden001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GrenFomos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Species&amp;Job</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Etc005_Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>notEmployed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bugreport</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CodeName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Archmage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Summoner</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아키르고 베니아</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Alchemist</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gingarsion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BultonKajon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가레멘 투스카 딘</x:t>
+  </x:si>
+  <x:si>
+    <x:t>continue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Etc001_Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IreanSorin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'종말전쟁'이 끝난 이후의 시대가 되며 사실상 유명무실한 용어가 되어 사실상 강력한 힘을 지닌 '초월자'들을 일컫는 용어가 되었다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마법의 신, 제샤스 데이틴의 일곱 제자들이 일으킨 내전. 이로 인해 세상의 모든 기록이 소실되어 사실상 모든 것이 초기화되었다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>방패</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KaroukWingent</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이라 모스 강제 개폐 사건</x:t>
+  </x:si>
+  <x:si>
+    <x:t>encyclopedia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DemonFighter</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term006_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RoutonWinner</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term007_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term005_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>???????????????</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'아키르고 베니아'가 아닌 때에 '이라 모스'를 개설한 충격으로 '본세계' 바깥의 세상이 무너져버린 사건.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character002_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초심극점을 마주하고 바라보고 있는 다른 세상, '역세계'와의 전쟁.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Etc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>암살자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>직업</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레디닌</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이레안</x:t>
+  </x:si>
   <x:si>
     <x:t>전체</x:t>
   </x:si>
   <x:si>
-    <x:t>늑대신이라 불리는 자. '짐토'가 '위대한 과실'의 생산 원리를 알아내고 그것을 독점하기 전까지, 사실상 유일한 '위대한 과실'의 유통을 담당했다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전 세계에서도 극히 발견하기 어려웠던 과실. 먹는 이의 모든 질병과 상처를 회복해주고, 육체를 가장 건강하던 때로 고정하며 새로운 수명을 하사한다.</x:t>
+    <x:t>나로사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가죽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>메뉴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>백랑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>재료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>성직자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그렌</x:t>
+  </x:si>
+  <x:si>
+    <x:t>바드락</x:t>
+  </x:si>
+  <x:si>
+    <x:t>역세계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>역사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무직</x:t>
+  </x:si>
+  <x:si>
+    <x:t>갑옷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로데크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카루크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>셀레나</x:t>
+  </x:si>
+  <x:si>
+    <x:t>투르카</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가레멘</x:t>
+  </x:si>
+  <x:si>
+    <x:t>흉켈링</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라우톤</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도감</x:t>
+  </x:si>
+  <x:si>
+    <x:t>본세계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>천</x:t>
+  </x:si>
+  <x:si>
+    <x:t>용어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신발</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장갑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마왕족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초월자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>페르스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>올베인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>판금</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Job</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레노드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>드래곤</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인물</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장비</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도적</x:t>
+  </x:si>
+  <x:si>
+    <x:t>귀걸이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목걸이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>티모르</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불튼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>All</x:t>
+  </x:si>
+  <x:si>
+    <x:t>머리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마법사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>반지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>궁수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소모품</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sandora</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Index</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종족전쟁</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이어하기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대마도사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종말전쟁</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cloth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dragon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rodec</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Selena</x:t>
+  </x:si>
+  <x:si>
+    <x:t>?????</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세이렌 알트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>menu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카루크 뷘젠트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Toorka</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Boots</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Armor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Warrior</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불러오기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대마도전쟁</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Badrak</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나로사 포모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Leather</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Head</x:t>
+  </x:si>
+  <x:si>
+    <x:t>강령술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소환술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코크루와</x:t>
+  </x:si>
+  <x:si>
+    <x:t>load</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Human</x:t>
+  </x:si>
+  <x:si>
+    <x:t>save</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Plate</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타르타로스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그렌 포모스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Unknown</x:t>
+  </x:si>
+  <x:si>
+    <x:t>copy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Archer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이레안 소린</x:t>
+  </x:si>
+  <x:si>
+    <x:t>option</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Korean</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마족 마법사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Comment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>exit</x:t>
+  </x:si>
+  <x:si>
+    <x:t>위대한 과실</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Redinin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Species</x:t>
+  </x:si>
+  <x:si>
+    <x:t>긴가르시온</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Priest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초심극점</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Demon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마족 전사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잡템003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타이틀로 이동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>newgame</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Array</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라우톤 윈너</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rogue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gloves</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Teemole</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Machine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새 시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종족&amp;직업</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Renod</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kalapok</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잡템002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연금술사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Perth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Earring</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에를로네</x:t>
+  </x:si>
+  <x:si>
+    <x:t>title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ring</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잡템001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불튼 카존</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잡템004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Weapon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Consume</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잡템005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ehrlone</x:t>
+  </x:si>
+  <x:si>
+    <x:t>산도라 태생</x:t>
+  </x:si>
+  <x:si>
+    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써 '태양절맥'을 갖고 태어난 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>드래곤을 포함해도 모든 종족 중에서는 물리력 최강의 종족 '바드락'의 생존자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'헤디 벤만 오프 모스' 출신, 역사상 가장 위대한 무인이라 불리는 자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써 '구음절맥'을 갖고 태어난 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 공격보다 정찰에 특화된 공격력보다는 연타에 치중한 風계열 서포터.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화룡왕이라 불리는 자. 악신룡 '지크리피언'에게 육체는 소멸 당하고, 육체가 아닌 정신만으로 살아있는 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 대장. 전투에 필요한 전반적인 능력을 두루 갖춘 氷계열 원거리 딜러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">역사에 기록될 정도로 강한 힘을 지닌, 무한히 강해질 수 있는 능력을 지닌 9성 대장, '암흑대제'의 영부인. </x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 지닌 능력 중 대부분이 상처를 치유하고 아군을 버프, 적을 디버프하는 水계열 후방 서포터.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 불튼이 버금가는 탱킹 능력에 '피를 입는 자'에 버금하는 물리력을 지닌 雷계열 근거리 딜러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:금속왕. 긴가르시온이 조립한 완전 기계인간 다만 이 세상에서 유일하게 전신이 '완벽한 신의 금속'으로 이뤄져서 모든 것을 무시할 수준의 방어력을 지니고 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자기 자신의 직계자손에 한정하여, 자신의 기억과 인격을 전달하는 '전생술'을 개발한 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'본세계' 내에서, '종말전쟁'의 결말을 지켜보던 강력한 존재들을 일컫는 용어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 대지의 종족 '티모르'의 생존저.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'본세계' 내에서 최초로 기록된 내전. 이로 인해 '불의 종족' 카르툼이 절멸하였다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 창공의 종족 '투르카'의 생존자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 바다의 종족 '셀레나'의 생존자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>평화로운 시기에도 전 세계에 그 개체 수가 5마리를 넘기지 못하던 이 세상 유일의 '초소수종'</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 자가방어와 자가치유에 치중된 地계열 순수 탱커.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:죽어도 되살아나는 자. 역사상 최초의 '초월자'이자 무한하게 강해지는 '암흑대제'의 원형.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 능력 중 대부분이 공격에 치중된 火계열 중거리 딜러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:암흑대제. 이 세상에서 유일하게 힘을 비축하는 시간에 비례하여 무한히 강해질 수 있는 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'본세계' 내의 다른 10개의 세계와의 연락을 차단했음에도 가장 독자적인 업적을 이룩한 대륙.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:시간의 마왕. 우리의 세상인 '본세계'와 '역세계'에서도 하나 이상을 찾아볼 수 없는 절대유일의 시간 능력자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이 세상 모든 것을 중독시키는 '페이튼'에 중독되어 스스로 의사를 갖고 움직이기 시작한 종족 '래머'의 마지막 생존자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:피를 입는 자. '본세계'와 '역세계'를 모두 포함해서도 비슷한 수준의 신체능력을 가진 존재를 찾기 힘들 정도로 압도적인 신체능력을 가지고 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>원래라면 죽었을 때 다시 되살아나지만, 죽을 경우 다시는 되살아나지 못하는 것을 조건으로 강력한 힘을 얻어 그의 희생으로 '종말전쟁'에서 승리할 수 있었다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제 와서는 이 세상에 절대유일한 '핏빛혈족의 유일한 생존자' 무시무시한 이능력을 지니고 있지만 그가 지닌 이능력의 정체를 아는 자를 이제는 찾을 수 없다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>창조신 'NM'이 창조한 11개로 겹쳐진 우리의 세상.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'본세계'와 '역세계'를 잇는 유일한 물리적 이동공간.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>창조신 'OM'이 창조한 초심극점 너머의 다른 세상.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이명:유령왕. 태생적으로 '산도라의 후예'인 대마도사였으나 그의 스승인 '푸 그레이'가 서술한 '초마도의 서'를 이해하여 마법사 중 최강의 존재인 '초마도사'가 되었다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 그가 공격의사를 갖던 말던 그의 주변에 존재하는 것만으로도 해독이 불가능한 '페이튼'에 중독되어 모든 존재가 소멸한다.</x:t>
   </x:si>
   <x:si>
     <x:t>이명:현명한 현자. 모든 코크루와 중 유일의 비전투원. 다만 이제는 기억하는 사람도 없는 '본카 일족'의 족장 '짐토'로써 사실상 이 세상의 모든 학문과 기술은 그로부터 비롯된 것이다.</x:t>
   </x:si>
   <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 그가 공격의사를 갖던 말던 그의 주변에 존재하는 것만으로도 해독이 불가능한 '페이튼'에 중독되어 모든 존재가 소멸한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:유령왕. 태생적으로 '산도라의 후예'인 대마도사였으나 그의 스승인 '푸 그레이'가 서술한 '초마도의 서'를 이해하여 마법사 중 최강의 존재인 '초마도사'가 되었다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마법의 신, 제샤스 데이틴의 일곱 제자들이 일으킨 내전. 이로 인해 세상의 모든 기록이 소실되어 사실상 모든 것이 초기화되었다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">역사에 기록될 정도로 강한 힘을 지닌, 무한히 강해질 수 있는 능력을 지닌 9성 대장, '암흑대제'의 영부인. </x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 공격보다 정찰에 특화된 공격력보다는 연타에 치중한 風계열 서포터.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:금속왕. 긴가르시온이 조립한 완전 기계인간 다만 이 세상에서 유일하게 전신이 '완벽한 신의 금속'으로 이뤄져서 모든 것을 무시할 수준의 방어력을 지니고 있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Etc003_Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Etc004_Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DemonMage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Etc002_Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>샤이나 반 고드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Equipment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NarosaFomos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tartaros</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Necklace</x:t>
-  </x:si>
-  <x:si>
-    <x:t>헤디 벤만 오프 모스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>버그리포트 바로가기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Alchemist</x:t>
-  </x:si>
-  <x:si>
-    <x:t>notEmployed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gingarsion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CodeName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GrenFomos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bugreport</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Summoner</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Archmage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hidden002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아키르고 베니아</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hidden001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Assassin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Necromancer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Species&amp;Job</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Etc005_Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BultonKajon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가레멘 투스카 딘</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IreanSorin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>continue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Etc001_Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 불튼이 버금가는 탱킹 능력에 '피를 입는 자'에 버금하는 물리력을 지닌 雷계열 근거리 딜러.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 지닌 능력 중 대부분이 상처를 치유하고 아군을 버프, 적을 디버프하는 水계열 후방 서포터.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>초심극점을 마주하고 바라보고 있는 다른 세상, '역세계'와의 전쟁.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>144년을 주기로 돌아오는 초자연 현상. 이 기간 중에는 성공적인 '이라 모스'의 개폐가 가능해진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그의 일정범위에 존재하는 모든 사물은 점점 느려지기  시작하고 그 본인은 그 속도만큼 점점 빨라진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'아키르고 베니아'가 아닌 때에 '이라 모스'를 개설한 충격으로 '본세계' 바깥의 세상이 무너져버린 사건.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Etc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>재료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>암살자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>메뉴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>역사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나로사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>바드락</x:t>
-  </x:si>
-  <x:si>
-    <x:t>성직자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>역세계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가죽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이레안</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그렌</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레디닌</x:t>
-  </x:si>
-  <x:si>
-    <x:t>백랑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>직업</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>흉켈링</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카루크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>갑옷</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라우톤</x:t>
-  </x:si>
-  <x:si>
-    <x:t>판금</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레노드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>올베인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신발</x:t>
-  </x:si>
-  <x:si>
-    <x:t>저장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>천</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마왕족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도감</x:t>
-  </x:si>
-  <x:si>
-    <x:t>드래곤</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>초월자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>본세계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Job</x:t>
-  </x:si>
-  <x:si>
-    <x:t>투르카</x:t>
-  </x:si>
-  <x:si>
-    <x:t>용어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장갑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가레멘</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인물</x:t>
-  </x:si>
-  <x:si>
-    <x:t>페르스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무직</x:t>
-  </x:si>
-  <x:si>
-    <x:t>로데크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>셀레나</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불튼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장비</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>티모르</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도적</x:t>
-  </x:si>
-  <x:si>
-    <x:t>머리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마법사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>궁수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>목걸이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>반지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>귀걸이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소모품</x:t>
-  </x:si>
-  <x:si>
-    <x:t>All</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character002_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character003_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character001_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Desc_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa006_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa010_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa005_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa005_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa009_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History002_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa010_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa002_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History003_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa011_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa014_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa014_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character004_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa001_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term004_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History004_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term003_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term002_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term007_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa007_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa001_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa013_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa009_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa008_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa003_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa014_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa013_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa013_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa006_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa004_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa008_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History001_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GaremenTooskaDin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term006_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa007_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa007_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term001_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa011_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa008_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History001_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History004_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa011_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa003_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term007_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa002_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa009_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa002_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa010_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History003_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa004_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term005_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa001_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History002_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화룡왕이라 불리는 자. 악신룡 '지크리피언'에게 육체는 소멸 당하고, 육체가 아닌 정신만으로 살아있는 존재.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 대장. 전투에 필요한 전반적인 능력을 두루 갖춘 氷계열 원거리 딜러.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종족전쟁</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이어하기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sandora</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대마도사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종말전쟁</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Index</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rodec</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Selena</x:t>
-  </x:si>
-  <x:si>
-    <x:t>?????</x:t>
-  </x:si>
-  <x:si>
-    <x:t>세이렌 알트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>menu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카루크 뷘젠트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Toorka</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cloth</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Dragon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Leather</x:t>
-  </x:si>
-  <x:si>
-    <x:t>강령술사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소환술사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>load</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Head</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코크루와</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Plate</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Human</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불러오기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>save</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대마도전쟁</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Boots</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Badrak</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나로사 포모스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Armor</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Warrior</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Demon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gloves</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Korean</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그렌 포모스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Renod</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Species</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Unknown</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Redinin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라우톤 윈너</x:t>
-  </x:si>
-  <x:si>
-    <x:t>copy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>긴가르시온</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rogue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Comment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Archer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이레안 소린</x:t>
-  </x:si>
-  <x:si>
-    <x:t>초심극점</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종족&amp;직업</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마족 마법사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>exit</x:t>
-  </x:si>
-  <x:si>
-    <x:t>위대한 과실</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Priest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>newgame</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Array</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마족 전사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타르타로스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>option</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Teemole</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잡템003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타이틀로 이동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Machine</x:t>
-  </x:si>
-  <x:si>
-    <x:t>새 시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잡템004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Earring</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연금술사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kalapok</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Perth</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에를로네</x:t>
-  </x:si>
-  <x:si>
-    <x:t>title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ring</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잡템001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불튼 카존</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잡템002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Weapon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잡템005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ehrlone</x:t>
-  </x:si>
-  <x:si>
-    <x:t>산도라 태생</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Consume</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자기 자신의 직계자손에 한정하여, 자신의 기억과 인격을 전달하는 '전생술'을 개발한 존재.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 대지의 종족 '티모르'의 생존저.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'본세계' 내에서 최초로 기록된 내전. 이로 인해 '불의 종족' 카르툼이 절멸하였다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 창공의 종족 '투르카'의 생존자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'본세계' 내에서, '종말전쟁'의 결말을 지켜보던 강력한 존재들을 일컫는 용어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁 시절 '종족말살정책'으로부터 살아남은 유일한 바다의 종족 '셀레나'의 생존자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:죽어도 되살아나는 자. 역사상 최초의 '초월자'이자 무한하게 강해지는 '암흑대제'의 원형.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:암흑대제. 이 세상에서 유일하게 힘을 비축하는 시간에 비례하여 무한히 강해질 수 있는 존재.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>평화로운 시기에도 전 세계에 그 개체 수가 5마리를 넘기지 못하던 이 세상 유일의 '초소수종'</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 자가방어와 자가치유에 치중된 地계열 순수 탱커.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대전쟁으로 인해 합류한 PoD 멤버 중 하나. 능력 중 대부분이 공격에 치중된 火계열 중거리 딜러.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'본세계' 내의 다른 10개의 세계와의 연락을 차단했음에도 가장 독자적인 업적을 이룩한 대륙.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RoutonWinner</x:t>
-  </x:si>
-  <x:si>
-    <x:t>???????????????</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term006_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term007_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term005_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이라 모스 강제 개폐 사건</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term004_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>encyclopedia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KaroukWingent</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term003_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term001_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DemonFighter</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term002_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써 '태양절맥'을 갖고 태어난 존재.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'헤디 벤만 오프 모스' 출신, 역사상 가장 위대한 무인이라 불리는 자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>드래곤을 포함해도 모든 종족 중에서는 물리력 최강의 종족 '바드락'의 생존자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>헤디 벤만 오프 모스에서 태어난 무인으로써 '구음절맥'을 갖고 태어난 존재.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'종말전쟁'이 끝난 이후의 시대가 되며 사실상 유명무실한 용어가 되어 사실상 강력한 힘을 지닌 '초월자'들을 일컫는 용어가 되었다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character002_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character002_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character004_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character001_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Character003_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>창조신 'NM'이 창조한 11개로 겹쳐진 우리의 세상.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'본세계'와 '역세계'를 잇는 유일한 물리적 이동공간.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>창조신 'OM'이 창조한 초심극점 너머의 다른 세상.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:시간의 마왕. 우리의 세상인 '본세계'와 '역세계'에서도 하나 이상을 찾아볼 수 없는 절대유일의 시간 능력자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이 세상 모든 것을 중독시키는 '페이튼'에 중독되어 스스로 의사를 갖고 움직이기 시작한 종족 '래머'의 마지막 생존자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이명:피를 입는 자. '본세계'와 '역세계'를 모두 포함해서도 비슷한 수준의 신체능력을 가진 존재를 찾기 힘들 정도로 압도적인 신체능력을 가지고 있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>원래라면 죽었을 때 다시 되살아나지만, 죽을 경우 다시는 되살아나지 못하는 것을 조건으로 강력한 힘을 얻어 그의 희생으로 '종말전쟁'에서 승리할 수 있었다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이제 와서는 이 세상에 절대유일한 '핏빛혈족의 유일한 생존자' 무시무시한 이능력을 지니고 있지만 그가 지닌 이능력의 정체를 아는 자를 이제는 찾을 수 없다.</x:t>
+    <x:t>Shield</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1668,7 +1674,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:N155"/>
+  <x:dimension ref="A1:N156"/>
   <x:sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="16.39999999999999857891"/>
   <x:cols>
     <x:col min="1" max="1" width="8.796875" bestFit="1" customWidth="1"/>
@@ -1677,31 +1683,31 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>249</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>249</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="D1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>210</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D2" s="1"/>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>230</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -1709,7 +1715,7 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>220</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B4" s="1"/>
       <x:c r="C4" s="1"/>
@@ -1720,10 +1726,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" t="s">
-        <x:v>229</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C5" t="s">
-        <x:v>238</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
@@ -1731,10 +1737,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" t="s">
-        <x:v>40</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C6" t="s">
-        <x:v>174</x:v>
+        <x:v>186</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
@@ -1742,10 +1748,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" t="s">
-        <x:v>233</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="C7" t="s">
-        <x:v>57</x:v>
+        <x:v>134</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
@@ -1753,10 +1759,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" t="s">
-        <x:v>226</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="C8" t="s">
-        <x:v>65</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
@@ -1764,10 +1770,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B9" t="s">
-        <x:v>199</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="C9" t="s">
-        <x:v>76</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
@@ -1775,10 +1781,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B10" t="s">
-        <x:v>193</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="C10" t="s">
-        <x:v>198</x:v>
+        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
@@ -1786,10 +1792,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B11" t="s">
-        <x:v>217</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C11" t="s">
-        <x:v>77</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
@@ -1797,10 +1803,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B12" t="s">
-        <x:v>184</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="C12" t="s">
-        <x:v>51</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
@@ -1808,10 +1814,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B13" t="s">
-        <x:v>245</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="C13" s="2" t="s">
-        <x:v>236</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
@@ -1819,10 +1825,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B14" t="s">
-        <x:v>26</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C14" t="s">
-        <x:v>20</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
@@ -1830,10 +1836,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B15" t="s">
-        <x:v>275</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C15" t="s">
-        <x:v>80</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
@@ -1841,10 +1847,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B16" t="s">
-        <x:v>180</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C16" t="s">
-        <x:v>83</x:v>
+        <x:v>157</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
@@ -1855,7 +1861,7 @@
         <x:v>200</x:v>
       </x:c>
       <x:c r="C17" t="s">
-        <x:v>87</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
@@ -1863,10 +1869,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B18" t="s">
-        <x:v>186</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="C18" t="s">
-        <x:v>52</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
@@ -1874,10 +1880,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B19" t="s">
-        <x:v>212</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="C19" t="s">
-        <x:v>72</x:v>
+        <x:v>165</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
@@ -1885,10 +1891,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B20" t="s">
-        <x:v>17</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C20" t="s">
-        <x:v>232</x:v>
+        <x:v>218</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
@@ -1896,10 +1902,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B21" t="s">
-        <x:v>215</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C21" t="s">
-        <x:v>61</x:v>
+        <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
@@ -1907,10 +1913,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B22" t="s">
-        <x:v>243</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="C22" t="s">
-        <x:v>92</x:v>
+        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
@@ -1918,10 +1924,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B23" t="s">
-        <x:v>253</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="C23" t="s">
-        <x:v>244</x:v>
+        <x:v>254</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
@@ -1929,10 +1935,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B24" t="s">
-        <x:v>23</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C24" t="s">
-        <x:v>218</x:v>
+        <x:v>232</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
@@ -1940,10 +1946,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B25" t="s">
-        <x:v>25</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C25" t="s">
-        <x:v>211</x:v>
+        <x:v>219</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
@@ -1951,10 +1957,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B26" t="s">
-        <x:v>16</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C26" t="s">
-        <x:v>205</x:v>
+        <x:v>208</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
@@ -1962,10 +1968,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B27" t="s">
-        <x:v>39</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C27" t="s">
-        <x:v>222</x:v>
+        <x:v>223</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
@@ -1973,10 +1979,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B28" t="s">
-        <x:v>37</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C28" t="s">
-        <x:v>248</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3">
@@ -1984,10 +1990,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B29" t="s">
-        <x:v>276</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C29" t="s">
-        <x:v>185</x:v>
+        <x:v>197</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">
@@ -1995,10 +2001,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B30" t="s">
-        <x:v>268</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C30" t="s">
-        <x:v>216</x:v>
+        <x:v>241</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
@@ -2006,10 +2012,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B31" t="s">
-        <x:v>149</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C31" t="s">
-        <x:v>38</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:3">
@@ -2017,10 +2023,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B32" t="s">
-        <x:v>213</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="C32" t="s">
-        <x:v>105</x:v>
+        <x:v>174</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:3">
@@ -2028,10 +2034,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B33" t="s">
-        <x:v>85</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C33" t="s">
-        <x:v>63</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:3">
@@ -2039,10 +2045,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B34" t="s">
-        <x:v>32</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C34" t="s">
-        <x:v>182</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:3">
@@ -2050,10 +2056,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B35" t="s">
-        <x:v>29</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C35" t="s">
-        <x:v>269</x:v>
+        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:3">
@@ -2061,10 +2067,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B36" t="s">
-        <x:v>22</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C36" t="s">
-        <x:v>93</x:v>
+        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:3">
@@ -2072,10 +2078,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B37" t="s">
-        <x:v>15</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C37" t="s">
-        <x:v>98</x:v>
+        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:3">
@@ -2083,10 +2089,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B38" t="s">
-        <x:v>35</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C38" t="s">
-        <x:v>224</x:v>
+        <x:v>247</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:3">
@@ -2094,10 +2100,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B39" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C39" t="s">
-        <x:v>78</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:3">
@@ -2105,10 +2111,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B40" t="s">
-        <x:v>190</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="C40" t="s">
-        <x:v>58</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:3">
@@ -2116,10 +2122,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B41" t="s">
-        <x:v>196</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C41" t="s">
-        <x:v>71</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:3">
@@ -2127,10 +2133,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B42" t="s">
-        <x:v>251</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="C42" t="s">
-        <x:v>99</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:3">
@@ -2138,10 +2144,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B43" t="s">
-        <x:v>194</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="C43" t="s">
-        <x:v>102</x:v>
+        <x:v>178</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:3">
@@ -2149,10 +2155,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B44" t="s">
-        <x:v>206</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C44" t="s">
-        <x:v>68</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:3">
@@ -2160,10 +2166,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B45" t="s">
-        <x:v>209</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C45" t="s">
-        <x:v>88</x:v>
+        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:3">
@@ -2171,10 +2177,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B46" t="s">
-        <x:v>202</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C46" t="s">
-        <x:v>75</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:3">
@@ -2182,10 +2188,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B47" t="s">
-        <x:v>246</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C47" t="s">
-        <x:v>107</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:3">
@@ -2193,10 +2199,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B48" t="s">
-        <x:v>240</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C48" t="s">
-        <x:v>108</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:3">
@@ -2204,10 +2210,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B49" t="s">
-        <x:v>18</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C49" t="s">
-        <x:v>106</x:v>
+        <x:v>173</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:3">
@@ -2215,10 +2221,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B50" s="2" t="s">
-        <x:v>197</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C50" t="s">
-        <x:v>82</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:3">
@@ -2226,10 +2232,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B51" s="2" t="s">
-        <x:v>179</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C51" t="s">
-        <x:v>94</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:3">
@@ -2237,10 +2243,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B52" s="2" t="s">
-        <x:v>187</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C52" t="s">
-        <x:v>86</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:3">
@@ -2248,10 +2254,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B53" t="s">
-        <x:v>234</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C53" t="s">
-        <x:v>100</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:3">
@@ -2259,10 +2265,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B54" t="s">
-        <x:v>181</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C54" t="s">
-        <x:v>95</x:v>
+        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:3">
@@ -2270,10 +2276,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B55" t="s">
-        <x:v>204</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C55" t="s">
-        <x:v>54</x:v>
+        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:3">
@@ -2281,10 +2287,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B56" t="s">
-        <x:v>237</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="C56" t="s">
-        <x:v>73</x:v>
+        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:3">
@@ -2292,10 +2298,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B57" t="s">
-        <x:v>208</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="C57" t="s">
-        <x:v>64</x:v>
+        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:3">
@@ -2303,10 +2309,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B58" t="s">
-        <x:v>175</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C58" t="s">
-        <x:v>254</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:3">
@@ -2314,10 +2320,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B59" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C59" t="s">
-        <x:v>81</x:v>
+        <x:v>166</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:3">
@@ -2325,10 +2331,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B60" t="s">
-        <x:v>242</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C60" t="s">
-        <x:v>79</x:v>
+        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:3">
@@ -2336,10 +2342,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B61" t="s">
-        <x:v>214</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C61" t="s">
-        <x:v>90</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:3">
@@ -2347,10 +2353,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B62" t="s">
-        <x:v>22</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C62" t="s">
-        <x:v>93</x:v>
+        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:3">
@@ -2358,10 +2364,10 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B63" t="s">
-        <x:v>207</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="C63" t="s">
-        <x:v>96</x:v>
+        <x:v>169</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:3">
@@ -2369,10 +2375,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B64" t="s">
-        <x:v>221</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="C64" t="s">
-        <x:v>104</x:v>
+        <x:v>181</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:3">
@@ -2380,10 +2386,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B65" t="s">
-        <x:v>203</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="C65" t="s">
-        <x:v>103</x:v>
+        <x:v>179</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:3">
@@ -2391,10 +2397,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B66" t="s">
-        <x:v>228</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C66" t="s">
-        <x:v>55</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:3">
@@ -2402,10 +2408,10 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B67" t="s">
-        <x:v>33</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C67" t="s">
-        <x:v>50</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:3">
@@ -2413,10 +2419,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B68" t="s">
-        <x:v>219</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C68" t="s">
-        <x:v>101</x:v>
+        <x:v>171</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:3">
@@ -2424,10 +2430,10 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B69" t="s">
-        <x:v>27</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C69" t="s">
-        <x:v>192</x:v>
+        <x:v>212</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:3">
@@ -2435,10 +2441,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B70" t="s">
-        <x:v>21</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C70" t="s">
-        <x:v>241</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:3">
@@ -2446,10 +2452,10 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B71" t="s">
-        <x:v>34</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C71" t="s">
-        <x:v>191</x:v>
+        <x:v>211</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:3">
@@ -2457,10 +2463,10 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B72" t="s">
-        <x:v>279</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C72" t="s">
-        <x:v>231</x:v>
+        <x:v>236</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:3">
@@ -2468,10 +2474,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B73" t="s">
-        <x:v>12</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C73" t="s">
-        <x:v>225</x:v>
+        <x:v>226</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:3">
@@ -2479,10 +2485,10 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B74" t="s">
-        <x:v>28</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C74" t="s">
-        <x:v>176</x:v>
+        <x:v>187</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:8">
@@ -2490,10 +2496,10 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B75" t="s">
-        <x:v>169</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C75" t="s">
-        <x:v>72</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="G75" s="2"/>
       <x:c r="H75" s="2"/>
@@ -2503,10 +2509,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="B76" t="s">
-        <x:v>162</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C76" t="s">
-        <x:v>232</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="G76" s="2"/>
       <x:c r="H76" s="2"/>
@@ -2516,10 +2522,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B77" t="s">
-        <x:v>140</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C77" t="s">
-        <x:v>61</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G77" s="2"/>
       <x:c r="H77" s="2"/>
@@ -2529,10 +2535,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B78" t="s">
-        <x:v>145</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C78" t="s">
-        <x:v>92</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="G78" s="2"/>
       <x:c r="H78" s="2"/>
@@ -2542,10 +2548,10 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B79" t="s">
-        <x:v>117</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C79" t="s">
-        <x:v>244</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="G79" s="2"/>
       <x:c r="H79" s="2"/>
@@ -2555,10 +2561,10 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B80" t="s">
-        <x:v>144</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C80" t="s">
-        <x:v>218</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="G80" s="2"/>
       <x:c r="H80" s="2"/>
@@ -2568,10 +2574,10 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="B81" t="s">
-        <x:v>152</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C81" t="s">
-        <x:v>60</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G81" s="2"/>
       <x:c r="H81" s="2"/>
@@ -2581,10 +2587,10 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B82" t="s">
-        <x:v>139</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C82" t="s">
-        <x:v>53</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="G82" s="2"/>
       <x:c r="H82" s="2"/>
@@ -2594,10 +2600,10 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B83" t="s">
-        <x:v>119</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C83" t="s">
-        <x:v>59</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G83" s="2"/>
       <x:c r="H83" s="2"/>
@@ -2607,10 +2613,10 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B84" t="s">
-        <x:v>165</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C84" t="s">
-        <x:v>97</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="G84" s="2"/>
       <x:c r="H84" s="2"/>
@@ -2620,10 +2626,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B85" t="s">
-        <x:v>159</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C85" t="s">
-        <x:v>67</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="G85" s="2"/>
       <x:c r="H85" s="2"/>
@@ -2633,10 +2639,10 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B86" t="s">
-        <x:v>154</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C86" t="s">
-        <x:v>70</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="G86" s="2"/>
       <x:c r="H86" s="2"/>
@@ -2646,10 +2652,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B87" t="s">
-        <x:v>143</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C87" t="s">
-        <x:v>89</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G87" s="2"/>
       <x:c r="H87" s="2"/>
@@ -2659,10 +2665,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B88" t="s">
-        <x:v>278</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C88" t="s">
-        <x:v>84</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="G88" s="2"/>
       <x:c r="H88" s="2"/>
@@ -2672,10 +2678,10 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="B89" t="s">
-        <x:v>280</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C89" t="s">
-        <x:v>56</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="G89" s="2"/>
       <x:c r="H89" s="2"/>
@@ -2685,10 +2691,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B90" t="s">
-        <x:v>277</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C90" t="s">
-        <x:v>223</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="G90" s="2"/>
       <x:c r="H90" s="2"/>
@@ -2698,10 +2704,10 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="B91" t="s">
-        <x:v>274</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C91" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="G91" s="2"/>
       <x:c r="H91" s="2"/>
@@ -2711,10 +2717,10 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="B92" t="s">
-        <x:v>272</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C92" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="G92" s="2"/>
       <x:c r="H92" s="2"/>
@@ -2724,10 +2730,10 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="B93" t="s">
-        <x:v>270</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C93" s="2" t="s">
-        <x:v>227</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="G93" s="2"/>
       <x:c r="H93" s="2"/>
@@ -2737,10 +2743,10 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="B94" t="s">
-        <x:v>157</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C94" t="s">
-        <x:v>173</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="G94" s="2"/>
       <x:c r="H94" s="2"/>
@@ -2750,10 +2756,10 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="B95" t="s">
-        <x:v>170</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C95" t="s">
-        <x:v>201</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="G95" s="2"/>
       <x:c r="H95" s="2"/>
@@ -2763,10 +2769,10 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="B96" t="s">
-        <x:v>123</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C96" t="s">
-        <x:v>177</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="G96" s="2"/>
       <x:c r="H96" s="2"/>
@@ -2776,10 +2782,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B97" t="s">
-        <x:v>158</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C97" t="s">
-        <x:v>273</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G97" s="2"/>
       <x:c r="H97" s="2"/>
@@ -2789,10 +2795,10 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="B98" t="s">
-        <x:v>129</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C98" t="s">
-        <x:v>294</x:v>
+        <x:v>289</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:3">
@@ -2800,10 +2806,10 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="B99" t="s">
-        <x:v>136</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C99" t="s">
-        <x:v>46</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:3">
@@ -2811,10 +2817,10 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="B100" s="2" t="s">
-        <x:v>164</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C100" t="s">
-        <x:v>296</x:v>
+        <x:v>291</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:3">
@@ -2822,10 +2828,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B101" s="2" t="s">
-        <x:v>122</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C101" t="s">
-        <x:v>298</x:v>
+        <x:v>293</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:3">
@@ -2833,10 +2839,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="B102" s="2" t="s">
-        <x:v>160</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C102" t="s">
-        <x:v>263</x:v>
+        <x:v>287</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:3">
@@ -2844,10 +2850,10 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="B103" s="2" t="s">
-        <x:v>167</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C103" t="s">
-        <x:v>9</x:v>
+        <x:v>276</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:3">
@@ -2855,10 +2861,10 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="B104" s="2" t="s">
-        <x:v>118</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C104" t="s">
-        <x:v>5</x:v>
+        <x:v>297</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:3">
@@ -2866,10 +2872,10 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="B105" s="2" t="s">
-        <x:v>115</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C105" t="s">
-        <x:v>3</x:v>
+        <x:v>299</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:3">
@@ -2877,10 +2883,10 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="B106" s="2" t="s">
-        <x:v>151</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C106" t="s">
-        <x:v>266</x:v>
+        <x:v>286</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:3">
@@ -2888,10 +2894,10 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="B107" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C107" t="s">
-        <x:v>281</x:v>
+        <x:v>266</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:3">
@@ -2899,10 +2905,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B108" s="2" t="s">
-        <x:v>156</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C108" t="s">
-        <x:v>172</x:v>
+        <x:v>272</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:3">
@@ -2910,10 +2916,10 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="B109" s="2" t="s">
-        <x:v>146</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C109" t="s">
-        <x:v>284</x:v>
+        <x:v>269</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:3">
@@ -2921,10 +2927,10 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="B110" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C110" t="s">
-        <x:v>43</x:v>
+        <x:v>274</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:3">
@@ -2932,10 +2938,10 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="B111" s="2" t="s">
-        <x:v>138</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C111" t="s">
-        <x:v>261</x:v>
+        <x:v>282</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:3">
@@ -2943,10 +2949,10 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="B112" s="2" t="s">
-        <x:v>116</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C112" t="s">
-        <x:v>265</x:v>
+        <x:v>284</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:3">
@@ -2954,10 +2960,10 @@
         <x:v>109</x:v>
       </x:c>
       <x:c r="B113" s="2" t="s">
-        <x:v>121</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C113" t="s">
-        <x:v>257</x:v>
+        <x:v>279</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:3">
@@ -2965,10 +2971,10 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="B114" s="2" t="s">
-        <x:v>155</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C114" t="s">
-        <x:v>8</x:v>
+        <x:v>270</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:3">
@@ -2976,10 +2982,10 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="B115" s="2" t="s">
-        <x:v>124</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C115" t="s">
-        <x:v>259</x:v>
+        <x:v>281</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:3">
@@ -2987,10 +2993,10 @@
         <x:v>112</x:v>
       </x:c>
       <x:c r="B116" s="2" t="s">
-        <x:v>147</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C116" t="s">
-        <x:v>42</x:v>
+        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:3">
@@ -2998,10 +3004,10 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="B117" s="2" t="s">
-        <x:v>127</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C117" t="s">
-        <x:v>283</x:v>
+        <x:v>267</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:3">
@@ -3009,10 +3015,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B118" s="2" t="s">
-        <x:v>114</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C118" t="s">
-        <x:v>264</x:v>
+        <x:v>283</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:3">
@@ -3020,10 +3026,10 @@
         <x:v>115</x:v>
       </x:c>
       <x:c r="B119" s="2" t="s">
-        <x:v>142</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C119" t="s">
-        <x:v>4</x:v>
+        <x:v>298</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:3">
@@ -3031,10 +3037,10 @@
         <x:v>116</x:v>
       </x:c>
       <x:c r="B120" s="2" t="s">
-        <x:v>137</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C120" t="s">
-        <x:v>295</x:v>
+        <x:v>290</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:3">
@@ -3042,10 +3048,10 @@
         <x:v>117</x:v>
       </x:c>
       <x:c r="B121" s="2" t="s">
-        <x:v>153</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C121" t="s">
-        <x:v>291</x:v>
+        <x:v>294</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:3">
@@ -3053,10 +3059,10 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="B122" s="2" t="s">
-        <x:v>133</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C122" t="s">
-        <x:v>293</x:v>
+        <x:v>296</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:14">
@@ -3064,10 +3070,10 @@
         <x:v>119</x:v>
       </x:c>
       <x:c r="B123" s="2" t="s">
-        <x:v>132</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C123" s="3" t="s">
-        <x:v>292</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="N123" s="4"/>
     </x:row>
@@ -3076,10 +3082,10 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="B124" s="2" t="s">
-        <x:v>130</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C124" s="2" t="s">
-        <x:v>45</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N124" s="2"/>
     </x:row>
@@ -3088,10 +3094,10 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="B125" s="2" t="s">
-        <x:v>168</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C125" s="4" t="s">
-        <x:v>267</x:v>
+        <x:v>288</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:3">
@@ -3099,10 +3105,10 @@
         <x:v>122</x:v>
       </x:c>
       <x:c r="B126" s="2" t="s">
-        <x:v>150</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C126" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:3">
@@ -3110,10 +3116,10 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="B127" s="2" t="s">
-        <x:v>148</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C127" s="3" t="s">
-        <x:v>258</x:v>
+        <x:v>280</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:3">
@@ -3121,10 +3127,10 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="B128" s="2" t="s">
-        <x:v>120</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C128" t="s">
-        <x:v>6</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:3">
@@ -3132,10 +3138,10 @@
         <x:v>125</x:v>
       </x:c>
       <x:c r="B129" s="2" t="s">
-        <x:v>166</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C129" t="s">
-        <x:v>44</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:3">
@@ -3143,10 +3149,10 @@
         <x:v>126</x:v>
       </x:c>
       <x:c r="B130" s="2" t="s">
-        <x:v>131</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C130" s="3" t="s">
-        <x:v>47</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:3">
@@ -3154,10 +3160,10 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="B131" s="2" t="s">
-        <x:v>271</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C131" t="s">
-        <x:v>195</x:v>
+        <x:v>213</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:3">
@@ -3165,10 +3171,10 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="B132" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C132" s="3" t="s">
-        <x:v>260</x:v>
+        <x:v>278</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:3">
@@ -3176,10 +3182,10 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="B133" s="2" t="s">
-        <x:v>161</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C133" s="3" t="s">
-        <x:v>285</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:3">
@@ -3187,10 +3193,10 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="B134" s="2" t="s">
-        <x:v>125</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C134" t="s">
-        <x:v>262</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:3">
@@ -3198,10 +3204,10 @@
         <x:v>131</x:v>
       </x:c>
       <x:c r="B135" s="2" t="s">
-        <x:v>141</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C135" t="s">
-        <x:v>183</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:3">
@@ -3209,10 +3215,10 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="B136" s="2" t="s">
-        <x:v>126</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C136" t="s">
-        <x:v>297</x:v>
+        <x:v>292</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:3">
@@ -3220,10 +3226,10 @@
         <x:v>133</x:v>
       </x:c>
       <x:c r="B137" t="s">
-        <x:v>31</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C137" t="s">
-        <x:v>91</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:3">
@@ -3231,10 +3237,10 @@
         <x:v>134</x:v>
       </x:c>
       <x:c r="B138" t="s">
-        <x:v>113</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C138" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:3">
@@ -3242,10 +3248,10 @@
         <x:v>135</x:v>
       </x:c>
       <x:c r="B139" t="s">
-        <x:v>289</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C139" t="s">
-        <x:v>7</x:v>
+        <x:v>273</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:3">
@@ -3253,10 +3259,10 @@
         <x:v>136</x:v>
       </x:c>
       <x:c r="B140" s="2" t="s">
-        <x:v>111</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C140" t="s">
-        <x:v>62</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:3">
@@ -3264,10 +3270,10 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="B141" s="2" t="s">
-        <x:v>287</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C141" s="3" t="s">
-        <x:v>282</x:v>
+        <x:v>268</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:3">
@@ -3275,10 +3281,10 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="B142" s="2" t="s">
-        <x:v>286</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C142" t="s">
-        <x:v>256</x:v>
+        <x:v>277</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:3">
@@ -3286,10 +3292,10 @@
         <x:v>139</x:v>
       </x:c>
       <x:c r="B143" s="2" t="s">
-        <x:v>112</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C143" t="s">
-        <x:v>74</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:3">
@@ -3297,10 +3303,10 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="B144" s="2" t="s">
-        <x:v>290</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C144" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:3">
@@ -3308,10 +3314,10 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="B145" s="2" t="s">
-        <x:v>128</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C145" t="s">
-        <x:v>66</x:v>
+        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:3">
@@ -3319,10 +3325,10 @@
         <x:v>142</x:v>
       </x:c>
       <x:c r="B146" s="2" t="s">
-        <x:v>288</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C146" t="s">
-        <x:v>171</x:v>
+        <x:v>271</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:3">
@@ -3330,10 +3336,10 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="B147" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C147" t="s">
-        <x:v>247</x:v>
+        <x:v>257</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:3">
@@ -3341,7 +3347,7 @@
         <x:v>144</x:v>
       </x:c>
       <x:c r="B148" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C148" t="s">
         <x:v>250</x:v>
@@ -3352,10 +3358,10 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="B149" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C149" t="s">
-        <x:v>235</x:v>
+        <x:v>237</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:3">
@@ -3363,10 +3369,10 @@
         <x:v>146</x:v>
       </x:c>
       <x:c r="B150" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C150" t="s">
-        <x:v>239</x:v>
+        <x:v>260</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:3">
@@ -3374,10 +3380,10 @@
         <x:v>147</x:v>
       </x:c>
       <x:c r="B151" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C151" t="s">
-        <x:v>252</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:3">
@@ -3385,10 +3391,10 @@
         <x:v>148</x:v>
       </x:c>
       <x:c r="B152" t="s">
-        <x:v>255</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C152" t="s">
-        <x:v>109</x:v>
+        <x:v>182</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:3">
@@ -3396,10 +3402,10 @@
         <x:v>149</x:v>
       </x:c>
       <x:c r="B153" t="s">
-        <x:v>15</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C153" t="s">
-        <x:v>98</x:v>
+        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:3">
@@ -3407,10 +3413,10 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="B154" t="s">
-        <x:v>48</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C154" t="s">
-        <x:v>49</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:3">
@@ -3418,10 +3424,21 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B155" t="s">
-        <x:v>110</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C155" t="s">
-        <x:v>0</x:v>
+        <x:v>124</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" spans="1:3">
+      <x:c r="A156">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="B156" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="C156" t="s">
+        <x:v>98</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
